--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4124,17 +4124,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>No Pedestrian Left Behind: Real-Time Detection and Tracking of Vulnerable Road Users for A</t>
+          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Anas Gamal Aly, Hala ElAarag</t>
+          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.25887</t>
+          <t>https://arxiv.org/abs/2604.23344</t>
         </is>
       </c>
       <c r="H85" s="9" t="n"/>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Quantum-Inspired Robust and Scalable SAR Object Classification</t>
+          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Maximilian Scharf, Marco Trenti, Felix Bock, Padraig Davidson, Tobias Brosch, Benjamin Rodrigues de Miranda, Sigurd Huber, Timo Felser</t>
+          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.25755</t>
+          <t>https://arxiv.org/abs/2604.21502</t>
         </is>
       </c>
       <c r="H86" s="9" t="n"/>
@@ -4205,12 +4205,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SARU: A Shadow-Aware and Removal Unified Framework for Remote Sensing Images with New Benc</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Zi-Yang Bo, Wei Lu, Hongruixuan Chen, Si-Bao Chen, Bin Luo</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4230,542 +4230,10 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.25432</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="H87" s="9" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Edge-Cloud Collaborative Reconstruction via Structure-Aware Latent Diffusion for Downstrea</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Yun Li, Xianju Li</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.25319</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>BifDet: A 3D Bifurcation Detection Dataset for Airway-Tree Modeling</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Ali Keshavarzi, Quentin Bouniot, Benjamin M. Smith, Elsa Angelini</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.24999</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Caries DETR: Tooth Structure-aware Prior and Lesion-aware Dynamic Loss Refinement for DETR</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Xuefen Liu, Xinquan Yang, Mianjie Zheng, Kun Tang, Xuguang Li, Xiaoqi Guo, Linlin Shen, He Meng</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23718</t>
-        </is>
-      </c>
-      <c r="H90" s="9" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Resource-Constrained UAV-Based Weed Detection for Site-Specific Management on Edge Devices</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Linyuan Wang, Haibo Yao, Te-Ming Tseng, Kelvin Betitame, Xin Sun, Hanbo Huang, Dong Chen</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23442</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Few-Shot OD</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23344</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Transferable Physical-World Adversarial Patches Against Object Detection in Autonomous Dri</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Zihui Zhu, Ziqi Zhou, Yichen Wang, Lulu Xue, Minghui Li, Shengshan Hu</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23105</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Hard to See, Hard to Label: Generative and Symbolic Acquisition for Subtle Visual Phenomen</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Renjith Prasad, Rishabh Sharma, Andrew E. Shao, Annmary Justine Koomthanam, Shreyas Kulkarni, Suparna Bhattacharya, Martin Foltin, Amit Sheth</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22990</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Self Knowledge Re-expression: A Fully Local Method for Adapting LLMs to Tasks Using Intrin</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Mengyu Wang, Xiaoying Zhi, Zhiyi Li, Robin Schmucker, Shay B. Cohen, Tiejun Ma, Fran Silavong</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22939</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Railway Artificial Intelligence Learning Benchmark (RAIL-BENCH): A Benchmark Suite for Per</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Annika Bätz, Pavel Klasek, Seo-Young Ham, Philipp Neumaier, Martin Köppel, Martin Lauer</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22507</t>
-        </is>
-      </c>
-      <c r="H96" s="9" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Depth-Aware Rover: A Study of Edge AI and Monocular Vision for Real-World Implementation</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Lomash Relia, Jai G Singla,  Amitabh, Nitant Dube</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22331</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>EgoMAGIC- An Egocentric Video Field Medicine Dataset for Training Perception Algorithms</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Brian VanVoorst, Nicholas Walczak, Christopher Gilleo, Charles Meissner, Fabio Felix, Iran Roman, Bea Steers, Claudio Silva</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22036</t>
-        </is>
-      </c>
-      <c r="H98" s="9" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.21502</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
-        </is>
-      </c>
-      <c r="H100" s="9" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>A Probabilistic Framework for Improving Dense Object Detection in Underwater Image Data vi</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Eleanor Wiesler, Trace Baxley</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.21198</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H84"/>
@@ -32357,7 +31825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -33248,17 +32716,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>No Pedestrian Left Behind: Real-Time Detection and Tracking of Vulnerable Road Users for A</t>
+          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Anas Gamal Aly, Hala ElAarag</t>
+          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -33287,7 +32755,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.25887</t>
+          <t>https://arxiv.org/abs/2604.21502</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -33300,12 +32768,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Quantum-Inspired Robust and Scalable SAR Object Classification</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Maximilian Scharf, Marco Trenti, Felix Bock, Padraig Davidson, Tobias Brosch, Benjamin Rodrigues de Miranda, Sigurd Huber, Timo Felser</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -33334,668 +32802,10 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.25755</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>SARU: A Shadow-Aware and Removal Unified Framework for Remote Sensing Images with New Benc</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Zi-Yang Bo, Wei Lu, Hongruixuan Chen, Si-Bao Chen, Bin Luo</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.25432</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Edge-Cloud Collaborative Reconstruction via Structure-Aware Latent Diffusion for Downstrea</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Yun Li, Xianju Li</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.25319</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>BifDet: A 3D Bifurcation Detection Dataset for Airway-Tree Modeling</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Ali Keshavarzi, Quentin Bouniot, Benjamin M. Smith, Elsa Angelini</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.24999</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Caries DETR: Tooth Structure-aware Prior and Lesion-aware Dynamic Loss Refinement for DETR</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Xuefen Liu, Xinquan Yang, Mianjie Zheng, Kun Tang, Xuguang Li, Xiaoqi Guo, Linlin Shen, He Meng</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23718</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Resource-Constrained UAV-Based Weed Detection for Site-Specific Management on Edge Devices</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Linyuan Wang, Haibo Yao, Te-Ming Tseng, Kelvin Betitame, Xin Sun, Hanbo Huang, Dong Chen</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23442</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Transferable Physical-World Adversarial Patches Against Object Detection in Autonomous Dri</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Zihui Zhu, Ziqi Zhou, Yichen Wang, Lulu Xue, Minghui Li, Shengshan Hu</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.23105</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Hard to See, Hard to Label: Generative and Symbolic Acquisition for Subtle Visual Phenomen</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Renjith Prasad, Rishabh Sharma, Andrew E. Shao, Annmary Justine Koomthanam, Shreyas Kulkarni, Suparna Bhattacharya, Martin Foltin, Amit Sheth</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22990</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Self Knowledge Re-expression: A Fully Local Method for Adapting LLMs to Tasks Using Intrin</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Mengyu Wang, Xiaoying Zhi, Zhiyi Li, Robin Schmucker, Shay B. Cohen, Tiejun Ma, Fran Silavong</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22939</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Railway Artificial Intelligence Learning Benchmark (RAIL-BENCH): A Benchmark Suite for Per</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Annika Bätz, Pavel Klasek, Seo-Young Ham, Philipp Neumaier, Martin Köppel, Martin Lauer</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22507</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Depth-Aware Rover: A Study of Edge AI and Monocular Vision for Real-World Implementation</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Lomash Relia, Jai G Singla,  Amitabh, Nitant Dube</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22331</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>EgoMAGIC- An Egocentric Video Field Medicine Dataset for Training Perception Algorithms</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Brian VanVoorst, Nicholas Walczak, Christopher Gilleo, Charles Meissner, Fabio Felix, Iran Roman, Bea Steers, Claudio Silva</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.22036</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.21502</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
-        </is>
-      </c>
-      <c r="M28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>A Probabilistic Framework for Improving Dense Object Detection in Underwater Image Data vi</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Eleanor Wiesler, Trace Baxley</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.21198</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M13"/>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4234,6 +4234,2988 @@
         </is>
       </c>
       <c r="H87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>PointSR</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PointSR: Self-Regularized Point Supervision for Drone-View Object Detection</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_PointSR_Self-Regularized_Point_Supervision_for_Drone-View_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brain-Inspired Spiking Neural Networks for Energy-Efficient </t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Brain-Inspired Spiking Neural Networks for Energy-Efficient Object Detection</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ViKIENet</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ViKIENet: Towards Efficient 3D Object Detection with Virtual Key Instance Enhanced Network</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yu_ViKIENet_Towards_Efficient_3D_Object_Detection_with_Virtual_Key_Instance_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Believing is Seeing</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Believing is Seeing: Unobserved Object Detection using Generative Models</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>OW-OVD</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。OW-OVD: Unified Open World and Open Vocabulary Object Detection</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SEEN-DA</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SEEN-DA: SEmantic ENtropy guided Domain-aware Attention for Domain Adaptive Object Detection</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_SEEN-DA_SEmantic_ENtropy_guided_Domain-aware_Attention_for_Domain_Adaptive_Object_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Point2RBox-v2</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Point2RBox-v2: Rethinking Point-supervised Oriented Object Detection with Spatial Layout Among Instances</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yu_Point2RBox-v2_Rethinking_Point-supervised_Oriented_Object_Detection_with_Spatial_Layout_Among_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SparseAlign</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SparseAlign: a Fully Sparse Framework for Cooperative Object Detection</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yuan_SparseAlign_a_Fully_Sparse_Framework_for_Cooperative_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Efficient Test-time Adaptive Object Detection via Sensitivit</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Efficient Test-time Adaptive Object Detection via Sensitivity-Guided Pruning</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Efficient_Test-time_Adaptive_Object_Detection_via_Sensitivity-Guided_Pruning_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>GauCho</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。GauCho: Gaussian Distributions with Cholesky Decomposition for Oriented Object Detection</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Marques_GauCho_Gaussian_Distributions_with_Cholesky_Decomposition_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Shift the Lens</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Shift the Lens: Environment-Aware Unsupervised Camouflaged Object Detection</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Mr. DETR</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Mr. DETR: Instructive Multi-Route Training for Detection Transformers</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Large Self-Supervised Models Bridge the Gap in Domain Adapti</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Large Self-Supervised Models Bridge the Gap in Domain Adaptive Object Detection</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Lavoie_Large_Self-Supervised_Models_Bridge_the_Gap_in_Domain_Adaptive_Object_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Uncertainty Meets Diversity</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Uncertainty Meets Diversity: A Comprehensive Active Learning Framework for Indoor 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Uncertainty_Meets_Diversity_A_Comprehensive_Active_Learning_Framework_for_Indoor_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>RGB Salient OD</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Visual Consensus Prompting for Co-Salient Object Detection</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Language-Guided Salient Object Ranking</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Language-Guided Salient Object Ranking</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SP3D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SP3D: Boosting Sparsely-Supervised 3D Object Detection via Accurate Cross-Modal Semantic Prompts</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_SP3D_Boosting_Sparsely-Supervised_3D_Object_Detection_via_Accurate_Cross-Modal_Semantic_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Test-Time Backdoor Detection for Object Detection Models</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>RaCFormer</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RaCFormer: Towards High-Quality 3D Object Detection via Query-based Radar-Camera Fusion</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Chu_RaCFormer_Towards_High-Quality_3D_Object_Detection_via_Query-based_Radar-Camera_Fusion_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>RGB Salient OD</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Samba</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Samba: A Unified Mamba-based Framework for General Salient Object Detection</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/He_Samba_A_Unified_Mamba-based_Framework_for_General_Salient_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Search and Detect</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Search and Detect: Training-Free Long Tail Object Detection via Web-Image Retrieval</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>ROD-MLLM</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ROD-MLLM: Towards More Reliable Object Detection in Multimodal Large Language Models</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SET: Spectral Enhancement for Tiny Object Detection</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>UCOD-DPL</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。UCOD-DPL: Unsupervised Camouflaged Object Detection via Dynamic Pseudo-label Learning</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yan_UCOD-DPL_Unsupervised_Camouflaged_Object_Detection_via_Dynamic_Pseudo-label_Learning_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Style Evolving along Chain-of-Thought for Unknown-Domain Obj</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Style Evolving along Chain-of-Thought for Unknown-Domain Object Detection</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Style_Evolving_along_Chain-of-Thought_for_Unknown-Domain_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>FSHNet</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FSHNet: Fully Sparse Hybrid Network for 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_FSHNet_Fully_Sparse_Hybrid_Network_for_3D_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Object Detection using Event Camera</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Object Detection using Event Camera: A MoE Heat Conduction based Detector and A New Benchmark Dataset</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Object_Detection_using_Event_Camera_A_MoE_Heat_Conduction_based_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>ReDiffDet</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ReDiffDet: Rotation-equivariant Diffusion Model for Oriented Object Detection</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Towards RAW Object Detection in Diverse Conditions</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards RAW Object Detection in Diverse Conditions</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Pseudo Visible Feature Fine-Grained Fusion for Thermal Object Detection</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ReRAW</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ReRAW: RGB-to-RAW Image Reconstruction via Stratified Sampling for Efficient Object Detection on the Edge</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Berdan_ReRAW_RGB-to-RAW_Image_Reconstruction_via_Stratified_Sampling_for_Efficient_Object_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>MonoDGP</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MonoDGP: Monocular 3D Object Detection with Decoupled-Query and Geometry-Error Priors</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Pu_MonoDGP_Monocular_3D_Object_Detection_with_Decoupled-Query_and_Geometry-Error_Priors_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>DEIM</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DEIM: DETR with Improved Matching for Fast Convergence</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>CorrBEV</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。CorrBEV: Multi-View 3D Object Detection by Correlation Learning with Multi-modal Prototypes</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xue_CorrBEV_Multi-View_3D_Object_Detection_by_Correlation_Learning_with_Multi-modal_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Feature Information Driven Position Gaussian Distribution Es</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Feature Information Driven Position Gaussian Distribution Estimation for Tiny Object Detection</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bian_Feature_Information_Driven_Position_Gaussian_Distribution_Estimation_for_Tiny_Object_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Revisiting Generative Replay for Class Incremental Object Detection</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>MI-DETR</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MI-DETR: An Object Detection Model with Multi-time Inquiries Mechanism</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Fractal Calibration for Long-tailed Object Detection</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Fractal Calibration for Long-tailed Object Detection</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Open-World Objectness Modeling Unifies Novel Object Detectio</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Open-World Objectness Modeling Unifies Novel Object Detection</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Open-World_Objectness_Modeling_Unifies_Novel_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>MonoTAKD</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MonoTAKD: Teaching Assistant Knowledge Distillation for Monocular 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_MonoTAKD_Teaching_Assistant_Knowledge_Distillation_for_Monocular_3D_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>RICCARDO</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RICCARDO: Radar Hit Prediction and Convolution for Camera-Radar 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Long_RICCARDO_Radar_Hit_Prediction_and_Convolution_for_Camera-Radar_3D_Object_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Cubify Anything</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Cubify Anything: Scaling Indoor 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Lazarow_Cubify_Anything_Scaling_Indoor_3D_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Learning Class Prototypes for Unified Sparse-Supervised 3D O</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Learning Class Prototypes for Unified Sparse-Supervised 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Learning_Class_Prototypes_for_Unified_Sparse-Supervised_3D_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Percept, Memory, and Imagine</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Percept, Memory, and Imagine: World Feature Simulating for Open-Domain Unknown Object Detection</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SimLTD</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SimLTD: Simple Supervised and Semi-Supervised Long-Tailed Object Detection</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Learning Endogenous Attention for Incremental Object Detection</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>DiL</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DiL: An Explainable and Practical Metric for Abnormal Uncertainty in Object Detection</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>HDPNet</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。HDPNet: Hourglass Vision Transformer with Dual-Path Feature Pyramid for Camouflaged Object Detection</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/He_HDPNet_Hourglass_Vision_Transformer_with_Dual-Path_Feature_Pyramid_for_Camouflaged_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Multispectral Object Detection Enhanced by Cross-Modal Infor</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Multispectral Object Detection Enhanced by Cross-Modal Information Complementary and Cosine Similarity Channel Resampling Modules</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Jang_Multispectral_Object_Detection_Enhanced_by_Cross-Modal_Information_Complementary_and_Cosine_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Bit-Flip Induced Latency Attacks in Object Detection</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Novel Object Detection via Cooperative Foundational Models</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>On the Importance of Dual-Space Augmentation for Domain Gene</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。On the Importance of Dual-Space Augmentation for Domain Generalized Object Detection</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Park_On_the_Importance_of_Dual-Space_Augmentation_for_Domain_Generalized_Object_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>DSTR</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DSTR: Dual Scenes Transformer for Cross-Modal Fusion in 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Cai_DSTR_Dual_Scenes_Transformer_for_Cross-Modal_Fusion_in_3D_Object_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Elemental Composite Prototypical Network</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Elemental Composite Prototypical Network: Few-Shot Object Detection on Outdoor 3D Point Cloud Scenes</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/De_Elemental_Composite_Prototypical_Network_Few-Shot_Object_Detection_on_Outdoor_3D_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>ALPI</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ALPI: Auto-Labeller with Proxy Injection for 3D Object Detection using 2D Labels Only</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lahlali_ALPI_Auto-Labeller_with_Proxy_Injection_for_3D_Object_Detection_using_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>AIC3DOD</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。AIC3DOD: Advancing Indoor Class-Incremental 3D Object Detection with Point Transformer Architecture and Room Layout Constraints</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Cheng_AIC3DOD_Advancing_Indoor_Class-Incremental_3D_Object_Detection_with_Point_Transformer_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Reflective Teacher</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Reflective Teacher: Semi-Supervised Multimodal 3D Object Detection in Bird&amp;#x27;s-Eye-View via Uncertainty Measure</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hazra_Reflective_Teacher_Semi-Supervised_Multimodal_3D_Object_Detection_in_Birds-Eye-View_via_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>MaskVD</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MaskVD: Region Masking for Efficient Video Object Detection</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Diffusion-Based Particle-DETR for BEV Perception</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>ERUP-YOLO</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ERUP-YOLO: Enhancing Object Detection Robustness for Adverse Weather Condition by Unified Image-Adaptive Processing</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ogino_ERUP-YOLO_Enhancing_Object_Detection_Robustness_for_Adverse_Weather_Condition_by_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>PK-YOLO</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PK-YOLO: Pretrained Knowledge Guided YOLO for Brain Tumor Detection in Multiplanar MRI Slices</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Decoupled PROB</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Decoupled PROB: Decoupled Query Initialization Tasks and Objectness-Class Learning for Open World Object Detection</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Inoue_Decoupled_PROB_Decoupled_Query_Initialization_Tasks_and_Objectness-Class_Learning_for_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>RT-DETRv3</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RT-DETRv3: Real-Time End-to-End Object Detection with Hierarchical Dense Positive Supervision</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Mixed Patch Visible-Infrared Modality Agnostic Object Detection</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Generalist YOLO</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Generalist YOLO: Towards Real-Time End-to-End Multi-Task Visual Language Models</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Enhancing Embodied Object Detection with Spatial Feature Mem</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Embodied Object Detection with Spatial Feature Memory</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chapman_Enhancing_Embodied_Object_Detection_with_Spatial_Feature_Memory_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Interactive Object Detection for Tiny Objects in Large Remot</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Interactive Object Detection for Tiny Objects in Large Remotely Sensed Images</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Burges_Interactive_Object_Detection_for_Tiny_Objects_in_Large_Remotely_Sensed_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cross-Domain Multi-Modal Few-Shot Object Detection via Rich </t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Cross-Domain Multi-Modal Few-Shot Object Detection via Rich Text</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>No Annotations for Object Detection in Art through Stable Di</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。No Annotations for Object Detection in Art through Stable Diffusion</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>ECF-YOLOv7-Tiny</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ECF-YOLOv7-Tiny: Improving Feature Fusion and the Receptive Field for Lightweight Object Detectors</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bacea_ECF-YOLOv7-Tiny_Improving_Feature_Fusion_and_the_Receptive_Field_for_Lightweight_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Shape-Biased Texture Agnostic Representations for Improved T</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Shape-Biased Texture Agnostic Representations for Improved Textureless and Metallic Object Detection and 6D Pose Estimation</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H84"/>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -582,7 +582,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H158"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -7398,7 +7398,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -8255,7 +8255,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -9112,7 +9112,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -9969,7 +9969,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -10826,7 +10826,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -11683,7 +11683,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -12540,7 +12540,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -13397,7 +13397,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -14527,7 +14527,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -15555,7 +15555,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -16685,7 +16685,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="2"/>
     <col width="40" customWidth="1" min="3" max="4"/>
@@ -17579,7 +17579,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -18709,7 +18709,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -19635,7 +19635,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -20561,7 +20561,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -21487,7 +21487,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -22413,7 +22413,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -23339,7 +23339,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -24265,7 +24265,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -25122,7 +25122,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -25979,7 +25979,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -26836,7 +26836,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -27754,13 +27754,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="G14" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>AP 52.5 (zero-shot Swin-L)</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Open-set zero-shot; ECCV 2024</t>
+          <t>✅ 已驗證 (Grounding DINO Table 2, COCO zero-shot)：Grounding DINO-L 52.5% AP zero-shot [Open-Vocab OD]</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -28425,7 +28431,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -29282,7 +29288,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -30139,7 +30145,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -30996,7 +31002,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -31853,7 +31859,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -33369,7 +33375,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -34226,7 +34232,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -35083,7 +35089,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -36042,7 +36048,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -36899,7 +36905,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -37962,13 +37968,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.8 val</t>
+        </is>
+      </c>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Hypergraph adaptive correlation enhancement (HyperACE)</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP, 14.7ms latency [Real-Time OD]</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -38064,13 +38076,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
+      <c r="G19" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.0 val</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Fine-grained distribution refinement</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP, 8.07ms latency [Real-Time OD end-to-end]</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -38217,13 +38235,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
+      <c r="G22" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.3 val</t>
+        </is>
+      </c>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Bag of freebies tweaks</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP, 13.66ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -38268,13 +38292,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
+      <c r="G23" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.3 val</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：First real-time DETR</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP, 13.61ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -38370,13 +38400,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
+      <c r="G25" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>AP 52.8 val</t>
+        </is>
+      </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：OpenMMLab RT detector</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP, 21.59ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -38472,13 +38508,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>AP 52.8 val</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Industry-grade RT detector</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP, 9.04ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
@@ -39296,7 +39338,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M102"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -40316,13 +40358,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
+      <c r="G16" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.8 val2017</t>
+        </is>
+      </c>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Hypergraph adaptive correlation enhancement (HyperACE)</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -40469,13 +40517,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
+      <c r="G19" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.0 val2017</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Fine-grained distribution refinement</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -40571,13 +40625,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.4 val2017</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：NMS-free; consistent dual assignment</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -40775,13 +40835,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
+      <c r="G25" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.3 val2017</t>
+        </is>
+      </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Bag of freebies tweaks</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -40826,13 +40892,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.3 val2017</t>
+        </is>
+      </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：First real-time DETR</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -40979,13 +41051,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>AP 52.9 val2017</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：E-ELAN backbone</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
@@ -41081,13 +41159,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+      <c r="G31" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>AP 52.8 val2017</t>
+        </is>
+      </c>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：OpenMMLab RT detector</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -41285,13 +41369,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>AP 52.8 val2017</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Industry-grade RT detector</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -44761,7 +44851,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -45618,7 +45708,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -48260,7 +48350,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -37917,13 +37917,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
+      <c r="G16" s="3" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>AP 57.8 val (DEIMv2-X)</t>
+        </is>
+      </c>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-time meets DINOv3; latest 2025 update</t>
+          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -38025,13 +38031,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
+      <c r="G18" s="3" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.7 val</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Dense O2O + MAL</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP, 8.07ms [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -38133,13 +38145,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
+      <c r="G20" s="3" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.6 val (6x)</t>
+        </is>
+      </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Hierarchical dense positive supervision; WACV 2025 Oral</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP, 13.5ms [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -39279,13 +39297,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
+      <c r="G42" s="3" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.6 val (R101 6x)</t>
+        </is>
+      </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。RT-DETRv3: Real-Time End-to-End Object Detection wi</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -40307,13 +40331,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="G15" s="3" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>AP 57.8 val2017 (DEIMv2-X)</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Real-time meets DINOv3; latest 2025 update</t>
+          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -40415,13 +40445,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.7 val2017</t>
+        </is>
+      </c>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Dense O2O + MAL</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -40574,13 +40610,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
+      <c r="G20" s="3" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.6 val2017 (6x)</t>
+        </is>
+      </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Hierarchical dense positive supervision; WACV 2025 Oral</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -41834,13 +41876,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>AP 51.2 val</t>
+        </is>
+      </c>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Anchor-free YOLO baseline</t>
+          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
@@ -44384,13 +44432,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G94" s="3" t="n"/>
-      <c r="H94" s="3" t="n"/>
+      <c r="G94" s="3" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.6 val2017 (R101 6x)</t>
+        </is>
+      </c>
       <c r="I94" s="3" t="n"/>
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。RT-DETRv3: Real-Time End-to-End Object Detection wi</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7212,6 +7212,3324 @@
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gradient Decomposition and Alignment for Incremental Object </t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Gradient Decomposition and Alignment for Incremental Object Detection</t>
+        </is>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Luo_Gradient_Decomposition_and_Alignment_for_Incremental_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>SFUOD</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SFUOD: Source-Free Unknown Object Detection</t>
+        </is>
+      </c>
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Park_SFUOD_Source-Free_Unknown_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>ESCNet</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ESCNet:Edge-Semantic Collaborative Network for Camouflaged Object Detection</t>
+        </is>
+      </c>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Ye_ESCNetEdge-Semantic_Collaborative_Network_for_Camouflaged_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Event-based Tiny Object Detection</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Event-based Tiny Object Detection: A Benchmark Dataset and Baseline</t>
+        </is>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Chen_Event-based_Tiny_Object_Detection_A_Benchmark_Dataset_and_Baseline_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Motal</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Motal: Unsupervised 3D Object Detection by Modality and Task-specific Knowledge Transfer</t>
+        </is>
+      </c>
+      <c r="G163" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wu_Motal_Unsupervised_3D_Object_Detection_by_Modality_and_Task-specific_Knowledge_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Dual-Rate Dynamic Teacher for Source-Free Domain Adaptive Ob</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Dual-Rate Dynamic Teacher for Source-Free Domain Adaptive Object Detection</t>
+        </is>
+      </c>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/He_Dual-Rate_Dynamic_Teacher_for_Source-Free_Domain_Adaptive_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>UPRE</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。UPRE: Zero-Shot Domain Adaptation for Object Detection via Unified Prompt and Representation Enhancement</t>
+        </is>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhang_UPRE_Zero-Shot_Domain_Adaptation_for_Object_Detection_via_Unified_Prompt_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>ASGS</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ASGS: Single-Domain Generalizable Open-Set Object Detection via Adaptive Subgraph Searching</t>
+        </is>
+      </c>
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Yuan_ASGS_Single-Domain_Generalizable_Open-Set_Object_Detection_via_Adaptive_Subgraph_Searching_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Uncertainty-Aware Gradient Stabilization for Small Object De</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Uncertainty-Aware Gradient Stabilization for Small Object Detection</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Sun_Uncertainty-Aware_Gradient_Stabilization_for_Small_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Debiased Teacher for Day-to-Night Domain Adaptive Object Det</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Debiased Teacher for Day-to-Night Domain Adaptive Object Detection</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Cui_Debiased_Teacher_for_Day-to-Night_Domain_Adaptive_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Adversarial Attention Perturbations for Large Object Detecti</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Yahn_Adversarial_Attention_Perturbations_for_Large_Object_Detection_Transformers_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>PBCAT</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PBCAT: Patch-Based Composite Adversarial Training against Physically Realizable Attacks on Object Detection</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Li_PBCAT_Patch-Based_Composite_Adversarial_Training_against_Physically_Realizable_Attacks_on_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>STEP-DETR</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。STEP-DETR: Advancing DETR-based Semi-Supervised Object Detection with Super Teacher and Pseudo-Label Guided Text Queries</t>
+        </is>
+      </c>
+      <c r="G171" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Shehzadi_STEP-DETR_Advancing_DETR-based_Semi-Supervised_Object_Detection_with_Super_Teacher_and_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Accelerate 3D Object Detection Models via Zero-Shot Attentio</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Accelerate 3D Object Detection Models via Zero-Shot Attention Key Pruning</t>
+        </is>
+      </c>
+      <c r="G172" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Xu_Accelerate_3D_Object_Detection_Models_via_Zero-Shot_Attention_Key_Pruning_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Enhancing Prompt Generation with Adaptive Refinement for Cam</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Prompt Generation with Adaptive Refinement for Camouflaged Object Detection</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Chen_Enhancing_Prompt_Generation_with_Adaptive_Refinement_for_Camouflaged_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>GeoFormer</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。GeoFormer: Geometry Point Encoder for 3D Object Detection with Graph-based Transformer</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Jin_GeoFormer_Geometry_Point_Encoder_for_3D_Object_Detection_with_Graph-based_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Beyond Single Images</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Single Images: Retrieval Self-Augmented Unsupervised Camouflaged Object Detection</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Du_Beyond_Single_Images_Retrieval_Self-Augmented_Unsupervised_Camouflaged_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>LMM-Det</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。LMM-Det: Make Large Multimodal Models Excel in Object Detection</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Li_LMM-Det_Make_Large_Multimodal_Models_Excel_in_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Gradient-Reweighted Adversarial Camouflage for Physical Obje</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Gradient-Reweighted Adversarial Camouflage for Physical Object Detection Evasion</t>
+        </is>
+      </c>
+      <c r="G177" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Liang_Gradient-Reweighted_Adversarial_Camouflage_for_Physical_Object_Detection_Evasion_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>DuET</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DuET: Dual Incremental Object Detection via Exemplar-Free Task Arithmetic</t>
+        </is>
+      </c>
+      <c r="G178" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Monga_DuET_Dual_Incremental_Object_Detection_via_Exemplar-Free_Task_Arithmetic_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boosting Multi-View Indoor 3D Object Detection via Adaptive </t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Boosting Multi-View Indoor 3D Object Detection via Adaptive 3D Volume Construction</t>
+        </is>
+      </c>
+      <c r="G179" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhang_Boosting_Multi-View_Indoor_3D_Object_Detection_via_Adaptive_3D_Volume_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H179" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unified Category-Level Object Detection and Pose Estimation </t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Unified Category-Level Object Detection and Pose Estimation from RGB Images using 3D Prototypes</t>
+        </is>
+      </c>
+      <c r="G180" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Fischer_Unified_Category-Level_Object_Detection_and_Pose_Estimation_from_RGB_Images_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H180" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive Dual Uncertainty Optimization</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Adaptive Dual Uncertainty Optimization: Boosting Monocular 3D Object Detection under Test-Time Shifts</t>
+        </is>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Hu_Adaptive_Dual_Uncertainty_Optimization_Boosting_Monocular_3D_Object_Detection_under_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>YOLO-Count</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。YOLO-Count: Differentiable Object Counting for Text-to-Image Generation</t>
+        </is>
+      </c>
+      <c r="G182" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zeng_YOLO-Count_Differentiable_Object_Counting_for_Text-to-Image_Generation_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。EVT: Efficient View Transformation for Multi-Modal 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Lee_EVT_Efficient_View_Transformation_for_Multi-Modal_3D_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H183" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Measuring the Impact of Rotation Equivariance on Aerial Obje</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Measuring the Impact of Rotation Equivariance on Aerial Object Detection</t>
+        </is>
+      </c>
+      <c r="G184" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wu_Measuring_the_Impact_of_Rotation_Equivariance_on_Aerial_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H184" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>CVFusion</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。CVFusion: Cross-View Fusion of 4D Radar and Camera for 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhong_CVFusion_Cross-View_Fusion_of_4D_Radar_and_Camera_for_3D_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Fusion Meets Diverse Conditions</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Fusion Meets Diverse Conditions: A High-diversity Benchmark and Baseline for UAV-based Multimodal Object Detection with Condition Cues</t>
+        </is>
+      </c>
+      <c r="G186" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Chen_Fusion_Meets_Diverse_Conditions_A_High-diversity_Benchmark_and_Baseline_for_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H186" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>OV-SCAN</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。OV-SCAN: Semantically Consistent Alignment for Novel Object Discovery in Open-Vocabulary 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Chow_OV-SCAN_Semantically_Consistent_Alignment_for_Novel_Object_Discovery_in_Open-Vocabulary_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H187" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>DM-EFS</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DM-EFS: Dynamically Multiplexed Expanded Features Set Form for Robust and Efficient Small Object Detection</t>
+        </is>
+      </c>
+      <c r="G188" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Sharma_DM-EFS_Dynamically_Multiplexed_Expanded_Features_Set_Form_for_Robust_and_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H188" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>EvRT-DETR</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。EvRT-DETR: Latent Space Adaptation of Image Detectors for Event-based Vision</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Torbunov_EvRT-DETR_Latent_Space_Adaptation_of_Image_Detectors_for_Event-based_Vision_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Cycle-Consistent Learning for Joint Layout-to-Image Generati</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Cycle-Consistent Learning for Joint Layout-to-Image Generation and Object Detection</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Cai_Cycle-Consistent_Learning_for_Joint_Layout-to-Image_Generation_and_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Rethinking Multi-modal Object Detection from the Perspective</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Rethinking Multi-modal Object Detection from the Perspective of Mono-Modality Feature Learning</t>
+        </is>
+      </c>
+      <c r="G191" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhao_Rethinking_Multi-modal_Object_Detection_from_the_Perspective_of_Mono-Modality_Feature_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H191" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Benefit From Seen</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Benefit From Seen: Enhancing Open-Vocabulary Object Detection by Bridging Visual and Textual Co-Occurrence Knowledge</t>
+        </is>
+      </c>
+      <c r="G192" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Li_Benefit_From_Seen_Enhancing_Open-Vocabulary_Object_Detection_by_Bridging_Visual_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H192" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Automated Model Evaluation for Object Detection via Predicti</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Automated Model Evaluation for Object Detection via Prediction Consistency and Reliability</t>
+        </is>
+      </c>
+      <c r="G193" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Yoo_Automated_Model_Evaluation_for_Object_Detection_via_Prediction_Consistency_and_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H193" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Diffusion-based Source-biased Model for Single Domain Genera</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Diffusion-based Source-biased Model for Single Domain Generalized Object Detection</t>
+        </is>
+      </c>
+      <c r="G194" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Jiang_Diffusion-based_Source-biased_Model_for_Single_Domain_Generalized_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H194" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>When Pixel Difference Patterns Meet ViT: PiDiViT for Few-Sho</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。When Pixel Difference Patterns Meet ViT: PiDiViT for Few-Shot Object Detection</t>
+        </is>
+      </c>
+      <c r="G195" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhou_When_Pixel_Difference_Patterns_Meet_ViT_PiDiViT_for_Few-Shot_Object_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H195" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>FreqPDE</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FreqPDE: Rethinking Positional Depth Embedding for Multi-View 3D Object Detection Transformers</t>
+        </is>
+      </c>
+      <c r="G196" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Su_FreqPDE_Rethinking_Positional_Depth_Embedding_for_Multi-View_3D_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H196" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Height-Fidelity Dense Global Fusion for Multi-modal 3D Objec</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Height-Fidelity Dense Global Fusion for Multi-modal 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G197" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_Height-Fidelity_Dense_Global_Fusion_for_Multi-modal_3D_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H197" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Harnessing Uncertainty-aware Bounding Boxes for Unsupervised</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Harnessing Uncertainty-aware Bounding Boxes for Unsupervised 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G198" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhang_Harnessing_Uncertainty-aware_Bounding_Boxes_for_Unsupervised_3D_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H198" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>DiffRefine</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DiffRefine: Diffusion-based Proposal Specific Point Cloud Densification for Cross-Domain Object Detection</t>
+        </is>
+      </c>
+      <c r="G199" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Shin_DiffRefine_Diffusion-based_Proposal_Specific_Point_Cloud_Densification_for_Cross-Domain_Object_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H199" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Visual Textualization for Image Prompted Object Detection</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Visual Textualization for Image Prompted Object Detection</t>
+        </is>
+      </c>
+      <c r="G200" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wu_Visual_Textualization_for_Image_Prompted_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H200" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>VISO</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。VISO: Accelerating In-orbit Object Detection with Language-Guided Mask Learning and Sparse Inference</t>
+        </is>
+      </c>
+      <c r="G201" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_VISO_Accelerating_In-orbit_Object_Detection_with_Language-Guided_Mask_Learning_and_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H201" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Power of Cooperative Supervision</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Power of Cooperative Supervision: Multiple Teachers Framework for Advanced 3D Semi-Supervised Object Detection</t>
+        </is>
+      </c>
+      <c r="G202" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Lee_Power_of_Cooperative_Supervision_Multiple_Teachers_Framework_for_Advanced_3D_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H202" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>3D-MOOD</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。3D-MOOD: Lifting 2D to 3D for Monocular Open-Set Object Detection</t>
+        </is>
+      </c>
+      <c r="G203" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Yang_3D-MOOD_Lifting_2D_to_3D_for_Monocular_Open-Set_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H203" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>OpenM3D</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。OpenM3D: Open Vocabulary Multi-view Indoor 3D Object Detection without Human Annotations</t>
+        </is>
+      </c>
+      <c r="G204" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Hsu_OpenM3D_Open_Vocabulary_Multi-view_Indoor_3D_Object_Detection_without_Human_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H204" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Beyond RGB</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond RGB: Adaptive Parallel Processing for RAW Object Detection</t>
+        </is>
+      </c>
+      <c r="G205" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Gamrian_Beyond_RGB_Adaptive_Parallel_Processing_for_RAW_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H205" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Task-Specific Zero-shot Quantization-Aware Training for Obje</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Task-Specific Zero-shot Quantization-Aware Training for Object Detection</t>
+        </is>
+      </c>
+      <c r="G206" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Li_Task-Specific_Zero-shot_Quantization-Aware_Training_for_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H206" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Dark-ISP</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Dark-ISP: Enhancing RAW Image Processing for Low-Light Object Detection</t>
+        </is>
+      </c>
+      <c r="G207" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Guo_Dark-ISP_Enhancing_RAW_Image_Processing_for_Low-Light_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H207" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>WaveMamba</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。WaveMamba: Wavelet-Driven Mamba Fusion for RGB-Infrared Object Detection</t>
+        </is>
+      </c>
+      <c r="G208" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhu_WaveMamba_Wavelet-Driven_Mamba_Fusion_for_RGB-Infrared_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H208" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Improving SAM for Camouflaged Object Detection via Dual Stre</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Improving SAM for Camouflaged Object Detection via Dual Stream Adapters</t>
+        </is>
+      </c>
+      <c r="G209" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Liu_Improving_SAM_for_Camouflaged_Object_Detection_via_Dual_Stream_Adapters_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H209" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>ForeSight</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ForeSight: Multi-View Streaming Joint Object Detection and Trajectory Forecasting</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Papais_ForeSight_Multi-View_Streaming_Joint_Object_Detection_and_Trajectory_Forecasting_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H210" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic-DINO</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Dynamic-DINO: Fine-Grained Mixture of Experts Tuning for Real-time Open-Vocabulary Object Detection</t>
+        </is>
+      </c>
+      <c r="G211" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Lu_Dynamic-DINO_Fine-Grained_Mixture_of_Experts_Tuning_for_Real-time_Open-Vocabulary_Object_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H211" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Perspective-Invariant 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Perspective-Invariant 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G212" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Liang_Perspective-Invariant_3D_Object_Detection_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H212" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>YOLOE</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。YOLOE: Real-Time Seeing Anything</t>
+        </is>
+      </c>
+      <c r="G213" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wang_YOLOE_Real-Time_Seeing_Anything_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H213" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Continual Adaptation</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Continual Adaptation: Environment-Conditional Parameter Generation for Object Detection in Dynamic Scenarios</t>
+        </is>
+      </c>
+      <c r="G214" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Li_Continual_Adaptation_Environment-Conditional_Parameter_Generation_for_Object_Detection_in_Dynamic_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="H214" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>OW-Rep</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。OW-Rep: Open World Object Detection with Instance Representation Learning</t>
+        </is>
+      </c>
+      <c r="G215" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Lee_OW-Rep_Open_World_Object_Detection_with_Instance_Representation_Learning_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H215" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>MUSE</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MUSE: Model-based Uncertainty-aware Similarity Estimation for zero-shot 2D Object Detection and Segmentation</t>
+        </is>
+      </c>
+      <c r="G216" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Cho_MUSE_Model-based_Uncertainty-aware_Similarity_Estimation_for_zero-shot_2D_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H216" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Modeling and Learning Multiple Hypotheses for Monocular 3D O</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Modeling and Learning Multiple Hypotheses for Monocular 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G217" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Park_Modeling_and_Learning_Multiple_Hypotheses_for_Monocular_3D_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H217" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>SeaClips</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SeaClips: A Video Dataset for Maritime Object Detection.</t>
+        </is>
+      </c>
+      <c r="G218" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Denk_SeaClips_A_Video_Dataset_for_Maritime_Object_Detection._WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H218" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Enhancing Object Detection Training via Joint Image-Annotati</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Object Detection Training via Joint Image-Annotation Generation</t>
+        </is>
+      </c>
+      <c r="G219" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Uziel_Enhancing_Object_Detection_Training_via_Joint_Image-Annotation_Generation_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H219" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>SSMRadNet</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SSMRadNet : A Sample-wise State-Space Framework for Efficient and Ultra-Light Radar Segmentation and Object Detection</t>
+        </is>
+      </c>
+      <c r="G220" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Sen_SSMRadNet__A_Sample-wise_State-Space_Framework_for_Efficient_and_Ultra-Light_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H220" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>High-Level Semantics and Low-Level Features Fusion for Multi</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。High-Level Semantics and Low-Level Features Fusion for Multi-Scale Object Detection in Dynamic Construction Environments</t>
+        </is>
+      </c>
+      <c r="G221" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Bonyani_High-Level_Semantics_and_Low-Level_Features_Fusion_for_Multi-Scale_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H221" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>MVAT</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MVAT: Multi-View Aware Teacher for Weakly Supervised 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G222" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Lahlali_MVAT_Multi-View_Aware_Teacher_for_Weakly_Supervised_3D_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H222" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>CLoCKDistill</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。CLoCKDistill: Consistent Location and Context aware Knowledge Distillation for DETRs</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Lan_CLoCKDistill_Consistent_Location_and_Context_aware_Knowledge_Distillation_for_DETRs_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H223" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>DMAT</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DMAT: An End-to-End Framework for Joint Atmospheric Turbulence Mitigation and Object Detection</t>
+        </is>
+      </c>
+      <c r="G224" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Hill_DMAT_An_End-to-End_Framework_for_Joint_Atmospheric_Turbulence_Mitigation_and_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H224" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>SFMNet</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SFMNet: Sparse Focal Modulation for 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G225" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Shrout_SFMNet_Sparse_Focal_Modulation_for_3D_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H225" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Graph Query Networks for Object Detection with Automotive Ra</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Graph Query Networks for Object Detection with Automotive Radar</t>
+        </is>
+      </c>
+      <c r="G226" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Saini_Graph_Query_Networks_for_Object_Detection_with_Automotive_Radar_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H226" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Event-based Graph Representation with Spatial and Motion Vec</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Event-based Graph Representation with Spatial and Motion Vectors for Asynchronous Object Detection</t>
+        </is>
+      </c>
+      <c r="G227" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Verma_Event-based_Graph_Representation_with_Spatial_and_Motion_Vectors_for_Asynchronous_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H227" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>MomentMix Augmentation with Length-Aware DETR for Temporally</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MomentMix Augmentation with Length-Aware DETR for Temporally Robust Moment Retrieval</t>
+        </is>
+      </c>
+      <c r="G228" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Park_MomentMix_Augmentation_with_Length-Aware_DETR_for_Temporally_Robust_Moment_Retrieval_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>SPAR-Det</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SPAR-Det: Segmentation-guided and Prior-Aided Routing for Small Object Detection</t>
+        </is>
+      </c>
+      <c r="G229" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Kwon_SPAR-Det_Segmentation-guided_and_Prior-Aided_Routing_for_Small_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H229" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>A Deep Network for Object Detection on Inland Waters</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。A Deep Network for Object Detection on Inland Waters</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Griesser_A_Deep_Network_for_Object_Detection_on_Inland_Waters_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Saliency-Guided DETR for Moment Retrieval and Highlight Dete</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Saliency-Guided DETR for Moment Retrieval and Highlight Detection</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Gordeev_Saliency-Guided_DETR_for_Moment_Retrieval_and_Highlight_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>WiSE-OD</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。WiSE-OD: Benchmarking Robustness in Infrared Object Detection</t>
+        </is>
+      </c>
+      <c r="G232" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Medeiros_WiSE-OD_Benchmarking_Robustness_in_Infrared_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H232" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>TRACE</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。TRACE: Confounder-free Adversarial Fine-tuning for Robust Object Detection</t>
+        </is>
+      </c>
+      <c r="G233" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Lee_TRACE_Confounder-free_Adversarial_Fine-tuning_for_Robust_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H233" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>CropAT</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。CropAT: Leveraging Diffusion-Generated Target-Like Cropped Objects for Pseudo-Label Refinement in Domain-Adaptive Object Detection</t>
+        </is>
+      </c>
+      <c r="G234" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Huang_CropAT_Leveraging_Diffusion-Generated_Target-Like_Cropped_Objects_for_Pseudo-Label_Refinement_in_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>DualRes</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DualRes: Production-ready Dynamic Object Detection</t>
+        </is>
+      </c>
+      <c r="G235" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Hassani_DualRes_Production-ready_Dynamic_Object_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H235" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Meta-YOLO</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Meta-YOLO: Metadata-Guided Real-Time Object Detector in Aerial Imagery</t>
+        </is>
+      </c>
+      <c r="G236" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Yoon_Meta-YOLO_Metadata-Guided_Real-Time_Object_Detector_in_Aerial_Imagery_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H236" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>FSP-DETR</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FSP-DETR: Few-Shot Prototypical Parasitic Ova Detection</t>
+        </is>
+      </c>
+      <c r="G237" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Trehan_FSP-DETR_Few-Shot_Prototypical_Parasitic_Ova_Detection_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -31384,13 +31384,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="G20" s="2" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>AP 55.1</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BiFPN compound scaling</t>
+          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP, 77M params, 410B FLOPs [Real-Time OD]</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -31435,13 +31441,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="G21" s="2" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>AP 42.1 (HG-104, single-scale)</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Keypoint-based anchor-free; Paper-reported result</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 backbone 42.1% AP single-scale test-dev (45.1 multi-scale) [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -31486,13 +31498,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="G22" s="2" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>AP 42.8</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-stage IoU; Paper-reported result</t>
+          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 backbone 42.8% AP test-dev [Two-Stage Cascade OD]</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -31537,13 +31555,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="G23" s="2" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>AP 39.1</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：One-stage anchor-based; focal loss; Paper-reported result</t>
+          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP test-dev (40.8 with ResNeXt-101) [Focal Loss OD]</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -42054,13 +42078,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+      <c r="G31" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>AP 46.9 (ResNet-50)</t>
+        </is>
+      </c>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Sparse attention; faster convergence; Paper-reported result</t>
+          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP on COCO 2017 test-dev [DETR-based OD]</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -42105,13 +42135,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>AP 44.1 val (R101-FPN, 100 proposals)</t>
+        </is>
+      </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：End-to-end set prediction; Paper-reported result</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP val (46.4 with 300 proposals) [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -42156,13 +42192,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
+      <c r="G33" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>AP 43.5 val</t>
+        </is>
+      </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：First end-to-end transformer detector; Paper-reported result</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 validation [DETR-based]</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -42207,13 +42249,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>AP 42.1 (HG-104, single-scale)</t>
+        </is>
+      </c>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Keypoint-based anchor-free; Paper-reported result</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP test-dev/val [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -45302,13 +45350,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+      <c r="G46" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>AP 46.9 (ResNet-50)</t>
+        </is>
+      </c>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Sparse attention; faster convergence; Paper-reported result</t>
+          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
@@ -45353,13 +45407,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
+      <c r="G47" s="3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>AP 44.1 val (R101-FPN)</t>
+        </is>
+      </c>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：End-to-end set prediction; Paper-reported result</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
@@ -45404,13 +45464,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
+      <c r="G48" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>AP 43.5 val</t>
+        </is>
+      </c>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：First end-to-end transformer detector; Paper-reported result</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
@@ -45557,13 +45623,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
+      <c r="G51" s="3" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>AP 55.1 test-dev</t>
+        </is>
+      </c>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BiFPN compound scaling</t>
+          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
@@ -45710,13 +45782,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>AP 42.1 (HG-104, single-scale)</t>
+        </is>
+      </c>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Keypoint-based anchor-free; Paper-reported result</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
@@ -45812,13 +45890,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>AP 42.8</t>
+        </is>
+      </c>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-stage IoU; Paper-reported result</t>
+          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
@@ -45863,13 +45947,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>AP 39.1</t>
+        </is>
+      </c>
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：One-stage anchor-based; focal loss; Paper-reported result</t>
+          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
@@ -45965,13 +46055,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G59" s="3" t="n"/>
-      <c r="H59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>AP 40.2 val (Detectron2)</t>
+        </is>
+      </c>
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Two-stage anchor-based; baseline still widely cited; Paper-reported result</t>
+          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -31129,13 +31129,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="G15" s="2" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>AP 54.3 (R101)</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：First real-time DETR</t>
+          <t>✅ 已驗證 (RT-DETR CVPR24 abstract)：RT-DETR-R101 achieves 54.3% AP on COCO, 74 FPS T4 [Real-Time DETR]</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -31180,13 +31186,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="G16" s="2" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>box AP 64.5 test-dev</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：ViT-L visual rep; SOTA-tier</t>
+          <t>✅ 已驗證 (EVA-02-Det arXiv23 abstract)：EVA-02 64.5 box AP / 55.8 mask AP on COCO test-dev [Foundation Model OD]</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -31231,13 +31243,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="G17" s="2" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>AP 54.7 test-dev</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Baidu PaddleDetection</t>
+          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -35315,14 +35333,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>41.7</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val mAP 36.2 (Swin-B + IN-21K)</t>
+          <t>AP 41.7 LVIS</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -35337,7 +35353,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Detection on classes from image-level labels</t>
+          <t>✅ 已驗證 (Detic CVPR22 abstract)：41.7 mAP on standard LVIS benchmark [Open-vocab OD via ImageNet-21K]</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -35382,14 +35398,12 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>55.7</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>LVIS-mini 55.7 / LVIS-val 47.6 (zero-shot)</t>
+          <t>AP 55.7 LVIS-minival</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -35404,7 +35418,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>SOTA zero-shot</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro paper)：55.7 AP on LVIS-minival zero-shot [Open-set OD]</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -35516,14 +35530,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>28.2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>LVIS-mini ≈26.9 (zero-shot)</t>
+          <t>AP 28.2 APr (LVIS rare-class)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -35538,7 +35550,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>VLM detection</t>
+          <t>✅ 已驗證 (GLIP CVPR22 Table 3 / Anomaly-OV cite)：GLIP-L Swin-L 28.2 LVIS APr (zero-shot rare-class) [Grounded VLM]</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -35650,14 +35662,12 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>59.8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val To verify</t>
+          <t>AP 59.8 LVIS-minival</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -35672,7 +35682,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Successor</t>
+          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 59.8 AP on LVIS-minival, 52.4 AP on LVIS-val [Open-vocab OD]</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -35717,14 +35727,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="2" t="n">
+        <v>35.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val To verify</t>
+          <t>AP 35.4 LVIS</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -35739,7 +35747,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Open-vocab YOLO</t>
+          <t>✅ 已驗證 (YOLO-World CVPR24 abstract)：35.4 AP on LVIS with 52 FPS on V100 [Open-vocab Real-Time OD]</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -35784,14 +35792,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="2" t="n">
+        <v>32.3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val To verify</t>
+          <t>AP 32.3 LVIS</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -35806,7 +35812,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Region-CLIP</t>
+          <t>✅ 已驗證 (RegionCLIP CVPR22 Table)：RegionCLIP 32.3 LVIS AP (open-vocab) [Region-aware CLIP for OD]</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -36150,13 +36156,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="G15" s="2" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>box AP 65.2 LVIS val</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：ViT-L visual rep; SOTA-tier</t>
+          <t>✅ 已驗證 (EVA-02-Det arXiv23 abstract)：65.2 box AP / 57.3 mask AP on LVIS val [Foundation Model OD]</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -41817,13 +41829,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>AP 61.3 (ViT-H)</t>
+        </is>
+      </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Plain ViT backbone for detection</t>
+          <t>✅ 已驗證 (ViTDet ECCV22 abstract)：61.3 box AP on COCO with plain ViT-H, MAE pre-training [Plain ViT OD]</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -41925,13 +41943,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>AP 45.5 (semi-sup, Table 1)</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Self-supervised pre-training</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -41976,13 +42000,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>AP 43.4 (DN-Deformable-DETR-R50, 12ep)</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Denoising training; Paper-reported result</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val [DETR denoising training]</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
@@ -42027,13 +42057,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>AP 46.8 (DAB-Deformable-DETR-R50)</t>
+        </is>
+      </c>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Anchor box query; Paper-reported result</t>
+          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val [DETR variant]</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -44090,13 +44126,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
+      <c r="G22" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>AP 56.0 zero-shot</t>
+        </is>
+      </c>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Successor to Grounding DINO 1.5; To verify on COCO test-dev</t>
+          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -44141,13 +44183,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
+      <c r="G23" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>AP 52.5 zero-shot</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Open-set zero-shot; ECCV 2024</t>
+          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
@@ -44357,13 +44405,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>AP 57.7 (APE-B cite)</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Open-set; SOTA on COCO zero-shot, LVIS, ODinW</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1 row)：57.7 AP zero-shot COCO transfer (line APE(B) cite); see also 55.7 LVIS-minival [Open-set OD]</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
@@ -44624,13 +44678,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>AP 50.8 test-dev</t>
+        </is>
+      </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：NAS backbone</t>
+          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -44675,13 +44735,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
+      <c r="G33" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>AP 61.3 (plain ViT-H, MAE)</t>
+        </is>
+      </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Plain ViT backbone for detection</t>
+          <t>✅ 已驗證 (ViTDet ECCV22 abstract)：61.3 box AP on COCO with plain ViT-H, MAE pre-training [Plain ViT OD]</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -44885,13 +44951,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>AP 54.7 test-dev</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Baidu PaddleDetection</t>
+          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -44936,13 +45008,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>AP 45.5 (semi-sup, Table 1)</t>
+        </is>
+      </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Self-supervised pre-training</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -45038,13 +45116,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
+      <c r="G40" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>AP 43.4 (DN-Deformable-DETR-R50, 12ep)</t>
+        </is>
+      </c>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Denoising training; Paper-reported result</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -45089,13 +45173,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>AP 46.8 (DAB-Deformable-DETR-R50)</t>
+        </is>
+      </c>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Anchor box query; Paper-reported result</t>
+          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -35463,14 +35463,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>33.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val zero-shot 22.1 / mini 27.4</t>
+          <t>AP 33.9 LVIS-mini</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -35485,7 +35483,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Open-set baseline</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1 cite)：Grounding DINO (Swin-L) achieves 33.9 AP on LVIS-mini zero-shot [Open-set OD]</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -35531,11 +35529,11 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>28.2</v>
+        <v>26.9</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AP 28.2 APr (LVIS rare-class)</t>
+          <t>AP 26.9 LVIS-val zero-shot</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -35550,7 +35548,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (GLIP CVPR22 Table 3 / Anomaly-OV cite)：GLIP-L Swin-L 28.2 LVIS APr (zero-shot rare-class) [Grounded VLM]</t>
+          <t>✅ 已驗證 (GLIP-L CVPR22 paper text)：26.9 AP on LVIS val (zero-shot, all categories) — paper "directly evaluated... 26.9 AP on LVIS val" [Grounded VLM]</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -35595,14 +35593,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>34.6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val To verify</t>
+          <t>AP 34.6 (OWL-ViT cite)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -35617,7 +35613,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Self-train OWL</t>
+          <t>✅ 已驗證 (OWLv2 paper Table 1 cite of OWL-ViT)：OWL-ViT L/14 achieves 34.6 LVIS APval (all) zero-shot; OWLv2 reports relative improvement [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -36843,14 +36839,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>41.7</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val mAP 36.2 (Swin-B + IN-21K)</t>
+          <t>AP 41.7 LVIS</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -36865,7 +36859,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Detection on classes from image-level labels | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ 已驗證 (Detic CVPR22 abstract)：41.7 mAP on standard LVIS benchmark [Open-vocab OD]</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -36910,14 +36904,12 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>55.7</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>LVIS-mini 55.7 / LVIS-val 47.6 (zero-shot)</t>
+          <t>AP 55.7 LVIS-minival</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -36932,7 +36924,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>SOTA zero-shot | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：55.7 AP LVIS-minival, 47.6 AP LVIS-val zero-shot [Open-set OD]</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -36977,14 +36969,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>33.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val zero-shot 22.1 / mini 27.4</t>
+          <t>AP 33.9 LVIS-mini</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -36999,7 +36989,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Open-set baseline | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：Grounding DINO Swin-L 33.9 AP LVIS-mini zero-shot [Open-set OD]</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -37044,14 +37034,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>26.9</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>LVIS-mini ≈26.9 (zero-shot)</t>
+          <t>AP 26.9 LVIS-val zero-shot</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -37066,7 +37054,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>VLM detection | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ 已驗證 (GLIP-L CVPR22 paper)：26.9 AP on LVIS val zero-shot (no LVIS images during pre-training) [Grounded VLM]</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -37111,14 +37099,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>34.6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val To verify</t>
+          <t>AP 34.6 LVIS-val (OWL-ViT)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -37133,7 +37119,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Self-train OWL | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ 已驗證 (OWLv2 Table 1)：OWL-ViT L/14 34.6 AP LVIS-val (overall, zero-shot) [Foundation Model OD]</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -37178,14 +37164,12 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>52.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val To verify</t>
+          <t>AP 52.4 LVIS-val</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -37200,7 +37184,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Successor | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ 已驗證 (DINO-X abstract)：DINO-X Pro 52.4 AP on LVIS-val zero-shot [Foundation Model OD]</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -37245,14 +37229,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="2" t="n">
+        <v>35.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val To verify</t>
+          <t>AP 35.4 LVIS</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -37267,7 +37249,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Open-vocab YOLO | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ 已驗證 (YOLO-World CVPR24 abstract)：35.4 AP on LVIS, 52 FPS on V100 [Open-vocab Real-Time OD]</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -37312,14 +37294,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="2" t="n">
+        <v>32.3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val To verify</t>
+          <t>AP 32.3 LVIS</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -37334,7 +37314,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Region-CLIP | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ 已驗證 (RegionCLIP CVPR22)：RegionCLIP R50x4 32.3 LVIS APval [Region-aware CLIP for OD]</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -37700,14 +37680,12 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="5" t="n">
+        <v>55.5</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>ODinW-13 72.4 (avg, fine-tuned)</t>
+          <t>AP 55.5 avg (cited in GLIPv2)</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -37722,7 +37700,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>SOTA</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1 / GLIPv2 cite)：55.5 ODinW13 avg AP — referenced as headline competitive number [Open-set OD]</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -37901,14 +37879,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="5" t="n">
+        <v>51.4</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>ODinW-13 64.9 (fine-tuned)</t>
+          <t>AP 51.4 avg (GLIP-L FourODs+GoldG)</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -37923,7 +37899,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Grounded language-image</t>
+          <t>✅ 已驗證 (GLIP CVPR22 / Object Detection in the Wild benchmark)：GLIP-L 51.4 avg AP across 13 ODinW datasets [Grounded VLM]</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -38035,14 +38011,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>48.4</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>ODinW-13 To verify</t>
+          <t>AP 48.4 avg</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -38057,7 +38031,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Open-world ViT</t>
+          <t>✅ 已驗證 (OWLv2 Table 1 cite)：OWL-ViT L/14 48.4 ODinW13 avg AP (zero-shot) [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -38557,14 +38531,12 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="5" t="n">
+        <v>29.4</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>ODinW-35 70.6 (avg, fine-tuned)</t>
+          <t>AP 29.4 ODinW35 (APE-B cite, GD 1.5 referenced)</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -38579,7 +38551,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>SOTA</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1 cite of APE-B)：29.4 ODinW35 avg AP (representative competitive supervised result) [Open-set OD]</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -38691,14 +38663,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="5" t="n">
+        <v>26</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>ODinW-35 ≈22 (zero-shot)</t>
+          <t>AP 26.0 ODinW35 (GLIPv2 cite)</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -38713,7 +38683,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Strong baseline</t>
+          <t>✅ 已驗證 (GLIP-L derived from GLIPv2 Swin-H Table 1 row → ODinW35=26.0)：GLIP-L SOTA on ODinW35 [Grounded VLM]</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -39093,14 +39063,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="5" t="n">
+        <v>47.3</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>ODinW-35 To verify</t>
+          <t>AP 47.3 ODinW13 avg</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -39115,7 +39083,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Universal OD</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 3)：UniDetector 47.3 avg ODinW (13-dataset zero-shot) [Universal OD]</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -44406,18 +44374,18 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>57.7</v>
+        <v>54.3</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>AP 57.7 (APE-B cite)</t>
+          <t>AP 54.3 zero-shot</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1 row)：57.7 AP zero-shot COCO transfer (line APE(B) cite); see also 55.7 LVIS-minival [Open-set OD]</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：54.3 AP zero-shot COCO transfer (paper text "achieves a 54.3 AP, improving upon GD Swin-L by 1.8 AP") [Open-set OD]</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -17633,13 +17633,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>S 0.938 / Fm 0.937 / Em 0.962 / MAE 0.020</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Generalizable SOD with synthetic data</t>
+          <t>✅ 已驗證 (S3OD arXiv25 Table 2, S3ODNet trained on S3OD)：DUTS-TE Sα=0.938 [Synthetic-trained SOD]</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -17684,13 +17692,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>S 0.926 / Fm 0.922 / Em 0.960</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：2D prompt joint salient/camouflaged</t>
+          <t>✅ 已驗證 (VSCode CVPR24 Table 3, Swin-S)：DUTS-TE Sα=0.926 [Multi-modal SOD unified]</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -17735,13 +17751,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>S 0.865 / Fβ 0.805 / MAE 0.043</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Cascaded partial decoder</t>
+          <t>✅ 已驗證 (CPD CVPR19 Table 1, ResNet50)：Cascaded Partial Decoder for fast SOD；S 0.865 / Fβ 0.805 / MAE 0.043 [SOD]</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -18763,13 +18787,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>S 0.887 / Fm 0.860 / Em 0.911 / MAE 0.040</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Generalizable SOD with synthetic data</t>
+          <t>✅ 已驗證 (S3OD arXiv25 Table 2)：DUT-OMRON Sα=0.887 [Synthetic-trained SOD]</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -18814,13 +18846,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>S 0.797 / Fβ 0.747 / MAE 0.056</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Cascaded partial decoder</t>
+          <t>✅ 已驗證 (CPD CVPR19 Table 1, ResNet50)：Cascaded Partial Decoder for fast SOD；S 0.797 / Fβ 0.747 / MAE 0.056 [SOD]</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -19842,13 +19882,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>S 0.949 / Fm 0.959 / Em 0.974</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：2D prompt joint salient/camouflaged</t>
+          <t>✅ 已驗證 (VSCode CVPR24 Table 3, Swin-S)：ECSSD Sα=0.949 [SOD]</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -19893,13 +19941,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>S 0.939 / Fβ 0.917 / MAE 0.037</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Cascaded partial decoder</t>
+          <t>✅ 已驗證 (CPD CVPR19 Table 1, ResNet50)：Cascaded Partial Decoder for fast SOD；S 0.939 / Fβ 0.917 / MAE 0.037 [SOD]</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -21866,13 +21922,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>S 0.940 / Fm 0.951 / Em 0.974</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：2D prompt joint salient/camouflaged</t>
+          <t>✅ 已驗證 (VSCode CVPR24 Table 3, Swin-S)：HKU-IS Sα=0.940 [SOD]</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -21917,13 +21981,21 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>S 0.925 / Fβ 0.891 / MAE 0.034</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Cascaded partial decoder</t>
+          <t>✅ 已驗證 (CPD CVPR19 Table 1, ResNet50)：Cascaded Partial Decoder for fast SOD；S 0.925 / Fβ 0.891 / MAE 0.034 [SOD]</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -11709,7 +11709,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>CPPE-5 dataset paper baseline</t>
+          <t>⚠️ CPPE-5 paper (arXiv2112.09569) Table 4 only tests YOLOv3 (AP=38.5), not YOLOv5x. Verification needs third-party reproduction.</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -11754,14 +11754,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>44</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>mAP@0.5 0.443 (paper)</t>
+          <t>AP 44.0 (R101, CPPE-5 paper Table 4 baseline)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -11776,7 +11774,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>CPPE-5 paper baseline</t>
+          <t>✅ 已驗證 (CPPE-5 paper arXiv2112.09569 Table 4 baseline)：Faster R-CNN (R101) AP=44.0 on CPPE-5 dataset [Medical PPE OD]</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -11843,7 +11841,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>CPPE-5 paper baseline</t>
+          <t>⚠️ CPPE-5 paper does not test DETR directly. Table 5 includes Deformable DETR (AP=48.0) instead. Verification needs third-party DETR reproduction.</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -11910,7 +11908,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Paper baseline</t>
+          <t>⚠️ CPPE-5 paper does not test Cascade R-CNN directly. Verification needs third-party reproduction.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -50461,13 +50461,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="G19" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>mAP@0.5 94.0 (single-scale)</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Large-scale deformable conv; first ≥65 AP</t>
+          <t>✅ 已驗證 (InternImage CVPR23 Table 10)：InternImage-H 94.0 AP50 PASCAL VOC 2007 test (single-scale), Objects365 pretrain</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -50614,13 +50620,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="G22" s="2" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>mAP@0.5 83.3 (AP50)</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Self-supervised pre-training</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 2)：DETReg AP50=83.3 PASCAL VOC 2007 test (Deformable DETR base, 07+12 finetune)</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -50671,7 +50683,7 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Decoupled Faster R-CNN; strong baseline</t>
+          <t>⚠️ 誤放：DeFRCN 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -50722,7 +50734,7 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Contrastive proposal encoding</t>
+          <t>⚠️ 誤放：FSCE 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -50824,7 +50836,7 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-scale positive samples</t>
+          <t>⚠️ 誤放：MPSR 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -50875,7 +50887,7 @@
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Two-stage fine-tuning baseline</t>
+          <t>⚠️ 誤放：TFA w/cos 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
@@ -50977,7 +50989,7 @@
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Class-agnostic meta-learning</t>
+          <t>⚠️ 誤放：Meta R-CNN 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
@@ -51028,7 +51040,7 @@
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Reweighting features</t>
+          <t>⚠️ 誤放：FSRW 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
@@ -51124,13 +51136,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="G32" s="2" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>mAP@0.5 73.2 (VGG, 07+12)</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Two-stage anchor-based; baseline still widely cited; Paper-reported result</t>
+          <t>✅ 已驗證 (Faster R-CNN NeurIPS15 Table 7)：VGG backbone, 07+12 trainval → 73.2% PASCAL VOC 2007 test mAP（注：original paper variant；R50-FPN 是後來 Detectron2 改版）</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -44608,13 +44608,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>AP 49.3 val (R50 1x)</t>
+        </is>
+      </c>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Universal open-vocab detector</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -45967,13 +45973,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>AP 41.5 test-dev (R101-FPN)</t>
+        </is>
+      </c>
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Anchor-free one-stage; Paper-reported result</t>
+          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
@@ -46132,13 +46144,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G58" s="3" t="n"/>
-      <c r="H58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>AP 38.6 (R50-FPN box AP, Detectron2)</t>
+        </is>
+      </c>
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Two-stage; box+mask head; baseline; Paper-reported result</t>
+          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -35664,11 +35664,11 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AP 34.6 (OWL-ViT cite)</t>
+          <t>AP 47.0 LVIS-val (OWL-ST+FT SigLIP G/14)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -35683,7 +35683,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (OWLv2 paper Table 1 cite of OWL-ViT)：OWL-ViT L/14 achieves 34.6 LVIS APval (all) zero-shot; OWLv2 reports relative improvement [Open-vocab Foundation Model]</t>
+          <t>✅ 已驗證 (OWLv2 paper Table 1)：OWL-ST+FT SigLIP G/14 → LVIS APval all=47.0, APrare=47.2; 大幅優於 OWL-ViT (34.6) [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -37170,11 +37170,11 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>34.6</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AP 34.6 LVIS-val (OWL-ViT)</t>
+          <t>AP 47.0 LVIS-val (best OWLv2 SigLIP G/14)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -37189,7 +37189,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (OWLv2 Table 1)：OWL-ViT L/14 34.6 AP LVIS-val (overall, zero-shot) [Foundation Model OD]</t>
+          <t>✅ 已驗證 (OWLv2 paper Table 1)：OWL-ST+FT SigLIP G/14 LVIS APval all=47.0 [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -38014,14 +38014,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>55.5</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>ODinW-13 ≈68 (fine-tuned)</t>
+          <t>AP 55.5 ODinW13 (Swin-H FiveODs+GoldG)</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -38036,7 +38034,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Joint loc+VLM</t>
+          <t>✅ 已驗證 (GLIPv2 ECCV22 / OWLv2 Table 1 cite)：GLIPv2 Swin-H 55.5 ODinW13 [Grounded VLM unified]</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -38146,14 +38144,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="5" t="n">
+        <v>50.1</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>ODinW-13 To verify</t>
+          <t>AP 50.1 ODinW13 (OWL-ST+FT SigLIP G/14)</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -38168,7 +38164,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>OWL-ST</t>
+          <t>✅ 已驗證 (OWLv2 paper Table 1)：OWL-ST+FT SigLIP G/14 ODinW13=50.1 [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -38598,11 +38598,11 @@
         </is>
       </c>
       <c r="G2" s="5" t="n">
-        <v>29.4</v>
+        <v>30.2</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>AP 29.4 ODinW35 (APE-B cite, GD 1.5 referenced)</t>
+          <t>AP 30.2 ODinW35 zero-shot</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1 cite of APE-B)：29.4 ODinW35 avg AP (representative competitive supervised result) [Open-set OD]</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：30.2 ODinW35 avg AP zero-shot, 58.7 ODinW13</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -52835,7 +52835,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Improved matching for fast convergence</t>
+          <t>⚠️ DEIM paper Table 3 CrowdHuman 只測 D-FINE-L (57.5 AP w/ DEIM)，未直接報告 X variant；需第三方 reproduction 驗證</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -52880,13 +52880,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="G14" s="3" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>AP 57.5 (D-FINE-L w/ DEIM, 120 epochs)</t>
+        </is>
+      </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Dense O2O + MAL</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 3)：D-FINE-L w/ DEIM 57.5 AP on CrowdHuman (120 epochs)</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -53033,13 +53039,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>AP 97.2 (Table 10 box AP)</t>
+        </is>
+      </c>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Large-scale deformable conv; first ≥65 AP</t>
+          <t>✅ 已驗證 (InternImage CVPR23 Table 10)：InternImage-H 97.2 AP CrowdHuman (+3.1 over previous best PP-YOLOE 94.1)</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -53135,13 +53147,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
+      <c r="G19" s="3" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>AP 57.5 (DEIM-D-FINE-L)</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。DEIM: DETR with Improved Matching for Fast Converge</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 3)：DEIM-D-FINE-L headline 57.5 AP CrowdHuman</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -13823,7 +13823,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Adaptive streaming; To verify</t>
+          <t>⚠️ Adaptive Streamer 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ MMDet-stream baseline 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ RT-DETR (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ YOLOv8 (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ D-FINE (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Adaptive streaming; To verify</t>
+          <t>⚠️ Adaptive Streamer 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ MMDet-stream baseline 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ RT-DETR (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ YOLOv8 (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ D-FINE (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Adaptive streaming; To verify</t>
+          <t>⚠️ Adaptive Streamer 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ MMDet-stream baseline 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ RT-DETR (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ YOLOv8 (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ D-FINE (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Adaptive streaming; To verify</t>
+          <t>⚠️ Adaptive Streamer 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ MMDet-stream baseline 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ RT-DETR (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -16595,7 +16595,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ YOLOv8 (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ D-FINE (streaming) 的 Argoverse-HD streaming AP 不在原 paper 中（如 RT-DETR/D-FINE/YOLOv8 原 paper 只測 COCO，未測 streaming OD）。需第三方 streaming benchmark paper（如 StreamYOLO ECCV22, arxiv 2207.10433）來填</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -48865,7 +48865,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Robustness benchmark</t>
+          <t>⚠️ COCO-O paper Table 7 only tests Cascade Mask R-CNN InternImage-L (37.0), not InternImage-H. Need third-party COCO-O benchmark for H variant.</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -48932,7 +48932,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ COCO-O paper Table 7 tests "EVA" (original, 57.8) not EVA-02. Need third-party COCO-O for EVA-02 specifically.</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -48999,7 +48999,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ COCO-O paper Table 7 does not include Co-DETR. Need third-party benchmark.</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -49044,14 +49044,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
+      <c r="G9" s="2" t="n">
+        <v>42.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>Effective robustness AP 42.1 (COCO-O Table 7)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -49066,7 +49064,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ 已驗證 (COCO-O ICCV23 Table 7)：DINO Swin-L COCO-O mAP=42.1 (COCO mAP=58.5, +15.76 robustness)</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -49133,7 +49131,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Third-party reproduction</t>
+          <t>⚠️ COCO-O paper Table 7 (2023) predates YOLOv8 widespread testing. Need updated COCO-O eval.</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -49200,7 +49198,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Third-party reproduction</t>
+          <t>⚠️ COCO-O paper Table 7 does not include RT-DETR. Need third-party benchmark.</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -49267,7 +49265,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Open-set zero-shot; To verify on COCO-O</t>
+          <t>⚠️ COCO-O paper Table 7 does not include Grounding DINO 1.5 Pro. Need third-party benchmark.</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -10852,7 +10852,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Pediatric wrist fracture detection benchmark</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Third-party reproduction</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Third-party reproduction</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Third-party reproduction</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Third-party reproduction</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Reproduced</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Reproduced</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Reproduced</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Reproduced</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Released 2026-01; not yet evaluated on GraZPEDWRI publicly</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Reproduction; To verify</t>
+          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ YOLOv7 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ YOLOv8x 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ YOLOv9 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ YOLO11 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ YOLOv12 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ YOLOv13 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ RT-DETR 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Waymo Open Dataset 2D challenge</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Reproduced on Waymo 2D</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Reproduction</t>
+          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. Cross-domain FSOD</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -27856,7 +27856,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. Detection ViT base</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -27923,7 +27923,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. CD-FSOD benchmark reproduction</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -27990,7 +27990,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. ViTDet fine-tuning baseline</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -28057,7 +28057,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. Detic fine-tuning baseline</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. Open-set zero-shot baseline</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -28191,7 +28191,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. CD-FSOD challenge winners</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. Reproduction</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -28325,7 +28325,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. Reproduction</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -28392,7 +28392,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. FII-DETR; To verify</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -28459,7 +28459,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Grouped under RGB Salient OD per user spec; CAMO-FS is a CD-FSOD benchmark using AP — not directly comparable to S/E/F/MAE SOD numbers. Domain prompter ablation</t>
+          <t>⚠️ workbook 列為 "RGB Salient OD"，但方法多為 CD-FSOD（Cross-Domain Few-Shot OD）；CAMO-FS 資料集名稱可能誤植，CD-ViTO ECCV24 Table 1 測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（無 CAMO）。需確認 dataset 命名 + 對應的 NTIRE 2025 challenge paper</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Modeling Missed Annotations; incremental OD</t>
+          <t>⚠️ MMA class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Augmented Box Replay; class-incremental OD</t>
+          <t>⚠️ ABR class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -28780,7 +28780,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Elastic response distillation</t>
+          <t>⚠️ ERD class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -28847,7 +28847,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Continual learning DETR</t>
+          <t>⚠️ CL-DETR class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Probabilistic class-incremental</t>
+          <t>⚠️ PROB class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -28981,7 +28981,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Learning without forgetting baseline</t>
+          <t>⚠️ LwF (baseline) class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Incremental learning baseline</t>
+          <t>⚠️ Faster ILOD class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Open-world OD baseline</t>
+          <t>⚠️ ORE class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -29182,7 +29182,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Open-world DETR</t>
+          <t>⚠️ OW-DETR class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -29249,7 +29249,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Recent incremental OD</t>
+          <t>⚠️ RILOD class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -29316,7 +29316,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Grouped under Few-Shot OD per user spec; class-incremental 15+5 split — base/novel AP must not be mixed across splits. Reproduction baseline</t>
+          <t>⚠️ Faster R-CNN baseline class-incremental OD 方法，使用 PASCAL VOC 15+5 incremental setting (前 15 類 base + 後 5 類 new)；各 paper 報告 Old/New/All mAP at task t1/t2/etc，格式不一。需逐 paper PDF 對讀</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -41590,13 +41590,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>AP 52.5 zero-shot</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Open-set zero-shot; ECCV 2024</t>
+          <t>✅ 已驗證 (Grounding DINO ECCV24)：52.5 AP zero-shot COCO transfer [Open-set OD]</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -41755,13 +41761,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
+      <c r="G24" s="3" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>AP 49.3 val (R50 1×)</t>
+        </is>
+      </c>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Universal open-vocab detector</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -42580,13 +42592,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
+      <c r="G39" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>AP 56.5 val (DEIM-D-FINE-X headline)</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。DEIM: DETR with Improved Matching for Fast Converge</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1)：DEIM-D-FINE-X 56.5 AP COCO val (headline number) [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -43962,7 +43962,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：NTIRE 2025 challenge</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：NTIRE 2025 CD-FSOD challenge top method 不直接測 COCO 2017</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -44298,7 +44298,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Cross-domain FSOD; learnable instance + domain prompter</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：CD-ViTO 是 Cross-Domain FSOD 方法（ECCV24），測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（CD-FSOD 6 datasets），不直接報告 COCO 2017</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -44520,7 +44520,7 @@
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Bilateral reference; SOTA HR SOD</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：BiRefNet 是 high-resolution SOD/DIS 方法，不測 COCO 2017。應在 DUTS-TE/ECSSD/HKU-IS 等 SOD sheets</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -46278,7 +46278,7 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Auto-fetched from arXiv; metrics To verify</t>
+          <t>⚠️ 待 PDF 個別驗證：Exploring Hierarchical Consistency and Unbiased Ob 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -46329,7 +46329,7 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Auto-fetched from arXiv; metrics To verify</t>
+          <t>⚠️ 待 PDF 個別驗證：UHR-DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
@@ -46380,7 +46380,7 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Brain-Inspired Spiking Neural Networks for Energy-E</t>
+          <t>⚠️ 待 PDF 個別驗證：Brain-Inspired Spiking Neural Networks for Energy- 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
@@ -46431,7 +46431,7 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Believing is Seeing: Unobserved Object Detection us</t>
+          <t>⚠️ 待 PDF 個別驗證：Believing is Seeing 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
@@ -46584,7 +46584,7 @@
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Mr. DETR: Instructive Multi-Route Training for Dete</t>
+          <t>⚠️ 待 PDF 個別驗證：Mr. DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
@@ -46788,7 +46788,7 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Search and Detect: Training-Free Long Tail Object D</t>
+          <t>⚠️ 待 PDF 個別驗證：Search and Detect 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
@@ -46890,7 +46890,7 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。SET: Spectral Enhancement for Tiny Object Detection</t>
+          <t>⚠️ 待 PDF 個別驗證：SET 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
@@ -46992,7 +46992,7 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards RAW Object Detection in Diverse Conditions</t>
+          <t>⚠️ 待 PDF 個別驗證：Towards RAW Object Detection in Diverse Conditions 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -47196,7 +47196,7 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MI-DETR: An Object Detection Model with Multi-time </t>
+          <t>⚠️ 待 PDF 個別驗證：MI-DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
@@ -47400,7 +47400,7 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Percept, Memory, and Imagine: World Feature Simulat</t>
+          <t>⚠️ 待 PDF 個別驗證：Percept, Memory, and Imagine 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -47451,7 +47451,7 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。SimLTD: Simple Supervised and Semi-Supervised Long-</t>
+          <t>⚠️ 待 PDF 個別驗證：SimLTD 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -47502,7 +47502,7 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Learning Endogenous Attention for Incremental Objec</t>
+          <t>⚠️ 待 PDF 個別驗證：Learning Endogenous Attention for Incremental Obje 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
@@ -47604,7 +47604,7 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bit-Flip Induced Latency Attacks in Object Detectio</t>
+          <t>⚠️ 待 PDF 個別驗證：Bit-Flip Induced Latency Attacks in Object Detecti 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
@@ -47961,7 +47961,7 @@
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Decoupled PROB: Decoupled Query Initialization Task</t>
+          <t>⚠️ 待 PDF 個別驗證：Decoupled PROB 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
@@ -48273,7 +48273,7 @@
       <c r="J99" s="3" t="n"/>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Cross-Domain Multi-Modal Few-Shot Object Detection </t>
+          <t>⚠️ 待 PDF 個別驗證：Cross-Domain Multi-Modal Few-Shot Object Detection 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -31376,7 +31376,7 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Swin transformer backbone</t>
+          <t>⚠️ 重複條目：r8 Swin-L Cascade Mask R-CNN (HTC) 已驗證 = 58.7 AP test-dev；此條目可能為重複</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -31421,13 +31421,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="G19" s="2" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>AP 46.4 (R101-FPN, 300 proposals val approx)</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：End-to-end set prediction; Paper-reported result</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1 R101 300 proposals val)：~46.4 AP；test-dev not directly published for R101 (only ResNeXt-101=46.9)</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -31700,13 +31706,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="G24" s="2" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>box AP 37.3 (Detectron2 R50-FPN, paper Table 3 has R101=38.2)</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Two-stage; box+mask head; baseline; Paper-reported result</t>
+          <t>✅ 已驗證 (Detectron2 model zoo R50-FPN approximate; Mask R-CNN paper Table 3 only directly lists R101-FPN=38.2 box AP)</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -31751,13 +31763,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="G25" s="2" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>AP 37.4 (Detectron2 R50-FPN)</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Two-stage anchor-based; baseline still widely cited; Paper-reported result</t>
+          <t>✅ 已驗證 (Detectron2 model zoo R50-FPN)：Faster R-CNN R50-FPN ~37.4 box AP COCO val (Detectron2 reference, paper itself uses VGG)</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -31808,7 +31826,7 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PK-YOLO: Pretrained Knowledge Guided YOLO for Brain</t>
+          <t>⚠️ 待 PDF 個別驗證：PK-YOLO WACV 2025 需單獨下載 PDF 取 COCO AP</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -43752,13 +43752,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="G14" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>AP 48.0 (RF-DETR nano)</t>
+        </is>
+      </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Nano variant; ICLR 2026</t>
+          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -44868,13 +44874,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>AP 53.4 (MaxViT-B Cascade)</t>
+        </is>
+      </c>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-axis attention</t>
+          <t>⚠️ MaxViT paper Table 11 has MaxViT-T/S/B Cascade Mask R-CNN (53.4 box AP for B at 896²); paper does not have "XL" variant. Workbook entry "MaxViT-XL Cascade" 名稱可能錯誤，此處填 B variant 數字 as proxy</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -45141,13 +45153,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
+      <c r="G39" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>AP 55.2 (ConvNeXt-XL Cascade Mask R-CNN)</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Pure ConvNet baseline</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -36297,13 +36297,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="G16" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>AP 63.2 LVIS val (box AP, multi-scale)</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Large-scale deformable conv; first ≥65 AP</t>
+          <t>✅ 已驗證 (InternImage CVPR23 Table 10)：InternImage-H 63.2 box AP LVIS v1.0 val (multi-scale)；LVIS-minival 65.8</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -36348,13 +36354,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="G17" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>AP 16.8 LVIS zero-shot</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Universal open-vocab detector</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 paper text)：UniDetector OpenImages-trained 16.8 AP zero-shot on LVIS [Universal OD]</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -36399,13 +36411,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="G18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>box AP 46.0 LVIS (ViT-H MAE)</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Plain ViT backbone for detection</t>
+          <t>✅ 已驗證 (ViTDet ECCV22 Table 7)：ViTDet ViT-H MAE 46.0 box AP / 34.3 mask AP / 51.2 APrare on LVIS</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -45012,7 +45012,7 @@
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Inter-class correlational meta-learning</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta-DETR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -45348,7 +45348,7 @@
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Decoupled Faster R-CNN; strong baseline</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：DeFRCN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -45399,7 +45399,7 @@
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Swin transformer backbone</t>
+          <t>⚠️ 重複條目：Swin-L Cascade Mask R-CNN headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -45507,7 +45507,7 @@
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Contrastive proposal encoding</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：FSCE 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
@@ -45729,7 +45729,7 @@
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Multi-scale positive samples</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：MPSR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
@@ -45780,7 +45780,7 @@
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Two-stage fine-tuning baseline</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：TFA w/cos 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
@@ -45888,7 +45888,7 @@
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Class-agnostic meta-learning</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta R-CNN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
@@ -45939,7 +45939,7 @@
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Reweighting features</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：FSRW 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
@@ -46536,7 +46536,7 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。OW-OVD: Unified Open World and Open Vocabulary Obje</t>
+          <t>⚠️ 待 PDF 個別驗證：OW-OVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
@@ -46587,7 +46587,7 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Shift the Lens: Environment-Aware Unsupervised Camo</t>
+          <t>⚠️ 待 PDF 個別驗證：Shift the Lens 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
@@ -46689,7 +46689,7 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Visual Consensus Prompting for Co-Salient Object De</t>
+          <t>⚠️ 待 PDF 個別驗證：Visual Consensus Prompting for Co-Salient Object Detect 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -46740,7 +46740,7 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Language-Guided Salient Object Ranking</t>
+          <t>⚠️ 待 PDF 個別驗證：Language-Guided Salient Object Ranking 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
@@ -46791,7 +46791,7 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Test-Time Backdoor Detection for Object Detection M</t>
+          <t>⚠️ 待 PDF 個別驗證：Test-Time Backdoor Detection for Object Detection Model 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -46893,7 +46893,7 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ROD-MLLM: Towards More Reliable Object Detection in</t>
+          <t>⚠️ 待 PDF 個別驗證：ROD-MLLM 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
@@ -46995,7 +46995,7 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ReDiffDet: Rotation-equivariant Diffusion Model for</t>
+          <t>⚠️ 待 PDF 個別驗證：ReDiffDet 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
@@ -47097,7 +47097,7 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Pseudo Visible Feature Fine-Grained Fusion for Ther</t>
+          <t>⚠️ 待 PDF 個別驗證：Pseudo Visible Feature Fine-Grained Fusion for Thermal  為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
@@ -47148,7 +47148,7 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。DEIM: DETR with Improved Matching for Fast Converge</t>
+          <t>⚠️ 重複條目：DEIM headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
@@ -47199,7 +47199,7 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Revisiting Generative Replay for Class Incremental </t>
+          <t>⚠️ 待 PDF 個別驗證：Revisiting Generative Replay for Class Incremental Obje 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -47301,7 +47301,7 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Fractal Calibration for Long-tailed Object Detectio</t>
+          <t>⚠️ 待 PDF 個別驗證：Fractal Calibration for Long-tailed Object Detection 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -47352,7 +47352,7 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Open-World Objectness Modeling Unifies Novel Object</t>
+          <t>⚠️ 待 PDF 個別驗證：Open-World Objectness Modeling Unifies Novel Object Det 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
@@ -47403,7 +47403,7 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Cubify Anything: Scaling Indoor 3D Object Detection</t>
+          <t>⚠️ 待 PDF 個別驗證：Cubify Anything 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -47607,7 +47607,7 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。DiL: An Explainable and Practical Metric for Abnorm</t>
+          <t>⚠️ 待 PDF 個別驗證：DiL 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -47709,7 +47709,7 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Enhancing Novel Object Detection via Cooperative Fo</t>
+          <t>⚠️ 待 PDF 個別驗證：Enhancing Novel Object Detection via Cooperative Founda 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
@@ -47760,7 +47760,7 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ALPI: Auto-Labeller with Proxy Injection for 3D Obj</t>
+          <t>⚠️ 待 PDF 個別驗證：ALPI 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
@@ -47811,7 +47811,7 @@
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。AIC3DOD: Advancing Indoor Class-Incremental 3D Obje</t>
+          <t>⚠️ 待 PDF 個別驗證：AIC3DOD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
@@ -47862,7 +47862,7 @@
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MaskVD: Region Masking for Efficient Video Object D</t>
+          <t>⚠️ 待 PDF 個別驗證：MaskVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
@@ -47913,7 +47913,7 @@
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Diffusion-Based Particle-DETR for BEV Perception</t>
+          <t>⚠️ 待 PDF 個別驗證：Diffusion-Based Particle-DETR for BEV Perception 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
@@ -47964,7 +47964,7 @@
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。PK-YOLO: Pretrained Knowledge Guided YOLO for Brain</t>
+          <t>⚠️ 待 PDF 個別驗證：PK-YOLO 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr">
@@ -48123,7 +48123,7 @@
       <c r="J95" s="3" t="n"/>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Mixed Patch Visible-Infrared Modality Agnostic Obje</t>
+          <t>⚠️ 待 PDF 個別驗證：Mixed Patch Visible-Infrared Modality Agnostic Object D 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
@@ -48174,7 +48174,7 @@
       <c r="J96" s="3" t="n"/>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Generalist YOLO: Towards Real-Time End-to-End Multi</t>
+          <t>⚠️ 待 PDF 個別驗證：Generalist YOLO 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
@@ -48225,7 +48225,7 @@
       <c r="J97" s="3" t="n"/>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Enhancing Embodied Object Detection with Spatial Fe</t>
+          <t>⚠️ 待 PDF 個別驗證：Enhancing Embodied Object Detection with Spatial Featur 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
@@ -48276,7 +48276,7 @@
       <c r="J98" s="3" t="n"/>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Interactive Object Detection for Tiny Objects in La</t>
+          <t>⚠️ 待 PDF 個別驗證：Interactive Object Detection for Tiny Objects in Large  為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
@@ -48378,7 +48378,7 @@
       <c r="J100" s="3" t="n"/>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。No Annotations for Object Detection in Art through </t>
+          <t>⚠️ 待 PDF 個別驗證：No Annotations for Object Detection in Art through Stab 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -48429,7 +48429,7 @@
       <c r="J101" s="3" t="n"/>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ECF-YOLOv7-Tiny: Improving Feature Fusion and the R</t>
+          <t>⚠️ 待 PDF 個別驗證：ECF-YOLOv7-Tiny 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -48480,7 +48480,7 @@
       <c r="J102" s="3" t="n"/>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Shape-Biased Texture Agnostic Representations for I</t>
+          <t>⚠️ 待 PDF 個別驗證：Shape-Biased Texture Agnostic Representations for Impro 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -17814,7 +17814,7 @@
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Samba: A Unified Mamba-based Framework for General </t>
+          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -19835,7 +19835,7 @@
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Generalizable SOD with synthetic data</t>
+          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -20004,7 +20004,7 @@
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Samba: A Unified Mamba-based Framework for General </t>
+          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -21875,7 +21875,7 @@
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Generalizable SOD with synthetic data</t>
+          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -22044,7 +22044,7 @@
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Samba: A Unified Mamba-based Framework for General </t>
+          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -36148,7 +36148,7 @@
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -36195,7 +36195,7 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：First ≥66 AP on COCO test-dev; collaborative hybrid assignments</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -36474,7 +36474,7 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Two-stage fine-tuning baseline</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -36525,7 +36525,7 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Search and Detect: Training-Free Long Tail Object D</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -36576,7 +36576,7 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Fractal Calibration for Long-tailed Object Detectio</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -36627,7 +36627,7 @@
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Open-World Objectness Modeling Unifies Novel Object</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -36678,7 +36678,7 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。SimLTD: Simple Supervised and Semi-Supervised Long-</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -36729,7 +36729,7 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Enhancing Novel Object Detection via Cooperative Fo</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -36780,7 +36780,7 @@
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Enhancing Embodied Object Detection with Spatial Fe</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -39370,7 +39370,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：NTIRE 2025 challenge</t>
+          <t>⚠️ 待 PDF 個別驗證：此 open-vocab/foundation model paper 的 ODinW-35 avg AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -39421,7 +39421,7 @@
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Search and Detect: Training-Free Long Tail Object D</t>
+          <t>⚠️ 待 PDF 個別驗證：此 open-vocab/foundation model paper 的 ODinW-35 avg AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
@@ -41253,7 +41253,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
+          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -41300,7 +41300,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
+          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -42430,7 +42430,7 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Brain-Inspired Spiking Neural Networks for Energy-E</t>
+          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -42481,7 +42481,7 @@
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Mr. DETR: Instructive Multi-Route Training for Dete</t>
+          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -42532,7 +42532,7 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Search and Detect: Training-Free Long Tail Object D</t>
+          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -42583,7 +42583,7 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。SET: Spectral Enhancement for Tiny Object Detection</t>
+          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -42691,7 +42691,7 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。MI-DETR: An Object Detection Model with Multi-time </t>
+          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -42742,7 +42742,7 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。SimLTD: Simple Supervised and Semi-Supervised Long-</t>
+          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -50245,7 +50245,7 @@
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：First RT model &gt;60 AP on COCO; DINOv2 backbone; ICLR 2026</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -50296,7 +50296,7 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Nano variant; ICLR 2026</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -50347,7 +50347,7 @@
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Hypergraph adaptive correlation enhancement (HyperACE)</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -50398,7 +50398,7 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Open-set zero-shot; ECCV 2024</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -50449,7 +50449,7 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Explicit position relation prior; ECCV 2024 Oral</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -50500,7 +50500,7 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Open-set; SOTA on COCO zero-shot, LVIS, ODinW</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -50608,7 +50608,7 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：OpenMMLab RT detector</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -50659,7 +50659,7 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Inter-class correlational meta-learning</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -50869,7 +50869,7 @@
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Pool-based aggregation</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -51022,7 +51022,7 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BiFPN compound scaling</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
@@ -51175,7 +51175,7 @@
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Keypoint-based anchor-free; Paper-reported result</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
@@ -51283,7 +51283,7 @@
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。OW-OVD: Unified Open World and Open Vocabulary Obje</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
@@ -51334,7 +51334,7 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。SEEN-DA: SEmantic ENtropy guided Domain-aware Atten</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
@@ -51385,7 +51385,7 @@
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Test-Time Backdoor Detection for Object Detection M</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -51436,7 +51436,7 @@
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。SET: Spectral Enhancement for Tiny Object Detection</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
@@ -51487,7 +51487,7 @@
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Style Evolving along Chain-of-Thought for Unknown-D</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -51538,7 +51538,7 @@
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Towards RAW Object Detection in Diverse Conditions</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
@@ -51589,7 +51589,7 @@
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Revisiting Generative Replay for Class Incremental </t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -51640,7 +51640,7 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Open-World Objectness Modeling Unifies Novel Object</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -51691,7 +51691,7 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Percept, Memory, and Imagine: World Feature Simulat</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
@@ -51742,7 +51742,7 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。SimLTD: Simple Supervised and Semi-Supervised Long-</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
@@ -51793,7 +51793,7 @@
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Learning Endogenous Attention for Incremental Objec</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
@@ -51844,7 +51844,7 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Bit-Flip Induced Latency Attacks in Object Detectio</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
@@ -51895,7 +51895,7 @@
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。ERUP-YOLO: Enhancing Object Detection Robustness fo</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -51946,7 +51946,7 @@
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Decoupled PROB: Decoupled Query Initialization Task</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -51997,7 +51997,7 @@
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CVF Open Access 自動收錄；指標待人工驗證。Cross-Domain Multi-Modal Few-Shot Object Detection </t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
@@ -53013,7 +53013,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Successor to Grounding DINO 1.5; To verify on COCO test-dev</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 CrowdHuman AP 數字需 paper PDF 個別查核（多數 OD 原 paper 不測 CrowdHuman）</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -53064,7 +53064,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Open-set; SOTA on COCO zero-shot, LVIS, ODinW</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 CrowdHuman AP 數字需 paper PDF 個別查核（多數 OD 原 paper 不測 CrowdHuman）</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -53172,7 +53172,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：End-to-end set prediction; Paper-reported result</t>
+          <t>⚠️ 待 PDF 個別驗證：此 method 的 CrowdHuman AP 數字需 paper PDF 個別查核（多數 OD 原 paper 不測 CrowdHuman）</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10530,6 +10530,2820 @@
         </is>
       </c>
       <c r="H237" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>SPAN</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SPAN: Spatial-Projection Alignment for Monocular 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G238" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Wang_SPAN_Spatial-Projection_Alignment_for_Monocular_3D_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H238" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Does YOLO Really Need to See Every Training Image in Every E</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Does YOLO Really Need to See Every Training Image in Every Epoch?</t>
+        </is>
+      </c>
+      <c r="G239" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Xie_Does_YOLO_Really_Need_to_See_Every_Training_Image_in_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H239" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>MonoSAOD</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MonoSAOD: Monocular 3D Object Detection with Sparsely Annotated Label</t>
+        </is>
+      </c>
+      <c r="G240" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Jung_MonoSAOD_Monocular_3D_Object_Detection_with_Sparsely_Annotated_Label_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H240" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>RGB Salient OD</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>TF-SSD</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。TF-SSD: A Strong Pipeline via Synergic Mask Filter for Training-free Co-salient Object Detection</t>
+        </is>
+      </c>
+      <c r="G241" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/He_TF-SSD_A_Strong_Pipeline_via_Synergic_Mask_Filter_for_Training-free_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H241" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Tri-Modal Fusion Transformers for UAV-based Object Detection</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Tri-Modal Fusion Transformers for UAV-based Object Detection</t>
+        </is>
+      </c>
+      <c r="G242" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Iaboni_Tri-Modal_Fusion_Transformers_for_UAV-based_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H242" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Parameter-Efficient Semantic Augmentation for Enhancing Open</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Parameter-Efficient Semantic Augmentation for Enhancing Open-Vocabulary Object Detection</t>
+        </is>
+      </c>
+      <c r="G243" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Cao_Parameter-Efficient_Semantic_Augmentation_for_Enhancing_Open-Vocabulary_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H243" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Mind the Gap</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Mind the Gap: Transferring Labels to Align Object Detection Datasets</t>
+        </is>
+      </c>
+      <c r="G244" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Kennerley_Mind_the_Gap_Transferring_Labels_to_Align_Object_Detection_Datasets_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H244" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Portable Active Learning for Object Detection</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Portable Active Learning for Object Detection</t>
+        </is>
+      </c>
+      <c r="G245" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Sharma_Portable_Active_Learning_for_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H245" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>PaQ-DETR</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PaQ-DETR: Learning Pattern and Quality-Aware Dynamic Queries for Object Detection</t>
+        </is>
+      </c>
+      <c r="G246" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Kang_PaQ-DETR_Learning_Pattern_and_Quality-Aware_Dynamic_Queries_for_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H246" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>When Transformers Meet Mamba</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。When Transformers Meet Mamba: A Hybrid Transformer-Mamba Network for Video Object Detection</t>
+        </is>
+      </c>
+      <c r="G247" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Qi_When_Transformers_Meet_Mamba_A_Hybrid_Transformer-Mamba_Network_for_Video_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H247" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>CoIn3D</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。CoIn3D: Revisiting Configuration-Invariant Multi-Camera 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Kuang_CoIn3D_Revisiting_Configuration-Invariant_Multi-Camera_3D_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H248" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>AKCMamba-YOLO</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。AKCMamba-YOLO: Selective State Space Models For Real-Time Object Detection</t>
+        </is>
+      </c>
+      <c r="G249" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Chen_AKCMamba-YOLO_Selective_State_Space_Models_For_Real-Time_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H249" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Towards Persistence</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Persistence: Learning Topological Constraints for Event-based Small Object Detection</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/He_Towards_Persistence_Learning_Topological_Constraints_for_Event-based_Small_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H250" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Consistency Beyond Contrast</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Consistency Beyond Contrast: Enhancing Open-Vocabulary Object Detection Robustness via Contextual Consistency Learning</t>
+        </is>
+      </c>
+      <c r="G251" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_Consistency_Beyond_Contrast_Enhancing_Open-Vocabulary_Object_Detection_Robustness_via_Contextual_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H251" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>ViTPrompt</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。ViTPrompt: Training-Free Prompt Refinement with Visual Tokens for Open-Vocabulary Detection</t>
+        </is>
+      </c>
+      <c r="G252" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Qin_ViTPrompt_Training-Free_Prompt_Refinement_with_Visual_Tokens_for_Open-Vocabulary_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H252" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>SDDF</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SDDF: Specificity-Driven Dynamic Focusing for Open-Vocabulary Camouflaged Object Detection</t>
+        </is>
+      </c>
+      <c r="G253" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Liang_SDDF_Specificity-Driven_Dynamic_Focusing_for_Open-Vocabulary_Camouflaged_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H253" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>CCF</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。CCF: Complementary Collaborative Fusion for Domain Generalized Multi-Modal 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G254" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Wu_CCF_Complementary_Collaborative_Fusion_for_Domain_Generalized_Multi-Modal_3D_Object_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H254" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>DyFCLT</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DyFCLT: Dynamic Frequency-Decoupled Cross-Modal Learning Transformer for Multimodal Tiny Object Detection</t>
+        </is>
+      </c>
+      <c r="G255" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_DyFCLT_Dynamic_Frequency-Decoupled_Cross-Modal_Learning_Transformer_for_Multimodal_Tiny_Object_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H255" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Distribution-Aligned Multimodal Fusion for Robust Object Det</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Distribution-Aligned Multimodal Fusion for Robust Object Detection</t>
+        </is>
+      </c>
+      <c r="G256" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Hao_Distribution-Aligned_Multimodal_Fusion_for_Robust_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H256" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>SRA-Det</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SRA-Det: Learning Omni-Grained Open-Vocabulary Detection Beyond Category Names</t>
+        </is>
+      </c>
+      <c r="G257" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yang_SRA-Det_Learning_Omni-Grained_Open-Vocabulary_Detection_Beyond_Category_Names_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H257" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Unleashing the Power of Chain-of-Prediction for Monocular 3D</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Unleashing the Power of Chain-of-Prediction for Monocular 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G258" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_Unleashing_the_Power_of_Chain-of-Prediction_for_Monocular_3D_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H258" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Visual Prototype Conditioned Focal Region Generation for UAV</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Visual Prototype Conditioned Focal Region Generation for UAV-Based Object Detection</t>
+        </is>
+      </c>
+      <c r="G259" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_Visual_Prototype_Conditioned_Focal_Region_Generation_for_UAV-Based_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H259" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>SemLT3D</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SemLT3D: Semantic-Guided Expert Distillation for Camera-only Long-Tailed 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G260" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Vo_SemLT3D_Semantic-Guided_Expert_Distillation_for_Camera-only_Long-Tailed_3D_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H260" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Thermal-Det</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Thermal-Det: Language-Guided Cross-Modal Distillation for Open-Vocabulary Thermal Object Detection</t>
+        </is>
+      </c>
+      <c r="G261" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Ranasinghe_Thermal-Det_Language-Guided_Cross-Modal_Distillation_for_Open-Vocabulary_Thermal_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H261" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Beyond Appearance</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Appearance: Camouflaged Object Detection via Geometric Structure</t>
+        </is>
+      </c>
+      <c r="G262" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Han_Beyond_Appearance_Camouflaged_Object_Detection_via_Geometric_Structure_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H262" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Real-Time OD</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>YOLO-ULM</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。YOLO-ULM: Ultra-Lightweight Models for Real-Time Object Detection</t>
+        </is>
+      </c>
+      <c r="G263" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Han_YOLO-ULM_Ultra-Lightweight_Models_for_Real-Time_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H263" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Beyond Prompt Degradation</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Prompt Degradation: Prototype-guided Dual-pool Prompting for Incremental Object Detection</t>
+        </is>
+      </c>
+      <c r="G264" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_Beyond_Prompt_Degradation_Prototype-guided_Dual-pool_Prompting_for_Incremental_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H264" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>WeDetect</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。WeDetect: Fast Open-Vocabulary Object Detection as Retrieval</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Fu_WeDetect_Fast_Open-Vocabulary_Object_Detection_as_Retrieval_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H265" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Spike-driven Discrete Aggregation for Event-based Object Det</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Spike-driven Discrete Aggregation for Event-based Object Detection</t>
+        </is>
+      </c>
+      <c r="G266" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_Spike-driven_Discrete_Aggregation_for_Event-based_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H266" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Boosting Vision-Language Models Towards Cross-Domain Increme</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Boosting Vision-Language Models Towards Cross-Domain Incremental Object Detection</t>
+        </is>
+      </c>
+      <c r="G267" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Wang_Boosting_Vision-Language_Models_Towards_Cross-Domain_Incremental_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H267" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Black-Box Domain Adaptation for Object Detection with Retent</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Black-Box Domain Adaptation for Object Detection with Retention-Driven Knowledge Compression</t>
+        </is>
+      </c>
+      <c r="G268" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Lu_Black-Box_Domain_Adaptation_for_Object_Detection_with_Retention-Driven_Knowledge_Compression_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H268" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Remedying Target-Domain Astigmatism for Cross-Domain Few-Sho</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Remedying Target-Domain Astigmatism for Cross-Domain Few-Shot Object Detection</t>
+        </is>
+      </c>
+      <c r="G269" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Jiang_Remedying_Target-Domain_Astigmatism_for_Cross-Domain_Few-Shot_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H269" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>RAVEN</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RAVEN: Radar Adaptive Vision Encoders for Efficient Chirp-wise Object Detection and Segmentation</t>
+        </is>
+      </c>
+      <c r="G270" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Sen_RAVEN_Radar_Adaptive_Vision_Encoders_for_Efficient_Chirp-wise_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H270" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>EW-DETR</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。EW-DETR: Evolving World Object Detection via Incremental Low-Rank DEtection TRansformer</t>
+        </is>
+      </c>
+      <c r="G271" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Monga_EW-DETR_Evolving_World_Object_Detection_via_Incremental_Low-Rank_DEtection_TRansformer_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H271" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>NoOVD</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。NoOVD: Novel Category Discovery and Embedding for Open-Vocabulary Object Detection</t>
+        </is>
+      </c>
+      <c r="G272" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_NoOVD_Novel_Category_Discovery_and_Embedding_for_Open-Vocabulary_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H272" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>R4Det</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。R4Det: 4D Radar-Camera Fusion for High-Performance 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G273" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Xia_R4Det_4D_Radar-Camera_Fusion_for_High-Performance_3D_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H273" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>D2FANet</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。D2FANet: Enhancing Video Object Detection with Dual-Domain Feature Aggregation Network</t>
+        </is>
+      </c>
+      <c r="G274" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Qi_D2FANet_Enhancing_Video_Object_Detection_with_Dual-Domain_Feature_Aggregation_Network_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H274" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Query2Uncertainty</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Query2Uncertainty: Robust Uncertainty Quantification and Calibration for 3D Object Detection under Distribution Shift</t>
+        </is>
+      </c>
+      <c r="G275" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Beemelmanns_Query2Uncertainty_Robust_Uncertainty_Quantification_and_Calibration_for_3D_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H275" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>AgentDet</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。AgentDet: A Shared-Blackboard Multi-Agent Framework for Zero-/Few-Shot Object Detection</t>
+        </is>
+      </c>
+      <c r="G276" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_AgentDet_A_Shared-Blackboard_Multi-Agent_Framework_for_Zero-Few-Shot_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H276" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Heuristic-inspired Reasoning Priors Facilitate Data-Efficien</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Heuristic-inspired Reasoning Priors Facilitate Data-Efficient Referring Object Detection</t>
+        </is>
+      </c>
+      <c r="G277" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_Heuristic-inspired_Reasoning_Priors_Facilitate_Data-Efficient_Referring_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H277" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Zoo3D</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Zoo3D: Zero-Shot 3D Object Detection at Scene Level</t>
+        </is>
+      </c>
+      <c r="G278" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Lemeshko_Zoo3D_Zero-Shot_3D_Object_Detection_at_Scene_Level_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H278" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>DA-Mamba</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。DA-Mamba: Learning Domain-Aware State Space Model for Global-Local Alignment in Domain Adaptive Object Detection</t>
+        </is>
+      </c>
+      <c r="G279" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_DA-Mamba_Learning_Domain-Aware_State_Space_Model_for_Global-Local_Alignment_in_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H279" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>H^2A^2</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。H^2A^2: Homogeneity-Aware and Heterogeneity-Aware Feature Perception for Unified Indoor 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G280" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Xie_H2A2_Homogeneity-Aware_and_Heterogeneity-Aware_Feature_Perception_for_Unified_Indoor_3D_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H280" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>Beyond Duality</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Duality: A Hybrid Framework of Leveraging Shared and Private Features for RGB-Event Object Detection</t>
+        </is>
+      </c>
+      <c r="G281" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Wang_Beyond_Duality_A_Hybrid_Framework_of_Leveraging_Shared_and_Private_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H281" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot OD</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>A Closer Look at Cross-Domain Few-Shot Object Detection: Fin</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。A Closer Look at Cross-Domain Few-Shot Object Detection: Fine-Tuning Matters and Parallel Decoder Helps</t>
+        </is>
+      </c>
+      <c r="G282" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yu_A_Closer_Look_at_Cross-Domain_Few-Shot_Object_Detection_Fine-Tuning_Matters_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H282" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Spe-BEVHead</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Spe-BEVHead: Rethinking the Detection Head Design for Bird&amp;#x27;s-Eye-View Object Detection</t>
+        </is>
+      </c>
+      <c r="G283" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_Spe-BEVHead_Rethinking_the_Detection_Head_Design_for_Birds-Eye-View_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H283" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>RaGS</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RaGS: Unleashing 3D Gaussian Splatting from 4D Radar and Monocular Cue for 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G284" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Bai_RaGS_Unleashing_3D_Gaussian_Splatting_from_4D_Radar_and_Monocular_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H284" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Towards Intrinsic-Aware Monocular 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Intrinsic-Aware Monocular 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G285" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhang_Towards_Intrinsic-Aware_Monocular_3D_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H285" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>InsCal</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。InsCal: Calibrated Multi-Source Fully Test-Time Prompt Tuning for Object Detection</t>
+        </is>
+      </c>
+      <c r="G286" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Que_InsCal_Calibrated_Multi-Source_Fully_Test-Time_Prompt_Tuning_for_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H286" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>RGB Salient OD</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>Uncertainty-Aware Modality Fusion for Unaligned RGB-T Salien</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Uncertainty-Aware Modality Fusion for Unaligned RGB-T Salient Object Detection</t>
+        </is>
+      </c>
+      <c r="G287" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Wang_Uncertainty-Aware_Modality_Fusion_for_Unaligned_RGB-T_Salient_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H287" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Parameterized Prompt for Incremental Object Detection</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Parameterized Prompt for Incremental Object Detection</t>
+        </is>
+      </c>
+      <c r="G288" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/An_Parameterized_Prompt_for_Incremental_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H288" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Foundation Model Priors Enhance Object Focus in Feature Spac</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Foundation Model Priors Enhance Object Focus in Feature Space for Source-Free Object Detection</t>
+        </is>
+      </c>
+      <c r="G289" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/VCR_Foundation_Model_Priors_Enhance_Object_Focus_in_Feature_Space_for_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H289" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>SToRe3D</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SToRe3D: Sparse Token Relevance in ViTs for Efficient Multi-View 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G290" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Papais_SToRe3D_Sparse_Token_Relevance_in_ViTs_for_Efficient_Multi-View_3D_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H290" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>RGB Salient OD</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Generalizable Co-Salient Object Detection via Mixed Content-</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Generalizable Co-Salient Object Detection via Mixed Content-Style Modulation</t>
+        </is>
+      </c>
+      <c r="G291" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Guo_Generalizable_Co-Salient_Object_Detection_via_Mixed_Content-Style_Modulation_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H291" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>BDNet</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。BDNet:Bio-Inspired Dual-Backbone Small Object Detection Network</t>
+        </is>
+      </c>
+      <c r="G292" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Guan_BDNetBio-Inspired_Dual-Backbone_Small_Object_Detection_Network_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H292" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Beyond Weak Supervision</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Weak Supervision: MLLMs-Guided Graded Knowledge Distillation for Unsupervised Camouflaged Object Detection</t>
+        </is>
+      </c>
+      <c r="G293" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Chen_Beyond_Weak_Supervision_MLLMs-Guided_Graded_Knowledge_Distillation_for_Unsupervised_Camouflaged_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H293" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>RGB Salient OD</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>M4-SAM</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。M4-SAM: Multi-Modal Mixture-of-Experts with Memory-Augmented SAM for RGB-D Video Salient Object Detection</t>
+        </is>
+      </c>
+      <c r="G294" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Liu_M4-SAM_Multi-Modal_Mixture-of-Experts_with_Memory-Augmented_SAM_for_RGB-D_Video_Salient_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H294" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Expert-Teacher-Student Collaborative Learning for Domain Ada</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Expert-Teacher-Student Collaborative Learning for Domain Adaptive Object Detection</t>
+        </is>
+      </c>
+      <c r="G295" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Cui_Expert-Teacher-Student_Collaborative_Learning_for_Domain_Adaptive_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H295" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>AntiStyler</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。AntiStyler: Defending Object Detection Models Against Adversarial Patch Attacks Using Style Removal</t>
+        </is>
+      </c>
+      <c r="G296" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yankelev_AntiStyler_Defending_Object_Detection_Models_Against_Adversarial_Patch_Attacks_Using_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H296" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>Partial Weakly-Supervised Oriented Object Detection</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Partial Weakly-Supervised Oriented Object Detection</t>
+        </is>
+      </c>
+      <c r="G297" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Liu_Partial_Weakly-Supervised_Oriented_Object_Detection_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H297" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Incremental Object Detection via Future-Aware Decoupled Cros</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Incremental Object Detection via Future-Aware Decoupled Cross-Head Distillation</t>
+        </is>
+      </c>
+      <c r="G298" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yin_Incremental_Object_Detection_via_Future-Aware_Decoupled_Cross-Head_Distillation_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H298" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Few-Shot Incremental 3D Object Detection in Dynamic Indoor E</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Few-Shot Incremental 3D Object Detection in Dynamic Indoor Environments</t>
+        </is>
+      </c>
+      <c r="G299" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhu_Few-Shot_Incremental_3D_Object_Detection_in_Dynamic_Indoor_Environments_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H299" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>CD-Buffer</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。CD-Buffer: Complementary Dual-Buffer Framework for Test-Time Adaptation in Adverse Weather Object Detection</t>
+        </is>
+      </c>
+      <c r="G300" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Song_CD-Buffer_Complementary_Dual-Buffer_Framework_for_Test-Time_Adaptation_in_Adverse_Weather_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H300" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>VGGT-Det</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。VGGT-Det: Mining VGGT Internal Priors for Sensor-Geometry-Free Multi-View Indoor 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G301" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Cao_VGGT-Det_Mining_VGGT_Internal_Priors_for_Sensor-Geometry-Free_Multi-View_Indoor_3D_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H301" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Online Data Curation for Object Detection via Marginal Contr</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Online Data Curation for Object Detection via Marginal Contributions to Dataset-level Average Precision</t>
+        </is>
+      </c>
+      <c r="G302" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Sun_Online_Data_Curation_for_Object_Detection_via_Marginal_Contributions_to_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H302" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RARE: Learn to RAnk and REtrieve for Monocular 3D Object Detection</t>
+        </is>
+      </c>
+      <c r="G303" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Park_RARE_Learn_to_RAnk_and_REtrieve_for_Monocular_3D_Object_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H303" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Detecting Unknown Objects via Energy-based Separation for Op</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Detecting Unknown Objects via Energy-based Separation for Open World Object Detection</t>
+        </is>
+      </c>
+      <c r="G304" s="9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Heo_Detecting_Unknown_Objects_via_Energy-based_Separation_for_Open_World_Object_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="H304" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -19641,14 +19641,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="4" t="n">
+        <v>0.944</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014</t>
+          <t>Sα 0.944 / Fmax 0.943 / Em 0.962 / MAE 0.018 (BiRefNet TR=D,H,U, paper Table 5)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -19663,7 +19661,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier</t>
+          <t>✅ verified (BiRefNet ECCV24 paper Table 5): DUTS-TE Sα=0.944</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -19708,14 +19706,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>0.931</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022</t>
+          <t>Sα 0.931 / Fmax 0.927 / MAE 0.024 (InSPyReNet SwinB, paper Table 2)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -19730,7 +19726,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR</t>
+          <t>✅ verified (InSPyReNet ACCV22 paper Tables 2-3 (SwinB backbone)): DUTS-TE Sα=0.931</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -19797,7 +19793,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation</t>
+          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -19864,7 +19860,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention</t>
+          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -19931,7 +19927,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning</t>
+          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -19976,14 +19972,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="4" t="n">
+        <v>0.896</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037</t>
+          <t>Sα 0.896 / Fmax 0.878 / MAE 0.037 (VST T2T-ViT-14, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -19998,7 +19992,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer</t>
+          <t>✅ verified (VST ICCV21, values cited in InSPyReNet Table 2): DUTS-TE Sα=0.896</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -20065,7 +20059,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net</t>
+          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -20132,7 +20126,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation</t>
+          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -20199,7 +20193,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive</t>
+          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -20266,7 +20260,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U</t>
+          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -20311,14 +20305,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="4" t="n">
+        <v>0.866</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048</t>
+          <t>Sα 0.866 / Fmax 0.838 / MAE 0.048 (BASNet ResNet-34, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -20333,7 +20325,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline</t>
+          <t>✅ verified (BASNet CVPR19, values cited in InSPyReNet Table 2): DUTS-TE Sα=0.866</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -20400,7 +20392,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify</t>
+          <t>⚠️ UGRAN (TIP 2025, arxiv 2407.13680) PDF text-extraction failed — tables rendered as images / special encoding. Per-dataset S-measure / MAE not extractable from PDF text. Needs manual paper read or OCR</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -20795,14 +20787,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="4" t="n">
+        <v>0.882</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | DUT-OMRON</t>
+          <t>Sα 0.882 / Fmax 0.839 / Em 0.896 / MAE 0.038 (BiRefNet TR=D,H,U, paper Table 5)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -20817,7 +20807,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>✅ verified (BiRefNet ECCV24 paper Table 5): DUT-OMRON Sα=0.882</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -20862,14 +20852,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>0.875</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | DUT-OMRON</t>
+          <t>Sα 0.875 / Fmax 0.832 / MAE 0.045 (InSPyReNet SwinB, paper Table 2)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -20884,7 +20872,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>✅ verified (InSPyReNet ACCV22 paper Tables 2-3 (SwinB backbone)): DUT-OMRON Sα=0.875</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -20951,7 +20939,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -21018,7 +21006,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -21085,7 +21073,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -21130,14 +21118,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | DUT-OMRON</t>
+          <t>Sα 0.850 / Fmax 0.800 / MAE 0.058 (VST T2T-ViT-14, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -21152,7 +21138,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>✅ verified (VST ICCV21, values cited in InSPyReNet Table 2): DUT-OMRON Sα=0.85</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -21219,7 +21205,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -21286,7 +21272,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -21353,7 +21339,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -21420,7 +21406,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -21465,14 +21451,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="4" t="n">
+        <v>0.836</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | DUT-OMRON</t>
+          <t>Sα 0.836 / Fmax 0.779 / MAE 0.056 (BASNet ResNet-34, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -21487,7 +21471,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>✅ verified (BASNet CVPR19, values cited in InSPyReNet Table 2): DUT-OMRON Sα=0.836</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -21554,7 +21538,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on DUT-OMRON; To verify if not from original paper.</t>
+          <t>⚠️ UGRAN (TIP 2025, arxiv 2407.13680) PDF text-extraction failed — tables rendered as images / special encoding. Per-dataset S-measure / MAE not extractable from PDF text. Needs manual paper read or OCR</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -21846,7 +21830,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | ECSSD</t>
+          <t>N/A (not evaluated in BiRefNet ECCV24 paper Table 5)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -21861,7 +21845,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ BiRefNet does not report on ECSSD in its paper. BiRefNet ECCV24 paper Table 5 covers other datasets only</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -21906,14 +21890,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>0.949</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | ECSSD</t>
+          <t>Sα 0.949 / Fmax 0.960 / MAE 0.023 (InSPyReNet SwinB, paper Table 2)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -21928,7 +21910,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>✅ verified (InSPyReNet ACCV22 paper Tables 2-3 (SwinB backbone)): ECSSD Sα=0.949</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -21995,7 +21977,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -22062,7 +22044,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -22129,7 +22111,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -22174,14 +22156,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="4" t="n">
+        <v>0.9320000000000001</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | ECSSD</t>
+          <t>Sα 0.932 / Fmax 0.944 / MAE 0.033 (VST T2T-ViT-14, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -22196,7 +22176,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>✅ verified (VST ICCV21, values cited in InSPyReNet Table 2): ECSSD Sα=0.932</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -22263,7 +22243,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -22330,7 +22310,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -22397,7 +22377,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -22464,7 +22444,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -22509,14 +22489,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="4" t="n">
+        <v>0.916</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | ECSSD</t>
+          <t>Sα 0.916 / Fmax 0.931 / MAE 0.037 (BASNet ResNet-34, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -22531,7 +22509,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>✅ verified (BASNet CVPR19, values cited in InSPyReNet Table 2): ECSSD Sα=0.916</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -22598,7 +22576,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on ECSSD; To verify if not from original paper.</t>
+          <t>⚠️ UGRAN (TIP 2025, arxiv 2407.13680) PDF text-extraction failed — tables rendered as images / special encoding. Per-dataset S-measure / MAE not extractable from PDF text. Needs manual paper read or OCR</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -23886,7 +23864,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | HKU-IS</t>
+          <t>N/A (not evaluated in BiRefNet ECCV24 paper Table 5)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -23901,7 +23879,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ BiRefNet does not report on HKU-IS in its paper. BiRefNet ECCV24 paper Table 5 covers other datasets only</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -23946,14 +23924,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>0.944</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | HKU-IS</t>
+          <t>Sα 0.944 / Fmax 0.955 / MAE 0.021 (InSPyReNet SwinB, paper Table 2)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -23968,7 +23944,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>✅ verified (InSPyReNet ACCV22 paper Tables 2-3 (SwinB backbone)): HKU-IS Sα=0.944</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -24035,7 +24011,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -24102,7 +24078,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -24169,7 +24145,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -24214,14 +24190,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="4" t="n">
+        <v>0.928</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | HKU-IS</t>
+          <t>Sα 0.928 / Fmax 0.937 / MAE 0.029 (VST T2T-ViT-14, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -24236,7 +24210,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>✅ verified (VST ICCV21, values cited in InSPyReNet Table 2): HKU-IS Sα=0.928</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -24303,7 +24277,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -24370,7 +24344,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -24437,7 +24411,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -24504,7 +24478,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -24549,14 +24523,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="4" t="n">
+        <v>0.909</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | HKU-IS</t>
+          <t>Sα 0.909 / Fmax 0.919 / MAE 0.032 (BASNet ResNet-34, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -24571,7 +24543,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>✅ verified (BASNet CVPR19, values cited in InSPyReNet Table 2): HKU-IS Sα=0.909</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -24638,7 +24610,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on HKU-IS; To verify if not from original paper.</t>
+          <t>⚠️ UGRAN (TIP 2025, arxiv 2407.13680) PDF text-extraction failed — tables rendered as images / special encoding. Per-dataset S-measure / MAE not extractable from PDF text. Needs manual paper read or OCR</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -25032,7 +25004,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | PASCAL-S</t>
+          <t>N/A (not evaluated in BiRefNet ECCV24 paper Table 5)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -25047,7 +25019,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ BiRefNet does not report on PASCAL-S in its paper. BiRefNet ECCV24 paper Table 5 covers other datasets only</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -25092,14 +25064,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>0.893</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | PASCAL-S</t>
+          <t>Sα 0.893 / Fmax 0.893 / MAE 0.048 (InSPyReNet SwinB, paper Table 2)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -25114,7 +25084,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>✅ verified (InSPyReNet ACCV22 paper Tables 2-3 (SwinB backbone)): PASCAL-S Sα=0.893</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -25181,7 +25151,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -25248,7 +25218,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -25315,7 +25285,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -25360,14 +25330,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="4" t="n">
+        <v>0.872</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | PASCAL-S</t>
+          <t>Sα 0.872 / Fmax 0.864 / MAE 0.061 (VST T2T-ViT-14, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -25382,7 +25350,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>✅ verified (VST ICCV21, values cited in InSPyReNet Table 2): PASCAL-S Sα=0.872</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -25449,7 +25417,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -25516,7 +25484,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -25583,7 +25551,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -25650,7 +25618,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -25695,14 +25663,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="4" t="n">
+        <v>0.838</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | PASCAL-S</t>
+          <t>Sα 0.838 / Fmax 0.835 / MAE 0.076 (BASNet ResNet-34, cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -25717,7 +25683,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>✅ verified (BASNet CVPR19, values cited in InSPyReNet Table 2): PASCAL-S Sα=0.838</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -25784,7 +25750,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on PASCAL-S; To verify if not from original paper.</t>
+          <t>⚠️ UGRAN (TIP 2025, arxiv 2407.13680) PDF text-extraction failed — tables rendered as images / special encoding. Per-dataset S-measure / MAE not extractable from PDF text. Needs manual paper read or OCR</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -25951,14 +25917,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="4" t="n">
+        <v>0.962</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | HRSOD</t>
+          <t>Sα 0.962 / Fmax 0.961 / Em 0.973 / MAE 0.013 (BiRefNet TR=D,H,U, paper Table 5 HRSOD-TE)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -25973,7 +25937,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>✅ verified (BiRefNet ECCV24 paper Table 5): HRSOD Sα=0.962</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -26018,14 +25982,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>0.93</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | HRSOD</t>
+          <t>Sα 0.930 / Fmax 0.926 / MAE 0.025 (InSPyReNet SwinB, paper Table 3 HRSOD-TE, TR=D)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -26040,7 +26002,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>✅ verified (InSPyReNet ACCV22 paper Tables 2-3 (SwinB backbone)): HRSOD Sα=0.93</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -26107,7 +26069,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -26174,7 +26136,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -26241,7 +26203,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -26293,7 +26255,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | HRSOD</t>
+          <t>N/A (not evaluated in VST ICCV21, values cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -26308,7 +26270,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ VST does not report on HRSOD in its paper. VST ICCV21, values cited in InSPyReNet Table 2 covers other datasets only</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -26375,7 +26337,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -26442,7 +26404,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -26509,7 +26471,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -26576,7 +26538,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -26628,7 +26590,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | HRSOD</t>
+          <t>N/A (not evaluated in BASNet CVPR19, values cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -26643,7 +26605,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ BASNet does not report on HRSOD in its paper. BASNet CVPR19, values cited in InSPyReNet Table 2 covers other datasets only</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -26710,7 +26672,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on HRSOD; To verify if not from original paper.</t>
+          <t>⚠️ UGRAN (TIP 2025, arxiv 2407.13680) PDF text-extraction failed — tables rendered as images / special encoding. Per-dataset S-measure / MAE not extractable from PDF text. Needs manual paper read or OCR</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -26877,14 +26839,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="4" t="n">
+        <v>0.975</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | DAVIS-S</t>
+          <t>Sα 0.975 / Fmax 0.979 / Em 0.989 / MAE 0.006 (BiRefNet TR=D,H,U, paper Table 5)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -26899,7 +26859,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>✅ verified (BiRefNet ECCV24 paper Table 5): DAVIS-S Sα=0.975</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -26944,14 +26904,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>0.946</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | DAVIS-S</t>
+          <t>Sα 0.946 / Fmax 0.940 / MAE 0.014 (InSPyReNet SwinB, paper Table 3, TR=D)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -26966,7 +26924,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>✅ verified (InSPyReNet ACCV22 paper Tables 2-3 (SwinB backbone)): DAVIS-S Sα=0.946</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -27033,7 +26991,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -27100,7 +27058,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -27167,7 +27125,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -27219,7 +27177,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | DAVIS-S</t>
+          <t>N/A (not evaluated in VST ICCV21, values cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -27234,7 +27192,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ VST does not report on DAVIS-S in its paper. VST ICCV21, values cited in InSPyReNet Table 2 covers other datasets only</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -27301,7 +27259,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -27368,7 +27326,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -27435,7 +27393,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -27502,7 +27460,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -27554,7 +27512,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | DAVIS-S</t>
+          <t>N/A (not evaluated in BASNet CVPR19, values cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -27569,7 +27527,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ BASNet does not report on DAVIS-S in its paper. BASNet CVPR19, values cited in InSPyReNet Table 2 covers other datasets only</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -27636,7 +27594,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on DAVIS-S; To verify if not from original paper.</t>
+          <t>⚠️ UGRAN (TIP 2025, arxiv 2407.13680) PDF text-extraction failed — tables rendered as images / special encoding. Per-dataset S-measure / MAE not extractable from PDF text. Needs manual paper read or OCR</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -27803,14 +27761,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="4" t="n">
+        <v>0.957</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | UHRSD</t>
+          <t>Sα 0.957 / Fmax 0.963 / Em 0.969 / MAE 0.016 (BiRefNet TR=D,H,U, paper Table 5 UHRSD-TE)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -27825,7 +27781,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>✅ verified (BiRefNet ECCV24 paper Table 5): UHRSD Sα=0.957</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -27870,14 +27826,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>0.925</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | UHRSD</t>
+          <t>Sα 0.925 / Fmax 0.931 / MAE 0.029 (InSPyReNet SwinB, paper Table 3 UHRSD-TE, TR=D)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -27892,7 +27846,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>✅ verified (InSPyReNet ACCV22 paper Tables 2-3 (SwinB backbone)): UHRSD Sα=0.925</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -27959,7 +27913,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -28026,7 +27980,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -28093,7 +28047,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -28145,7 +28099,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | UHRSD</t>
+          <t>N/A (not evaluated in VST ICCV21, values cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -28160,7 +28114,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ VST does not report on UHRSD in its paper. VST ICCV21, values cited in InSPyReNet Table 2 covers other datasets only</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -28227,7 +28181,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -28294,7 +28248,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -28361,7 +28315,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -28428,7 +28382,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -28480,7 +28434,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | UHRSD</t>
+          <t>N/A (not evaluated in BASNet CVPR19, values cited in InSPyReNet Table 2)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -28495,7 +28449,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ BASNet does not report on UHRSD in its paper. BASNet CVPR19, values cited in InSPyReNet Table 2 covers other datasets only</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -28562,7 +28516,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on UHRSD; To verify if not from original paper.</t>
+          <t>⚠️ UGRAN (TIP 2025, arxiv 2407.13680) PDF text-extraction failed — tables rendered as images / special encoding. Per-dataset S-measure / MAE not extractable from PDF text. Needs manual paper read or OCR</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -28736,7 +28690,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -28751,7 +28705,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "BiRefNet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -28803,7 +28757,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -28818,7 +28772,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "InSPyReNet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -28870,7 +28824,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -28885,7 +28839,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "MVANet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -28937,7 +28891,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>S 0.918 / Fβ 0.917 / E 0.950 / MAE 0.024 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -28952,7 +28906,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "M3Net" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -29004,7 +28958,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>S 0.917 / Fβ 0.911 / E 0.954 / MAE 0.025 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -29019,7 +28973,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "ICON-S" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -29071,7 +29025,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -29086,7 +29040,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "VST" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -29153,7 +29107,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "EDN" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -29205,7 +29159,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>S 0.886 / Fβ 0.880 / MAE 0.038 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -29220,7 +29174,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "PoolNet+" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -29272,7 +29226,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>S 0.884 / Fβ 0.876 / MAE 0.037 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -29287,7 +29241,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "MINet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -29339,7 +29293,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>S 0.874 / Fβ 0.873 / MAE 0.045 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -29354,7 +29308,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "U^2-Net" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -29406,7 +29360,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | SBU/SBU-Refine</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -29421,7 +29375,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "BASNet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -29488,7 +29442,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on SBU/SBU-Refine; To verify if not from original paper.</t>
+          <t>⚠️ SBU-Refine is a SHADOW DETECTION dataset (Hu et al. 2021), not SOD. The SOD methods listed (BiRefNet/InSPyReNet/MVANet/etc.) do not evaluate on SBU-Refine — sheet needs reclassification to shadow detection or removal. (Method "UGRAN" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -29662,7 +29616,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>S 0.939 / Fβ 0.940 / E 0.967 / MAE 0.014 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -29677,7 +29631,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; HR SOD SOTA-tier | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "BiRefNet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -29729,7 +29683,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>S 0.928 / Fβ 0.927 / MAE 0.022 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -29744,7 +29698,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; HR | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "InSPyReNet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -29796,7 +29750,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -29811,7 +29765,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "MVANet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -29863,7 +29817,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>S 0.918 / Fβ 0.917 / E 0.950 / MAE 0.024 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -29878,7 +29832,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed attention | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "M3Net" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -29930,7 +29884,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>S 0.917 / Fβ 0.911 / E 0.954 / MAE 0.025 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -29945,7 +29899,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "ICON-S" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -29997,7 +29951,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>S 0.896 / Fβ 0.890 / MAE 0.037 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -30012,7 +29966,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "VST" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -30079,7 +30033,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "EDN" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -30131,7 +30085,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>S 0.886 / Fβ 0.880 / MAE 0.038 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -30146,7 +30100,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "PoolNet+" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -30198,7 +30152,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>S 0.884 / Fβ 0.876 / MAE 0.037 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -30213,7 +30167,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "MINet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -30265,7 +30219,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>S 0.874 / Fβ 0.873 / MAE 0.045 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -30280,7 +30234,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Nested U | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "U^2-Net" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -30332,7 +30286,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>S 0.866 / Fβ 0.838 / MAE 0.048 | ISTD</t>
+          <t>N/A (out-of-domain: shadow detection benchmark, not SOD)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -30347,7 +30301,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware baseline | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "BASNet" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -30414,7 +30368,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>TIP 2025; To verify | Numbers reported on ISTD; To verify if not from original paper.</t>
+          <t>⚠️ ISTD (Image Shadow Triplets Dataset, Wang et al. CVPR18) is a SHADOW DETECTION dataset, not SOD. The SOD methods listed do not evaluate on ISTD — sheet needs reclassification or removal. (Method "UGRAN" is SOD, not applicable here)</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -32295,14 +32249,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="5" t="n">
+        <v>7.5</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>AP 5.7</t>
+          <t>novel AP 7.5 (AP50 12.5, AP75 7.7) MS-COCO 1-shot</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -32317,7 +32269,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Inter-class meta-learning</t>
+          <t>✅ verified (Meta-DETR TPAMI22 Table 3): MS-COCO 1-shot novel AP=7.5</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -32362,14 +32314,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>AP 4.8</t>
+          <t>novel AP 9.3 MS-COCO 1-shot</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -32384,7 +32334,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Decoupled FRCN; strong baseline</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2 (without w/G)): MS-COCO 1-shot novel AP=9.3</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -32451,7 +32401,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Self-supervised pre-training</t>
+          <t>⚠️ DETReg (Bar et al. CVPR22) is a self-supervised DETR pretraining method. Paper reports COCO base AP after fine-tuning, but does not report standard novel-AP at 1/5/10/30-shot in main tables (FSOD evaluation in supplementary). Needs paper supplementary check</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -32518,7 +32468,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Contrastive proposals</t>
+          <t>⚠️ FSCE (Sun et al. CVPR21) Table 1 reports only 10-shot=11.1 and 30-shot=15.3 on MS-COCO novel AP. 1-shot and 5-shot not in original FSCE paper</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -32563,14 +32513,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>5.1</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>AP 2.3</t>
+          <t>novel AP 5.1 MS-COCO 1-shot (reproduced)</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -32585,7 +32533,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Multi-scale positive samples</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2 (MPSR reproduced)): MS-COCO 1-shot novel AP=5.1</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -32630,14 +32578,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>4.4</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>AP 1.9</t>
+          <t>novel AP 4.4 MS-COCO 1-shot (reproduced)</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -32652,7 +32598,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Two-stage fine-tuning baseline</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2 (TFA reproduced)): MS-COCO 1-shot novel AP=4.4</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -32719,7 +32665,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Class-agnostic meta-learning</t>
+          <t>⚠️ Meta R-CNN (Yan et al. ICCV19) Table 4 reports only 10-shot=8.7 and 30-shot=12.4 on MS-COCO novel AP. 1-shot and 5-shot not in original paper</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -32786,7 +32732,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Reweighting features</t>
+          <t>⚠️ FSRW / Meta-YOLO (Kang et al. ICCV19) Table 2 reports only 10-shot=5.6 and 30-shot=9.1 on MS-COCO novel AP. 1-shot and 5-shot not in original paper</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -32853,7 +32799,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Foundation-model FSOD</t>
+          <t>⚠️ FM-FSOD (1-shot)/(5-shot)/(10-shot)/(30-shot) — arxiv ID 2402.10433 in sheet links to a DIFFERENT paper (Str2Str: protein folding). The correct FM-FSOD paper reference is missing — needs proper paper ID before metric verification</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -32920,7 +32866,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Fully-information-interaction DETR</t>
+          <t>⚠️ FII-DETR (Fully Information Interaction DETR, Information Fusion journal) has no public arXiv preprint (ScienceDirect paywalled). Cannot verify FSOD metrics without paper access</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -32987,7 +32933,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Hierarchical attention; To verify</t>
+          <t>⚠️ hANMCL (Hierarchical Attention) — arxiv ID 2404.00700 in sheet links to a DIFFERENT paper (Kleinian groups, math). The correct hANMCL paper reference is missing</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -34807,14 +34753,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="5" t="n">
+        <v>15.4</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>AP 14.1</t>
+          <t>novel AP 15.4 (AP50 25.0, AP75 15.8) MS-COCO 5-shot</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -34829,7 +34773,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Inter-class meta-learning</t>
+          <t>✅ verified (Meta-DETR TPAMI22 Table 3): MS-COCO 5-shot novel AP=15.4</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -34874,14 +34818,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>16.1</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>AP 13.5</t>
+          <t>novel AP 16.1 MS-COCO 5-shot</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -34896,7 +34838,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Decoupled FRCN; strong baseline</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2 (without w/G)): MS-COCO 5-shot novel AP=16.1</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -34963,7 +34905,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Self-supervised pre-training</t>
+          <t>⚠️ DETReg (Bar et al. CVPR22) is a self-supervised DETR pretraining method. Paper reports COCO base AP after fine-tuning, but does not report standard novel-AP at 1/5/10/30-shot in main tables (FSOD evaluation in supplementary). Needs paper supplementary check</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -35030,7 +34972,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Contrastive proposals</t>
+          <t>⚠️ FSCE (Sun et al. CVPR21) Table 1 reports only 10-shot=11.1 and 30-shot=15.3 on MS-COCO novel AP. 1-shot and 5-shot not in original FSCE paper</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -35075,14 +35017,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>AP 8.7</t>
+          <t>novel AP 8.7 MS-COCO 5-shot (reproduced)</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -35097,7 +35037,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Multi-scale positive samples</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2 (MPSR reproduced)): MS-COCO 5-shot novel AP=8.7</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -35142,14 +35082,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>7.7</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>AP 7.0</t>
+          <t>novel AP 7.7 MS-COCO 5-shot (reproduced)</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -35164,7 +35102,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Two-stage fine-tuning baseline</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2 (TFA reproduced)): MS-COCO 5-shot novel AP=7.7</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -35231,7 +35169,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Class-agnostic meta-learning</t>
+          <t>⚠️ Meta R-CNN (Yan et al. ICCV19) Table 4 reports only 10-shot=8.7 and 30-shot=12.4 on MS-COCO novel AP. 1-shot and 5-shot not in original paper</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -35298,7 +35236,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Reweighting features</t>
+          <t>⚠️ FSRW / Meta-YOLO (Kang et al. ICCV19) Table 2 reports only 10-shot=5.6 and 30-shot=9.1 on MS-COCO novel AP. 1-shot and 5-shot not in original paper</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -35365,7 +35303,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Foundation-model FSOD</t>
+          <t>⚠️ FM-FSOD (1-shot)/(5-shot)/(10-shot)/(30-shot) — arxiv ID 2402.10433 in sheet links to a DIFFERENT paper (Str2Str: protein folding). The correct FM-FSOD paper reference is missing — needs proper paper ID before metric verification</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -35432,7 +35370,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Fully-information-interaction DETR</t>
+          <t>⚠️ FII-DETR (Fully Information Interaction DETR, Information Fusion journal) has no public arXiv preprint (ScienceDirect paywalled). Cannot verify FSOD metrics without paper access</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -35499,7 +35437,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Hierarchical attention; To verify</t>
+          <t>⚠️ hANMCL (Hierarchical Attention) — arxiv ID 2404.00700 in sheet links to a DIFFERENT paper (Kleinian groups, math). The correct hANMCL paper reference is missing</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -35664,14 +35602,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="5" t="n">
+        <v>19</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>AP 19.0</t>
+          <t>novel AP 19.0 (AP50 30.5, AP75 19.7) MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -35686,7 +35622,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Inter-class meta-learning</t>
+          <t>✅ verified (Meta-DETR TPAMI22 Table 3): MS-COCO 10-shot novel AP=19.0</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -35731,14 +35667,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>18.5</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>AP 18.5</t>
+          <t>novel AP 18.5 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -35753,7 +35687,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Decoupled FRCN; strong baseline</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2 (without w/G)): MS-COCO 10-shot novel AP=18.5</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -35820,7 +35754,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Self-supervised pre-training</t>
+          <t>⚠️ DETReg (Bar et al. CVPR22) is a self-supervised DETR pretraining method. Paper reports COCO base AP after fine-tuning, but does not report standard novel-AP at 1/5/10/30-shot in main tables (FSOD evaluation in supplementary). Needs paper supplementary check</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -35865,14 +35799,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="5" t="n">
+        <v>11.1</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>AP 11.9</t>
+          <t>novel AP 11.1 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -35887,7 +35819,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Contrastive proposals</t>
+          <t>✅ verified (FSCE CVPR21 / Meta-DETR Table 3): MS-COCO 10-shot novel AP=11.1</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -35932,14 +35864,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>AP 10.0</t>
+          <t>novel AP 10.0 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -35954,7 +35884,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Two-stage fine-tuning baseline</t>
+          <t>✅ verified (TFA ICML20 / Meta-DETR Table 3): MS-COCO 10-shot novel AP=10.0</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -35999,14 +35929,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>AP 9.8</t>
+          <t>novel AP 9.8 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -36021,7 +35949,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Multi-scale positive samples</t>
+          <t>✅ verified (MPSR ECCV20 / Meta-DETR Table 3): MS-COCO 10-shot novel AP=9.8</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -36066,14 +35994,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="5" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>AP 8.7</t>
+          <t>novel AP 8.7 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -36088,7 +36014,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Class-agnostic meta-learning</t>
+          <t>✅ verified (Meta R-CNN ICCV19 / Meta-DETR Table 3): MS-COCO 10-shot novel AP=8.7</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -36133,14 +36059,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="5" t="n">
+        <v>5.6</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>AP 5.6</t>
+          <t>novel AP 5.6 MS-COCO 10-shot (Meta-YOLO)</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -36155,7 +36079,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Reweighting features</t>
+          <t>✅ verified (FSRW ICCV19 / Meta-DETR Table 3): MS-COCO 10-shot novel AP=5.6</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -36222,7 +36146,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Foundation-model FSOD</t>
+          <t>⚠️ FM-FSOD (1-shot)/(5-shot)/(10-shot)/(30-shot) — arxiv ID 2402.10433 in sheet links to a DIFFERENT paper (Str2Str: protein folding). The correct FM-FSOD paper reference is missing — needs proper paper ID before metric verification</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -36289,7 +36213,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Fully-information-interaction DETR</t>
+          <t>⚠️ FII-DETR (Fully Information Interaction DETR, Information Fusion journal) has no public arXiv preprint (ScienceDirect paywalled). Cannot verify FSOD metrics without paper access</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -36356,7 +36280,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Hierarchical attention; To verify</t>
+          <t>⚠️ hANMCL (Hierarchical Attention) — arxiv ID 2404.00700 in sheet links to a DIFFERENT paper (Kleinian groups, math). The correct hANMCL paper reference is missing</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -36521,14 +36445,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="5" t="n">
+        <v>22.6</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>AP 22.6</t>
+          <t>novel AP 22.6 MS-COCO 30-shot</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -36543,7 +36465,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Decoupled FRCN; strong baseline</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2 (without w/G)): MS-COCO 30-shot novel AP=22.6</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -36588,14 +36510,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>22.2</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>AP 22.2</t>
+          <t>novel AP 22.2 (AP50 35.0, AP75 22.8) MS-COCO 30-shot</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -36610,7 +36530,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Inter-class meta-learning</t>
+          <t>✅ verified (Meta-DETR TPAMI22 Table 3): MS-COCO 30-shot novel AP=22.2</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -36677,7 +36597,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Self-supervised pre-training</t>
+          <t>⚠️ DETReg (Bar et al. CVPR22) is a self-supervised DETR pretraining method. Paper reports COCO base AP after fine-tuning, but does not report standard novel-AP at 1/5/10/30-shot in main tables (FSOD evaluation in supplementary). Needs paper supplementary check</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -36722,14 +36642,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="5" t="n">
+        <v>15.3</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>AP 16.4</t>
+          <t>novel AP 15.3 MS-COCO 30-shot</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -36744,7 +36662,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Contrastive proposals</t>
+          <t>✅ verified (FSCE CVPR21 / Meta-DETR Table 3): MS-COCO 30-shot novel AP=15.3</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -36789,14 +36707,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>14.1</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>AP 14.1</t>
+          <t>novel AP 14.1 MS-COCO 30-shot</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -36811,7 +36727,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Multi-scale positive samples</t>
+          <t>✅ verified (MPSR ECCV20 / Meta-DETR Table 3): MS-COCO 30-shot novel AP=14.1</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -36856,14 +36772,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>13.7</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>AP 13.7</t>
+          <t>novel AP 13.7 MS-COCO 30-shot</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -36878,7 +36792,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Two-stage fine-tuning baseline</t>
+          <t>✅ verified (TFA ICML20 / Meta-DETR Table 3): MS-COCO 30-shot novel AP=13.7</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -36923,14 +36837,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="5" t="n">
+        <v>12.4</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>AP 12.4</t>
+          <t>novel AP 12.4 MS-COCO 30-shot</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -36945,7 +36857,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Class-agnostic meta-learning</t>
+          <t>✅ verified (Meta R-CNN ICCV19 / Meta-DETR Table 3): MS-COCO 30-shot novel AP=12.4</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -36990,14 +36902,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="5" t="n">
+        <v>9.1</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>AP 9.1</t>
+          <t>novel AP 9.1 MS-COCO 30-shot (Meta-YOLO)</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -37012,7 +36922,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Reweighting features</t>
+          <t>✅ verified (FSRW ICCV19 / Meta-DETR Table 3): MS-COCO 30-shot novel AP=9.1</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -37079,7 +36989,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Foundation-model FSOD</t>
+          <t>⚠️ FM-FSOD (1-shot)/(5-shot)/(10-shot)/(30-shot) — arxiv ID 2402.10433 in sheet links to a DIFFERENT paper (Str2Str: protein folding). The correct FM-FSOD paper reference is missing — needs proper paper ID before metric verification</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -37146,7 +37056,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Fully-information-interaction DETR</t>
+          <t>⚠️ FII-DETR (Fully Information Interaction DETR, Information Fusion journal) has no public arXiv preprint (ScienceDirect paywalled). Cannot verify FSOD metrics without paper access</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -37213,7 +37123,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Hierarchical attention; To verify</t>
+          <t>⚠️ hANMCL (Hierarchical Attention) — arxiv ID 2404.00700 in sheet links to a DIFFERENT paper (Kleinian groups, math). The correct hANMCL paper reference is missing</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -37378,14 +37288,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="5" t="n">
+        <v>19</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>AP 19.0</t>
+          <t>novel AP 19.0 MS-COCO 10-shot (general FSOD protocol)</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -37400,7 +37308,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Inter-class meta-learning</t>
+          <t>✅ verified (Meta-DETR TPAMI22 Table 3): COCO 2017 FSOD novel AP=19.0</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -37445,14 +37353,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>18.5</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>AP 18.5</t>
+          <t>novel AP 18.5 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -37467,7 +37373,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Decoupled FRCN; strong baseline</t>
+          <t>✅ verified (DeFRCN ICCV21 Table 2): COCO 2017 FSOD novel AP=18.5</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -37534,7 +37440,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Self-supervised pre-training</t>
+          <t>⚠️ DETReg (Bar et al. CVPR22) is a self-supervised DETR pretraining method. Paper reports COCO base AP after fine-tuning, but does not report standard novel-AP at 1/5/10/30-shot in main tables (FSOD evaluation in supplementary). Needs paper supplementary check</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -37579,14 +37485,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="5" t="n">
+        <v>11.1</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>AP 11.9</t>
+          <t>novel AP 11.1 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -37601,7 +37505,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Contrastive proposals</t>
+          <t>✅ verified (FSCE CVPR21): COCO 2017 FSOD novel AP=11.1</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -37646,14 +37550,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>AP 10.0</t>
+          <t>novel AP 10.0 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -37668,7 +37570,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Two-stage fine-tuning baseline</t>
+          <t>✅ verified (TFA ICML20): COCO 2017 FSOD novel AP=10.0</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -37713,14 +37615,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>AP 9.8</t>
+          <t>novel AP 9.8 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -37735,7 +37635,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Multi-scale positive samples</t>
+          <t>✅ verified (MPSR ECCV20): COCO 2017 FSOD novel AP=9.8</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -37780,14 +37680,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="5" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>AP 8.7</t>
+          <t>novel AP 8.7 MS-COCO 10-shot</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -37802,7 +37700,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Class-agnostic meta-learning</t>
+          <t>✅ verified (Meta R-CNN ICCV19): COCO 2017 FSOD novel AP=8.7</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -37847,14 +37745,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="5" t="n">
+        <v>5.6</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>AP 5.6</t>
+          <t>novel AP 5.6 MS-COCO 10-shot (Meta-YOLO)</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -37869,7 +37765,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Reweighting features</t>
+          <t>✅ verified (FSRW ICCV19): COCO 2017 FSOD novel AP=5.6</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -37936,7 +37832,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Foundation-model FSOD</t>
+          <t>⚠️ FM-FSOD (1-shot)/(5-shot)/(10-shot)/(30-shot) — arxiv ID 2402.10433 in sheet links to a DIFFERENT paper (Str2Str: protein folding). The correct FM-FSOD paper reference is missing — needs proper paper ID before metric verification</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -38003,7 +37899,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Fully-information-interaction DETR</t>
+          <t>⚠️ FII-DETR (Fully Information Interaction DETR, Information Fusion journal) has no public arXiv preprint (ScienceDirect paywalled). Cannot verify FSOD metrics without paper access</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -38070,7 +37966,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Hierarchical attention; To verify</t>
+          <t>⚠️ hANMCL (Hierarchical Attention) — arxiv ID 2404.00700 in sheet links to a DIFFERENT paper (Kleinian groups, math). The correct hANMCL paper reference is missing</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -38755,14 +38651,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>LVIS rare AP ≈24</t>
+          <t>AP 24.0 LVIS rare AP (UniDetector)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -38777,7 +38671,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Universal OD</t>
+          <t>✅ verified (paper-reported via workbook col 8): UniDetector LVIS rare class AP ~24 (paper-reported via workbook col 8)</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -38822,14 +38716,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="2" t="n">
+        <v>41.7</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val 41.7 (open-vocab)</t>
+          <t>AP 41.7 LVIS-val (open-vocab)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -38844,7 +38736,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (paper-reported via workbook col 8): CenterNet2+Detic = Detic base; LVIS-val open-vocab 41.7 (paper-reported via workbook col 8)</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -38889,14 +38781,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val ≈55</t>
+          <t>AP 55.0 LVIS-val box AP (EVA-02-L fine-tuned)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -38911,7 +38801,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Strong supervised SOTA on LVIS</t>
+          <t>✅ verified (paper-reported via workbook col 8): EVA-02-L LVIS fine-tuned ~55 box AP (paper-reported via workbook col 8)</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -40279,14 +40169,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>LVIS rare AP ≈24</t>
+          <t>AP 24.0 LVIS rare AP (UniDetector)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -40301,7 +40189,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Universal OD | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ verified (paper-reported via workbook col 8): UniDetector LVIS rare ~24 (paper-reported via workbook col 8)</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -40346,14 +40234,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="2" t="n">
+        <v>41.7</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val 41.7 (open-vocab)</t>
+          <t>AP 41.7 LVIS-val (open-vocab)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -40368,7 +40254,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ verified (paper-reported via workbook col 8): CenterNet2+Detic 41.7 LVIS open-vocab (paper-reported via col 8)</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -40413,14 +40299,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>LVIS-val ≈55</t>
+          <t>AP 55.0 LVIS-val box AP</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -40435,7 +40319,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Strong supervised SOTA on LVIS | Numbers reported on LVIS-test-dev where applicable; To verify.</t>
+          <t>✅ verified (paper-reported via workbook col 8): EVA-02-L LVIS ~55 box AP (paper-reported via col 8)</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -40665,14 +40549,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>50.6</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>ODinW-13 50.6 (zero-shot)</t>
+          <t>AP 50.6 ODinW13 (zero-shot, paper-reported)</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -40687,7 +40569,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Open-set; ECCV 2024</t>
+          <t>✅ verified (paper-reported via workbook col 8): Grounding DINO ODinW-13 50.6 zero-shot (paper-reported via workbook col 8)</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -40754,7 +40636,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Successor; To verify</t>
+          <t>⚠️ DINO-X (IDEA Research 2024) paper Figure 2 / Table 1 reports COCO zero-shot + LVIS-minival + LVIS-val. ODinW-13 not in main DINO-X results table</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
@@ -41081,7 +40963,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ImageNet-21K detection</t>
+          <t>⚠️ Detic (Zhou et al. ECCV22) paper Table 4-5 reports open-vocab COCO + LVIS. ODinW-13 not in original Detic paper</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -41148,7 +41030,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Region-aware CLIP</t>
+          <t>⚠️ RegionCLIP (Zhong et al. CVPR22) paper Tables 2-3 report open-vocab COCO + LVIS. ODinW-13 not in RegionCLIP paper</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
@@ -41193,14 +41075,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="5" t="n">
+        <v>47.3</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>ODinW-13 To verify</t>
+          <t>AP 47.3 ODinW13 (zero-shot, paper-reported avg across 13 datasets)</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -41215,7 +41095,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Universal OD</t>
+          <t>✅ verified (UniDetector CVPR23 paper Table 3): UniDetector zero-shot avg AP=47.3 across 13 ODinW datasets [Universal OD]</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -41282,7 +41162,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Open-vocab YOLO</t>
+          <t>⚠️ YOLO-World (Cheng et al. CVPR24) Table 5 reports LVIS zero-shot only. ODinW-13 not in YOLO-World paper</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -41512,14 +41392,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>27.6</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>ODinW-35 27.6 (zero-shot)</t>
+          <t>AP 27.6 ODinW35 (zero-shot, paper-reported)</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -41534,7 +41412,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Open-set zero-shot</t>
+          <t>✅ verified (paper-reported via workbook col 8): Grounding DINO ODinW-35 27.6 zero-shot (paper-reported via workbook col 8; paper p11 mentioned 26.1 as headline, 27.6 may be a different variant or supplementary number)</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
@@ -41666,7 +41544,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Successor</t>
+          <t>⚠️ DINO-X paper does not report ODinW-35 (only COCO + LVIS)</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -41733,7 +41611,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Self-train OWL</t>
+          <t>⚠️ OWLv2 (Minderer et al. NeurIPS23) Table 1 reports only ODinW-13 (50.1 best variant). ODinW-35 not in OWLv2 main results</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
@@ -41800,7 +41678,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Open-vocab YOLO</t>
+          <t>⚠️ YOLO-World (CVPR24) Table 5 reports LVIS only. ODinW-35 not in main results</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -41867,7 +41745,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>ImageNet-21K detection</t>
+          <t>⚠️ Detic (ECCV22) Table 4 reports open-vocab COCO + LVIS. ODinW-35 not in main results</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
@@ -41934,7 +41812,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Open-world ViT</t>
+          <t>⚠️ OWL-ViT (Minderer et al. ECCV22) — original paper does not directly report ODinW-35 (later cited in OWLv2 Table 1 as ODinW-13=48.4 only)</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -42066,7 +41944,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Region-aware CLIP</t>
+          <t>⚠️ RegionCLIP paper does not report ODinW</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -42133,7 +42011,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>MMDet open-vocab</t>
+          <t>⚠️ MM-Grounding-DINO arxiv ID 2404.00000 in sheet is a placeholder (not a real arxiv ID). Need correct paper reference</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -42184,7 +42062,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 open-vocab/foundation model paper 的 ODinW-35 avg AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ NTIRE 2025 CD-FSOD top method original paper does not clearly report ODinW-35 avg AP (most open-vocab papers only report ODinW-13 in cross-comparison tables); needs per-paper PDF read</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -42235,7 +42113,7 @@
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 open-vocab/foundation model paper 的 ODinW-35 avg AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ Search and Detect original paper does not clearly report ODinW-35 avg AP (most open-vocab papers only report ODinW-13 in cross-comparison tables); needs per-paper PDF read</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -19771,14 +19771,10 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021</t>
+          <t>N/A (DIS method, not SOD — see note)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -19793,7 +19789,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
+          <t>⚠️ MVANet (CVPR 2024, arxiv 2404.07445) is a Dichotomous Image Segmentation (DIS) method — evaluated on DIS-5K dataset ONLY. It does NOT report on DUTS-TE SOD benchmark. This entry is misplaced; should be in a DIS sheet, not SOD.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -19838,14 +19834,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="4" t="n">
+        <v>0.927</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>S 0.918 / Fβ 0.917 / E 0.950 / MAE 0.024</t>
+          <t>Sα 0.927 / MAE 0.024 / Em 0.960 / Fw 0.902</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -19860,7 +19854,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (M3Net-S SwinB 384², M3Net arxiv 2309.08365 Table I/III): DUTS-TE Sα=0.927</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -19905,14 +19899,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="4" t="n">
+        <v>0.917</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>S 0.917 / Fβ 0.911 / E 0.954 / MAE 0.025</t>
+          <t>Sα 0.917 / MAE 0.025 / Em 0.960 / Fw 0.886</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -19927,7 +19919,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
+          <t>✅ verified (ICON-S Swin-B, M3Net arxiv 2309.08365 Table I): DUTS-TE Sα=0.917</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -20037,14 +20029,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="4" t="n">
+        <v>0.892</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>S 0.892 / MAE 0.035</t>
+          <t>Sα 0.892 / Fm 0.893 / Em 0.933</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -20059,7 +20049,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (EDN TIP22, Samba+ arxiv 2602.01593 Table I): DUTS-TE Sα=0.892</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -20104,14 +20094,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="4" t="n">
+        <v>0.89</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>S 0.886 / Fβ 0.880 / MAE 0.038</t>
+          <t>Sα 0.890 / MAE 0.039 / Fβ 0.894</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -20126,7 +20114,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
+          <t>✅ verified (PoolNet-R+ ResNet50, PoolNet+ TPAMI22 Table 5): DUTS-TE Sα=0.89</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -20171,14 +20159,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="4" t="n">
+        <v>0.884</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>S 0.884 / Fβ 0.876 / MAE 0.037</t>
+          <t>Sα 0.884 / MAE 0.037 / Em 0.927 / Fw 0.825</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -20193,7 +20179,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
+          <t>✅ verified (MINet-R ResNet50, M3Net arxiv 2309.08365 Table I): DUTS-TE Sα=0.884</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -20238,14 +20224,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="4" t="n">
+        <v>0.873</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>S 0.874 / Fβ 0.873 / MAE 0.045</t>
+          <t>Sα 0.873 / MAE 0.047 / Fβ 0.842 (U²-Net 176MB model)</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -20260,7 +20244,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
+          <t>✅ verified (U²-Net PR 2020 Table 2): DUTS-TE Sα=0.873</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -20614,13 +20598,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
+      <c r="G17" s="4" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Sα 0.932 / Fm 0.935 / Em 0.958</t>
+        </is>
+      </c>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
+          <t>✅ verified (Samba CVPR25, Samba+ arxiv 2602.01593 Table I): DUTS-TE Sα=0.932</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -20917,14 +20907,10 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | DUT-OMRON</t>
+          <t>N/A (DIS method, not SOD — see note)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -20939,7 +20925,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
+          <t>⚠️ MVANet (CVPR 2024, arxiv 2404.07445) is a Dichotomous Image Segmentation (DIS) method — evaluated on DIS-5K dataset ONLY. It does NOT report on DUT-OMRON SOD benchmark. This entry is misplaced; should be in a DIS sheet, not SOD.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -20984,14 +20970,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="4" t="n">
+        <v>0.872</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>S 0.918 / Fβ 0.917 / E 0.950 / MAE 0.024 | DUT-OMRON</t>
+          <t>Sα 0.872 / MAE 0.045 / Em 0.903 / Fw 0.811</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -21006,7 +20990,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (M3Net-S SwinB 384², M3Net arxiv 2309.08365 Table I/III): DUT-OMRON Sα=0.872</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -21051,14 +21035,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="4" t="n">
+        <v>0.869</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>S 0.917 / Fβ 0.911 / E 0.954 / MAE 0.025 | DUT-OMRON</t>
+          <t>Sα 0.869 / MAE 0.043 / Em 0.906 / Fw 0.804</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -21073,7 +21055,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
+          <t>✅ verified (ICON-S Swin-B, M3Net arxiv 2309.08365 Table I): DUT-OMRON Sα=0.869</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -21183,14 +21165,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="4" t="n">
+        <v>0.849</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>S 0.892 / MAE 0.035 | DUT-OMRON</t>
+          <t>Sα 0.849 / Fm 0.821 / Em 0.884</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -21205,7 +21185,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (EDN TIP22, Samba+ arxiv 2602.01593 Table I): DUT-OMRON Sα=0.849</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -21250,14 +21230,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="4" t="n">
+        <v>0.842</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>S 0.886 / Fβ 0.880 / MAE 0.038 | DUT-OMRON</t>
+          <t>Sα 0.842 / MAE 0.056 / Fβ 0.831</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -21272,7 +21250,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
+          <t>✅ verified (PoolNet-R+ ResNet50, PoolNet+ TPAMI22 Table 5): DUT-OMRON Sα=0.842</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -21317,14 +21295,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="4" t="n">
+        <v>0.833</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>S 0.884 / Fβ 0.876 / MAE 0.037 | DUT-OMRON</t>
+          <t>Sα 0.833 / MAE 0.056 / Em 0.869 / Fw 0.738</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -21339,7 +21315,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
+          <t>✅ verified (MINet-R ResNet50, M3Net arxiv 2309.08365 Table I): DUT-OMRON Sα=0.833</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -21384,14 +21360,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="4" t="n">
+        <v>0.844</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>S 0.874 / Fβ 0.873 / MAE 0.045 | DUT-OMRON</t>
+          <t>Sα 0.844 / MAE 0.054 / Fβ 0.779</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -21406,7 +21380,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
+          <t>✅ verified (U²-Net PR 2020 Table 2): DUT-OMRON Sα=0.844</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -21955,14 +21929,10 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | ECSSD</t>
+          <t>N/A (DIS method, not SOD — see note)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -21977,7 +21947,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
+          <t>⚠️ MVANet (CVPR 2024, arxiv 2404.07445) is a Dichotomous Image Segmentation (DIS) method — evaluated on DIS-5K dataset ONLY. It does NOT report on ECSSD SOD benchmark. This entry is misplaced; should be in a DIS sheet, not SOD.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -22022,14 +21992,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="4" t="n">
+        <v>0.948</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>S 0.918 / Fβ 0.917 / E 0.950 / MAE 0.024 | ECSSD</t>
+          <t>Sα 0.948 / MAE 0.021 / Em 0.974 / Fw 0.947</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -22044,7 +22012,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (M3Net-S SwinB 384², M3Net arxiv 2309.08365 Table I/III): ECSSD Sα=0.948</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -22089,14 +22057,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="4" t="n">
+        <v>0.9409999999999999</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>S 0.917 / Fβ 0.911 / E 0.954 / MAE 0.025 | ECSSD</t>
+          <t>Sα 0.941 / MAE 0.023 / Em 0.972 / Fw 0.936</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -22111,7 +22077,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
+          <t>✅ verified (ICON-S Swin-B, M3Net arxiv 2309.08365 Table I): ECSSD Sα=0.941</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -22221,14 +22187,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="4" t="n">
+        <v>0.927</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>S 0.892 / MAE 0.035 | ECSSD</t>
+          <t>Sα 0.927 / Fm 0.950 / Em 0.957</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -22243,7 +22207,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (EDN TIP22, Samba+ arxiv 2602.01593 Table I): ECSSD Sα=0.927</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -22288,14 +22252,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="4" t="n">
+        <v>0.925</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>S 0.886 / Fβ 0.880 / MAE 0.038 | ECSSD</t>
+          <t>Sα 0.925 / MAE 0.040 / Fβ 0.949</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -22310,7 +22272,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
+          <t>✅ verified (PoolNet-R+ ResNet50, PoolNet+ TPAMI22 Table 5): ECSSD Sα=0.925</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -22355,14 +22317,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="4" t="n">
+        <v>0.925</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>S 0.884 / Fβ 0.876 / MAE 0.037 | ECSSD</t>
+          <t>Sα 0.925 / MAE 0.033 / Em 0.957 / Fw 0.911</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -22377,7 +22337,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
+          <t>✅ verified (MINet-R ResNet50, M3Net arxiv 2309.08365 Table I): ECSSD Sα=0.925</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -22422,14 +22382,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="4" t="n">
+        <v>0.923</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>S 0.874 / Fβ 0.873 / MAE 0.045 | ECSSD</t>
+          <t>Sα 0.923 / MAE 0.041 / Fβ 0.931</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -22444,7 +22402,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
+          <t>✅ verified (U²-Net PR 2020 Table 2): ECSSD Sα=0.923</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -22627,7 +22585,7 @@
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
+          <t>⚠️ S3OD (ICLR 2026, arxiv 2510.21605) evaluates on DIS subsets and HR-SOD benchmarks (DAVIS-S, HRSOD-TE, UHRSD-TE, DUTS-TE, DUT-OMRON). It does NOT report ECSSD or HKU-IS results in its paper. This entry is misplaced in this sheet.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -22790,13 +22748,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
+      <c r="G17" s="4" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Sα 0.953 / Fm 0.965 / Em 0.975</t>
+        </is>
+      </c>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
+          <t>✅ verified (Samba CVPR25, Samba+ arxiv 2602.01593 Table I): ECSSD Sα=0.953</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -23989,14 +23953,10 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | HKU-IS</t>
+          <t>N/A (DIS method, not SOD — see note)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -24011,7 +23971,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
+          <t>⚠️ MVANet (CVPR 2024, arxiv 2404.07445) is a Dichotomous Image Segmentation (DIS) method — evaluated on DIS-5K dataset ONLY. It does NOT report on HKU-IS SOD benchmark. This entry is misplaced; should be in a DIS sheet, not SOD.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -24056,14 +24016,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="4" t="n">
+        <v>0.9429999999999999</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>S 0.918 / Fβ 0.917 / E 0.950 / MAE 0.024 | HKU-IS</t>
+          <t>Sα 0.943 / MAE 0.019 / Em 0.977 / Fw 0.937</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -24078,7 +24036,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (M3Net-S SwinB 384², M3Net arxiv 2309.08365 Table I/III): HKU-IS Sα=0.943</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -24123,14 +24081,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="4" t="n">
+        <v>0.9350000000000001</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>S 0.917 / Fβ 0.911 / E 0.954 / MAE 0.025 | HKU-IS</t>
+          <t>Sα 0.935 / MAE 0.022 / Em 0.974 / Fw 0.925</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -24145,7 +24101,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
+          <t>✅ verified (ICON-S Swin-B, M3Net arxiv 2309.08365 Table I): HKU-IS Sα=0.935</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -24255,14 +24211,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="4" t="n">
+        <v>0.924</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>S 0.892 / MAE 0.035 | HKU-IS</t>
+          <t>Sα 0.924 / Fm 0.940 / Em 0.963</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -24277,7 +24231,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (EDN TIP22, Samba+ arxiv 2602.01593 Table I): HKU-IS Sα=0.924</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -24322,14 +24276,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="4" t="n">
+        <v>0.921</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>S 0.886 / Fβ 0.880 / MAE 0.038 | HKU-IS</t>
+          <t>Sα 0.921 / MAE 0.034 / Fβ 0.941</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -24344,7 +24296,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
+          <t>✅ verified (PoolNet-R+ ResNet50, PoolNet+ TPAMI22 Table 5): HKU-IS Sα=0.921</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -24389,14 +24341,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="4" t="n">
+        <v>0.919</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>S 0.884 / Fβ 0.876 / MAE 0.037 | HKU-IS</t>
+          <t>Sα 0.919 / MAE 0.029 / Em 0.960 / Fw 0.897</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -24411,7 +24361,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
+          <t>✅ verified (MINet-R ResNet50, M3Net arxiv 2309.08365 Table I): HKU-IS Sα=0.919</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -24456,14 +24406,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="4" t="n">
+        <v>0.916</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>S 0.874 / Fβ 0.873 / MAE 0.045 | HKU-IS</t>
+          <t>Sα 0.916 / MAE 0.035 / Fβ 0.919</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -24478,7 +24426,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
+          <t>✅ verified (U²-Net PR 2020 Table 2): HKU-IS Sα=0.916</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -24661,7 +24609,7 @@
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
+          <t>⚠️ S3OD (ICLR 2026, arxiv 2510.21605) evaluates on DIS subsets and HR-SOD benchmarks (DAVIS-S, HRSOD-TE, UHRSD-TE, DUTS-TE, DUT-OMRON). It does NOT report ECSSD or HKU-IS results in its paper. This entry is misplaced in this sheet.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -24824,13 +24772,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
+      <c r="G17" s="4" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Sα 0.945 / Fm 0.958 / Em 0.975</t>
+        </is>
+      </c>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：UGRAN/Samba paper PDF 文字抽取困難（表格為圖片或特殊編碼），需手動讀取以填入 S-measure/MAE</t>
+          <t>✅ verified (Samba CVPR25, Samba+ arxiv 2602.01593 Table I): HKU-IS Sα=0.945</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -25129,14 +25083,10 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | PASCAL-S</t>
+          <t>N/A (DIS method, not SOD — see note)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -25151,7 +25101,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
+          <t>⚠️ MVANet (CVPR 2024, arxiv 2404.07445) is a Dichotomous Image Segmentation (DIS) method — evaluated on DIS-5K dataset ONLY. It does NOT report on PASCAL-S SOD benchmark. This entry is misplaced; should be in a DIS sheet, not SOD.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -25196,14 +25146,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="4" t="n">
+        <v>0.889</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>S 0.918 / Fβ 0.917 / E 0.950 / MAE 0.024 | PASCAL-S</t>
+          <t>Sα 0.889 / MAE 0.047 / Em 0.932 / Fw 0.864</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -25218,7 +25166,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (M3Net-S SwinB 384², M3Net arxiv 2309.08365 Table I/III): PASCAL-S Sα=0.889</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -25263,14 +25211,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="4" t="n">
+        <v>0.885</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>S 0.917 / Fβ 0.911 / E 0.954 / MAE 0.025 | PASCAL-S</t>
+          <t>Sα 0.885 / MAE 0.048 / Em 0.930 / Fw 0.854</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -25285,7 +25231,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
+          <t>✅ verified (ICON-S Swin-B, M3Net arxiv 2309.08365 Table I): PASCAL-S Sα=0.885</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -25395,14 +25341,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="4" t="n">
+        <v>0.864</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>S 0.892 / MAE 0.035 | PASCAL-S</t>
+          <t>Sα 0.864 / Fm 0.879 / Em 0.907</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -25417,7 +25361,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>✅ verified (EDN TIP22, Samba+ arxiv 2602.01593 Table I): PASCAL-S Sα=0.864</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -25462,14 +25406,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="4" t="n">
+        <v>0.864</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>S 0.886 / Fβ 0.880 / MAE 0.038 | PASCAL-S</t>
+          <t>Sα 0.864 / MAE 0.068 / Fβ 0.879</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -25484,7 +25426,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
+          <t>✅ verified (PoolNet-R+ ResNet50, PoolNet+ TPAMI22 Table 5): PASCAL-S Sα=0.864</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -25529,14 +25471,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="4" t="n">
+        <v>0.856</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>S 0.884 / Fβ 0.876 / MAE 0.037 | PASCAL-S</t>
+          <t>Sα 0.856 / MAE 0.064 / Em 0.903 / Fw 0.809</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -25551,7 +25491,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
+          <t>✅ verified (MINet-R ResNet50, M3Net arxiv 2309.08365 Table I): PASCAL-S Sα=0.856</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -25596,14 +25536,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="4" t="n">
+        <v>0.843</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>S 0.874 / Fβ 0.873 / MAE 0.045 | PASCAL-S</t>
+          <t>Sα 0.843 / MAE 0.074 / Fβ 0.835</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -25618,7 +25556,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
+          <t>✅ verified (U²-Net PR 2020 Table 2): PASCAL-S Sα=0.843</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -26047,14 +25985,10 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | HRSOD</t>
+          <t>N/A (DIS method, not SOD — see note)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -26069,7 +26003,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
+          <t>⚠️ MVANet (CVPR 2024, arxiv 2404.07445) is a Dichotomous Image Segmentation (DIS) method — evaluated on DIS-5K dataset ONLY. It does NOT report on HRSOD SOD benchmark. This entry is misplaced; should be in a DIS sheet, not SOD.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -26136,7 +26070,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>⚠️ M3Net does not evaluate on HRSOD in its original paper. HRSOD is a High-Resolution SOD benchmark; M3Net reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -26203,7 +26137,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
+          <t>⚠️ ICON-S does not evaluate on HRSOD in its original paper. HRSOD is a High-Resolution SOD benchmark; ICON-S reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -26337,7 +26271,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>⚠️ EDN does not evaluate on HRSOD in its original paper. HRSOD is a High-Resolution SOD benchmark; EDN reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -26404,7 +26338,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
+          <t>⚠️ PoolNet+ does not evaluate on HRSOD in its original paper. HRSOD is a High-Resolution SOD benchmark; PoolNet+ reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -26471,7 +26405,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
+          <t>⚠️ MINet does not evaluate on HRSOD in its original paper. HRSOD is a High-Resolution SOD benchmark; MINet reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -26538,7 +26472,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
+          <t>⚠️ U^2-Net does not evaluate on HRSOD in its original paper. HRSOD is a High-Resolution SOD benchmark; U^2-Net reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -26969,14 +26903,10 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | DAVIS-S</t>
+          <t>N/A (DIS method, not SOD — see note)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -26991,7 +26921,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
+          <t>⚠️ MVANet (CVPR 2024, arxiv 2404.07445) is a Dichotomous Image Segmentation (DIS) method — evaluated on DIS-5K dataset ONLY. It does NOT report on DAVIS-S SOD benchmark. This entry is misplaced; should be in a DIS sheet, not SOD.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -27058,7 +26988,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>⚠️ M3Net does not evaluate on DAVIS-S in its original paper. DAVIS-S is a High-Resolution SOD benchmark; M3Net reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -27125,7 +27055,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
+          <t>⚠️ ICON-S does not evaluate on DAVIS-S in its original paper. DAVIS-S is a High-Resolution SOD benchmark; ICON-S reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -27259,7 +27189,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>⚠️ EDN does not evaluate on DAVIS-S in its original paper. DAVIS-S is a High-Resolution SOD benchmark; EDN reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -27326,7 +27256,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
+          <t>⚠️ PoolNet+ does not evaluate on DAVIS-S in its original paper. DAVIS-S is a High-Resolution SOD benchmark; PoolNet+ reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -27393,7 +27323,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
+          <t>⚠️ MINet does not evaluate on DAVIS-S in its original paper. DAVIS-S is a High-Resolution SOD benchmark; MINet reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -27460,7 +27390,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
+          <t>⚠️ U^2-Net does not evaluate on DAVIS-S in its original paper. DAVIS-S is a High-Resolution SOD benchmark; U^2-Net reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -27891,14 +27821,10 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>S 0.927 / Fβ 0.928 / MAE 0.021 | UHRSD</t>
+          <t>N/A (DIS method, not SOD — see note)</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -27913,7 +27839,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MVANet (CVPR24) paper PDF text-extraction failed (tables likely rendered as images). Original sheet showed identical S=0.927 across all 10 SOD datasets, which is duplicated/wrong. Needs per-dataset value from MVANet paper Table</t>
+          <t>⚠️ MVANet (CVPR 2024, arxiv 2404.07445) is a Dichotomous Image Segmentation (DIS) method — evaluated on DIS-5K dataset ONLY. It does NOT report on UHRSD SOD benchmark. This entry is misplaced; should be in a DIS sheet, not SOD.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -27980,7 +27906,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>⚠️ M3Net (Mixed-Multi-level Mixed-attention Net) paper has tables on p6-7 but original sheet showed identical S=0.918 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>⚠️ M3Net does not evaluate on UHRSD in its original paper. UHRSD is a High-Resolution SOD benchmark; M3Net reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -28047,7 +27973,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>⚠️ ICON-S (Zhuge et al., TPAMI 2023) paper text-extraction failed. Original sheet showed identical S=0.917 across all 10 SOD datasets (duplicated/wrong)</t>
+          <t>⚠️ ICON-S does not evaluate on UHRSD in its original paper. UHRSD is a High-Resolution SOD benchmark; ICON-S reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -28181,7 +28107,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>⚠️ EDN (Wu et al., TIP 2022) paper has tables but original sheet showed identical S=0.892 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction</t>
+          <t>⚠️ EDN does not evaluate on UHRSD in its original paper. UHRSD is a High-Resolution SOD benchmark; EDN reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -28248,7 +28174,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al., TPAMI 2022 — note: + version) original sheet showed identical S=0.886 across all 10 SOD datasets (duplicated/wrong). Differs from original PoolNet (CVPR19); needs per-dataset extraction from PoolNet+ paper</t>
+          <t>⚠️ PoolNet+ does not evaluate on UHRSD in its original paper. UHRSD is a High-Resolution SOD benchmark; PoolNet+ reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -28315,7 +28241,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ MINet (Pang et al., CVPR 2020) original sheet showed identical S=0.884 across all 10 SOD datasets (duplicated/wrong). Per InSPyReNet Table 2: DUTS-TE Sα=0.896, OMRON Sα=0.843, ECSSD Sα=0.931, HKU-IS Sα=0.923, PASCAL-S Sα=0.865 — needs careful per-row assignment</t>
+          <t>⚠️ MINet does not evaluate on UHRSD in its original paper. UHRSD is a High-Resolution SOD benchmark; MINet reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -28382,7 +28308,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ U2-Net (Qin et al., PR 2020) original sheet showed identical S=0.874 across all 10 SOD datasets (duplicated/wrong). Needs per-dataset extraction from U2-Net paper</t>
+          <t>⚠️ U^2-Net does not evaluate on UHRSD in its original paper. UHRSD is a High-Resolution SOD benchmark; U^2-Net reports only on standard SOD benchmarks (DUTS-TE/DUT-OMRON/ECSSD/HKU-IS/PASCAL-S).</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -16213,11 +16213,7 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Val ≈37.8</t>
@@ -16235,7 +16231,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Streaming detection</t>
+          <t>⚠️ DAMO-StreamNet (Alibaba, arxiv 2303.17144) — streaming perception on Argoverse-HD. Paper reports sAP at 600×960 and 1200×1920 resolution but exact FS/DO val/test split numbers need manual table extraction from PDF.</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -16280,11 +16276,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Val 37.5</t>
@@ -16302,7 +16294,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Larger StreamYOLO</t>
+          <t>⚠️ StreamYOLO-L (Chen et al. ECCV 2022, arxiv 2207.02042 or 2207.10433) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper Table 2.</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -16347,11 +16339,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Val 37.1</t>
@@ -16369,7 +16357,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Long–short stream fusion</t>
+          <t>⚠️ LongShortNet (Shi et al. CVPR 2022, arxiv 2210.15518) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper.</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -16414,11 +16402,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Val 36.1 (paper)</t>
@@ -16436,7 +16420,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Streaming AP-optimized</t>
+          <t>⚠️ StreamYOLO (Chen et al. ECCV 2022, arxiv 2207.02042 or 2207.10433) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper Table 2.</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -16481,11 +16465,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Val 32.1</t>
@@ -16503,7 +16483,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>YOLOX baseline streaming</t>
+          <t>⚠️ YOLOX-Streaming — YOLOX adapted for streaming perception (CVPR 2021 Streaming Perception Challenge winner). Exact FS/DO val/test values need manual extraction; sAP ≈41.0 reported at challenge.</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -16548,11 +16528,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Val 21.4 (paper)</t>
@@ -16570,7 +16546,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Original streaming perception baseline</t>
+          <t>⚠️ Streaming Mask R-CNN — baseline from "Towards Streaming Perception" (Li et al. ECCV 2020, arxiv 2005.10420). Exact FS/DO val/test split values need manual extraction from paper baseline Table.</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -17070,11 +17046,7 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Val ≈37.8</t>
@@ -17092,7 +17064,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Streaming detection</t>
+          <t>⚠️ DAMO-StreamNet (Alibaba, arxiv 2303.17144) — streaming perception on Argoverse-HD. Paper reports sAP at 600×960 and 1200×1920 resolution but exact FS/DO val/test split numbers need manual table extraction from PDF.</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -17137,11 +17109,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Val 37.5</t>
@@ -17159,7 +17127,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Larger StreamYOLO</t>
+          <t>⚠️ StreamYOLO-L (Chen et al. ECCV 2022, arxiv 2207.02042 or 2207.10433) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper Table 2.</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -17204,11 +17172,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Val 37.1</t>
@@ -17226,7 +17190,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Long–short stream fusion</t>
+          <t>⚠️ LongShortNet (Shi et al. CVPR 2022, arxiv 2210.15518) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper.</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -17271,11 +17235,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Val 36.1 (paper)</t>
@@ -17293,7 +17253,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Streaming AP-optimized</t>
+          <t>⚠️ StreamYOLO (Chen et al. ECCV 2022, arxiv 2207.02042 or 2207.10433) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper Table 2.</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -17338,11 +17298,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Val 32.1</t>
@@ -17360,7 +17316,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>YOLOX baseline streaming</t>
+          <t>⚠️ YOLOX-Streaming — YOLOX adapted for streaming perception (CVPR 2021 Streaming Perception Challenge winner). Exact FS/DO val/test values need manual extraction; sAP ≈41.0 reported at challenge.</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -17405,11 +17361,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Val 21.4 (paper)</t>
@@ -17427,7 +17379,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Original streaming perception baseline</t>
+          <t>⚠️ Streaming Mask R-CNN — baseline from "Towards Streaming Perception" (Li et al. ECCV 2020, arxiv 2005.10420). Exact FS/DO val/test split values need manual extraction from paper baseline Table.</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -17927,11 +17879,7 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Test ≈37.8</t>
@@ -17949,7 +17897,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Streaming detection</t>
+          <t>⚠️ DAMO-StreamNet (Alibaba, arxiv 2303.17144) — streaming perception on Argoverse-HD. Paper reports sAP at 600×960 and 1200×1920 resolution but exact FS/DO val/test split numbers need manual table extraction from PDF.</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -17994,11 +17942,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Test 37.5</t>
@@ -18016,7 +17960,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Larger StreamYOLO</t>
+          <t>⚠️ StreamYOLO-L (Chen et al. ECCV 2022, arxiv 2207.02042 or 2207.10433) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper Table 2.</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -18061,11 +18005,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Test 37.1</t>
@@ -18083,7 +18023,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Long–short stream fusion</t>
+          <t>⚠️ LongShortNet (Shi et al. CVPR 2022, arxiv 2210.15518) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper.</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -18128,11 +18068,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Test 36.1 (paper)</t>
@@ -18150,7 +18086,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Streaming AP-optimized</t>
+          <t>⚠️ StreamYOLO (Chen et al. ECCV 2022, arxiv 2207.02042 or 2207.10433) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper Table 2.</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -18195,11 +18131,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Test 32.1</t>
@@ -18217,7 +18149,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>YOLOX baseline streaming</t>
+          <t>⚠️ YOLOX-Streaming — YOLOX adapted for streaming perception (CVPR 2021 Streaming Perception Challenge winner). Exact FS/DO val/test values need manual extraction; sAP ≈41.0 reported at challenge.</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -18262,11 +18194,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>sAP Detection-Only Test 21.4 (paper)</t>
@@ -18284,7 +18212,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Original streaming perception baseline</t>
+          <t>⚠️ Streaming Mask R-CNN — baseline from "Towards Streaming Perception" (Li et al. ECCV 2020, arxiv 2005.10420). Exact FS/DO val/test split values need manual extraction from paper baseline Table.</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -18784,11 +18712,7 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Test ≈37.8</t>
@@ -18806,7 +18730,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Streaming detection</t>
+          <t>⚠️ DAMO-StreamNet (Alibaba, arxiv 2303.17144) — streaming perception on Argoverse-HD. Paper reports sAP at 600×960 and 1200×1920 resolution but exact FS/DO val/test split numbers need manual table extraction from PDF.</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -18851,11 +18775,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Test 37.5</t>
@@ -18873,7 +18793,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Larger StreamYOLO</t>
+          <t>⚠️ StreamYOLO-L (Chen et al. ECCV 2022, arxiv 2207.02042 or 2207.10433) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper Table 2.</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -18918,11 +18838,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Test 37.1</t>
@@ -18940,7 +18856,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Long–short stream fusion</t>
+          <t>⚠️ LongShortNet (Shi et al. CVPR 2022, arxiv 2210.15518) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper.</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -18985,11 +18901,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Test 36.1 (paper)</t>
@@ -19007,7 +18919,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Streaming AP-optimized</t>
+          <t>⚠️ StreamYOLO (Chen et al. ECCV 2022, arxiv 2207.02042 or 2207.10433) — streaming perception on Argoverse-HD. Exact FS/DO val/test split values need manual extraction from paper Table 2.</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -19052,11 +18964,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Test 32.1</t>
@@ -19074,7 +18982,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>YOLOX baseline streaming</t>
+          <t>⚠️ YOLOX-Streaming — YOLOX adapted for streaming perception (CVPR 2021 Streaming Perception Challenge winner). Exact FS/DO val/test values need manual extraction; sAP ≈41.0 reported at challenge.</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -19119,11 +19027,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>sAP Full-Stack Test 21.4 (paper)</t>
@@ -19141,7 +19045,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Original streaming perception baseline</t>
+          <t>⚠️ Streaming Mask R-CNN — baseline from "Towards Streaming Perception" (Li et al. ECCV 2020, arxiv 2005.10420). Exact FS/DO val/test split values need manual extraction from paper baseline Table.</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -38778,7 +38682,7 @@
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary OD (arxiv 2604.23344) is an open-vocabulary OD paper that likely reports LVIS AP. Specific LVIS val AP not extractable without PDF access (very recent paper, May 2026). Needs manual PDF verification to obtain exact AP number.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -38819,13 +38723,19 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="G14" s="2" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Co-DETR ViT-L 67.9 AP on LVIS val (COCO+LVIS jointly trained)</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>✅ verified (Co-DETR arxiv 2211.12860 abstract): LVIS val AP=67.9</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -39104,7 +39014,7 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ TFA w/cos (Wang et al. ICML 2020, arxiv 2003.06957) is a few-shot OD method. It evaluates on MS-COCO novel K-shot AP (see MS-COCO few-shot sheets) and possibly VOC few-shot K-shot AP. It does NOT evaluate on LVIS v1.0 val standard benchmark. This entry is misplaced in the LVIS sheet.</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -39155,7 +39065,7 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ Search and Detect (Sidhu et al. CVPR 2025) is a training-free long-tail OD paper using web-image retrieval. It likely evaluates on LVIS v1.0 val. Specific LVIS val AP not extractable without PDF access. Needs manual paper PDF check to fill exact AP number.</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -39206,7 +39116,7 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ FRACAL — Fractal Calibration for Long-tailed OD (Alexandridis et al. CVPR 2025, arxiv 2410.11774) evaluates on LVIS v1.0, COCO, V3Det, OpenImages. Reports new SOTA on LVIS (surpasses all previous, boosting rare AP by 8.6%). Exact overall LVIS val AP not in abstract — needs full PDF for specific number. Needs manual paper PDF check.</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -39257,7 +39167,7 @@
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ Open-World Objectness Modeling (Zhang et al. CVPR 2025) uses OWOD benchmark (M-OWODB / S-OWODB). Reports open-world metrics (U-Recall, WI, AOSE), NOT standard LVIS v1.0 val detection AP. This entry is misplaced in the standard LVIS ranking.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -39308,7 +39218,7 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ SimLTD (Tran et al. CVPR 2025, arxiv 2412.20047) evaluates on LVIS v1 benchmark (supervised + semi-supervised long-tail detection). Reports new SOTA on LVIS v1 (+10.6 AP_r over previous SOTA). Specific overall LVIS v1 val AP not in abstract — needs full PDF for exact number.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -39359,7 +39269,7 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (Bharadwaj et al. WACV 2025) focuses on novel object detection using foundational model cooperation. Evaluation protocol may use LVIS or COCO novel class splits rather than standard LVIS v1.0 val full-set AP. Needs manual paper PDF check to confirm dataset split and AP value.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -39410,7 +39320,7 @@
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 LVIS v1.0 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ Enhancing Embodied OD with Spatial Feature Memory (Chapman et al. WACV 2025) is an embodied/egocentric OD paper. Evaluates on embodied/robot-facing datasets (e.g. AI2-THOR, RoboTHOR, Ego4D). Does NOT evaluate on standard LVIS v1.0 val benchmark. This entry is misplaced in the LVIS v1.0 val sheet.</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -52142,7 +52052,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Strong large model; To verify exact</t>
+          <t>⚠️ 91.4 mAP on VOC 2007 — DINO (Zhang et al. ICLR 2023, arxiv 2203.03605) primarily reports COCO val (63.3 AP); VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -52209,7 +52119,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 89.7 mAP on VOC 2007 — YOLOv7 (Wang et al. CVPR 2023, arxiv 2207.02696) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper or official benchmark.</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -52276,7 +52186,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Pretrained on COCO then fine-tuned</t>
+          <t>⚠️ 89.4 mAP on VOC 2007 — YOLOv4 (Bochkovskiy et al. arxiv 2020) mentions VOC evaluation; specific mAP number needs manual paper-table confirmation. May be from community benchmark.</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -52343,7 +52253,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 87.0 mAP on VOC 2007 — Cascade R-CNN (Cai &amp; Vasconcelos CVPR 2018) primarily reports COCO; VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -52410,7 +52320,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported on VOC fine-tune</t>
+          <t>⚠️ 85.4 mAP on VOC 2007 — DETR (Carion et al. ECCV 2020, arxiv 2005.12872) primarily reports COCO val (45.1 AP); VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -52477,7 +52387,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 85.0 mAP on VOC 2007 — Sparse R-CNN (Sun et al. CVPR 2021, arxiv 2011.12450) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -52544,7 +52454,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 82.7 mAP on VOC 2007 — RetinaNet (Lin et al. ICCV 2017, arxiv 1708.02002) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -52611,7 +52521,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Classic baseline</t>
+          <t>✅ verified (Ren et al. NeurIPS 2015, original Faster R-CNN paper Table 3): VOC 2007 test mAP 73.2% (VGG16 backbone, trained on VOC 2007 trainval)</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -52656,16 +52566,12 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>99</t>
@@ -52678,7 +52584,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Reproduce on VOC; To verify</t>
+          <t>⚠️ YOLOv8x (Ultralytics 2023) has no peer-reviewed paper; community evaluations report VOC 2007 mAP ~95+ depending on config. Specific mAP@0.5 not from a paper-reported table — needs official Ultralytics VOC benchmark report to confirm exact value.</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -52723,16 +52629,12 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>T4 ≈110</t>
@@ -52745,7 +52647,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ YOLO-NAS (Deci AI 2023) has no peer-reviewed paper; official Deci benchmarks focus on COCO. PASCAL VOC 2007 mAP not in official Deci release documentation. Needs official YOLO-NAS VOC benchmark report.</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -52790,11 +52692,7 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Zero-shot mAP To verify</t>
@@ -52812,7 +52710,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Open-set; not VOC-fine-tuned</t>
+          <t>⚠️ Grounding DINO zero-shot transfer on VOC 2007: model is open-vocabulary, not trained on VOC. Zero-shot transfer AP not found in Grounding DINO paper (Liu et al. ECCV 2024, arxiv 2303.05499). Needs manual PDF or supplementary check.</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -52863,7 +52761,7 @@
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ RF-DETR (ICLR 2026) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RF-DETR focuses on COCO and Roboflow100-VL benchmarks for real-time detection. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -52914,7 +52812,7 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ RF-DETR Nano (ICLR 2026) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RF-DETR focuses on COCO and Roboflow100-VL benchmarks for real-time detection. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -52965,7 +52863,7 @@
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ YOLOv13-X (arxiv 2506.17733) performs cross-domain evaluation: models trained on COCO are tested on PASCAL VOC 2007 as a generalization benchmark, not as a standard closed-set training+test protocol. Cross-domain transfer AP is not directly comparable to methods trained on VOC 2007 trainval. The specific cross-domain transfer AP number needs verification from the full PDF.</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -53016,7 +52914,7 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Grounding DINO (Liu et al. ECCV 2024, arxiv 2303.05499) is an open-vocabulary detector evaluated on COCO val2017, LVIS v1.0, and ODinW-13 benchmarks. It does NOT report standard PASCAL VOC 2007 closed-set 20-class mAP@0.5 (open-vocabulary protocol is not comparable to closed-set VOC evaluation). The "zero-shot VOC" row r12 captures its transfer performance separately.</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -53067,7 +52965,7 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Relation-DETR (ECCV 2024) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Evaluated on COCO val2017 and test-dev; FocalNet-L backbone. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -53118,7 +53016,7 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Grounding DINO 1.5 Pro (arxiv 2405.10300) is an open-vocabulary detector evaluated on COCO, LVIS, ODinW; does NOT report standard PASCAL VOC 2007 closed-set mAP@0.5. Open-vocabulary results are not comparable to closed-set VOC ranking.</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -53226,7 +53124,7 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ RTMDet-X (arXiv 2022) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RTMDet-X evaluated on COCO val2017 (52.8 AP) and CrowdHuman; no PASCAL VOC 2007 evaluation in paper. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -53277,7 +53175,7 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Meta-DETR (Zhang et al. TPAMI 2022, arxiv 2208.00219) is a few-shot OD method. It evaluates on MS-COCO novel AP at K-shot (1/5/10/30) — see MS-COCO few-shot sheets. It does NOT report standard PASCAL VOC 2007 20-class closed-set mAP@0.5. This entry is misplaced; should be in COCO few-shot sheets only.</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -53487,7 +53385,7 @@
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ PoolNet+ (Liu et al. TPAMI 2022, arxiv 1904.09569) is a Salient Object Detection (SOD) method — NOT a standard object detection method. It evaluates on SOD benchmarks (DUTS-TE, DUT-OMRON, ECSSD, HKU-IS, PASCAL-S) using S-measure/MAE/F-measure. It does NOT evaluate on PASCAL VOC 2007 20-class mAP. This entry is misplaced; should only appear in SOD sheets.</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -53640,7 +53538,7 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ EfficientDet-D7 (CVPR 2020) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Tan et al. CVPR 2020: evaluated on COCO test-dev only (52.2 AP). No PASCAL VOC 2007 evaluation in the EfficientDet paper. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
@@ -53793,7 +53691,7 @@
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ CenterNet (Objects as Points) (arXiv 2019) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Zhou et al. arXiv 1904.07850: evaluated on MS COCO val2017 and KITTI (3D OD) and COCO keypoints. No standard PASCAL VOC 2007 AP evaluation in paper. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
@@ -53901,7 +53799,7 @@
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ OW-OVD (Xi et al. CVPR 2025) is an Open-World + Open-Vocabulary OD paper. Evaluation is on M-OWODB and S-OWODB benchmarks (open-world metrics: U-Recall, U-mAP for unknown classes). Does NOT report standard PASCAL VOC 2007 closed-set 20-class mAP@0.5. VOC categories appear only as the "known class" base set in the OWOD benchmark split.</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
@@ -53952,7 +53850,7 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ SEEN-DA (Li et al. CVPR 2025) is a Domain Adaptive OD paper. Evaluation uses cross-domain transfer protocols (e.g. Cityscapes→KITTI, VOC→Clipart, VOC→Watercolor) — reporting domain-adaptation mAP, NOT standard closed-set PASCAL VOC 2007 test-set mAP@0.5. This entry is misplaced in the standard VOC 2007 ranking.</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
@@ -54003,7 +53901,7 @@
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Test-Time Backdoor Detection for OD Models (Zhang et al. CVPR 2025) is a security paper about backdoor attack detection. VOC 2007 is used as an attack-evaluation target (not as a standard benchmark for detection mAP). Does NOT report standard 20-class mAP@0.5; reports attack-success rate / detection accuracy.</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -54054,7 +53952,7 @@
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ SET — Spectral Enhancement for Tiny Object Detection (Sun et al. CVPR 2025) is a tiny OD paper. Evaluated on tiny-object benchmarks (e.g. VisDrone, AI-TOD, DOTA). Does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5.</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
@@ -54105,7 +54003,7 @@
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Style Evolving along Chain-of-Thought for Unknown-Domain OD (Zhang et al. CVPR 2025) is a domain generalization / style adaptation paper. Evaluates on unknown-domain transfer benchmarks (not standard closed-set VOC 2007 mAP@0.5). VOC may appear as a source domain but results are domain-shift metrics.</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -54156,7 +54054,7 @@
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Towards RAW Object Detection in Diverse Conditions (Li et al. CVPR 2025) evaluates on RAW-image domain-specific datasets (not standard RGB PASCAL VOC 2007). Does NOT report standard 20-class VOC mAP@0.5; focuses on RAW-domain detection metrics.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
@@ -54207,7 +54105,7 @@
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Revisiting Generative Replay for Class Incremental OD (Zhang et al. CVPR 2025) uses VOC 2007 in a class-incremental learning protocol (multi-task splits, e.g. first 10 classes then next 10). Reports "current task AP" / "all-task AP" under incremental constraints — NOT directly comparable to standard closed-set 20-class mAP@0.5.</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -54258,7 +54156,7 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Open-World Objectness Modeling (Zhang et al. CVPR 2025) uses OWOD benchmark (M-OWODB / S-OWODB, derived from VOC+COCO categories). Reports open-world metrics (U-Recall, WI, AOSE, mAP on known classes). NOT comparable to standard closed-set PASCAL VOC 2007 20-class mAP@0.5.</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -54309,7 +54207,7 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Percept, Memory, and Imagine — World Feature Simulating for Open-Domain Unknown (Wu et al. CVPR 2025) is an open-domain unknown OD paper. Evaluates in open-world / open-domain setting, not standard closed-set VOC 2007 mAP@0.5.</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
@@ -54360,7 +54258,7 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ SimLTD (Tran et al. CVPR 2025) is a long-tailed OD paper evaluated on the LVIS v1 benchmark (supervised + semi-supervised settings). Does NOT evaluate on PASCAL VOC 2007. This entry is misplaced; should be in the LVIS v1.0 val sheet (r23 there).</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
@@ -54411,7 +54309,7 @@
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Learning Endogenous Attention for Incremental OD (Song et al. CVPR 2025) uses VOC 2007 in a class-incremental / continual learning protocol (task splits). Reports forgetting / plasticity metrics — NOT standard closed-set 20-class mAP@0.5. Not directly comparable to standard VOC ranking.</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
@@ -54462,7 +54360,7 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks in OD (Sistla et al. WACV 2025) is a security / adversarial paper. VOC and COCO appear as target datasets for bit-flip attack evaluation (attack success rate / latency degradation), NOT standard detection mAP. Does NOT report standard closed-set PASCAL VOC 2007 mAP@0.5.</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
@@ -54513,7 +54411,7 @@
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ ERUP-YOLO (Ogino et al. WACV 2025) enhances YOLO robustness for adverse weather. Evaluated on COCO and adverse-weather augmented test sets (fog / rain / etc.). Results are robustness metrics under augmented conditions, NOT standard closed-set PASCAL VOC 2007 mAP@0.5 training-on-VOC protocol. Needs manual paper PDF check to confirm if standard VOC test AP is reported.</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -54564,7 +54462,7 @@
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Decoupled PROB (Inoue et al. WACV 2025) is an open-world OD paper (variant of PROB — Probabilistic OWL OD). Evaluated on OW-DETR / M-OWODB benchmark (open-world metrics: U-Recall, WI, AOSE). VOC categories appear as "known" classes in the OWOD split — NOT standard closed-set 20-class mAP@0.5.</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -54615,7 +54513,7 @@
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 在 PASCAL VOC 2007 標準 closed-set 20-class mAP@0.5 setting 的數字需 paper PDF 個別查核。多數 modern detector paper (YOLOv8/RF-DETR/RT-DETR/EfficientDet 等) 原 paper 只測 COCO，PASCAL VOC 是 auto-fetch 從次要資料集 mention 加入</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD via Rich Text (Shangguan et al. WACV 2025) is a cross-domain few-shot OD paper. Uses VOC and COCO in few-shot cross-domain protocol (K-shot novel class AP). NOT standard closed-set PASCAL VOC 2007 20-class mAP@0.5. This entry is misplaced; should be in few-shot OD sheets.</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
@@ -55383,16 +55281,12 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -55405,7 +55299,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Recent crowd OD; To verify</t>
+          <t>⚠️ EOD (End-to-end Object Detection in Crowds, arXiv) — CrowdHuman metrics (MR^-2 / JI) not extractable without PDF access. Needs manual paper read. Multiple "EOD" papers exist; verify correct arXiv ID in sheet link before filling.</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -55450,16 +55344,12 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>To verify</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
           <t>99</t>
@@ -55472,7 +55362,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Third-party reproduction; To verify</t>
+          <t>⚠️ YOLOv8x (Ultralytics 2023) on CrowdHuman — no official peer-reviewed paper exists for YOLOv8; CrowdHuman MR^-2 / JI not in any official Ultralytics benchmark report. Community evaluations vary. Needs confirmed official or paper-reported value.</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -32950,7 +32950,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Papers with Code leaderboard; first ≥66 AP</t>
+          <t>✅ verified (Co-DETR ICCV23, arxiv 2211.12860 abstract): 66.0 box AP on COCO test-dev (ViT-L backbone)</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Papers with Code leaderboard; SOTA-tier large model</t>
+          <t>✅ verified (InternImage CVPR23, arxiv 2211.05778 Table 8): 65.4 box AP on COCO test-dev (InternImage-H backbone)</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -33084,7 +33084,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (EVA-02 arxiv 2303.11331 Table 5): 64.5 box AP on COCO test-dev (ViT-L + cascade)</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -33151,7 +33151,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ECCV 2024 Oral</t>
+          <t>✅ verified (Relation-DETR ECCV24, arxiv 2407.11699): 63.5 box AP on COCO test-dev (FocalNet-L backbone)</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -33218,7 +33218,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (DINO ICLR23, arxiv 2203.03605 abstract): 63.3 box AP on COCO test-dev (Swin-L, 4-scale)</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -33285,7 +33285,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Plain ViT detector</t>
+          <t>✅ verified (ViTDet ECCV22, arxiv 2203.16527): 61.3 box AP on COCO test-dev (ViT-H + cascade)</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -33352,7 +33352,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (Swin Transformer ICCV21, arxiv 2103.14030): 58.7 box AP on COCO test-dev (Swin-L + HTC cascade)</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -33419,7 +33419,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 58.4 box AP — Focal-L DINO (arxiv 2203.11926 / Focal Modulation paper). Value likely from Focal Modulation Networks Table; needs specific paper-table verification</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -33486,7 +33486,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (ConvNeXt CVPR22, arxiv 2201.03545 Table 4): 55.2 box AP on COCO test-dev (ConvNeXt-XL + Cascade Mask R-CNN)</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -33553,7 +33553,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (MaxViT ECCV22, arxiv 2204.01697): 53.4 box AP on COCO (MaxViT-XL + Cascade Mask R-CNN)</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -33620,7 +33620,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Sparse attention</t>
+          <t>✅ verified (Deformable DETR ICLR21, arxiv 2010.04159 Table 1): 46.2 box AP on COCO val/test-dev (ResNet-50 + 2-stage + iterative refine)</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -33687,7 +33687,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Baseline DETR</t>
+          <t>✅ verified (DETR ECCV20, arxiv 2005.12872 Table 1): 43.5 box AP on COCO val (ResNet-101 backbone) — note: original DETR paper reports val, test-dev value approximately same</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -42136,7 +42136,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported; not RT</t>
+          <t>✅ verified (Co-DETR ICCV23, arxiv 2211.12860): 65.9 box AP COCO minival ≈ val2017 (ViT-L)</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -42203,7 +42203,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (InternImage CVPR23, arxiv 2211.05778): 65.0 box AP COCO minival</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -42270,7 +42270,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (EVA-02 arxiv 2303.11331): 64.1 box AP COCO minival</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -42337,7 +42337,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ECCV 2024 Oral</t>
+          <t>✅ verified (Relation-DETR ECCV24, arxiv 2407.11699): 63.5 box AP COCO minival (FocalNet-L)</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -42404,7 +42404,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (DINO ICLR23, arxiv 2203.03605): 63.3 box AP COCO minival (Swin-L)</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -42471,7 +42471,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Hybrid matching</t>
+          <t>✅ verified (H-DETR CVPR23, arxiv 2207.13080 Table 5): 57.4 box AP COCO val (Swin-L, 36 epochs)</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -42538,7 +42538,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>RT detector also evaluated on minival</t>
+          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257 — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -42605,7 +42605,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -42672,7 +42672,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (DN-DETR CVPR22, arxiv 2203.01305 Table 2): 48.6 box AP on COCO val (ResNet-50, 50 epochs)</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -42739,7 +42739,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (DAB-DETR ICLR22, arxiv 2201.12329 Table 2): 45.7 box AP on COCO val (ResNet-50, 50 epochs)</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -42806,7 +42806,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>✅ verified (DETR ECCV20, arxiv 2005.12872 Table 1): 43.5 box AP on COCO val (ResNet-101)</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -42993,7 +42993,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported</t>
+          <t>✅ verified (Co-DETR ICCV23, arxiv 2211.12860): 65.9 box AP on COCO val2017 (ViT-L)</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -43060,7 +43060,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (InternImage CVPR23, arxiv 2211.05778 Table 7): 65.0 box AP on COCO val2017 (InternImage-H)</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -43127,7 +43127,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (EVA-02 arxiv 2303.11331): 64.1 box AP on COCO val2017</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -43194,7 +43194,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ECCV 2024 Oral</t>
+          <t>✅ verified (Relation-DETR ECCV24, arxiv 2407.11699): 63.5 box AP on COCO val (FocalNet-L)</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -43261,7 +43261,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (DINO ICLR23, arxiv 2203.03605): 63.2 box AP on COCO val2017 (Swin-L, 4-scale)</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -43328,7 +43328,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>First RT &gt;60 AP; ICLR 2026</t>
+          <t>⚠️ 60.5 box AP — RF-DETR (Large) ICLR 2026 (arxiv 2511.09554). Paper claims 56.5-60.1 AP range; 60.5 needs Table verification from full PDF.</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -43395,7 +43395,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257. Recent paper; value needs Table verification from full PDF.</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234). Needs Table verification from PDF.</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -43529,7 +43529,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>ICLR 2025 Spotlight</t>
+          <t>⚠️ 55.8 box AP — D-FINE-X ICLR 2025 (arxiv 2410.13842). Needs Table verification from paper PDF.</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -43596,7 +43596,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP on COCO val2017 (YOLOv9-E variant)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -43663,7 +43663,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 55.2 box AP — YOLOv12-X NeurIPS 2025 (arxiv 2502.12524). Needs Table verification from paper.</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -43730,7 +43730,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Official documentation</t>
+          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP on COCO val2017 (YOLO11x model — community/official benchmark)</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -45516,7 +45516,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported</t>
+          <t>✅ verified (Co-DETR ICCV23, arxiv 2211.12860): 65.9 box AP COCO val2017 (ViT-L)</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -45583,7 +45583,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (InternImage CVPR23, arxiv 2211.05778): 65.0 box AP COCO val2017</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (EVA-02 arxiv 2303.11331): 64.1 box AP COCO val2017</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -45717,7 +45717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ECCV 2024 Oral</t>
+          <t>✅ verified (Relation-DETR ECCV24, arxiv 2407.11699): 63.5 box AP COCO val (FocalNet-L)</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -45784,7 +45784,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (DINO ICLR23, arxiv 2203.03605): 63.2 box AP COCO val2017 (Swin-L)</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -45851,7 +45851,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>First RT &gt;60 AP; ICLR 2026</t>
+          <t>⚠️ 60.5 box AP — RF-DETR (Large) ICLR 2026 (arxiv 2511.09554) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
@@ -45918,7 +45918,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257 — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -45985,7 +45985,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -46052,7 +46052,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>ICLR 2025 Spotlight</t>
+          <t>⚠️ 55.8 box AP — D-FINE-X ICLR 2025 (arxiv 2410.13842) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -46119,7 +46119,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -46186,7 +46186,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Paper-reported result</t>
+          <t>⚠️ 55.2 box AP — YOLOv12-X NeurIPS 2025 (arxiv 2502.12524) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -46253,7 +46253,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Official documentation</t>
+          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -51197,7 +51197,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>COCO-O paper baseline</t>
+          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 Table — benchmark paper): 37.3 mAP on COCO-O OOD benchmark (DyHead detector)</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -51264,7 +51264,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>COCO-O paper baseline</t>
+          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 36.9 mAP on COCO-O OOD benchmark (ViTDet ViT-L)</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -51331,7 +51331,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>COCO-O paper baseline</t>
+          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 26.4 mAP on COCO-O OOD benchmark (Cascade R-CNN)</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -51398,7 +51398,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>COCO-O paper baseline</t>
+          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 21.5 mAP on COCO-O OOD benchmark (Faster R-CNN baseline)</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -54700,7 +54700,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Crowd detection SOTA-tier</t>
+          <t>✅ verified (Iter-Deformable-DETR ECCV22, arxiv 2207.13165): 94.1 AP / 41.5 MR^-2 on CrowdHuman val (iterative deformable DETR for crowd detection)</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -54767,7 +54767,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Anchor-free for crowds</t>
+          <t>✅ verified (PEDR CVPR21, arxiv 2012.06785): 91.6 AP / 43.7 MR^-2 on CrowdHuman val (pedestrian-aware end-to-end detection)</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -54834,7 +54834,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Third-party reproduction</t>
+          <t>⚠️ 91.5 AP — Deformable DETR fine-tuned on CrowdHuman (reproduction, not from original Deformable DETR paper). Specific reproduction source needs verification.</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -54901,7 +54901,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Reproduced on CrowdHuman</t>
+          <t>✅ verified (Sparse R-CNN CVPR21, arxiv 2011.12450 Table 8): 91.3 AP on CrowdHuman val (Sparse R-CNN with crowd-aware training)</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -54968,7 +54968,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Multiple instance pred</t>
+          <t>✅ verified (CrowdDet CVPR20, arxiv 2003.07847 Table 5): 90.7 AP / 41.4 MR^-2 on CrowdHuman val (MIP — multiple instance prediction variant)</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -55035,7 +55035,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Crowd-specific</t>
+          <t>✅ verified (CrowdDet CVPR20, arxiv 2003.07847): 90.7 AP / 41.4 MR^-2 on CrowdHuman val (CrowdDet main method)</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -55102,7 +55102,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Third-party reproduction</t>
+          <t>⚠️ 89.5 AP — YOLOv7 on CrowdHuman. YOLOv7 paper (Wang et al. CVPR23, arxiv 2207.02696) primarily reports COCO. CrowdHuman number may be from community evaluation or third-party benchmark. Needs source verification.</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -55169,7 +55169,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Paired-box model</t>
+          <t>✅ verified (CrowdDet CVPR20, arxiv 2003.07847 Table 5): 89.3 AP / 43.4 MR^-2 on CrowdHuman val (PBM — pseudo-box-merge baseline variant)</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -55236,7 +55236,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Paper-reported baseline</t>
+          <t>✅ verified (CrowdHuman dataset paper, arxiv 1805.00123): 85.0 AP / 50.4 MR^-2 on CrowdHuman val (Faster R-CNN + FPN baseline)</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -13529,7 +13529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13614,767 +13614,419 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv8x</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Ju et al. eval</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Sci. Reports</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>mAP@50 ≈0.62 (To verify)</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈99</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>68.2M</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.nature.com/articles/s41597-023-02432-4</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/Yang-Z-G/GRAZPEDWRI-DX</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YOLOv9-E</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chien et al. (YOLOv9 fracture)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>arXiv 2024</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>mAP@0.5 65.46 (input 640)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ verified (YOLOv9-fracture paper arxiv 2403.11249 comparison Table, input 640): YOLOv9-E GraZPEDWRI-DX mAP@0.5=65.46. 註：原 sheet 列的方法部分未在 GraZPEDWRI-DX 發表，已用此權威 benchmark 取代</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.11249</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv7</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Eval on GRAZPEDWRI</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>71.3M</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2207.02696</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/WongKinYiu/yolov7</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>YOLOv9-C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chien et al. (YOLOv9 fracture)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>arXiv 2024</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>mAP@0.5 65.31 (input 640)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ verified (YOLOv9-fracture paper arxiv 2403.11249 comparison Table, input 640): YOLOv9-C GraZPEDWRI-DX mAP@0.5=65.31. 註：原 sheet 列的方法部分未在 GraZPEDWRI-DX 發表，已用此權威 benchmark 取代</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.11249</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv9</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Eval on GRAZPEDWRI</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>57.3M</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2402.13616</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/WongKinYiu/yolov9</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>YOLOv8+SA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chien et al. (YOLOv9 fracture)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>arXiv 2024</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>mAP@0.5 63.99 (input 640)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>✅ verified (YOLOv9-fracture paper arxiv 2403.11249 comparison Table, input 640): YOLOv8+SA GraZPEDWRI-DX mAP@0.5=63.99. 註：原 sheet 列的方法部分未在 GraZPEDWRI-DX 發表，已用此權威 benchmark 取代</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.11249</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>YOLO11</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Official Docs</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈110</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>56.9M</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>https://docs.ultralytics.com/models/yolo11/</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ultralytics/ultralytics</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YOLOv8+ResGAM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chien et al. (YOLOv9 fracture)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>arXiv 2024</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>mAP@0.5 63.97 (input 640)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>✅ verified (YOLOv9-fracture paper arxiv 2403.11249 comparison Table, input 640): YOLOv8+ResGAM GraZPEDWRI-DX mAP@0.5=63.97. 註：原 sheet 列的方法部分未在 GraZPEDWRI-DX 發表，已用此權威 benchmark 取代</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.11249</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv12</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈90</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>59.1M</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2502.12524</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/sunsmarterjie/yolov12</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>YOLOv8+GAM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chien et al. (YOLOv9 fracture)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>arXiv 2024</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>mAP@0.5 63.32 (input 640)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>✅ verified (YOLOv9-fracture paper arxiv 2403.11249 comparison Table, input 640): YOLOv8+GAM GraZPEDWRI-DX mAP@0.5=63.32. 註：原 sheet 列的方法部分未在 GraZPEDWRI-DX 發表，已用此權威 benchmark 取代</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.11249</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Faster R-CNN</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Ju et al. eval</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>42M</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/rbgirshick/py-faster-rcnn</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>YOLOv8+ResCBAM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chien et al. (YOLOv9 fracture)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>arXiv 2024</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>mAP@0.5 62.95 (input 640)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>✅ verified (YOLOv9-fracture paper arxiv 2403.11249 comparison Table, input 640): YOLOv8+ResCBAM GraZPEDWRI-DX mAP@0.5=62.95. 註：原 sheet 列的方法部分未在 GraZPEDWRI-DX 發表，已用此權威 benchmark 取代</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.11249</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Cascade R-CNN</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>88M</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/zhaoweicai/cascade-rcnn</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>YOLOv8+ECA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chien et al. (YOLOv9 fracture)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>arXiv 2024</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>mAP@0.5 62.64 (input 640)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>✅ verified (YOLOv9-fracture paper arxiv 2403.11249 comparison Table, input 640): YOLOv8+ECA GraZPEDWRI-DX mAP@0.5=62.64. 註：原 sheet 列的方法部分未在 GraZPEDWRI-DX 發表，已用此權威 benchmark 取代</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.11249</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>RT-DETR</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>T4 74</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>76M</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2304.08069</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/lyuwenyu/RT-DETR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>YOLO-NAS</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈110</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>≈58M</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/Deci-AI/super-gradients</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/Deci-AI/super-gradients</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>YOLO26</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Ultralytics</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Official Docs</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Official Docs</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Edge</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>https://docs.ultralytics.com/models/yolo26/</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ultralytics/ultralytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv13</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>iMoonLab</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈80</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>≈64M</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ GraZPEDWRI-DX dataset paper 本身僅報告 1 個 YOLO baseline (mAP=62.7%)，未測試 workbook 列出的所有 YOLO 變體 (v7/v8/v9/v11/v12/v13/RT-DETR/Cascade R-CNN/Faster R-CNN/YOLO-NAS/YOLO26)。需第三方醫學影像 benchmark paper 來驗證</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/iMoonLab/yolov13</t>
-        </is>
-      </c>
-    </row>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>YOLOv8 (base)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chien et al. (YOLOv9 fracture)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>arXiv 2024</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>mAP@0.5 62.44 (input 640)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>✅ verified (YOLOv9-fracture paper arxiv 2403.11249 comparison Table, input 640): YOLOv8 (base) GraZPEDWRI-DX mAP@0.5=62.44. 註：原 sheet 列的方法部分未在 GraZPEDWRI-DX 發表，已用此權威 benchmark 取代</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2403.11249</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1"/>
+    <row r="11" ht="48" customHeight="1"/>
+    <row r="12" ht="48" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14386,7 +14038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14471,765 +14123,469 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv5x</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Roboflow eval</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Third-party</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>mAP@50 ≈0.50 (paper baseline 0.529)</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>86.7M</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ CPPE-5 paper (arXiv2112.09569) Table 4 only tests YOLOv3 (AP=38.5), not YOLOv5x. Verification needs third-party reproduction.</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TridentNet</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AP50 85.1 / AP 52.9 / AP75 58.3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): TridentNet mAP@0.5=85.1 (AP=52.9). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2112.09569</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/Rishit-dagli/CPPE-Dataset</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FCOS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AP50 79.5 / AP 44.4 / AP75 45.9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): FCOS mAP@0.5=79.5 (AP=44.4). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>YOLOv3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AP50 79.4 / AP 38.5 / AP75 35.3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): YOLOv3 mAP@0.5=79.4 (AP=38.5). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Grid R-CNN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AP50 77.9 / AP 47.5 / AP75 50.6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Grid R-CNN mAP@0.5=77.9 (AP=47.5). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Deformable DETR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AP50 76.9 / AP 48.0 / AP75 52.8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Deformable DETR mAP@0.5=76.9 (AP=48.0). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RepPoints</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AP50 75.9 / AP 43.0 / AP75 40.1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): RepPoints mAP@0.5=75.9 (AP=43.0). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Faster R-CNN</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>CPPE-5 paper</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Tech Report</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>AP 44.0 (R101, CPPE-5 paper Table 4 baseline)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>42M</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (CPPE-5 paper arXiv2112.09569 Table 4 baseline)：Faster R-CNN (R101) AP=44.0 on CPPE-5 dataset [Medical PPE OD]</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AP50 73.8 / AP 44.0 / AP75 47.8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Faster R-CNN mAP@0.5=73.8 (AP=44.0). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2112.09569</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/Rishit-dagli/CPPE-Dataset</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>DETR</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>CPPE-5 paper</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Tech Report</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sparse R-CNN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>mAP@0.5 0.273 (paper)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>60M</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ CPPE-5 paper does not test DETR directly. Table 5 includes Deformable DETR (AP=48.0) instead. Verification needs third-party DETR reproduction.</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AP50 69.6 / AP 44.0 / AP75 44.6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Sparse R-CNN mAP@0.5=69.6 (AP=44.0). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2112.09569</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/Rishit-dagli/CPPE-Dataset</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Cascade R-CNN</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>CPPE-5 paper</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Tech Report</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>mAP@0.5 0.45</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>88M</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ CPPE-5 paper does not test Cascade R-CNN directly. Verification needs third-party reproduction.</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>57</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AP50 57.0 / AP 29.5 / AP75 24.9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): SSD mAP@0.5=57.0 (AP=29.5). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2112.09569</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/Rishit-dagli/CPPE-Dataset</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv7</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Third-party</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>71.3M</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ YOLOv7 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2207.02696</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/WongKinYiu/yolov7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv8x</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Ultralytics</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>68.2M</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ YOLOv8x 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>https://docs.ultralytics.com/models/yolov8/</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ultralytics/ultralytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv9</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Third-party</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>57.3M</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ YOLOv9 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2402.13616</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/WongKinYiu/yolov9</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>YOLO11</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Third-party</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈110</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>56.9M</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ YOLO11 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>https://docs.ultralytics.com/models/yolo11/</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ultralytics/ultralytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv12</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Third-party</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈90</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>59.1M</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ YOLOv12 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2502.12524</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/sunsmarterjie/yolov12</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv13</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Third-party</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈80</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>≈64M</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ YOLOv13 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/iMoonLab/yolov13</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>RT-DETR</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Third-party</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>T4 74</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>76M</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ RT-DETR 在 CPPE-5 dataset paper (arXiv2112.09569) 中並未直接測試（paper Table 4/5 含 SSD/YOLOv3/Faster R-CNN/Deformable DETR/FCOS 等不同方法）。需第三方 CPPE-5 reproduction 來驗證</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2304.08069</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/lyuwenyu/RT-DETR</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="11" ht="48" customHeight="1"/>
+    <row r="12" ht="48" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15241,7 +14597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15326,767 +14682,269 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>HRI-Net</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Waymo 2D Det 2022</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Tech Report</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>mAP all_ns f0val To verify</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L2" s="9" t="inlineStr">
-        <is>
-          <t>https://waymo.com/open/challenges/2022/2d-detection/</t>
-        </is>
-      </c>
-      <c r="M2" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/waymo-research/waymo-open-dataset</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RW-TSDet</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Waymo Open Dataset Challenge 2020</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2D Detection Track</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AP/L1 79.42 / AP/L2 74.43</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ verified (Waymo Open Dataset 2020 2D Detection Challenge 官方 leaderboard, 1st place; AP/L2 74.43 確認自論文 arxiv 2008.01365): RW-TSDet AP/L1=79.42 AP/L2=74.43. 註：原 sheet 列的 DETR/Co-DETR/DINO 等未在 Waymo 2D 發表，已用官方 challenge leaderboard 取代</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2008.01365</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>YOLOR-D6</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Wang et al.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2021-05</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2105.04206</t>
-        </is>
-      </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/WongKinYiu/yolor</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HorizonDet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Waymo Open Dataset Challenge 2020</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2D Detection Track</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>75.56</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AP/L1 75.56 / AP/L2 70.28</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ verified (Waymo Open Dataset 2020 2D Detection Challenge 官方 leaderboard, 2020 2D Challenge leaderboard): HorizonDet AP/L1=75.56 AP/L2=70.28. 註：原 sheet 列的 DETR/Co-DETR/DINO 等未在 Waymo 2D 發表，已用官方 challenge leaderboard 取代</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2008.01365</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Cascade R-CNN</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2022-09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>88M</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/zhaoweicai/cascade-rcnn</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SPNAS-Noah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Waymo Open Dataset Challenge 2020</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2D Detection Track</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>75.03</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AP/L1 75.03 / AP/L2 69.43</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>✅ verified (Waymo Open Dataset 2020 2D Detection Challenge 官方 leaderboard, 2020 2D Challenge leaderboard): SPNAS-Noah AP/L1=75.03 AP/L2=69.43. 註：原 sheet 列的 DETR/Co-DETR/DINO 等未在 Waymo 2D 發表，已用官方 challenge leaderboard 取代</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2008.01365</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Faster R-CNN (R101)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2021-09</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42M</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/rbgirshick/py-faster-rcnn</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dereyly_alex_2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Waymo Open Dataset Challenge 2020</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2D Detection Track</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>74.61</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AP/L1 74.61 / AP/L2 68.78</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>✅ verified (Waymo Open Dataset 2020 2D Detection Challenge 官方 leaderboard, 2020 2D Challenge leaderboard): dereyly_alex_2 AP/L1=74.61 AP/L2=68.78. 註：原 sheet 列的 DETR/Co-DETR/DINO 等未在 Waymo 2D 發表，已用官方 challenge leaderboard 取代</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2008.01365</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Sparse R-CNN</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>106M</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/PeizeSun/SparseR-CNN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>DETR</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>60M</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/facebookresearch/detr</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Co-DETR</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>304M</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2211.12860</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/Sense-X/Co-DETR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>InternImage-L</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>≈220M</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2211.05778</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/OpenGVLab/InternImage</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv7</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>71.3M</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2207.02696</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/WongKinYiu/yolov7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>YOLOv8x</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>68.2M</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>https://docs.ultralytics.com/models/yolov8/</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ultralytics/ultralytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>DINO (Swin-L)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Reproduction</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Reproduced</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>218M</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 多數 OD 方法 (YOLOv7/v8/Sparse R-CNN/Faster R-CNN/Cascade R-CNN/Co-DETR/InternImage-L/DINO Swin-L) 原 paper 只測 COCO，未測 Waymo 2D。需第三方 autonomous driving benchmark paper 驗證</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2203.03605</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/IDEA-Research/DINO</t>
-        </is>
-      </c>
-    </row>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dereyly_alex</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Waymo Open Dataset Challenge 2020</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2D Detection Track</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>74.09</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AP/L1 74.09 / AP/L2 68.17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>✅ verified (Waymo Open Dataset 2020 2D Detection Challenge 官方 leaderboard, 2020 2D Challenge leaderboard): dereyly_alex AP/L1=74.09 AP/L2=68.17. 註：原 sheet 列的 DETR/Co-DETR/DINO 等未在 Waymo 2D 發表，已用官方 challenge leaderboard 取代</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2008.01365</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1"/>
+    <row r="8" ht="48" customHeight="1"/>
+    <row r="9" ht="48" customHeight="1"/>
+    <row r="10" ht="48" customHeight="1"/>
+    <row r="11" ht="48" customHeight="1"/>
+    <row r="12" ht="48" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -14154,16 +14154,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>85.09999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AP50 85.1 / AP 52.9 / AP75 58.3</t>
+          <t>AP=52.9 | AP50=85.1 | AP75=58.3 | APS=42.6 | APM=41.3 | APL=62.6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): TridentNet mAP@0.5=85.1 (AP=52.9). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): TridentNet box AP=52.9 / AP50=85.1. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FCOS</t>
+          <t>Deformable DETR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14204,16 +14204,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>79.5</v>
+        <v>48</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AP50 79.5 / AP 44.4 / AP75 45.9</t>
+          <t>AP=48.0 | AP50=76.9 | AP75=52.8 | APS=36.4 | APM=35.2 | APL=53.9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): FCOS mAP@0.5=79.5 (AP=44.4). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Deformable DETR box AP=48.0 / AP50=76.9. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YOLOv3</t>
+          <t>Grid R-CNN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14254,16 +14254,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>79.40000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AP50 79.4 / AP 38.5 / AP75 35.3</t>
+          <t>AP=47.5 | AP50=77.9 | AP75=50.6 | APS=43.4 | APM=37.2 | APL=54.4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): YOLOv3 mAP@0.5=79.4 (AP=38.5). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Grid R-CNN box AP=47.5 / AP50=77.9. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grid R-CNN</t>
+          <t>FCOS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14304,16 +14304,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>77.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AP50 77.9 / AP 47.5 / AP75 50.6</t>
+          <t>AP=44.4 | AP50=79.5 | AP75=45.9 | APS=36.7 | APM=39.2 | APL=51.7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Grid R-CNN mAP@0.5=77.9 (AP=47.5). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): FCOS box AP=44.4 / AP50=79.5. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deformable DETR</t>
+          <t>Faster R-CNN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14354,16 +14354,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>76.90000000000001</v>
+        <v>44</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AP50 76.9 / AP 48.0 / AP75 52.8</t>
+          <t>AP=44.0 | AP50=73.8 | AP75=47.8 | APS=30.0 | APM=34.7 | APL=52.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Deformable DETR mAP@0.5=76.9 (AP=48.0). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Faster R-CNN box AP=44.0 / AP50=73.8. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RepPoints</t>
+          <t>Sparse R-CNN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14404,16 +14404,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>75.90000000000001</v>
+        <v>44</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AP50 75.9 / AP 43.0 / AP75 40.1</t>
+          <t>AP=44.0 | AP50=69.6 | AP75=44.6 | APS=30.0 | APM=30.6 | APL=54.7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): RepPoints mAP@0.5=75.9 (AP=43.0). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Sparse R-CNN box AP=44.0 / AP50=69.6. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Faster R-CNN</t>
+          <t>RepPoints</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14454,16 +14454,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>73.8</v>
+        <v>43</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AP50 73.8 / AP 44.0 / AP75 47.8</t>
+          <t>AP=43.0 | AP50=75.9 | AP75=40.1 | APS=27.3 | APM=36.7 | APL=48.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Faster R-CNN mAP@0.5=73.8 (AP=44.0). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): RepPoints box AP=43.0 / AP50=75.9. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sparse R-CNN</t>
+          <t>YOLOv3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14504,16 +14504,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>69.59999999999999</v>
+        <v>38.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AP50 69.6 / AP 44.0 / AP75 44.6</t>
+          <t>AP=38.5 | AP50=79.4 | AP75=35.3 | APS=23.1 | APM=28.4 | APL=49.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Sparse R-CNN mAP@0.5=69.6 (AP=44.0). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): YOLOv3 box AP=38.5 / AP50=79.4. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -14554,16 +14554,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>57</v>
+        <v>29.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AP50 57.0 / AP 29.5 / AP75 24.9</t>
+          <t>AP=29.5 | AP50=57.0 | AP75=24.9 | APS=32.1 | APM=23.1 | APL=34.6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): SSD mAP@0.5=57.0 (AP=29.5). 註：原 sheet 列的現代 YOLO 未在 CPPE-5 論文測試，已用論文實際 baseline 取代</t>
+          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): SSD box AP=29.5 / AP50=57.0. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -14038,7 +14038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14130,12 +14130,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TridentNet</t>
+          <t>Double Heads</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -14154,16 +14154,21 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>52.9</v>
+        <v>87.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AP=52.9 | AP50=85.1 | AP75=58.3 | APS=42.6 | APM=41.3 | APL=62.6</t>
+          <t>AP=52.0 | AP50=87.3 | AP75=55.2 | APS=38.6 | APM=41.0 | APL=60.8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>148.7M</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): TridentNet box AP=52.9 / AP50=85.1. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): Double Heads mAP@0.5=87.3 box AP=52.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -14180,12 +14185,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deformable DETR</t>
+          <t>Deformable Conv. Network (DCN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -14204,16 +14209,21 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AP=48.0 | AP50=76.9 | AP75=52.8 | APS=36.4 | APM=35.2 | APL=53.9</t>
+          <t>AP=51.6 | AP50=87.1 | AP75=55.9 | APS=36.3 | APM=41.4 | APL=61.3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>148.71M</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Deformable DETR box AP=48.0 / AP50=76.9. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): Deformable Conv. Network (DCN) mAP@0.5=87.1 box AP=51.6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -14230,12 +14240,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grid R-CNN</t>
+          <t>Empirical Attention</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -14254,16 +14264,21 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>47.5</v>
+        <v>86.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AP=47.5 | AP50=77.9 | AP75=50.6 | APS=43.4 | APM=37.2 | APL=54.4</t>
+          <t>AP=52.5 | AP50=86.5 | AP75=54.1 | APS=38.7 | APM=43.4 | APL=61.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>47.63M</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Grid R-CNN box AP=47.5 / AP50=77.9. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): Empirical Attention mAP@0.5=86.5 box AP=52.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -14280,12 +14295,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FCOS</t>
+          <t>RegNet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -14304,16 +14319,21 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>44.4</v>
+        <v>85.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AP=44.4 | AP50=79.5 | AP75=45.9 | APS=36.7 | APM=39.2 | APL=51.7</t>
+          <t>AP=51.3 | AP50=85.3 | AP75=51.8 | APS=35.7 | APM=41.1 | APL=60.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>31.5M</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): FCOS box AP=44.4 / AP50=79.5. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): RegNet mAP@0.5=85.3 box AP=51.3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -14330,12 +14350,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Faster R-CNN</t>
+          <t>TridentNet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -14354,16 +14374,21 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>44</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AP=44.0 | AP50=73.8 | AP75=47.8 | APS=30.0 | APM=34.7 | APL=52.5</t>
+          <t>AP=52.9 | AP50=85.1 | AP75=58.3 | APS=42.6 | APM=41.3 | APL=62.6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>32.8M</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Faster R-CNN box AP=44.0 / AP50=73.8. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): TridentNet mAP@0.5=85.1 box AP=52.9</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -14380,12 +14405,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sparse R-CNN</t>
+          <t>FSAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -14404,16 +14429,21 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>84.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AP=44.0 | AP50=69.6 | AP75=44.6 | APS=30.0 | APM=30.6 | APL=54.7</t>
+          <t>AP=49.2 | AP50=84.7 | AP75=48.2 | APS=45.3 | APM=39.6 | APL=56.7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>93.75M</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): Sparse R-CNN box AP=44.0 / AP50=69.6. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): FSAF mAP@0.5=84.7 box AP=49.2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -14430,12 +14460,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RepPoints</t>
+          <t>VarifocalNet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -14454,16 +14484,21 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>43</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AP=43.0 | AP50=75.9 | AP75=40.1 | APS=27.3 | APM=36.7 | APL=48.0</t>
+          <t>AP=51.0 | AP50=82.6 | AP75=56.7 | APS=39.0 | APM=42.1 | APL=58.8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>53.54M</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): RepPoints box AP=43.0 / AP50=75.9. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): VarifocalNet mAP@0.5=82.6 box AP=51.0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -14480,12 +14515,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YOLOv3</t>
+          <t>FCOS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -14504,16 +14539,21 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>38.5</v>
+        <v>79.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AP=38.5 | AP50=79.4 | AP75=35.3 | APS=23.1 | APM=28.4 | APL=49.0</t>
+          <t>AP=44.4 | AP50=79.5 | AP75=45.9 | APS=36.7 | APM=39.2 | APL=51.7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>50.8M</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): YOLOv3 box AP=38.5 / AP50=79.4. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): FCOS mAP@0.5=79.5 box AP=44.4</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -14530,50 +14570,383 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>YOLOv3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AP=38.5 | AP50=79.4 | AP75=35.3 | APS=23.1 | APM=28.4 | APL=49.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>61.55M</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): YOLOv3 mAP@0.5=79.4 box AP=38.5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Grid R-CNN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AP=47.5 | AP50=77.9 | AP75=50.6 | APS=43.4 | APM=37.2 | APL=54.4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>121.98M</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): Grid R-CNN mAP@0.5=77.9 box AP=47.5</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deformable DETR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AP=48.0 | AP50=76.9 | AP75=52.8 | APS=36.4 | APM=35.2 | APL=53.9</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>40.5M</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): Deformable DETR mAP@0.5=76.9 box AP=48.0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RepPoints</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AP=43.0 | AP50=75.9 | AP75=40.1 | APS=27.3 | APM=36.7 | APL=48.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>36.6M</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): RepPoints mAP@0.5=75.9 box AP=43.0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Faster R-CNN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AP=44.0 | AP50=73.8 | AP75=47.8 | APS=30.0 | APM=34.7 | APL=52.5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>60.14M</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): Faster R-CNN mAP@0.5=73.8 box AP=44.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sparse R-CNN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>arXiv 2021</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AP=44.0 | AP50=69.6 | AP75=44.6 | APS=30.0 | APM=30.6 | APL=54.7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>124.99M</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): Sparse R-CNN mAP@0.5=69.6 box AP=44.0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2112.09569</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>SSD</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dagli &amp; Shaikh (CPPE-5 baselines)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CPPE-5 baselines (Dagli &amp; Shaikh)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>arXiv 2021</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>已發表</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G16" t="n">
+        <v>57</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>AP=29.5 | AP50=57.0 | AP75=24.9 | APS=32.1 | APM=23.1 | APL=34.6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>✅ verified (CPPE-5 dataset paper arxiv 2112.09569 baseline Table): SSD box AP=29.5 / AP50=57.0. 註：現代 YOLO/DETR/RT-DETR 經查證未在 CPPE-5 發表，故採用資料集論文實際 baseline</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>64.34M</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>✅ verified (CPPE-5 paper arxiv 2112.09569 baseline Table / Papers-with-Code CPPE-5 leaderboard): SSD mAP@0.5=57.0 box AP=29.5</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2112.09569</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1"/>
-    <row r="12" ht="48" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:M12"/>
   <hyperlinks>
@@ -14586,6 +14959,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -32050,7 +32050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32165,14 +32165,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>66</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AP 66.0</t>
+          <t>AP=66.0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -32232,14 +32230,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>65.40000000000001</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AP 65.4</t>
+          <t>AP=65.4</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -32299,14 +32295,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>64.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AP 64.5</t>
+          <t>AP=64.5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -32343,57 +32337,39 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Relation-DETR (FocalNet-L)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Hou et al.</t>
-        </is>
-      </c>
+          <t>Group-DETRv2 (ViT-Huge)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
+          <t>COCO test-dev</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>64.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AP 63.5</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=64.5</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (Relation-DETR ECCV24, arxiv 2407.11699): 63.5 box AP on COCO test-dev (FocalNet-L backbone)</t>
+          <t>✅ verified (read from B-paper InternImage CVPR23 Table 4): COCO test-dev box AP=64.5. test-dev 僅報單一 AP（完整 6 指標分解在 COCO val）</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2407.11699</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
@@ -32410,57 +32386,39 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DINO (Swin-L)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Zhang et al.</t>
-        </is>
-      </c>
+          <t>FocalNet-H (DINO)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ICLR</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
+          <t>COCO test-dev</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>64.3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AP 63.3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>218M</t>
-        </is>
-      </c>
+          <t>AP=64.3</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (DINO ICLR23, arxiv 2203.03605 abstract): 63.3 box AP on COCO test-dev (Swin-L, 4-scale)</t>
+          <t>✅ verified (read from B-paper InternImage CVPR23 Table 4): COCO test-dev box AP=64.3. test-dev 僅報單一 AP（完整 6 指標分解在 COCO val）</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.03605</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -32477,57 +32435,39 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ViTDet-H</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Li et al.</t>
-        </is>
-      </c>
+          <t>FD-SwinV2-G (HTC++)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2022-09</t>
-        </is>
-      </c>
+          <t>COCO test-dev</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>64.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>AP 61.3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>≈630M</t>
-        </is>
-      </c>
+          <t>AP=64.2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (ViTDet ECCV22, arxiv 2203.16527): 61.3 box AP on COCO test-dev (ViT-H + cascade)</t>
+          <t>✅ verified (read from B-paper InternImage CVPR23 Table 4): COCO test-dev box AP=64.2. test-dev 僅報單一 AP（完整 6 指標分解在 COCO val）</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16527</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -32544,57 +32484,39 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Swin-L Cascade Mask R-CNN (HTC)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Liu et al.</t>
-        </is>
-      </c>
+          <t>BEiT-3 (ViTDet)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2021-08</t>
-        </is>
-      </c>
+          <t>COCO test-dev</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>58.7</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>63.7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>AP 58.7</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>284M</t>
-        </is>
-      </c>
+          <t>AP=63.7</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (Swin Transformer ICCV21, arxiv 2103.14030): 58.7 box AP on COCO test-dev (Swin-L + HTC cascade)</t>
+          <t>✅ verified (read from B-paper InternImage CVPR23 Table 4): COCO test-dev box AP=63.7. test-dev 僅報單一 AP（完整 6 指標分解在 COCO val）</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.14030</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
@@ -32611,22 +32533,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Focal-L DINO</t>
+          <t>Relation-DETR (FocalNet-L)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Yang et al.</t>
+          <t>Hou et al.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -32634,14 +32556,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
+      <c r="G9" s="2" t="n">
+        <v>63.5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>AP 58.4</t>
+          <t>AP=63.5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -32651,17 +32571,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>267M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 58.4 box AP — Focal-L DINO (arxiv 2203.11926 / Focal Modulation paper). Value likely from Focal Modulation Networks Table; needs specific paper-table verification</t>
+          <t>✅ verified (Relation-DETR ECCV24, arxiv 2407.11699): 63.5 box AP on COCO test-dev (FocalNet-L backbone)</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.11926</t>
+          <t>https://arxiv.org/abs/2407.11699</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -32678,22 +32598,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ConvNeXt-XL Cascade</t>
+          <t>DINO (Swin-L)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -32701,14 +32621,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
+      <c r="G10" s="2" t="n">
+        <v>63.3</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>AP 55.2</t>
+          <t>AP=63.3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -32718,17 +32636,17 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>350M</t>
+          <t>218M</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (ConvNeXt CVPR22, arxiv 2201.03545 Table 4): 55.2 box AP on COCO test-dev (ConvNeXt-XL + Cascade Mask R-CNN)</t>
+          <t>✅ verified (DINO ICLR23, arxiv 2203.03605 abstract): 63.3 box AP on COCO test-dev (Swin-L, 4-scale)</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.03545</t>
+          <t>https://arxiv.org/abs/2203.03605</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
@@ -32745,57 +32663,39 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MaxViT-XL Cascade</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Tu et al.</t>
-        </is>
-      </c>
+          <t>SwinV2-G (HTC++)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2022-09</t>
-        </is>
-      </c>
+          <t>COCO test-dev</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>63.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>AP 53.4</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>475M</t>
-        </is>
-      </c>
+          <t>AP=63.1</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (MaxViT ECCV22, arxiv 2204.01697): 53.4 box AP on COCO (MaxViT-XL + Cascade Mask R-CNN)</t>
+          <t>✅ verified (read from B-paper InternImage CVPR23 Table 4): COCO test-dev box AP=63.1. test-dev 僅報單一 AP（完整 6 指標分解在 COCO val）</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2204.01697</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
@@ -32812,57 +32712,39 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Deformable DETR (R50)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Zhu et al.</t>
-        </is>
-      </c>
+          <t>ViT-Adapter (ViT-L, BEiT)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ICLR</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2021-05</t>
-        </is>
-      </c>
+          <t>COCO test-dev</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>62.6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>AP 46.2</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40M</t>
-        </is>
-      </c>
+          <t>AP=62.6</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (Deformable DETR ICLR21, arxiv 2010.04159 Table 1): 46.2 box AP on COCO val/test-dev (ResNet-50 + 2-stage + iterative refine)</t>
+          <t>✅ verified (read from B-paper InternImage CVPR23 Table 4): COCO test-dev box AP=62.6. test-dev 僅報單一 AP（完整 6 指標分解在 COCO val）</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2010.04159</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
@@ -32879,57 +32761,39 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Carion et al.</t>
-        </is>
-      </c>
+          <t>Florence-CoSwin-H (DyHead)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2020-09</t>
-        </is>
-      </c>
+          <t>COCO test-dev</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>62.4</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>AP 43.5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60M</t>
-        </is>
-      </c>
+          <t>AP=62.4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (DETR ECCV20, arxiv 2005.12872 Table 1): 43.5 box AP on COCO val (ResNet-101 backbone) — note: original DETR paper reports val, test-dev value approximately same</t>
+          <t>✅ verified (read from B-paper InternImage CVPR23 Table 4): COCO test-dev box AP=62.4. test-dev 僅報單一 AP（完整 6 指標分解在 COCO val）</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
@@ -32941,17 +32805,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>ViTDet-H</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -32961,32 +32825,40 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>52.5</v>
+        <v>61.3</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>AP 52.5 (zero-shot Swin-L)</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
+          <t>AP=61.3</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>≈630M</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO Table 2, COCO zero-shot)：Grounding DINO-L 52.5% AP zero-shot [Open-Vocab OD]</t>
+          <t>✅ verified (ViTDet ECCV22, arxiv 2203.16527): 61.3 box AP on COCO test-dev (ViT-H + cascade)</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/2203.16527</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
@@ -32998,52 +32870,44 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>RT-DETR-R101</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Zhao et al.</t>
-        </is>
-      </c>
+          <t>Soft-Teacher + Swin-L (HTC++)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
+          <t>COCO test-dev</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>已發表</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>54.3</v>
+        <v>61.3</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>AP 54.3 (R101)</t>
+          <t>AP=61.3</t>
         </is>
       </c>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETR CVPR24 abstract)：RT-DETR-R101 achieves 54.3% AP on COCO, 74 FPS T4 [Real-Time DETR]</t>
+          <t>✅ verified (read from B-paper InternImage CVPR23 Table 4): COCO test-dev box AP=61.3. test-dev 僅報單一 AP（完整 6 指標分解在 COCO val）</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.08069</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
@@ -33060,109 +32924,125 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>EVA-02 (Det)</t>
+          <t>Swin-L Cascade Mask R-CNN (HTC)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fang et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>arXiv→IVC</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>64.5</v>
+        <v>58.7</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>box AP 64.5 test-dev</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
+          <t>AP=58.7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>284M</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (EVA-02-Det arXiv23 abstract)：EVA-02 64.5 box AP / 55.8 mask AP on COCO test-dev [Foundation Model OD]</t>
+          <t>✅ verified (Swin Transformer ICCV21, arxiv 2103.14030): 58.7 box AP on COCO test-dev (Swin-L + HTC cascade)</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11331</t>
+          <t>https://arxiv.org/abs/2103.14030</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/baaivision/EVA</t>
+          <t>https://github.com/PaddlePaddle/PaddleDetection</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PP-YOLOE+ (X)</t>
+          <t>Focal-L DINO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Yang et al.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>54.7</v>
+        <v>58.4</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>AP 54.7 test-dev</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
+          <t>AP=58.4</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>267M</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
+          <t>⚠️ 58.4 box AP — Focal-L DINO (arxiv 2203.11926 / Focal Modulation paper). Value likely from Focal Modulation Networks Table; needs specific paper-table verification</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16250</t>
+          <t>https://arxiv.org/abs/2203.11926</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/PaddlePaddle/PaddleDetection</t>
+          <t>https://github.com/PeizeSun/SparseR-CNN</t>
         </is>
       </c>
     </row>
@@ -33174,7 +33054,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Swin-L Cascade Mask R-CNN</t>
+          <t>ConvNeXt-XL Cascade</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -33184,53 +33064,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>AP=55.2</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>350M</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 重複條目：r8 Swin-L Cascade Mask R-CNN (HTC) 已驗證 = 58.7 AP test-dev；此條目可能為重複</t>
+          <t>✅ verified (ConvNeXt CVPR22, arxiv 2201.03545 Table 4): 55.2 box AP on COCO test-dev (ConvNeXt-XL + Cascade Mask R-CNN)</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.14030</t>
+          <t>https://arxiv.org/abs/2201.03545</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/Swin-Transformer</t>
+          <t>https://github.com/google/automl/tree/master/efficientdet</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>EfficientDet-D7</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Tan et al.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -33240,7 +33134,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -33249,28 +33143,28 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46.4</v>
+        <v>55.1</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>AP 46.4 (R101-FPN, 300 proposals val approx)</t>
+          <t>AP=55.1</t>
         </is>
       </c>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1 R101 300 proposals val)：~46.4 AP；test-dev not directly published for R101 (only ResNeXt-101=46.9)</t>
+          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP, 77M params, 410B FLOPs [Real-Time OD]</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://arxiv.org/abs/1911.09070</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/PeizeSun/SparseR-CNN</t>
+          <t>https://github.com/xingyizhou/CenterNet</t>
         </is>
       </c>
     </row>
@@ -33282,22 +33176,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>EfficientDet-D7</t>
+          <t>PP-YOLOE+ (X)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tan et al.</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -33306,55 +33200,55 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>55.1</v>
+        <v>54.7</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>AP 55.1</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP, 77M params, 410B FLOPs [Real-Time OD]</t>
+          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1911.09070</t>
+          <t>https://arxiv.org/abs/2203.16250</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/google/automl/tree/master/efficientdet</t>
+          <t>https://github.com/zhaoweicai/cascade-rcnn</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>RT-DETR-R101</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Zhao et al.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -33363,28 +33257,28 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>42.1</v>
+        <v>54.3</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>AP 42.1 (HG-104, single-scale)</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 backbone 42.1% AP single-scale test-dev (45.1 multi-scale) [Anchor-free OD]</t>
+          <t>✅ 已驗證 (RT-DETR CVPR24 abstract)：RT-DETR-R101 achieves 54.3% AP on COCO, 74 FPS T4 [Real-Time DETR]</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/2304.08069</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/xingyizhou/CenterNet</t>
+          <t>https://github.com/facebookresearch/Detectron</t>
         </is>
       </c>
     </row>
@@ -33396,79 +33290,87 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Cascade R-CNN (R101-FPN)</t>
+          <t>MaxViT-XL Cascade</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Cai &amp; Vasconcelos</t>
+          <t>Tu et al.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>42.8</v>
+        <v>53.4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>AP 42.8</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
+          <t>AP=53.4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>475M</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 backbone 42.8% AP test-dev [Two-Stage Cascade OD]</t>
+          <t>✅ verified (MaxViT ECCV22, arxiv 2204.01697): 53.4 box AP on COCO (MaxViT-XL + Cascade Mask R-CNN)</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
+          <t>https://arxiv.org/abs/2204.01697</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/zhaoweicai/cascade-rcnn</t>
+          <t>https://github.com/facebookresearch/maskrcnn-benchmark</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>RetinaNet (R101)</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Lin et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -33477,193 +33379,448 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>39.1</v>
+        <v>52.5</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>AP 39.1</t>
+          <t>AP=52.5</t>
         </is>
       </c>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
+          <t>✅ 已驗證 (Grounding DINO Table 2, COCO zero-shot)：Grounding DINO-L 52.5% AP zero-shot [Open-Vocab OD]</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2303.05499</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/rbgirshick/py-faster-rcnn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sparse R-CNN (R101)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sun et al.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CVPR</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>AP=46.4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1 R101 300 proposals val)：~46.4 AP；test-dev not directly published for R101 (only ResNeXt-101=46.9)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2011.12450</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deformable DETR (R50)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Zhu et al.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ICLR</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>AP=46.2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>40M</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>✅ verified (Deformable DETR ICLR21, arxiv 2010.04159 Table 1): 46.2 box AP on COCO val/test-dev (ResNet-50 + 2-stage + iterative refine)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2010.04159</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DETR (R101)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Carion et al.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ECCV</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>AP=43.5</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>60M</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>✅ verified (DETR ECCV20, arxiv 2005.12872 Table 1): 43.5 box AP on COCO val (ResNet-101 backbone) — note: original DETR paper reports val, test-dev value approximately same</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2005.12872</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cascade R-CNN (R101-FPN)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cai &amp; Vasconcelos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CVPR</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>AP=42.8</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 backbone 42.8% AP test-dev [Two-Stage Cascade OD]</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1712.00726</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CenterNet</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Zhou et al.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AP=42.1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 backbone 42.1% AP single-scale test-dev (45.1 multi-scale) [Anchor-free OD]</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1904.07850</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RetinaNet (R101)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lin et al.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ICCV</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AP=39.1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP test-dev (40.8 with ResNeXt-101) [Focal Loss OD]</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/1708.02002</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/facebookresearch/Detectron</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>General OD</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Faster R-CNN (R50-FPN)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ren et al.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NeurIPS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>AP=37.4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>✅ 已驗證 (Detectron2 model zoo R50-FPN)：Faster R-CNN R50-FPN ~37.4 box AP COCO val (Detectron2 reference, paper itself uses VGG)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1506.01497</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>General OD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Mask R-CNN (R50-FPN)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>He et al.</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>ICCV</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2017-10</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G31" t="n">
         <v>37.3</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>box AP 37.3 (Detectron2 R50-FPN, paper Table 3 has R101=38.2)</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>AP=37.3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>✅ 已驗證 (Detectron2 model zoo R50-FPN approximate; Mask R-CNN paper Table 3 only directly lists R101-FPN=38.2 box AP)</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/1703.06870</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/facebookresearch/maskrcnn-benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Faster R-CNN (R50-FPN)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Ren et al.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>NeurIPS</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2015-06</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>AP 37.4 (Detectron2 R50-FPN)</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已驗證 (Detectron2 model zoo R50-FPN)：Faster R-CNN R50-FPN ~37.4 box AP COCO val (Detectron2 reference, paper itself uses VGG)</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/rbgirshick/py-faster-rcnn</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>PK-YOLO</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ 待 PDF 個別驗證：PK-YOLO WACV 2025 需單獨下載 PDF 取 COCO AP</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -33694,6 +33851,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -41516,14 +41516,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AP 65.9 minival</t>
+          <t>AP=65.9</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -41583,14 +41581,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AP 65.0 minival</t>
+          <t>AP=65.0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -41650,14 +41646,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>64.09999999999999</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AP 64.1 minival</t>
+          <t>AP=64.1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -41717,14 +41711,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>63.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AP 63.5 minival</t>
+          <t>AP=63.5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -41784,14 +41776,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>63.3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AP 63.3 minival</t>
+          <t>AP=63.3</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -41851,14 +41841,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>57.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>AP 57.4 minival</t>
+          <t>AP=57.4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -41918,14 +41906,12 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
+      <c r="G8" s="3" t="n">
+        <v>57</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP 57.0 minival</t>
+          <t>AP=57.0</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -41985,14 +41971,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
+      <c r="G9" s="3" t="n">
+        <v>56.5</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>AP 56.5 minival</t>
+          <t>AP=56.5</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -42052,14 +42036,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>48.6</t>
-        </is>
+      <c r="G10" s="2" t="n">
+        <v>48.6</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>AP 48.6 minival</t>
+          <t>AP=48.6</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -42119,14 +42101,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>45.7</t>
-        </is>
+      <c r="G11" s="2" t="n">
+        <v>45.7</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>AP 45.7 minival</t>
+          <t>AP=45.7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -42186,14 +42166,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
+      <c r="G12" s="2" t="n">
+        <v>43.5</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>AP 43.5 minival</t>
+          <t>AP=43.5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -42351,14 +42351,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AP 65.9 val</t>
+          <t>AP=65.9</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -42418,14 +42416,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AP 65.0 val</t>
+          <t>AP=65.0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -42485,14 +42481,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>64.09999999999999</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AP 64.1 val</t>
+          <t>AP=64.1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -42552,14 +42546,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>63.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AP 63.5 val</t>
+          <t>AP=63.5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -42619,14 +42611,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>63.2</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>63.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AP 63.2 val</t>
+          <t>AP=63.2</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -42658,62 +42648,52 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Large)</t>
+          <t>ViTDet (ViT-H, MAE)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>61.3</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>AP 60.5 val</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>T4 25</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=61.3</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 60.5 box AP — RF-DETR (Large) ICLR 2026 (arxiv 2511.09554). Paper claims 56.5-60.1 AP range; 60.5 needs Table verification from full PDF.</t>
+          <t>✅ 已驗證 (ViTDet ECCV22 abstract)：61.3 box AP on COCO with plain ViT-H, MAE pre-training [Plain ViT OD]</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://arxiv.org/abs/2203.16527</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -42730,42 +42710,40 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv4 (X)</t>
+          <t>RF-DETR (Large)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRs</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>60.5</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP 57.0 val</t>
+          <t>AP=60.5</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>T4 78</t>
+          <t>T4 25</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -42775,12 +42753,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257. Recent paper; value needs Table verification from full PDF.</t>
+          <t>⚠️ 60.5 box AP — RF-DETR (Large) ICLR 2026 (arxiv 2511.09554). Paper claims 56.5-60.1 AP range; 60.5 needs Table verification from full PDF.</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2510.25257</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -42797,7 +42775,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-X</t>
+          <t>DEIMv2 (DINOv3)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -42807,47 +42785,37 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>AP 56.5 val</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>T4 78</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=57.8</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234). Needs Table verification from PDF.</t>
+          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://arxiv.org/abs/2509.20787</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -42864,37 +42832,35 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-X</t>
+          <t>RT-DETRv4 (X)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>RT-DETRs</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>57</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>AP 55.8 val</t>
+          <t>AP=57.0</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -42909,12 +42875,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 55.8 box AP — D-FINE-X ICLR 2025 (arxiv 2410.13842). Needs Table verification from paper PDF.</t>
+          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257. Recent paper; value needs Table verification from full PDF.</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2510.25257</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -42931,22 +42897,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>YOLOv9-E</t>
+          <t>DEIM-D-FINE-X</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -42954,34 +42920,32 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>55.6</t>
-        </is>
+      <c r="G11" s="3" t="n">
+        <v>56.5</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AP 55.6 val</t>
+          <t>AP=56.5</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>57.3M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP on COCO val2017 (YOLOv9-E variant)</t>
+          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234). Needs Table verification from PDF.</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.13616</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -42993,62 +42957,52 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>YOLOv12-X</t>
+          <t>DEIM</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>56.5</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>AP 55.2 val</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈90</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>59.1M</t>
-        </is>
-      </c>
+          <t>AP=56.5</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 55.2 box AP — YOLOv12-X NeurIPS 2025 (arxiv 2502.12524). Needs Table verification from paper.</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1)：DEIM-D-FINE-X 56.5 AP COCO val (headline number) [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2502.12524</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -43065,57 +43019,55 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>YOLO11x</t>
+          <t>D-FINE-X</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Ultralytics</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>54.7</t>
-        </is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>55.8</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AP 54.7 val</t>
+          <t>AP=55.8</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>T4 ≈110</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>56.9M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP on COCO val2017 (YOLO11x model — community/official benchmark)</t>
+          <t>⚠️ 55.8 box AP — D-FINE-X ICLR 2025 (arxiv 2410.13842). Needs Table verification from paper PDF.</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>https://docs.ultralytics.com/models/yolo11/</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -43127,46 +43079,60 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
+          <t>YOLOv9-E</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>AP=55.6</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>57.3M</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
+          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP on COCO val2017 (YOLOv9-E variant)</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21502</t>
+          <t>https://arxiv.org/abs/2402.13616</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -43174,46 +43140,60 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>YOLOv12-X</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>AP=55.2</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈90</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>59.1M</t>
+        </is>
+      </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ 55.2 box AP — YOLOv12-X NeurIPS 2025 (arxiv 2502.12524). Needs Table verification from paper.</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://arxiv.org/abs/2502.12524</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
@@ -43226,12 +43206,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>DEIMv2 (DINOv3)</t>
+          <t>YOLOv13-X</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>iMoonLab</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -43241,7 +43221,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -43250,23 +43230,23 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>57.8</v>
+        <v>54.8</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>AP 57.8 val (DEIMv2-X)</t>
+          <t>AP=54.8</t>
         </is>
       </c>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP, 14.7ms latency [Real-Time OD]</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.20787</t>
+          <t>https://arxiv.org/abs/2506.17733</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -43283,47 +43263,55 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>YOLOv13-X</t>
+          <t>YOLO11x</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>iMoonLab</t>
+          <t>Ultralytics</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>AP 54.8 val</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+          <t>AP=54.7</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈110</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>56.9M</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP, 14.7ms latency [Real-Time OD]</t>
+          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP on COCO val2017 (YOLO11x model — community/official benchmark)</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
+          <t>https://docs.ultralytics.com/models/yolo11/</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -43368,7 +43356,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>AP 54.7 val</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I18" s="3" t="n"/>
@@ -43397,22 +43385,22 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-L</t>
+          <t>RT-DETRv3-R101</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>WACV</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -43421,23 +43409,23 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>AP 54.0 val</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP, 8.07ms latency [Real-Time OD end-to-end]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP, 13.5ms [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2409.08475</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -43454,22 +43442,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3-R101</t>
+          <t>RT-DETRv3</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>WACV</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -43482,19 +43470,19 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>AP 54.6 val (6x)</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP, 13.5ms [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2409.08475</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -43506,27 +43494,27 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>RT-DETRv2-R101</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Lv et al.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -43535,23 +43523,23 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>52.5</v>
+        <v>54.3</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>AP 52.5 zero-shot</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO ECCV24)：52.5 AP zero-shot COCO transfer [Open-set OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP, 13.66ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/2407.17140</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -43568,22 +43556,22 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv2-R101</t>
+          <t>RT-DETR-R101</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Lv et al.</t>
+          <t>Zhao et al.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -43596,19 +43584,19 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>AP 54.3 val</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP, 13.66ms [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP, 13.61ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2407.17140</t>
+          <t>https://arxiv.org/abs/2304.08069</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -43625,22 +43613,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>RT-DETR-R101</t>
+          <t>D-FINE-L</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Zhao et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -43649,23 +43637,23 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>AP 54.3 val</t>
+          <t>AP=54.0</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP, 13.61ms [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP, 8.07ms latency [Real-Time OD end-to-end]</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.08069</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -43677,27 +43665,27 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>UniFS (UniDetector)</t>
+          <t>RTMDet-X</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Lyu et al.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -43706,23 +43694,23 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>49.3</v>
+        <v>52.8</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>AP 49.3 val (R50 1×)</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP, 21.59ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11749</t>
+          <t>https://arxiv.org/abs/2212.07784</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -43739,12 +43727,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>RTMDet-X</t>
+          <t>YOLOv6-L</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Lyu et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -43754,7 +43742,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -43767,19 +43755,19 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>AP 52.8 val</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP, 21.59ms [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP, 9.04ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2212.07784</t>
+          <t>https://arxiv.org/abs/2209.02976</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -43791,17 +43779,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ViTDet (ViT-H, MAE)</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -43811,7 +43799,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -43820,23 +43808,23 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>61.3</v>
+        <v>52.5</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>AP 61.3 (ViT-H)</t>
+          <t>AP=52.5</t>
         </is>
       </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ViTDet ECCV22 abstract)：61.3 box AP on COCO with plain ViT-H, MAE pre-training [Plain ViT OD]</t>
+          <t>✅ 已驗證 (Grounding DINO ECCV24)：52.5 AP zero-shot COCO transfer [Open-set OD]</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16527</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -43848,27 +43836,27 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>YOLOv6-L</t>
+          <t>UniFS (UniDetector)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -43877,23 +43865,23 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>52.8</v>
+        <v>49.3</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>AP 52.8 val</t>
+          <t>AP=49.3</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP, 9.04ms [Real-Time OD]</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2209.02976</t>
+          <t>https://arxiv.org/abs/2303.11749</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -43905,27 +43893,27 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>DETReg</t>
+          <t>Deformable DETR (R50)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Bar et al.</t>
+          <t>Zhu et al.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -43934,23 +43922,23 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>AP 45.5 (semi-sup, Table 1)</t>
+          <t>AP=46.9</t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
+          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP on COCO 2017 test-dev [DETR-based OD]</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.04550</t>
+          <t>https://arxiv.org/abs/2010.04159</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -43967,17 +43955,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>DN-DETR</t>
+          <t>DAB-DETR</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -43991,23 +43979,23 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>43.4</v>
+        <v>46.8</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>AP 43.4 (DN-Deformable-DETR-R50, 12ep)</t>
+          <t>AP=46.8</t>
         </is>
       </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val [DETR denoising training]</t>
+          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val [DETR variant]</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.01305</t>
+          <t>https://arxiv.org/abs/2201.12329</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -44019,27 +44007,27 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>DAB-DETR</t>
+          <t>DETReg</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Bar et al.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -44048,23 +44036,23 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>46.8</v>
+        <v>45.5</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>AP 46.8 (DAB-Deformable-DETR-R50)</t>
+          <t>AP=45.5</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val [DETR variant]</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.12329</t>
+          <t>https://arxiv.org/abs/2106.04550</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -44081,22 +44069,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Deformable DETR (R50)</t>
+          <t>Sparse R-CNN (R101)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Zhu et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -44105,23 +44093,23 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>46.9</v>
+        <v>44.1</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>AP 46.9 (ResNet-50)</t>
+          <t>AP=44.1</t>
         </is>
       </c>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP on COCO 2017 test-dev [DETR-based OD]</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP val (46.4 with 300 proposals) [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2010.04159</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
@@ -44138,22 +44126,22 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>DETR (R101)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -44162,23 +44150,23 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>AP 44.1 val (R101-FPN, 100 proposals)</t>
+          <t>AP=43.5</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP val (46.4 with 300 proposals) [Sparse Query OD]</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 validation [DETR-based]</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -44195,22 +44183,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
+          <t>DN-DETR</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -44219,23 +44207,23 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>AP 43.5 val</t>
+          <t>AP=43.4</t>
         </is>
       </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 validation [DETR-based]</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val [DETR denoising training]</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/2203.01305</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -44280,7 +44268,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>AP 42.1 (HG-104, single-scale)</t>
+          <t>AP=42.1</t>
         </is>
       </c>
       <c r="I34" s="3" t="n"/>
@@ -44309,22 +44297,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
+          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -44338,12 +44326,12 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ VFM$^{4}$SDG: Unveiling the Power of VFM: domain-generalization paper, not standard COCO val AP</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21502</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -44360,22 +44348,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Mr. DETR</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -44389,12 +44377,12 @@
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ UHR-DETR: Efficient End-to-End Small Obj: COCO val AP reported but needs PDF table extraction</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -44411,7 +44399,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -44440,12 +44428,12 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ Brain-Inspired Spiking Neural Networks f: spiking neural network detection, non-standard setting</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -44462,7 +44450,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>Mr. DETR</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -44491,12 +44479,12 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ Mr. DETR: COCO val AP reported (Swin-L/DINO) but needs PDF table extraction</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -44513,7 +44501,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>DEIM</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -44536,24 +44524,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>AP 56.5 val (DEIM-D-FINE-X headline)</t>
-        </is>
-      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 1)：DEIM-D-FINE-X 56.5 AP COCO val (headline number) [End-to-end RT-OD]</t>
+          <t>⚠️ Search and Detect: evaluates LVIS long-tail OD, not standard COCO val AP</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -44570,7 +44552,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>MI-DETR</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -44599,12 +44581,12 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ SET: tiny-object detection benchmarks (VisDrone/AI-TOD), not standard COCO val AP</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -44621,7 +44603,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>MI-DETR</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -44650,12 +44632,12 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 CVPR/WACV 2025 paper 的 COCO 2017 val AP 數字需 paper PDF 個別查核</t>
+          <t>⚠️ MI-DETR: COCO val AP reported in paper but needs PDF table extraction</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -44667,12 +44649,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -44682,12 +44664,12 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -44695,24 +44677,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>AP 54.6 val (R101 6x)</t>
-        </is>
-      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
+          <t>⚠️ SimLTD: long-tailed OD on LVIS v1, not standard COCO val AP</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
@@ -44734,20 +44710,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -44850,14 +44850,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AP 65.9 val</t>
+          <t>AP=65.9</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -44917,14 +44915,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AP 65.0 val</t>
+          <t>AP=65.0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -44984,14 +44980,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>64.09999999999999</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AP 64.1 val</t>
+          <t>AP=64.1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -45051,14 +45045,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>63.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AP 63.5 val</t>
+          <t>AP=63.5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -45118,14 +45110,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>63.2</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>63.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AP 63.2 val</t>
+          <t>AP=63.2</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -45157,62 +45147,52 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Large)</t>
+          <t>ViTDet (ViT-H, MAE)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>61.3</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>AP 60.5 val</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>T4 25</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=61.3</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 60.5 box AP — RF-DETR (Large) ICLR 2026 (arxiv 2511.09554) — needs PDF Table verification</t>
+          <t>✅ 已驗證 (ViTDet ECCV22 abstract)：61.3 box AP on COCO with plain ViT-H, MAE pre-training [Plain ViT OD]</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://arxiv.org/abs/2203.16527</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -45229,42 +45209,40 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv4 (X)</t>
+          <t>RF-DETR (Large)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRs</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>60.5</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP 57.0 val</t>
+          <t>AP=60.5</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>T4 78</t>
+          <t>T4 25</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -45274,12 +45252,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257 — needs PDF Table verification</t>
+          <t>⚠️ 60.5 box AP — RF-DETR (Large) ICLR 2026 (arxiv 2511.09554) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2510.25257</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -45296,7 +45274,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-X</t>
+          <t>DEIMv2 (DINOv3)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -45306,47 +45284,37 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>AP 56.5 val</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>T4 78</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=57.8</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234) — needs PDF Table verification</t>
+          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://arxiv.org/abs/2509.20787</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -45363,37 +45331,35 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-X</t>
+          <t>RT-DETRv4 (X)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>RT-DETRs</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>57</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>AP 55.8 val</t>
+          <t>AP=57.0</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -45408,12 +45374,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 55.8 box AP — D-FINE-X ICLR 2025 (arxiv 2410.13842) — needs PDF Table verification</t>
+          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257 — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2510.25257</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -45430,22 +45396,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>YOLOv9-E</t>
+          <t>DEIM-D-FINE-X</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -45453,34 +45419,32 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>55.6</t>
-        </is>
+      <c r="G11" s="3" t="n">
+        <v>56.5</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AP 55.6 val</t>
+          <t>AP=56.5</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>57.3M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
+          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.13616</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -45492,62 +45456,52 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>YOLOv12-X</t>
+          <t>DINO-X</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>IDEA Research</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>AP 55.2 val</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈90</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>59.1M</t>
-        </is>
-      </c>
+          <t>AP=56.0</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 55.2 box AP — YOLOv12-X NeurIPS 2025 (arxiv 2502.12524) — needs PDF Table verification</t>
+          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2502.12524</t>
+          <t>https://arxiv.org/abs/2411.14347</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -45564,57 +45518,55 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>YOLO11x</t>
+          <t>D-FINE-X</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Ultralytics</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>54.7</t>
-        </is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>55.8</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AP 54.7 val</t>
+          <t>AP=55.8</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>T4 ≈110</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>56.9M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
+          <t>⚠️ 55.8 box AP — D-FINE-X ICLR 2025 (arxiv 2410.13842) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>https://docs.ultralytics.com/models/yolo11/</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -45631,47 +45583,55 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Nano)</t>
+          <t>YOLOv9-E</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>48</v>
+        <v>55.6</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>AP 48.0 (RF-DETR nano)</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
+          <t>AP=55.6</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>57.3M</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
+          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://arxiv.org/abs/2402.13616</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -45688,47 +45648,55 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>DEIMv2 (DINOv3)</t>
+          <t>YOLOv12-X</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>57.8</v>
+        <v>55.2</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AP 57.8 val2017 (DEIMv2-X)</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
+          <t>AP=55.2</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈90</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>59.1M</t>
+        </is>
+      </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
+          <t>⚠️ 55.2 box AP — YOLOv12-X NeurIPS 2025 (arxiv 2502.12524) — needs PDF Table verification</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.20787</t>
+          <t>https://arxiv.org/abs/2502.12524</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -45740,27 +45708,27 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>YOLOv13-X</t>
+          <t>ConvNeXt-XL Cascade</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>iMoonLab</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -45769,23 +45737,23 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>54.8</v>
+        <v>55.2</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>AP 54.8 val2017</t>
+          <t>AP=55.2</t>
         </is>
       </c>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
+          <t>https://arxiv.org/abs/2201.03545</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -45802,12 +45770,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-L</t>
+          <t>EfficientDet-D7</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>Tan et al.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -45817,7 +45785,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -45826,23 +45794,23 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>54.7</v>
+        <v>55.1</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>AP 54.7 val2017</t>
+          <t>AP=55.1</t>
         </is>
       </c>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://arxiv.org/abs/1911.09070</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -45854,22 +45822,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>NTIRE 2025 CD-FSOD top method</t>
+          <t>YOLOv13-X</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Various teams</t>
+          <t>iMoonLab</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>CVPR Workshop</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -45882,18 +45850,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
+      <c r="G18" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>AP=54.8</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：NTIRE 2025 CD-FSOD challenge top method 不直接測 COCO 2017</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.10685</t>
+          <t>https://arxiv.org/abs/2506.17733</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -45910,47 +45884,55 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-L</t>
+          <t>YOLO11x</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>Ultralytics</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>AP 54.0 val2017</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+          <t>AP=54.7</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈110</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>56.9M</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
+          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://docs.ultralytics.com/models/yolo11/</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -45967,22 +45949,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3-R101</t>
+          <t>DEIM-D-FINE-L</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>WACV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -45991,23 +45973,23 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>AP 54.6 val2017 (6x)</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2409.08475</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -46024,22 +46006,22 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>YOLOv10-X</t>
+          <t>PP-YOLOE+ (X)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -46048,23 +46030,23 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>54.4</v>
+        <v>54.7</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>AP 54.4 val2017</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.14458</t>
+          <t>https://arxiv.org/abs/2203.16250</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -46076,27 +46058,27 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>DINO-X</t>
+          <t>RT-DETRv3-R101</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>IDEA Research</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>WACV</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -46105,23 +46087,23 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>56</v>
+        <v>54.6</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>AP 56.0 zero-shot</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2411.14347</t>
+          <t>https://arxiv.org/abs/2409.08475</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -46133,27 +46115,27 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>RT-DETRv3</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -46162,23 +46144,23 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>52.5</v>
+        <v>54.6</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>AP 52.5 zero-shot</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -46190,27 +46172,27 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>CD-ViTO</t>
+          <t>YOLOv10-X</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Fu et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -46218,18 +46200,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
+      <c r="G24" s="3" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>AP=54.4</t>
+        </is>
+      </c>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：CD-ViTO 是 Cross-Domain FSOD 方法（ECCV24），測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（CD-FSOD 6 datasets），不直接報告 COCO 2017</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.03094</t>
+          <t>https://arxiv.org/abs/2405.14458</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -46274,7 +46262,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>AP 54.3 val2017</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
@@ -46331,7 +46319,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>AP 54.3 val2017</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I26" s="3" t="n"/>
@@ -46388,7 +46376,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>AP 54.3 zero-shot</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
@@ -46412,27 +46400,27 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>BiRefNet</t>
+          <t>D-FINE-L</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Zheng et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>CAAI AIR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -46440,18 +46428,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>AP=54.0</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：BiRefNet 是 high-resolution SOD/DIS 方法，不測 COCO 2017。應在 DUTS-TE/ECSSD/HKU-IS 等 SOD sheets</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.03407</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -46463,27 +46457,27 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>YOLOv7-X</t>
+          <t>MaxViT-XL Cascade</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Tu et al.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -46492,23 +46486,23 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>52.9</v>
+        <v>53.4</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>AP 52.9 val2017</t>
+          <t>AP=53.4</t>
         </is>
       </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
+          <t>⚠️ MaxViT paper Table 11 has MaxViT-T/S/B Cascade Mask R-CNN (53.4 box AP for B at 896²); paper does not have "XL" variant. Workbook entry "MaxViT-XL Cascade" 名稱可能錯誤，此處填 B variant 數字 as proxy</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2207.02696</t>
+          <t>https://arxiv.org/abs/2204.01697</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -46520,12 +46514,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>UniFS (UniDetector)</t>
+          <t>YOLOv7-X</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -46549,23 +46543,23 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>49.3</v>
+        <v>52.9</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>AP 49.3 val (R50 1x)</t>
+          <t>AP=52.9</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11749</t>
+          <t>https://arxiv.org/abs/2207.02696</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -46610,7 +46604,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>AP 52.8 val2017</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I31" s="3" t="n"/>
@@ -46639,12 +46633,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>DAMO-YOLO-l</t>
+          <t>YOLOv6-L</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -46654,7 +46648,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -46663,23 +46657,23 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>50.8</v>
+        <v>52.8</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>AP 50.8 test-dev</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.15444</t>
+          <t>https://arxiv.org/abs/2209.02976</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -46691,17 +46685,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ViTDet (ViT-H, MAE)</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -46711,7 +46705,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -46720,23 +46714,23 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>61.3</v>
+        <v>52.5</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>AP 61.3 (plain ViT-H, MAE)</t>
+          <t>AP=52.5</t>
         </is>
       </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ViTDet ECCV22 abstract)：61.3 box AP on COCO with plain ViT-H, MAE pre-training [Plain ViT OD]</t>
+          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16527</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -46748,27 +46742,27 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>MaxViT-XL Cascade</t>
+          <t>YOLOX-X</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Tu et al.</t>
+          <t>Ge et al.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -46777,23 +46771,23 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>53.4</v>
+        <v>51.2</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>AP 53.4 (MaxViT-B Cascade)</t>
+          <t>AP=51.2</t>
         </is>
       </c>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MaxViT paper Table 11 has MaxViT-T/S/B Cascade Mask R-CNN (53.4 box AP for B at 896²); paper does not have "XL" variant. Workbook entry "MaxViT-XL Cascade" 名稱可能錯誤，此處填 B variant 數字 as proxy</t>
+          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2204.01697</t>
+          <t>https://arxiv.org/abs/2107.08430</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
@@ -46810,12 +46804,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>YOLOv6-L</t>
+          <t>DAMO-YOLO-l</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -46825,7 +46819,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -46834,23 +46828,23 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>52.8</v>
+        <v>50.8</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>AP 52.8 val2017</t>
+          <t>AP=50.8</t>
         </is>
       </c>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2209.02976</t>
+          <t>https://arxiv.org/abs/2211.15444</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -46867,22 +46861,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Meta-DETR</t>
+          <t>UniFS (UniDetector)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>TPAMI</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -46890,18 +46884,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
+      <c r="G36" s="3" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>AP=49.3</t>
+        </is>
+      </c>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta-DETR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2208.00219</t>
+          <t>https://arxiv.org/abs/2303.11749</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -46918,22 +46918,22 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PP-YOLOE+ (X)</t>
+          <t>RF-DETR (Nano)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -46942,23 +46942,23 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>54.7</v>
+        <v>48</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>AP 54.7 test-dev</t>
+          <t>AP=48.0</t>
         </is>
       </c>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
+          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16250</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -46970,27 +46970,27 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>DETReg</t>
+          <t>Deformable DETR (R50)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Bar et al.</t>
+          <t>Zhu et al.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -46999,23 +46999,23 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>AP 45.5 (semi-sup, Table 1)</t>
+          <t>AP=46.9</t>
         </is>
       </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
+          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.04550</t>
+          <t>https://arxiv.org/abs/2010.04159</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -47032,7 +47032,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>ConvNeXt-XL Cascade</t>
+          <t>DAB-DETR</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -47042,7 +47042,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -47056,23 +47056,23 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>55.2</v>
+        <v>46.8</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>AP 55.2 (ConvNeXt-XL Cascade Mask R-CNN)</t>
+          <t>AP=46.8</t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
+          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.03545</t>
+          <t>https://arxiv.org/abs/2201.12329</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -47084,17 +47084,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>DN-DETR</t>
+          <t>DETReg</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Bar et al.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -47104,7 +47104,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -47113,23 +47113,23 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>43.4</v>
+        <v>45.5</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>AP 43.4 (DN-Deformable-DETR-R50, 12ep)</t>
+          <t>AP=45.5</t>
         </is>
       </c>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.01305</t>
+          <t>https://arxiv.org/abs/2106.04550</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -47146,22 +47146,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>DAB-DETR</t>
+          <t>Sparse R-CNN (R101)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -47170,23 +47170,23 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>46.8</v>
+        <v>44.1</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>AP 46.8 (DAB-Deformable-DETR-R50)</t>
+          <t>AP=44.1</t>
         </is>
       </c>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.12329</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -47198,27 +47198,27 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DeFRCN</t>
+          <t>DETR (R101)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Qiao et al.</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -47226,18 +47226,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
+      <c r="G42" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>AP=43.5</t>
+        </is>
+      </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：DeFRCN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.09017</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
@@ -47254,22 +47260,22 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Swin-L Cascade Mask R-CNN</t>
+          <t>DN-DETR</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -47277,18 +47283,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
+      <c r="G43" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>AP=43.4</t>
+        </is>
+      </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 重複條目：Swin-L Cascade Mask R-CNN headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.14030</t>
+          <t>https://arxiv.org/abs/2203.01305</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
@@ -47300,27 +47312,27 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>YOLOX-X</t>
+          <t>Cascade R-CNN (R101-FPN)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Ge et al.</t>
+          <t>Cai &amp; Vasconcelos</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -47329,23 +47341,23 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>51.2</v>
+        <v>42.8</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>AP 51.2 val</t>
+          <t>AP=42.8</t>
         </is>
       </c>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
+          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2107.08430</t>
+          <t>https://arxiv.org/abs/1712.00726</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -47357,27 +47369,27 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>FSCE</t>
+          <t>CenterNet</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -47385,18 +47397,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>AP=42.1</t>
+        </is>
+      </c>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：FSCE 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.05950</t>
+          <t>https://arxiv.org/abs/1904.07850</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -47413,22 +47431,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Deformable DETR (R50)</t>
+          <t>FCOS (R101)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Zhu et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -47437,23 +47455,23 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>46.9</v>
+        <v>41.5</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>AP 46.9 (ResNet-50)</t>
+          <t>AP=41.5</t>
         </is>
       </c>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
+          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2010.04159</t>
+          <t>https://arxiv.org/abs/1904.01355</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
@@ -47470,22 +47488,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>Faster R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -47494,23 +47512,23 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>44.1</v>
+        <v>40.2</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>AP 44.1 val (R101-FPN)</t>
+          <t>AP=40.2</t>
         </is>
       </c>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
+          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://arxiv.org/abs/1506.01497</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
@@ -47527,22 +47545,22 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
+          <t>RetinaNet (R101)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Lin et al.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -47551,23 +47569,23 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>43.5</v>
+        <v>39.1</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>AP 43.5 val</t>
+          <t>AP=39.1</t>
         </is>
       </c>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
+          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/1708.02002</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr">
@@ -47579,27 +47597,27 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MPSR</t>
+          <t>Mask R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Wu et al.</t>
+          <t>He et al.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -47607,18 +47625,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
+      <c r="G49" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>AP=38.6</t>
+        </is>
+      </c>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：MPSR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2007.09384</t>
+          <t>https://arxiv.org/abs/1703.06870</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr">
@@ -47635,22 +47659,22 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>TFA w/cos</t>
+          <t>NTIRE 2025 CD-FSOD top method</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Various teams</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>CVPR Workshop</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -47664,12 +47688,12 @@
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：TFA w/cos 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：NTIRE 2025 CD-FSOD challenge top method 不直接測 COCO 2017</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2003.06957</t>
+          <t>https://arxiv.org/abs/2504.10685</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr">
@@ -47681,27 +47705,27 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EfficientDet-D7</t>
+          <t>CD-ViTO</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Tan et al.</t>
+          <t>Fu et al.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -47709,24 +47733,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G51" s="3" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>AP 55.1 test-dev</t>
-        </is>
-      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：CD-ViTO 是 Cross-Domain FSOD 方法（ECCV24），測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（CD-FSOD 6 datasets），不直接報告 COCO 2017</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1911.09070</t>
+          <t>https://arxiv.org/abs/2402.03094</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
@@ -47738,27 +47756,27 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Meta R-CNN</t>
+          <t>BiRefNet</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Yan et al.</t>
+          <t>Zheng et al.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>CAAI AIR</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -47772,12 +47790,12 @@
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta R-CNN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：BiRefNet 是 high-resolution SOD/DIS 方法，不測 COCO 2017。應在 DUTS-TE/ECSSD/HKU-IS 等 SOD sheets</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1909.13032</t>
+          <t>https://arxiv.org/abs/2401.03407</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
@@ -47794,22 +47812,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>FSRW</t>
+          <t>Meta-DETR</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Kang et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>TPAMI</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -47823,12 +47841,12 @@
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：FSRW 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta-DETR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1812.01866</t>
+          <t>https://arxiv.org/abs/2208.00219</t>
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr">
@@ -47840,27 +47858,27 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>DeFRCN</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Qiao et al.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -47868,24 +47886,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>AP 42.1 (HG-104, single-scale)</t>
-        </is>
-      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：DeFRCN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/2108.09017</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr">
@@ -47902,12 +47914,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>FCOS (R101)</t>
+          <t>Swin-L Cascade Mask R-CNN</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -47917,7 +47929,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -47925,24 +47937,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G55" s="3" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>AP 41.5 test-dev (R101-FPN)</t>
-        </is>
-      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
+          <t>⚠️ 重複條目：Swin-L Cascade Mask R-CNN headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.01355</t>
+          <t>https://arxiv.org/abs/2103.14030</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr">
@@ -47954,17 +47960,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Cascade R-CNN (R101-FPN)</t>
+          <t>FSCE</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Cai &amp; Vasconcelos</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -47974,7 +47980,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -47982,24 +47988,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>AP 42.8</t>
-        </is>
-      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：FSCE 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
+          <t>https://arxiv.org/abs/2103.05950</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr">
@@ -48011,27 +48011,27 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>RetinaNet (R101)</t>
+          <t>MPSR</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Lin et al.</t>
+          <t>Wu et al.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -48039,24 +48039,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G57" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>AP 39.1</t>
-        </is>
-      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：MPSR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1708.02002</t>
+          <t>https://arxiv.org/abs/2007.09384</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr">
@@ -48068,27 +48062,27 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Mask R-CNN (R50-FPN)</t>
+          <t>TFA w/cos</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>He et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ICML</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -48096,24 +48090,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G58" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>AP 38.6 (R50-FPN box AP, Detectron2)</t>
-        </is>
-      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：TFA w/cos 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1703.06870</t>
+          <t>https://arxiv.org/abs/2003.06957</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
@@ -48125,27 +48113,27 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Faster R-CNN (R50-FPN)</t>
+          <t>Meta R-CNN</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Yan et al.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -48153,24 +48141,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G59" s="3" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>AP 40.2 val (Detectron2)</t>
-        </is>
-      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta R-CNN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
+          <t>https://arxiv.org/abs/1909.13032</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
@@ -48187,22 +48169,22 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
+          <t>FSRW</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
+          <t>Kang et al.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -48216,12 +48198,12 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Exploring Hierarchical Consistency and Unbiased Ob 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：FSRW 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.23344</t>
+          <t>https://arxiv.org/abs/1812.01866</t>
         </is>
       </c>
       <c r="M60" s="6" t="inlineStr">
@@ -48233,17 +48215,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -48267,12 +48249,12 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：UHR-DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Exploring Hierarchical Consistency and Unbiased Ob 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://arxiv.org/abs/2604.23344</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr">
@@ -48289,22 +48271,22 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -48318,12 +48300,12 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Brain-Inspired Spiking Neural Networks for Energy- 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：UHR-DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -48340,7 +48322,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Believing is Seeing</t>
+          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -48369,12 +48351,12 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Believing is Seeing 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Brain-Inspired Spiking Neural Networks for Energy- 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr">
@@ -48391,7 +48373,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>OW-OVD</t>
+          <t>Believing is Seeing</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -48420,12 +48402,12 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：OW-OVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Believing is Seeing 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M64" s="6" t="inlineStr">
@@ -48442,7 +48424,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Shift the Lens</t>
+          <t>OW-OVD</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -48471,12 +48453,12 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Shift the Lens 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：OW-OVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr">
@@ -48493,7 +48475,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Mr. DETR</t>
+          <t>Shift the Lens</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -48522,12 +48504,12 @@
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Mr. DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Shift the Lens 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -48539,12 +48521,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
+          <t>Mr. DETR</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -48573,12 +48555,12 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Visual Consensus Prompting for Co-Salient Object Detect 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Mr. DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -48590,12 +48572,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Language-Guided Salient Object Ranking</t>
+          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -48624,12 +48606,12 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Language-Guided Salient Object Ranking 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Visual Consensus Prompting for Co-Salient Object Detect 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -48646,7 +48628,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>Language-Guided Salient Object Ranking</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -48675,12 +48657,12 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Test-Time Backdoor Detection for Object Detection Model 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Language-Guided Salient Object Ranking 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -48697,7 +48679,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -48726,12 +48708,12 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Search and Detect 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Test-Time Backdoor Detection for Object Detection Model 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -48748,7 +48730,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>ROD-MLLM</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -48777,12 +48759,12 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ROD-MLLM 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Search and Detect 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -48799,7 +48781,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>ROD-MLLM</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -48828,12 +48810,12 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：SET 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：ROD-MLLM 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -48850,7 +48832,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>ReDiffDet</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -48879,12 +48861,12 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ReDiffDet 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：SET 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr">
@@ -48901,7 +48883,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Towards RAW Object Detection in Diverse Conditions</t>
+          <t>ReDiffDet</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -48930,12 +48912,12 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Towards RAW Object Detection in Diverse Conditions 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：ReDiffDet 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -48952,7 +48934,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
+          <t>Towards RAW Object Detection in Diverse Conditions</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -48981,12 +48963,12 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Pseudo Visible Feature Fine-Grained Fusion for Thermal  為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Towards RAW Object Detection in Diverse Conditions 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -49003,7 +48985,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>DEIM</t>
+          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -49032,12 +49014,12 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 重複條目：DEIM headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
+          <t>⚠️ 待 PDF 個別驗證：Pseudo Visible Feature Fine-Grained Fusion for Thermal  為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -49054,7 +49036,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>DEIM</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -49083,12 +49065,12 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Revisiting Generative Replay for Class Incremental Obje 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 重複條目：DEIM headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -49105,7 +49087,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>MI-DETR</t>
+          <t>Revisiting Generative Replay for Class Incremental Object De</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -49134,12 +49116,12 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：MI-DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Revisiting Generative Replay for Class Incremental Obje 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M78" s="6" t="inlineStr">
@@ -49156,7 +49138,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Fractal Calibration for Long-tailed Object Detection</t>
+          <t>MI-DETR</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -49185,12 +49167,12 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Fractal Calibration for Long-tailed Object Detection 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：MI-DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr">
@@ -49207,7 +49189,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Open-World Objectness Modeling Unifies Novel Object Detectio</t>
+          <t>Fractal Calibration for Long-tailed Object Detection</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -49236,12 +49218,12 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Open-World Objectness Modeling Unifies Novel Object Det 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Fractal Calibration for Long-tailed Object Detection 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Open-World_Objectness_Modeling_Unifies_Novel_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M80" s="6" t="inlineStr">
@@ -49258,7 +49240,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Cubify Anything</t>
+          <t>Open-World Objectness Modeling Unifies Novel Object Detectio</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -49287,12 +49269,12 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Cubify Anything 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Open-World Objectness Modeling Unifies Novel Object Det 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Lazarow_Cubify_Anything_Scaling_Indoor_3D_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Open-World_Objectness_Modeling_Unifies_Novel_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr">
@@ -49309,7 +49291,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>Cubify Anything</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -49338,12 +49320,12 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Percept, Memory, and Imagine 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Cubify Anything 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Lazarow_Cubify_Anything_Scaling_Indoor_3D_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M82" s="6" t="inlineStr">
@@ -49360,7 +49342,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -49389,12 +49371,12 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：SimLTD 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Percept, Memory, and Imagine 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr">
@@ -49411,7 +49393,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -49440,12 +49422,12 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Learning Endogenous Attention for Incremental Obje 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：SimLTD 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M84" s="6" t="inlineStr">
@@ -49462,7 +49444,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>DiL</t>
+          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -49472,12 +49454,12 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -49491,12 +49473,12 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：DiL 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Learning Endogenous Attention for Incremental Obje 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr">
@@ -49513,7 +49495,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
+          <t>DiL</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -49542,12 +49524,12 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Bit-Flip Induced Latency Attacks in Object Detecti 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：DiL 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M86" s="6" t="inlineStr">
@@ -49564,7 +49546,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -49593,12 +49575,12 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Enhancing Novel Object Detection via Cooperative Founda 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Bit-Flip Induced Latency Attacks in Object Detecti 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr">
@@ -49615,7 +49597,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>ALPI</t>
+          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -49644,12 +49626,12 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ALPI 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Enhancing Novel Object Detection via Cooperative Founda 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lahlali_ALPI_Auto-Labeller_with_Proxy_Injection_for_3D_Object_Detection_using_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M88" s="6" t="inlineStr">
@@ -49666,7 +49648,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>AIC3DOD</t>
+          <t>ALPI</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -49695,12 +49677,12 @@
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：AIC3DOD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：ALPI 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Cheng_AIC3DOD_Advancing_Indoor_Class-Incremental_3D_Object_Detection_with_Point_Transformer_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lahlali_ALPI_Auto-Labeller_with_Proxy_Injection_for_3D_Object_Detection_using_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr">
@@ -49717,7 +49699,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>MaskVD</t>
+          <t>AIC3DOD</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -49746,12 +49728,12 @@
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：MaskVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：AIC3DOD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Cheng_AIC3DOD_Advancing_Indoor_Class-Incremental_3D_Object_Detection_with_Point_Transformer_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M90" s="6" t="inlineStr">
@@ -49768,7 +49750,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
+          <t>MaskVD</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -49797,12 +49779,12 @@
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Diffusion-Based Particle-DETR for BEV Perception 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：MaskVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr">
@@ -49814,12 +49796,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>PK-YOLO</t>
+          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -49848,12 +49830,12 @@
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：PK-YOLO 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Diffusion-Based Particle-DETR for BEV Perception 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M92" s="6" t="inlineStr">
@@ -49865,12 +49847,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Decoupled PROB</t>
+          <t>PK-YOLO</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -49899,12 +49881,12 @@
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Decoupled PROB 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：PK-YOLO 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Inoue_Decoupled_PROB_Decoupled_Query_Initialization_Tasks_and_Objectness-Class_Learning_for_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr">
@@ -49916,12 +49898,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3</t>
+          <t>Decoupled PROB</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -49944,24 +49926,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G94" s="3" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>AP 54.6 val2017 (R101 6x)</t>
-        </is>
-      </c>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
       <c r="I94" s="3" t="n"/>
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
+          <t>⚠️ 待 PDF 個別驗證：Decoupled PROB 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Inoue_Decoupled_PROB_Decoupled_Query_Initialization_Tasks_and_Objectness-Class_Learning_for_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M94" s="6" t="inlineStr">
@@ -50391,20 +50367,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -50484,22 +50484,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DyHead</t>
+          <t>DINO (Swin-L)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Mao et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -50507,14 +50507,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>37.3</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>42.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AP 37.3</t>
+          <t>AP=42.1</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -50524,17 +50522,17 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>≈55M</t>
+          <t>218M</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 Table — benchmark paper): 37.3 mAP on COCO-O OOD benchmark (DyHead detector)</t>
+          <t>✅ 已驗證 (COCO-O ICCV23 Table 7)：DINO Swin-L COCO-O mAP=42.1 (COCO mAP=58.5, +15.76 robustness)</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2307.12730</t>
+          <t>https://arxiv.org/abs/2203.03605</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -50551,7 +50549,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ViTDet (ViT-L)</t>
+          <t>DyHead</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -50574,14 +50572,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>37.3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AP 36.9</t>
+          <t>AP=37.3</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -50591,12 +50587,12 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>≈300M</t>
+          <t>≈55M</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 36.9 mAP on COCO-O OOD benchmark (ViTDet ViT-L)</t>
+          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 Table — benchmark paper): 37.3 mAP on COCO-O OOD benchmark (DyHead detector)</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -50618,7 +50614,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Cascade R-CNN</t>
+          <t>ViTDet (ViT-L)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -50641,14 +50637,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26.4</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>36.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AP 26.4</t>
+          <t>AP=36.9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -50658,12 +50652,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>88M</t>
+          <t>≈300M</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 26.4 mAP on COCO-O OOD benchmark (Cascade R-CNN)</t>
+          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 36.9 mAP on COCO-O OOD benchmark (ViTDet ViT-L)</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -50685,7 +50679,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Faster R-CNN baseline</t>
+          <t>Cascade R-CNN</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -50708,14 +50702,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21.5</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>26.4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AP 21.5</t>
+          <t>AP=26.4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -50725,12 +50717,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42M</t>
+          <t>88M</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 21.5 mAP on COCO-O OOD benchmark (Faster R-CNN baseline)</t>
+          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 26.4 mAP on COCO-O OOD benchmark (Cascade R-CNN)</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -50752,22 +50744,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>InternImage-H</t>
+          <t>Faster R-CNN baseline</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Mao et al.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -50775,14 +50767,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>21.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>COCO-O effective robustness; To verify</t>
+          <t>AP=21.5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -50792,17 +50782,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>≈1.08B</t>
+          <t>42M</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>⚠️ COCO-O paper Table 7 only tests Cascade Mask R-CNN InternImage-L (37.0), not InternImage-H. Need third-party COCO-O benchmark for H variant.</t>
+          <t>✅ verified (COCO-O ICCV23 arxiv 2307.12730 — benchmark paper): 21.5 mAP on COCO-O OOD benchmark (Faster R-CNN baseline)</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.05778</t>
+          <t>https://arxiv.org/abs/2307.12730</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -50819,22 +50809,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EVA-02-Det</t>
+          <t>InternImage-H</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Fang et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -50842,16 +50832,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -50859,17 +50841,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>≈600M</t>
+          <t>≈1.08B</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>⚠️ COCO-O paper Table 7 tests "EVA" (original, 57.8) not EVA-02. Need third-party COCO-O for EVA-02 specifically.</t>
+          <t>⚠️ InternImage-H: COCO-O benchmark paper (arxiv 2307.12730) 未測試此方法（0 次提及）；查無可驗證的 COCO-O AP — 此 robustness benchmark 多數現代 SOTA 未評估</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11331</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -50886,17 +50868,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Co-DETR</t>
+          <t>EVA-02-Det</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Zong et al.</t>
+          <t>Fang et al.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -50909,16 +50891,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -50926,17 +50900,17 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>304M</t>
+          <t>≈600M</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>⚠️ COCO-O paper Table 7 does not include Co-DETR. Need third-party benchmark.</t>
+          <t>⚠️ EVA-02-Det: COCO-O benchmark paper (arxiv 2307.12730) 未測試此方法（0 次提及）；查無可驗證的 COCO-O AP — 此 robustness benchmark 多數現代 SOTA 未評估</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.12860</t>
+          <t>https://arxiv.org/abs/2303.11331</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
@@ -50953,22 +50927,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>DINO (Swin-L)</t>
+          <t>Co-DETR</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Zong et al.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -50976,14 +50950,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Effective robustness AP 42.1 (COCO-O Table 7)</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -50991,17 +50959,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>218M</t>
+          <t>304M</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (COCO-O ICCV23 Table 7)：DINO Swin-L COCO-O mAP=42.1 (COCO mAP=58.5, +15.76 robustness)</t>
+          <t>⚠️ Co-DETR: COCO-O benchmark paper (arxiv 2307.12730) 未測試此方法（0 次提及）；查無可驗證的 COCO-O AP — 此 robustness benchmark 多數現代 SOTA 未評估</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.03605</t>
+          <t>https://arxiv.org/abs/2211.12860</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -51041,16 +51009,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>99</t>
@@ -51063,7 +51023,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>⚠️ COCO-O paper Table 7 (2023) predates YOLOv8 widespread testing. Need updated COCO-O eval.</t>
+          <t>⚠️ YOLOv8x: COCO-O benchmark paper (arxiv 2307.12730) 未測試此方法（0 次提及）；查無可驗證的 COCO-O AP — 此 robustness benchmark 多數現代 SOTA 未評估</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -51108,16 +51068,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>T4 74</t>
@@ -51130,7 +51082,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>⚠️ COCO-O paper Table 7 does not include RT-DETR. Need third-party benchmark.</t>
+          <t>⚠️ RT-DETR: COCO-O benchmark paper (arxiv 2307.12730) 未測試此方法（0 次提及）；查無可驗證的 COCO-O AP — 此 robustness benchmark 多數現代 SOTA 未評估</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -51175,16 +51127,8 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>To verify</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -51197,7 +51141,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>⚠️ COCO-O paper Table 7 does not include Grounding DINO 1.5 Pro. Need third-party benchmark.</t>
+          <t>⚠️ Grounding DINO 1.5 Pro: COCO-O benchmark paper (arxiv 2307.12730) 未測試此方法（0 次提及）；查無可驗證的 COCO-O AP — 此 robustness benchmark 多數現代 SOTA 未評估</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -51283,57 +51283,47 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DINO (Swin-L)</t>
+          <t>InternImage-H</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>91.4</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>mAP 91.4 (fine-tuned)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>218M</t>
-        </is>
-      </c>
+          <t>mAP@0.5=94.0</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 91.4 mAP on VOC 2007 — DINO (Zhang et al. ICLR 2023, arxiv 2203.03605) primarily reports COCO val (63.3 AP); VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
+          <t>✅ 已驗證 (InternImage CVPR23 Table 10)：InternImage-H 94.0 AP50 PASCAL VOC 2007 test (single-scale), Objects365 pretrain</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.03605</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -51345,27 +51335,27 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>YOLOv7</t>
+          <t>DINO (Swin-L)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -51373,34 +51363,32 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>89.7</t>
-        </is>
+      <c r="G3" s="3" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>mAP 89.7</t>
+          <t>mAP@0.5=91.4</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>71.3M</t>
+          <t>218M</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 89.7 mAP on VOC 2007 — YOLOv7 (Wang et al. CVPR 2023, arxiv 2207.02696) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper or official benchmark.</t>
+          <t>⚠️ 91.4 mAP on VOC 2007 — DINO (Zhang et al. ICLR 2023, arxiv 2203.03605) primarily reports COCO val (63.3 AP); VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2207.02696</t>
+          <t>https://arxiv.org/abs/2203.03605</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -51417,57 +51405,55 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>YOLOv4</t>
+          <t>YOLOv7</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Bochkovskiy et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>89.4</t>
-        </is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>89.7</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>mAP 89.4 (with COCO pretrain)</t>
+          <t>mAP@0.5=89.7</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>64M</t>
+          <t>71.3M</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 89.4 mAP on VOC 2007 — YOLOv4 (Bochkovskiy et al. arxiv 2020) mentions VOC evaluation; specific mAP number needs manual paper-table confirmation. May be from community benchmark.</t>
+          <t>⚠️ 89.7 mAP on VOC 2007 — YOLOv7 (Wang et al. CVPR 2023, arxiv 2207.02696) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper or official benchmark.</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2004.10934</t>
+          <t>https://arxiv.org/abs/2207.02696</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
@@ -51479,62 +51465,60 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Cascade R-CNN</t>
+          <t>YOLOv4</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Cai &amp; Vasconcelos</t>
+          <t>Bochkovskiy et al.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>mAP 87.0</t>
+          <t>mAP@0.5=89.4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88M</t>
+          <t>64M</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 87.0 mAP on VOC 2007 — Cascade R-CNN (Cai &amp; Vasconcelos CVPR 2018) primarily reports COCO; VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ 89.4 mAP on VOC 2007 — YOLOv4 (Bochkovskiy et al. arxiv 2020) mentions VOC evaluation; specific mAP number needs manual paper-table confirmation. May be from community benchmark.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
+          <t>https://arxiv.org/abs/2004.10934</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
@@ -51551,22 +51535,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DETR</t>
+          <t>Cascade R-CNN</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Cai &amp; Vasconcelos</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -51574,34 +51558,32 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>87</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>mAP 85.4 (estimated)</t>
+          <t>mAP@0.5=87.0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60M</t>
+          <t>88M</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 85.4 mAP on VOC 2007 — DETR (Carion et al. ECCV 2020, arxiv 2005.12872) primarily reports COCO val (45.1 AP); VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ 87.0 mAP on VOC 2007 — Cascade R-CNN (Cai &amp; Vasconcelos CVPR 2018) primarily reports COCO; VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/1712.00726</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -51618,22 +51600,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Sparse R-CNN</t>
+          <t>DETR</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -51641,34 +51623,32 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>85.40000000000001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>mAP 85.0 (fine-tuned)</t>
+          <t>mAP@0.5=85.4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>106M</t>
+          <t>60M</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 85.0 mAP on VOC 2007 — Sparse R-CNN (Sun et al. CVPR 2021, arxiv 2011.12450) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ 85.4 mAP on VOC 2007 — DETR (Carion et al. ECCV 2020, arxiv 2005.12872) primarily reports COCO val (45.1 AP); VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -51685,22 +51665,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RetinaNet (R101)</t>
+          <t>Sparse R-CNN</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Lin et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -51708,34 +51688,32 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>82.7</t>
-        </is>
+      <c r="G8" s="2" t="n">
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>mAP 82.7</t>
+          <t>mAP@0.5=85.0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57M</t>
+          <t>106M</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 82.7 mAP on VOC 2007 — RetinaNet (Lin et al. ICCV 2017, arxiv 1708.02002) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ 85.0 mAP on VOC 2007 — Sparse R-CNN (Sun et al. CVPR 2021, arxiv 2011.12450) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1708.02002</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
@@ -51747,62 +51725,52 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Faster R-CNN (VGG16)</t>
+          <t>DETReg</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Bar et al.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2015-12</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>73.2</t>
-        </is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>83.3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>mAP 73.2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>138M</t>
-        </is>
-      </c>
+          <t>mAP@0.5=83.3</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (Ren et al. NeurIPS 2015, original Faster R-CNN paper Table 3): VOC 2007 test mAP 73.2% (VGG16 backbone, trained on VOC 2007 trainval)</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 2)：DETReg AP50=83.3 PASCAL VOC 2007 test (Deformable DETR base, 07+12 finetune)</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
+          <t>https://arxiv.org/abs/2106.04550</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -51814,58 +51782,60 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>YOLOv8x</t>
+          <t>RetinaNet (R101)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Ultralytics</t>
+          <t>Lin et al.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>82.7</v>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>mAP@0.5=82.7</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>68.2M</t>
+          <t>57M</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>⚠️ YOLOv8x (Ultralytics 2023) has no peer-reviewed paper; community evaluations report VOC 2007 mAP ~95+ depending on config. Specific mAP@0.5 not from a paper-reported table — needs official Ultralytics VOC benchmark report to confirm exact value.</t>
+          <t>⚠️ 82.7 mAP on VOC 2007 — RetinaNet (Lin et al. ICCV 2017, arxiv 1708.02002) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper.</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>https://docs.ultralytics.com/models/yolov8/</t>
+          <t>https://arxiv.org/abs/1708.02002</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -51877,58 +51847,60 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>YOLO-NAS</t>
+          <t>Faster R-CNN (VGG16)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Deci</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2015-12</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>73.2</v>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>mAP@0.5=73.2</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>T4 ≈110</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>≈58M</t>
+          <t>138M</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>⚠️ YOLO-NAS (Deci AI 2023) has no peer-reviewed paper; official Deci benchmarks focus on COCO. PASCAL VOC 2007 mAP not in official Deci release documentation. Needs official YOLO-NAS VOC benchmark report.</t>
+          <t>✅ verified (Ren et al. NeurIPS 2015, original Faster R-CNN paper Table 3): VOC 2007 test mAP 73.2% (VGG16 backbone, trained on VOC 2007 trainval)</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/Deci-AI/super-gradients</t>
+          <t>https://arxiv.org/abs/1506.01497</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -51945,53 +51917,47 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Grounding DINO (zero-shot)</t>
+          <t>Faster R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n"/>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>73.2</v>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Zero-shot mAP To verify</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>≈173M</t>
-        </is>
-      </c>
+          <t>mAP@0.5=73.2</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Grounding DINO zero-shot transfer on VOC 2007: model is open-vocabulary, not trained on VOC. Zero-shot transfer AP not found in Grounding DINO paper (Liu et al. ECCV 2024, arxiv 2303.05499). Needs manual PDF or supplementary check.</t>
+          <t>✅ 已驗證 (Faster R-CNN NeurIPS15 Table 7)：VGG backbone, 07+12 trainval → 73.2% PASCAL VOC 2007 test mAP（注：original paper variant；R50-FPN 是後來 Detectron2 改版）</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/1506.01497</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
@@ -52008,41 +51974,53 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RF-DETR (Large)</t>
+          <t>YOLOv8x</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>Ultralytics</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>68.2M</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>⚠️ RF-DETR (ICLR 2026) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RF-DETR focuses on COCO and Roboflow100-VL benchmarks for real-time detection. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ YOLOv8x (Ultralytics 2023) has no peer-reviewed paper; community evaluations report VOC 2007 mAP ~95+ depending on config. Specific mAP@0.5 not from a paper-reported table — needs official Ultralytics VOC benchmark report to confirm exact value.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://docs.ultralytics.com/models/yolov8/</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
@@ -52059,41 +52037,53 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>RF-DETR (Nano)</t>
+          <t>YOLO-NAS</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>Deci</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>To verify</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>T4 ≈110</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>≈58M</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>⚠️ RF-DETR Nano (ICLR 2026) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RF-DETR focuses on COCO and Roboflow100-VL benchmarks for real-time detection. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ YOLO-NAS (Deci AI 2023) has no peer-reviewed paper; official Deci benchmarks focus on COCO. PASCAL VOC 2007 mAP not in official Deci release documentation. Needs official YOLO-NAS VOC benchmark report.</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://github.com/Deci-AI/super-gradients</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
@@ -52105,46 +52095,58 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>YOLOv13-X</t>
+          <t>Grounding DINO (zero-shot)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>iMoonLab</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Zero-shot mAP To verify</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>≈173M</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>⚠️ YOLOv13-X (arxiv 2506.17733) performs cross-domain evaluation: models trained on COCO are tested on PASCAL VOC 2007 as a generalization benchmark, not as a standard closed-set training+test protocol. Cross-domain transfer AP is not directly comparable to methods trained on VOC 2007 trainval. The specific cross-domain transfer AP number needs verification from the full PDF.</t>
+          <t>⚠️ Grounding DINO zero-shot transfer on VOC 2007: model is open-vocabulary, not trained on VOC. Zero-shot transfer AP not found in Grounding DINO paper (Liu et al. ECCV 2024, arxiv 2303.05499). Needs manual PDF or supplementary check.</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
@@ -52156,27 +52158,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>RF-DETR (Large)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -52190,12 +52192,12 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Grounding DINO (Liu et al. ECCV 2024, arxiv 2303.05499) is an open-vocabulary detector evaluated on COCO val2017, LVIS v1.0, and ODinW-13 benchmarks. It does NOT report standard PASCAL VOC 2007 closed-set 20-class mAP@0.5 (open-vocabulary protocol is not comparable to closed-set VOC evaluation). The "zero-shot VOC" row r12 captures its transfer performance separately.</t>
+          <t>⚠️ RF-DETR (ICLR 2026) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RF-DETR focuses on COCO and Roboflow100-VL benchmarks for real-time detection. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
@@ -52207,27 +52209,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Relation-DETR (FocalNet-L)</t>
+          <t>RF-DETR (Nano)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Hou et al.</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -52241,12 +52243,12 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Relation-DETR (ECCV 2024) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Evaluated on COCO val2017 and test-dev; FocalNet-L backbone. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ RF-DETR Nano (ICLR 2026) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RF-DETR focuses on COCO and Roboflow100-VL benchmarks for real-time detection. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2407.11699</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
@@ -52258,17 +52260,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Grounding DINO 1.5 Pro</t>
+          <t>YOLOv13-X</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>iMoonLab</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -52278,7 +52280,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -52292,12 +52294,12 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Grounding DINO 1.5 Pro (arxiv 2405.10300) is an open-vocabulary detector evaluated on COCO, LVIS, ODinW; does NOT report standard PASCAL VOC 2007 closed-set mAP@0.5. Open-vocabulary results are not comparable to closed-set VOC ranking.</t>
+          <t>⚠️ YOLOv13-X (arxiv 2506.17733) performs cross-domain evaluation: models trained on COCO are tested on PASCAL VOC 2007 as a generalization benchmark, not as a standard closed-set training+test protocol. Cross-domain transfer AP is not directly comparable to methods trained on VOC 2007 trainval. The specific cross-domain transfer AP number needs verification from the full PDF.</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.10300</t>
+          <t>https://arxiv.org/abs/2506.17733</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
@@ -52309,27 +52311,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>InternImage-H</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -52337,24 +52339,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>mAP@0.5 94.0 (single-scale)</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (InternImage CVPR23 Table 10)：InternImage-H 94.0 AP50 PASCAL VOC 2007 test (single-scale), Objects365 pretrain</t>
+          <t>⚠️ Grounding DINO (Liu et al. ECCV 2024, arxiv 2303.05499) is an open-vocabulary detector evaluated on COCO val2017, LVIS v1.0, and ODinW-13 benchmarks. It does NOT report standard PASCAL VOC 2007 closed-set 20-class mAP@0.5 (open-vocabulary protocol is not comparable to closed-set VOC evaluation). The "zero-shot VOC" row r12 captures its transfer performance separately.</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.05778</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
@@ -52366,27 +52362,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RTMDet-X</t>
+          <t>Relation-DETR (FocalNet-L)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Lyu et al.</t>
+          <t>Hou et al.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -52400,12 +52396,12 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>⚠️ RTMDet-X (arXiv 2022) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RTMDet-X evaluated on COCO val2017 (52.8 AP) and CrowdHuman; no PASCAL VOC 2007 evaluation in paper. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ Relation-DETR (ECCV 2024) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Evaluated on COCO val2017 and test-dev; FocalNet-L backbone. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2212.07784</t>
+          <t>https://arxiv.org/abs/2407.11699</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
@@ -52417,27 +52413,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Meta-DETR</t>
+          <t>Grounding DINO 1.5 Pro</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TPAMI</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -52451,12 +52447,12 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Meta-DETR (Zhang et al. TPAMI 2022, arxiv 2208.00219) is a few-shot OD method. It evaluates on MS-COCO novel AP at K-shot (1/5/10/30) — see MS-COCO few-shot sheets. It does NOT report standard PASCAL VOC 2007 20-class closed-set mAP@0.5. This entry is misplaced; should be in COCO few-shot sheets only.</t>
+          <t>⚠️ Grounding DINO 1.5 Pro (arxiv 2405.10300) is an open-vocabulary detector evaluated on COCO, LVIS, ODinW; does NOT report standard PASCAL VOC 2007 closed-set mAP@0.5. Open-vocabulary results are not comparable to closed-set VOC ranking.</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2208.00219</t>
+          <t>https://arxiv.org/abs/2405.10300</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
@@ -52468,27 +52464,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>DETReg</t>
+          <t>RTMDet-X</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Bar et al.</t>
+          <t>Lyu et al.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -52496,24 +52492,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>mAP@0.5 83.3 (AP50)</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETReg CVPR22 Table 2)：DETReg AP50=83.3 PASCAL VOC 2007 test (Deformable DETR base, 07+12 finetune)</t>
+          <t>⚠️ RTMDet-X (arXiv 2022) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RTMDet-X evaluated on COCO val2017 (52.8 AP) and CrowdHuman; no PASCAL VOC 2007 evaluation in paper. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.04550</t>
+          <t>https://arxiv.org/abs/2212.07784</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
@@ -52530,22 +52520,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>DeFRCN</t>
+          <t>Meta-DETR</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Qiao et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>TPAMI</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -52559,12 +52549,12 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 誤放：DeFRCN 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
+          <t>⚠️ Meta-DETR (Zhang et al. TPAMI 2022, arxiv 2208.00219) is a few-shot OD method. It evaluates on MS-COCO novel AP at K-shot (1/5/10/30) — see MS-COCO few-shot sheets. It does NOT report standard PASCAL VOC 2007 20-class closed-set mAP@0.5. This entry is misplaced; should be in COCO few-shot sheets only.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.09017</t>
+          <t>https://arxiv.org/abs/2208.00219</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
@@ -52581,22 +52571,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FSCE</t>
+          <t>DeFRCN</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Qiao et al.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -52610,12 +52600,12 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 誤放：FSCE 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
+          <t>⚠️ 誤放：DeFRCN 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.05950</t>
+          <t>https://arxiv.org/abs/2108.09017</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
@@ -52627,27 +52617,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PoolNet+</t>
+          <t>FSCE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>TPAMI</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -52661,12 +52651,12 @@
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al. TPAMI 2022, arxiv 1904.09569) is a Salient Object Detection (SOD) method — NOT a standard object detection method. It evaluates on SOD benchmarks (DUTS-TE, DUT-OMRON, ECSSD, HKU-IS, PASCAL-S) using S-measure/MAE/F-measure. It does NOT evaluate on PASCAL VOC 2007 20-class mAP. This entry is misplaced; should only appear in SOD sheets.</t>
+          <t>⚠️ 誤放：FSCE 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.09569</t>
+          <t>https://arxiv.org/abs/2103.05950</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
@@ -52678,27 +52668,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MPSR</t>
+          <t>PoolNet+</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Wu et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>TPAMI</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -52712,12 +52702,12 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 誤放：MPSR 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
+          <t>⚠️ PoolNet+ (Liu et al. TPAMI 2022, arxiv 1904.09569) is a Salient Object Detection (SOD) method — NOT a standard object detection method. It evaluates on SOD benchmarks (DUTS-TE, DUT-OMRON, ECSSD, HKU-IS, PASCAL-S) using S-measure/MAE/F-measure. It does NOT evaluate on PASCAL VOC 2007 20-class mAP. This entry is misplaced; should only appear in SOD sheets.</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2007.09384</t>
+          <t>https://arxiv.org/abs/1904.09569</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
@@ -52734,22 +52724,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TFA w/cos</t>
+          <t>MPSR</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Wu et al.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -52763,12 +52753,12 @@
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 誤放：TFA w/cos 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
+          <t>⚠️ 誤放：MPSR 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2003.06957</t>
+          <t>https://arxiv.org/abs/2007.09384</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr">
@@ -52780,27 +52770,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>EfficientDet-D7</t>
+          <t>TFA w/cos</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tan et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICML</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -52814,12 +52804,12 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>⚠️ EfficientDet-D7 (CVPR 2020) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Tan et al. CVPR 2020: evaluated on COCO test-dev only (52.2 AP). No PASCAL VOC 2007 evaluation in the EfficientDet paper. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ 誤放：TFA w/cos 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1911.09070</t>
+          <t>https://arxiv.org/abs/2003.06957</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
@@ -52831,27 +52821,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Meta R-CNN</t>
+          <t>EfficientDet-D7</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Yan et al.</t>
+          <t>Tan et al.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -52865,12 +52855,12 @@
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 誤放：Meta R-CNN 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
+          <t>⚠️ EfficientDet-D7 (CVPR 2020) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Tan et al. CVPR 2020: evaluated on COCO test-dev only (52.2 AP). No PASCAL VOC 2007 evaluation in the EfficientDet paper. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1909.13032</t>
+          <t>https://arxiv.org/abs/1911.09070</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
@@ -52887,12 +52877,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FSRW</t>
+          <t>Meta R-CNN</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Kang et al.</t>
+          <t>Yan et al.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -52916,12 +52906,12 @@
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 誤放：FSRW 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
+          <t>⚠️ 誤放：Meta R-CNN 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1812.01866</t>
+          <t>https://arxiv.org/abs/1909.13032</t>
         </is>
       </c>
       <c r="M30" s="9" t="inlineStr">
@@ -52933,27 +52923,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>FSRW</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Kang et al.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -52967,12 +52957,12 @@
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>⚠️ CenterNet (Objects as Points) (arXiv 2019) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Zhou et al. arXiv 1904.07850: evaluated on MS COCO val2017 and KITTI (3D OD) and COCO keypoints. No standard PASCAL VOC 2007 AP evaluation in paper. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ 誤放：FSRW 是 few-shot OD 方法，使用 PASCAL VOC novel splits（K-shot）而非標準 closed-set 20-class mAP；應移至 PASCAL VOC 2007 15+5 sheet 而非此 sheet</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/1812.01866</t>
         </is>
       </c>
       <c r="M31" s="9" t="inlineStr">
@@ -52989,22 +52979,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Faster R-CNN (R50-FPN)</t>
+          <t>CenterNet</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -53012,24 +53002,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>mAP@0.5 73.2 (VGG, 07+12)</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Faster R-CNN NeurIPS15 Table 7)：VGG backbone, 07+12 trainval → 73.2% PASCAL VOC 2007 test mAP（注：original paper variant；R50-FPN 是後來 Detectron2 改版）</t>
+          <t>⚠️ CenterNet (Objects as Points) (arXiv 2019) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Zhou et al. arXiv 1904.07850: evaluated on MS COCO val2017 and KITTI (3D OD) and COCO keypoints. No standard PASCAL VOC 2007 AP evaluation in paper. This entry is misplaced or pending migration to a COCO sheet.</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
+          <t>https://arxiv.org/abs/1904.07850</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
@@ -53806,28 +53790,28 @@
   </sheetData>
   <autoFilter ref="A1:M12"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -53938,14 +53938,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>94.1</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>94.09999999999999</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AP 94.1 / MR 41.5</t>
+          <t>AP=94.1 | MR^-2=41.5</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -54005,14 +54003,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AP 91.6 / MR 43.7</t>
+          <t>AP=91.6 | MR^-2=43.7</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -54072,14 +54068,12 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>91.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AP 91.5</t>
+          <t>AP=91.5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -54139,14 +54133,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91.3</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>91.3</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AP 91.3</t>
+          <t>AP=91.3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -54206,14 +54198,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>90.7</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>90.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AP 90.7 / MR 41.4</t>
+          <t>AP=90.7 | MR^-2=41.4</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -54273,14 +54263,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>90.7</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>90.7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>AP 90.7 / MR 41.4</t>
+          <t>AP=90.7 | MR^-2=41.4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -54340,14 +54328,12 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
+      <c r="G8" s="3" t="n">
+        <v>89.5</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP 89.5</t>
+          <t>AP=89.5</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -54407,14 +54393,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>89.3</t>
-        </is>
+      <c r="G9" s="2" t="n">
+        <v>89.3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>AP 89.3 / MR 43.4</t>
+          <t>AP=89.3 | MR^-2=43.4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -54474,14 +54458,12 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
+      <c r="G10" s="2" t="n">
+        <v>85</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>AP 85.0 / MR 50.4</t>
+          <t>AP=85.0 | MR^-2=50.4</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -54718,19 +54700,13 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>AP 57.5 (D-FINE-L w/ DEIM, 120 epochs)</t>
-        </is>
-      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 3)：D-FINE-L w/ DEIM 57.5 AP on CrowdHuman (120 epochs)</t>
+          <t>⚠️ DEIM-D-FINE-L: 57.5 為 COCO val AP（D-FINE-L+DEIM），非 CrowdHuman AP；DEIM/D-FINE 原論文未測 CrowdHuman — 誤放</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -54877,19 +54853,13 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>AP 97.2 (Table 10 box AP)</t>
-        </is>
-      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (InternImage CVPR23 Table 10)：InternImage-H 97.2 AP CrowdHuman (+3.1 over previous best PP-YOLOE 94.1)</t>
+          <t>⚠️ InternImage-H: 97.2 對 CrowdHuman 異常偏高（SOTA AP≈94）；InternImage Table 10 為 LVIS 非 CrowdHuman — 需查證</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -54985,19 +54955,13 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>AP 57.5 (DEIM-D-FINE-L)</t>
-        </is>
-      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 3)：DEIM-D-FINE-L headline 57.5 AP CrowdHuman</t>
+          <t>⚠️ DEIM: 57.5 為 COCO val AP，非 CrowdHuman AP；DEIM 原論文未測 CrowdHuman — 誤放</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -37340,55 +37340,47 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Detic</t>
+          <t>Co-DETR (ViT-L)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Zong et al.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>41.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AP 41.7 LVIS</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>≈100M</t>
-        </is>
-      </c>
+          <t>AP=67.9</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Detic CVPR22 abstract)：41.7 mAP on standard LVIS benchmark [Open-vocab OD via ImageNet-21K]</t>
+          <t>✅ verified (Co-DETR arxiv 2211.12860 abstract): LVIS val AP=67.9</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.02605</t>
+          <t>https://arxiv.org/abs/2211.12860</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr">
@@ -37400,27 +37392,27 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Grounding DINO 1.5 Pro</t>
+          <t>EVA-02 (Det)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Fang et al.</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>arXiv→IVC</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -37429,31 +37421,23 @@
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>55.7</v>
+        <v>65.2</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>AP 55.7 LVIS-minival</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=65.2</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO 1.5 Pro paper)：55.7 AP on LVIS-minival zero-shot [Open-set OD]</t>
+          <t>✅ 已驗證 (EVA-02-Det arXiv23 abstract)：65.2 box AP / 57.3 mask AP on LVIS val [Foundation Model OD]</t>
         </is>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.10300</t>
+          <t>https://arxiv.org/abs/2303.11331</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
@@ -37470,55 +37454,47 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>InternImage-H</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>33.9</v>
+        <v>63.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AP 33.9 LVIS-mini</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>≈173M</t>
-        </is>
-      </c>
+          <t>AP=63.2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1 cite)：Grounding DINO (Swin-L) achieves 33.9 AP on LVIS-mini zero-shot [Open-set OD]</t>
+          <t>✅ 已驗證 (InternImage CVPR23 Table 10)：InternImage-H 63.2 box AP LVIS v1.0 val (multi-scale)；LVIS-minival 65.8</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/2211.05778</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
@@ -37535,35 +37511,35 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>GLIP-L</t>
+          <t>DINO-X</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.9</v>
+        <v>59.8</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AP 26.9 LVIS-val zero-shot</t>
+          <t>AP=59.8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -37573,17 +37549,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>430M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (GLIP-L CVPR22 paper text)：26.9 AP on LVIS val (zero-shot, all categories) — paper "directly evaluated... 26.9 AP on LVIS val" [Grounded VLM]</t>
+          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 59.8 AP on LVIS-minival, 52.4 AP on LVIS-val [Open-vocab OD]</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2112.03857</t>
+          <t>https://arxiv.org/abs/2411.14347</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
@@ -37595,40 +37571,40 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>OWLv2</t>
+          <t>Grounding DINO 1.5 Pro</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Minderer et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>47</v>
+        <v>55.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AP 47.0 LVIS-val (OWL-ST+FT SigLIP G/14)</t>
+          <t>AP=55.7</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -37643,12 +37619,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (OWLv2 paper Table 1)：OWL-ST+FT SigLIP G/14 → LVIS APval all=47.0, APrare=47.2; 大幅優於 OWL-ViT (34.6) [Open-vocab Foundation Model]</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro paper)：55.7 AP on LVIS-minival zero-shot [Open-set OD]</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2306.09683</t>
+          <t>https://arxiv.org/abs/2405.10300</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -37665,12 +37641,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>DINO-X</t>
+          <t>EVA-02-L (LVIS ft)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>Fang et al.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -37680,20 +37656,20 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>59.8</v>
+        <v>55</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>AP 59.8 LVIS-minival</t>
+          <t>AP=55.0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -37703,17 +37679,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>≈600M</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 59.8 AP on LVIS-minival, 52.4 AP on LVIS-val [Open-vocab OD]</t>
+          <t>✅ verified (paper-reported via workbook col 8): EVA-02-L LVIS fine-tuned ~55 box AP (paper-reported via workbook col 8)</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2411.14347</t>
+          <t>https://arxiv.org/abs/2303.11331</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -37730,22 +37706,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>YOLO-World</t>
+          <t>OWLv2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Cheng et al.</t>
+          <t>Minderer et al.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -37754,16 +37730,16 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>35.4</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>AP 35.4 LVIS</t>
+          <t>AP=47.0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>T4 fast</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -37773,12 +37749,12 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLO-World CVPR24 abstract)：35.4 AP on LVIS with 52 FPS on V100 [Open-vocab Real-Time OD]</t>
+          <t>✅ 已驗證 (OWLv2 paper Table 1)：OWL-ST+FT SigLIP G/14 → LVIS APval all=47.0, APrare=47.2; 大幅優於 OWL-ViT (34.6) [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.17270</t>
+          <t>https://arxiv.org/abs/2306.09683</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
@@ -37795,55 +37771,47 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>RegionCLIP</t>
+          <t>ViTDet (ViT-H, MAE)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Zhong et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>32.3</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>AP 32.3 LVIS</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=46.0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RegionCLIP CVPR22 Table)：RegionCLIP 32.3 LVIS AP (open-vocab) [Region-aware CLIP for OD]</t>
+          <t>✅ 已驗證 (ViTDet ECCV22 Table 7)：ViTDet ViT-H MAE 46.0 box AP / 34.3 mask AP / 51.2 APrare on LVIS</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2112.09106</t>
+          <t>https://arxiv.org/abs/2203.16527</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -37860,22 +37828,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UniDetector</t>
+          <t>Detic</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -37884,11 +37852,11 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>24</v>
+        <v>41.7</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>AP 24.0 LVIS rare AP (UniDetector)</t>
+          <t>AP=41.7</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -37898,17 +37866,17 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>≈100M</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (paper-reported via workbook col 8): UniDetector LVIS rare class AP ~24 (paper-reported via workbook col 8)</t>
+          <t>✅ 已驗證 (Detic CVPR22 abstract)：41.7 mAP on standard LVIS benchmark [Open-vocab OD via ImageNet-21K]</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11749</t>
+          <t>https://arxiv.org/abs/2201.02605</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
@@ -37953,7 +37921,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>AP 41.7 LVIS-val (open-vocab)</t>
+          <t>AP=41.7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -37990,22 +37958,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>EVA-02-L (LVIS ft)</t>
+          <t>YOLO-World</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fang et al.</t>
+          <t>Cheng et al.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -38014,31 +37982,31 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>55</v>
+        <v>35.4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>AP 55.0 LVIS-val box AP (EVA-02-L fine-tuned)</t>
+          <t>AP=35.4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>T4 fast</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>≈600M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (paper-reported via workbook col 8): EVA-02-L LVIS fine-tuned ~55 box AP (paper-reported via workbook col 8)</t>
+          <t>✅ 已驗證 (YOLO-World CVPR24 abstract)：35.4 AP on LVIS with 52 FPS on V100 [Open-vocab Real-Time OD]</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11331</t>
+          <t>https://arxiv.org/abs/2401.17270</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
@@ -38050,46 +38018,60 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>AP=33.9</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>≈173M</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary OD (arxiv 2604.23344) is an open-vocabulary OD paper that likely reports LVIS AP. Specific LVIS val AP not extractable without PDF access (very recent paper, May 2026). Needs manual PDF verification to obtain exact AP number.</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1 cite)：Grounding DINO (Swin-L) achieves 33.9 AP on LVIS-mini zero-shot [Open-set OD] ⚠️ 注意：此為 LVIS-minival split（非 val），與 val box AP 不直接可比</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.23344</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M13" s="9" t="n"/>
@@ -38102,47 +38084,55 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Co-DETR (ViT-L)</t>
+          <t>RegionCLIP</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Zong et al.</t>
+          <t>Zhong et al.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>32.3</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Co-DETR ViT-L 67.9 AP on LVIS val (COCO+LVIS jointly trained)</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
+          <t>AP=32.3</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>✅ verified (Co-DETR arxiv 2211.12860 abstract): LVIS val AP=67.9</t>
+          <t>✅ 已驗證 (RegionCLIP CVPR22 Table)：RegionCLIP 32.3 LVIS AP (open-vocab) [Region-aware CLIP for OD]</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.12860</t>
+          <t>https://arxiv.org/abs/2112.09106</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr">
@@ -38159,47 +38149,55 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>EVA-02 (Det)</t>
+          <t>GLIP-L</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fang et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>arXiv→IVC</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>65.2</v>
+        <v>26.9</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>box AP 65.2 LVIS val</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
+          <t>AP=26.9</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>430M</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (EVA-02-Det arXiv23 abstract)：65.2 box AP / 57.3 mask AP on LVIS val [Foundation Model OD]</t>
+          <t>✅ 已驗證 (GLIP-L CVPR22 paper text)：26.9 AP on LVIS val (zero-shot, all categories) — paper "directly evaluated... 26.9 AP on LVIS val" [Grounded VLM]</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11331</t>
+          <t>https://arxiv.org/abs/2112.03857</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
@@ -38216,7 +38214,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>InternImage-H</t>
+          <t>UniDetector</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -38236,27 +38234,35 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>63.2</v>
+        <v>24</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>AP 63.2 LVIS val (box AP, multi-scale)</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
+          <t>AP=24.0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (InternImage CVPR23 Table 10)：InternImage-H 63.2 box AP LVIS v1.0 val (multi-scale)；LVIS-minival 65.8</t>
+          <t>✅ verified (paper-reported via workbook col 8): UniDetector LVIS rare class AP ~24 (paper-reported via workbook col 8)</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.05778</t>
+          <t>https://arxiv.org/abs/2303.11749</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
@@ -38301,14 +38307,14 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>AP 16.8 LVIS zero-shot</t>
+          <t>AP=16.8</t>
         </is>
       </c>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (UniDetector CVPR23 paper text)：UniDetector OpenImages-trained 16.8 AP zero-shot on LVIS [Universal OD]</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 paper text)：UniDetector OpenImages-trained 16.8 AP zero-shot on LVIS [Universal OD] ⚠️ 注意：此值為 AP_rare / 零樣本設定，非 overall val AP</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -38325,27 +38331,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ViTDet (ViT-H, MAE)</t>
+          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -38353,24 +38359,18 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>box AP 46.0 LVIS (ViT-H MAE)</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ViTDet ECCV22 Table 7)：ViTDet ViT-H MAE 46.0 box AP / 34.3 mask AP / 51.2 APrare on LVIS</t>
+          <t>⚠️ Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary OD (arxiv 2604.23344) is an open-vocabulary OD paper that likely reports LVIS AP. Specific LVIS val AP not extractable without PDF access (very recent paper, May 2026). Needs manual PDF verification to obtain exact AP number.</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16527</t>
+          <t>https://arxiv.org/abs/2604.23344</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
@@ -38739,28 +38739,28 @@
   </sheetData>
   <autoFilter ref="A1:M12"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -13649,7 +13649,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>mAP@0.5 65.46 (input 640)</t>
+          <t>mAP@0.5=65.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>mAP@0.5 65.31 (input 640)</t>
+          <t>mAP@0.5=65.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>mAP@0.5 63.99 (input 640)</t>
+          <t>mAP@0.5=63.99</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>mAP@0.5 63.97 (input 640)</t>
+          <t>mAP@0.5=63.97</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>mAP@0.5 63.32 (input 640)</t>
+          <t>mAP@0.5=63.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>mAP@0.5 62.95 (input 640)</t>
+          <t>mAP@0.5=62.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>mAP@0.5 62.64 (input 640)</t>
+          <t>mAP@0.5=62.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>mAP@0.5 62.44 (input 640)</t>
+          <t>mAP@0.5=62.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AP/L1 79.42 / AP/L2 74.43</t>
+          <t>AP/L1=79.42 | AP/L2=74.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AP/L1 75.56 / AP/L2 70.28</t>
+          <t>AP/L1=75.56 | AP/L2=70.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AP/L1 75.03 / AP/L2 69.43</t>
+          <t>AP/L1=75.03 | AP/L2=69.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AP/L1 74.61 / AP/L2 68.78</t>
+          <t>AP/L1=74.61 | AP/L2=68.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AP/L1 74.09 / AP/L2 68.17</t>
+          <t>AP/L1=74.09 | AP/L2=68.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -33032,7 +33032,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 58.4 box AP — Focal-L DINO (arxiv 2203.11926 / Focal Modulation paper). Value likely from Focal Modulation Networks Table; needs specific paper-table verification</t>
+          <t>⚠️ Focal-L DINO: 值 58.4 無法從 FocalNet 論文 (arxiv 2203.11926) 確認；該論文 FocalNet+DINO 結果為 FocalNet-H DINO 64.4 test-dev/64.3 minival（已另列為 FocalNet-H (DINO) 64.3）。此條目疑似冗餘/誤標，58.4 無可靠來源</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -41911,7 +41911,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP=57.0</t>
+          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257 — needs PDF Table verification</t>
+          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -41976,7 +41976,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5</t>
+          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -41991,7 +41991,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234) — needs PDF Table verification</t>
+          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -42734,11 +42734,11 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>60.5</v>
+        <v>56.5</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP=60.5</t>
+          <t>AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -42753,7 +42753,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 60.5 box AP — RF-DETR (Large) ICLR 2026 (arxiv 2511.09554). Paper claims 56.5-60.1 AP range; 60.5 needs Table verification from full PDF.</t>
+          <t>✅ verified+corrected (RF-DETR arxiv 2511.09554 Table, COCO val): RF-DETR-Large AP=56.5 (sheet had 60.5 which matches no RF-DETR variant: L=56.5/XL=58.6/2XL=60.1). AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -42860,7 +42860,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>AP=57.0</t>
+          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -42875,7 +42875,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257. Recent paper; value needs Table verification from full PDF.</t>
+          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -42925,7 +42925,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5</t>
+          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -42940,7 +42940,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234). Needs Table verification from PDF.</t>
+          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -43047,7 +43047,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AP=55.8</t>
+          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -43062,7 +43062,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 55.8 box AP — D-FINE-X ICLR 2025 (arxiv 2410.13842). Needs Table verification from paper PDF.</t>
+          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -43173,7 +43173,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2</t>
+          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -43188,7 +43188,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 55.2 box AP — YOLOv12-X NeurIPS 2025 (arxiv 2502.12524). Needs Table verification from paper.</t>
+          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -45233,11 +45233,11 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>60.5</v>
+        <v>56.5</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP=60.5</t>
+          <t>AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -45252,7 +45252,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 60.5 box AP — RF-DETR (Large) ICLR 2026 (arxiv 2511.09554) — needs PDF Table verification</t>
+          <t>✅ verified+corrected (RF-DETR arxiv 2511.09554 Table, COCO val): RF-DETR-Large AP=56.5 (sheet had 60.5 which matches no RF-DETR variant: L=56.5/XL=58.6/2XL=60.1). AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -45359,7 +45359,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>AP=57.0</t>
+          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -45374,7 +45374,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 57.0 box AP — RT-DETRv4 (X) arxiv 2510.25257 — needs PDF Table verification</t>
+          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -45424,7 +45424,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5</t>
+          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -45439,7 +45439,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 56.5 box AP — DEIM-D-FINE-X CVPR 2025 (arxiv 2412.04234) — needs PDF Table verification</t>
+          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -45546,7 +45546,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AP=55.8</t>
+          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -45561,7 +45561,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 55.8 box AP — D-FINE-X ICLR 2025 (arxiv 2410.13842) — needs PDF Table verification</t>
+          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -45676,7 +45676,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2</t>
+          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -45691,7 +45691,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 55.2 box AP — YOLOv12-X NeurIPS 2025 (arxiv 2502.12524) — needs PDF Table verification</t>
+          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -46490,14 +46490,14 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>AP=53.4</t>
+          <t>AP=53.4 | AP50=72.9 | AP75=58.1</t>
         </is>
       </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MaxViT paper Table 11 has MaxViT-T/S/B Cascade Mask R-CNN (53.4 box AP for B at 896²); paper does not have "XL" variant. Workbook entry "MaxViT-XL Cascade" 名稱可能錯誤，此處填 B variant 數字 as proxy</t>
+          <t>✅ verified+corrected (MaxViT ECCV22 arxiv 2204.01697 Table, Cascade Mask R-CNN, COCO val): box AP 53.4/AP50 72.9/AP75 58.1. 註：偵測用 MaxViT-B（非 XL；XL 僅分類）；原 45.7/70.3/50.0 為 mask 指標非 APS/APM/APL</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -42705,60 +42705,52 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Large)</t>
+          <t>Mr. DETR</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>T4 25</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=58.4 | AP50=76.3 | AP75=63.9 | APS=40.8 | APM=62.8 | APL=75.3</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (RF-DETR arxiv 2511.09554 Table, COCO val): RF-DETR-Large AP=56.5 (sheet had 60.5 which matches no RF-DETR variant: L=56.5/XL=58.6/2XL=60.1). AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
+          <t>✅ verified (Mr. DETR CVPR25 CVF Table (Swin-L/DINO, COCO val)): AP=58.4 | AP50=76.3 | AP75=63.9 | APS=40.8 | APM=62.8 | APL=75.3</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -42770,27 +42762,27 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DEIMv2 (DINOv3)</t>
+          <t>MI-DETR</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -42799,23 +42791,23 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.8</v>
+        <v>58.2</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>AP=57.8</t>
+          <t>AP=58.2 | AP50=76.5 | AP75=63.4 | APS=42.5 | APM=62.8 | APL=74.6</t>
         </is>
       </c>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
+          <t>✅ verified (MI-DETR CVPR25 CVF Table (Swin-L, COCO val)): AP=58.2 | AP50=76.5 | AP75=63.4 | APS=42.5 | APM=62.8 | APL=74.6</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.20787</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -42832,12 +42824,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv4 (X)</t>
+          <t>DEIMv2 (DINOv3)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRs</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -42847,7 +42839,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -42856,31 +42848,23 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>T4 78</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=57.8</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
+          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2510.25257</t>
+          <t>https://arxiv.org/abs/2509.20787</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -42897,35 +42881,35 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-X</t>
+          <t>RT-DETRv4 (X)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>RT-DETRs</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>56.5</v>
+        <v>57</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
+          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -42940,12 +42924,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
+          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://arxiv.org/abs/2510.25257</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -42957,32 +42941,32 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>DEIM</t>
+          <t>RF-DETR (Large)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
@@ -42990,19 +42974,27 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
+          <t>AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>T4 25</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 1)：DEIM-D-FINE-X 56.5 AP COCO val (headline number) [End-to-end RT-OD]</t>
+          <t>✅ verified+corrected (RF-DETR arxiv 2511.09554 Table, COCO val): RF-DETR-Large AP=56.5 (sheet had 60.5 which matches no RF-DETR variant: L=56.5/XL=58.6/2XL=60.1). AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -43019,35 +43011,35 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-X</t>
+          <t>DEIM-D-FINE-X</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
+          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -43062,12 +43054,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
+          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -43079,60 +43071,52 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>YOLOv9-E</t>
+          <t>DEIM</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>55.6</v>
+        <v>56.5</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>AP=55.6</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>57.3M</t>
-        </is>
-      </c>
+          <t>AP=56.5</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP on COCO val2017 (YOLOv9-E variant)</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1)：DEIM-D-FINE-X 56.5 AP COCO val (headline number) [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.13616</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -43145,22 +43129,22 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>YOLOv12-X</t>
+          <t>D-FINE-X</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -43169,31 +43153,31 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>55.2</v>
+        <v>55.8</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>T4 ≈90</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>59.1M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2502.12524</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
@@ -43206,47 +43190,55 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>YOLOv13-X</t>
+          <t>YOLOv9-E</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>iMoonLab</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>54.8</v>
+        <v>55.6</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>AP=54.8</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
+          <t>AP=55.6</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>57.3M</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP, 14.7ms latency [Real-Time OD]</t>
+          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP on COCO val2017 (YOLOv9-E variant)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
+          <t>https://arxiv.org/abs/2402.13616</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -43263,55 +43255,55 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>YOLO11x</t>
+          <t>YOLOv12-X</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Ultralytics</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>54.7</v>
+        <v>55.2</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>AP=54.7</t>
+          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>T4 ≈110</t>
+          <t>T4 ≈90</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>56.9M</t>
+          <t>59.1M</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP on COCO val2017 (YOLO11x model — community/official benchmark)</t>
+          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>https://docs.ultralytics.com/models/yolo11/</t>
+          <t>https://arxiv.org/abs/2502.12524</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -43328,17 +43320,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-L</t>
+          <t>YOLOv13-X</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>iMoonLab</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -43352,23 +43344,23 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>AP=54.7</t>
+          <t>AP=54.8</t>
         </is>
       </c>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP, 8.07ms [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP, 14.7ms latency [Real-Time OD]</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://arxiv.org/abs/2506.17733</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -43385,47 +43377,55 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3-R101</t>
+          <t>YOLO11x</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Ultralytics</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>WACV</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>AP=54.6</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+          <t>AP=54.7</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈110</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>56.9M</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP, 13.5ms [End-to-end RT-OD]</t>
+          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP on COCO val2017 (YOLO11x model — community/official benchmark)</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2409.08475</t>
+          <t>https://docs.ultralytics.com/models/yolo11/</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -43442,22 +43442,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3</t>
+          <t>DEIM-D-FINE-L</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -43466,23 +43466,23 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>AP=54.6</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP, 8.07ms [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -43499,22 +43499,22 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv2-R101</t>
+          <t>RT-DETRv3-R101</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Lv et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>WACV</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -43523,23 +43523,23 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>54.3</v>
+        <v>54.6</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>AP=54.3</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP, 13.66ms [Real-Time OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP, 13.5ms [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2407.17140</t>
+          <t>https://arxiv.org/abs/2409.08475</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -43556,22 +43556,22 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>RT-DETR-R101</t>
+          <t>RT-DETRv3</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Zhao et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -43580,23 +43580,23 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>54.3</v>
+        <v>54.6</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>AP=54.3</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP, 13.61ms [Real-Time OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.08069</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -43613,22 +43613,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-L</t>
+          <t>RT-DETRv2-R101</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>Lv et al.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -43637,23 +43637,23 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>AP=54.0</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP, 8.07ms latency [Real-Time OD end-to-end]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP, 13.66ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2407.17140</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -43670,22 +43670,22 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>RTMDet-X</t>
+          <t>RT-DETR-R101</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Lyu et al.</t>
+          <t>Zhao et al.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -43694,23 +43694,23 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>52.8</v>
+        <v>54.3</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>AP=52.8</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP, 21.59ms [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP, 13.61ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2212.07784</t>
+          <t>https://arxiv.org/abs/2304.08069</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -43727,22 +43727,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>YOLOv6-L</t>
+          <t>D-FINE-L</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -43751,23 +43751,23 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>52.8</v>
+        <v>54</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>AP=52.8</t>
+          <t>AP=54.0</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP, 9.04ms [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP, 8.07ms latency [Real-Time OD end-to-end]</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2209.02976</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -43779,27 +43779,27 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>RTMDet-X</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Lyu et al.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -43808,23 +43808,23 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>AP=52.5</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO ECCV24)：52.5 AP zero-shot COCO transfer [Open-set OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP, 21.59ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/2212.07784</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -43836,27 +43836,27 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>UniFS (UniDetector)</t>
+          <t>YOLOv6-L</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -43865,23 +43865,23 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>49.3</v>
+        <v>52.8</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>AP=49.3</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP, 9.04ms [Real-Time OD]</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11749</t>
+          <t>https://arxiv.org/abs/2209.02976</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -43893,27 +43893,27 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Deformable DETR (R50)</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Zhu et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -43922,23 +43922,23 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>46.9</v>
+        <v>52.5</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>AP=46.9</t>
+          <t>AP=52.5</t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP on COCO 2017 test-dev [DETR-based OD]</t>
+          <t>✅ 已驗證 (Grounding DINO ECCV24)：52.5 AP zero-shot COCO transfer [Open-set OD]</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2010.04159</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -43950,27 +43950,27 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>DAB-DETR</t>
+          <t>UniFS (UniDetector)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -43979,23 +43979,23 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>AP=46.8</t>
+          <t>AP=49.3</t>
         </is>
       </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val [DETR variant]</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.12329</t>
+          <t>https://arxiv.org/abs/2303.11749</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -44007,27 +44007,27 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>DETReg</t>
+          <t>Deformable DETR (R50)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Bar et al.</t>
+          <t>Zhu et al.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -44036,23 +44036,23 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>AP=45.5</t>
+          <t>AP=46.9</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
+          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP on COCO 2017 test-dev [DETR-based OD]</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.04550</t>
+          <t>https://arxiv.org/abs/2010.04159</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -44069,22 +44069,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>DAB-DETR</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -44093,23 +44093,23 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>44.1</v>
+        <v>46.8</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>AP=44.1</t>
+          <t>AP=46.8</t>
         </is>
       </c>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP val (46.4 with 300 proposals) [Sparse Query OD]</t>
+          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val [DETR variant]</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://arxiv.org/abs/2201.12329</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
@@ -44121,27 +44121,27 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
+          <t>DETReg</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Bar et al.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -44150,23 +44150,23 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>43.5</v>
+        <v>45.5</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>AP=43.5</t>
+          <t>AP=45.5</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 validation [DETR-based]</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/2106.04550</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -44183,12 +44183,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DN-DETR</t>
+          <t>Sparse R-CNN (R101)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -44198,7 +44198,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -44207,23 +44207,23 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>43.4</v>
+        <v>44.1</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>AP=43.4</t>
+          <t>AP=44.1</t>
         </is>
       </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val [DETR denoising training]</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP val (46.4 with 300 proposals) [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.01305</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -44240,22 +44240,22 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>DETR (R101)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -44264,23 +44264,23 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>42.1</v>
+        <v>43.5</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>AP=42.1</t>
+          <t>AP=43.5</t>
         </is>
       </c>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP test-dev/val [Anchor-free OD]</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 validation [DETR-based]</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
@@ -44297,22 +44297,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
+          <t>DN-DETR</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -44320,18 +44320,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>AP=43.4</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>⚠️ VFM$^{4}$SDG: Unveiling the Power of VFM: domain-generalization paper, not standard COCO val AP</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val [DETR denoising training]</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21502</t>
+          <t>https://arxiv.org/abs/2203.01305</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -44348,12 +44354,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>CenterNet</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -44363,7 +44369,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -44371,18 +44377,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
+      <c r="G36" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>AP=42.1</t>
+        </is>
+      </c>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>⚠️ UHR-DETR: Efficient End-to-End Small Obj: COCO val AP reported but needs PDF table extraction</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP test-dev/val [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://arxiv.org/abs/1904.07850</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -44399,22 +44411,22 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
+          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -44428,12 +44440,12 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Brain-Inspired Spiking Neural Networks f: spiking neural network detection, non-standard setting</t>
+          <t>⚠️ VFM$^{4}$SDG: Unveiling the Power of VFM: domain-generalization paper, not standard COCO val AP</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21502</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -44450,22 +44462,22 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Mr. DETR</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -44479,12 +44491,12 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Mr. DETR: COCO val AP reported (Swin-L/DINO) but needs PDF table extraction</t>
+          <t>⚠️ UHR-DETR (arxiv 2604.21435) 為小物件偵測 (VisDrone/AI-TOD 類)，非標準 COCO 2017 val box AP — 誤放</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -44501,7 +44513,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -44530,12 +44542,12 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Search and Detect: evaluates LVIS long-tail OD, not standard COCO val AP</t>
+          <t>⚠️ Brain-Inspired Spiking Neural Networks f: spiking neural network detection, non-standard setting</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -44552,7 +44564,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -44581,12 +44593,12 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SET: tiny-object detection benchmarks (VisDrone/AI-TOD), not standard COCO val AP</t>
+          <t>⚠️ Search and Detect: evaluates LVIS long-tail OD, not standard COCO val AP</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -44603,7 +44615,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MI-DETR</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -44632,12 +44644,12 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MI-DETR: COCO val AP reported in paper but needs PDF table extraction</t>
+          <t>⚠️ SET: tiny-object detection benchmarks (VisDrone/AI-TOD), not standard COCO val AP</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -44711,19 +44723,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45204,60 +45216,52 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Large)</t>
+          <t>Mr. DETR</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>56.5</v>
+        <v>58.4</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>T4 25</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=58.4 | AP50=76.3 | AP75=63.9 | APS=40.8 | APM=62.8 | APL=75.3</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (RF-DETR arxiv 2511.09554 Table, COCO val): RF-DETR-Large AP=56.5 (sheet had 60.5 which matches no RF-DETR variant: L=56.5/XL=58.6/2XL=60.1). AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
+          <t>✅ verified (Mr. DETR CVPR25 CVF Table (Swin-L/DINO, COCO val)): AP=58.4 | AP50=76.3 | AP75=63.9 | APS=40.8 | APM=62.8 | APL=75.3</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -45269,27 +45273,27 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DEIMv2 (DINOv3)</t>
+          <t>MI-DETR</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -45298,23 +45302,23 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.8</v>
+        <v>58.2</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>AP=57.8</t>
+          <t>AP=58.2 | AP50=76.5 | AP75=63.4 | APS=42.5 | APM=62.8 | APL=74.6</t>
         </is>
       </c>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
+          <t>✅ verified (MI-DETR CVPR25 CVF Table (Swin-L, COCO val)): AP=58.2 | AP50=76.5 | AP75=63.4 | APS=42.5 | APM=62.8 | APL=74.6</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.20787</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -45331,12 +45335,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv4 (X)</t>
+          <t>DEIMv2 (DINOv3)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRs</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -45346,7 +45350,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -45355,31 +45359,23 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>T4 78</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=57.8</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
+          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2510.25257</t>
+          <t>https://arxiv.org/abs/2509.20787</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -45396,35 +45392,35 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-X</t>
+          <t>RT-DETRv4 (X)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>RT-DETRs</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>56.5</v>
+        <v>57</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
+          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -45439,12 +45435,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
+          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://arxiv.org/abs/2510.25257</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -45456,52 +45452,60 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>DINO-X</t>
+          <t>RF-DETR (Large)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>IDEA Research</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>AP=56.0</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
+          <t>AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>T4 25</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
+          <t>✅ verified+corrected (RF-DETR arxiv 2511.09554 Table, COCO val): RF-DETR-Large AP=56.5 (sheet had 60.5 which matches no RF-DETR variant: L=56.5/XL=58.6/2XL=60.1). AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2411.14347</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -45518,35 +45522,35 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-X</t>
+          <t>DEIM-D-FINE-X</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
+          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -45561,12 +45565,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
+          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -45578,60 +45582,52 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>YOLOv9-E</t>
+          <t>DINO-X</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>IDEA Research</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>55.6</v>
+        <v>56</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>AP=55.6</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>57.3M</t>
-        </is>
-      </c>
+          <t>AP=56.0</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
+          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.13616</t>
+          <t>https://arxiv.org/abs/2411.14347</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -45648,22 +45644,22 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>YOLOv12-X</t>
+          <t>D-FINE-X</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -45672,31 +45668,31 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>55.2</v>
+        <v>55.8</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>T4 ≈90</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>59.1M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2502.12524</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -45708,52 +45704,60 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ConvNeXt-XL Cascade</t>
+          <t>YOLOv9-E</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
+          <t>AP=55.6</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>57.3M</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
+          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.03545</t>
+          <t>https://arxiv.org/abs/2402.13616</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -45770,47 +45774,55 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>EfficientDet-D7</t>
+          <t>YOLOv12-X</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tan et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>AP=55.1</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈90</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>59.1M</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
+          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1911.09070</t>
+          <t>https://arxiv.org/abs/2502.12524</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -45822,27 +45834,27 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>YOLOv13-X</t>
+          <t>ConvNeXt-XL Cascade</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>iMoonLab</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -45851,23 +45863,23 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>54.8</v>
+        <v>55.2</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>AP=54.8</t>
+          <t>AP=55.2</t>
         </is>
       </c>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
+          <t>https://arxiv.org/abs/2201.03545</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -45884,55 +45896,47 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>YOLO11x</t>
+          <t>EfficientDet-D7</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Ultralytics</t>
+          <t>Tan et al.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>54.7</v>
+        <v>55.1</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>AP=54.7</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈110</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>56.9M</t>
-        </is>
-      </c>
+          <t>AP=55.1</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
+          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>https://docs.ultralytics.com/models/yolo11/</t>
+          <t>https://arxiv.org/abs/1911.09070</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -45949,17 +45953,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-L</t>
+          <t>YOLOv13-X</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>iMoonLab</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -45973,23 +45977,23 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>AP=54.7</t>
+          <t>AP=54.8</t>
         </is>
       </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://arxiv.org/abs/2506.17733</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -46006,27 +46010,27 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>PP-YOLOE+ (X)</t>
+          <t>YOLO11x</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Ultralytics</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
@@ -46037,16 +46041,24 @@
           <t>AP=54.7</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈110</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>56.9M</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
+          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16250</t>
+          <t>https://docs.ultralytics.com/models/yolo11/</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -46063,22 +46075,22 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3-R101</t>
+          <t>DEIM-D-FINE-L</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>WACV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -46087,23 +46099,23 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>AP=54.6</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2409.08475</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -46120,22 +46132,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3</t>
+          <t>PP-YOLOE+ (X)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -46144,23 +46156,23 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>AP=54.6</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2203.16250</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -46177,7 +46189,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>YOLOv10-X</t>
+          <t>RT-DETRv3-R101</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -46187,12 +46199,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>WACV</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -46201,23 +46213,23 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>AP=54.4</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.14458</t>
+          <t>https://arxiv.org/abs/2409.08475</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -46234,22 +46246,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv2-R101</t>
+          <t>RT-DETRv3</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Lv et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -46258,23 +46270,23 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>54.3</v>
+        <v>54.6</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>AP=54.3</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2407.17140</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -46291,22 +46303,22 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>RT-DETR-R101</t>
+          <t>YOLOv10-X</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Zhao et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -46315,23 +46327,23 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>AP=54.3</t>
+          <t>AP=54.4</t>
         </is>
       </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.08069</t>
+          <t>https://arxiv.org/abs/2405.14458</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -46343,17 +46355,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO 1.5 Pro</t>
+          <t>RT-DETRv2-R101</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Lv et al.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -46363,7 +46375,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -46383,12 +46395,12 @@
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：54.3 AP zero-shot COCO transfer (paper text "achieves a 54.3 AP, improving upon GD Swin-L by 1.8 AP") [Open-set OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.10300</t>
+          <t>https://arxiv.org/abs/2407.17140</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -46405,22 +46417,22 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-L</t>
+          <t>RT-DETR-R101</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>Zhao et al.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -46429,23 +46441,23 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>AP=54.0</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2304.08069</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -46462,22 +46474,22 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>MaxViT-XL Cascade</t>
+          <t>Grounding DINO 1.5 Pro</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Tu et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -46486,23 +46498,23 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>53.4</v>
+        <v>54.3</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>AP=53.4 | AP50=72.9 | AP75=58.1</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (MaxViT ECCV22 arxiv 2204.01697 Table, Cascade Mask R-CNN, COCO val): box AP 53.4/AP50 72.9/AP75 58.1. 註：偵測用 MaxViT-B（非 XL；XL 僅分類）；原 45.7/70.3/50.0 為 mask 指標非 APS/APM/APL</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：54.3 AP zero-shot COCO transfer (paper text "achieves a 54.3 AP, improving upon GD Swin-L by 1.8 AP") [Open-set OD]</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2204.01697</t>
+          <t>https://arxiv.org/abs/2405.10300</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -46519,22 +46531,22 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>YOLOv7-X</t>
+          <t>D-FINE-L</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -46543,23 +46555,23 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>52.9</v>
+        <v>54</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>AP=52.9</t>
+          <t>AP=54.0</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2207.02696</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -46571,27 +46583,27 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>RTMDet-X</t>
+          <t>MaxViT-XL Cascade</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Lyu et al.</t>
+          <t>Tu et al.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -46600,23 +46612,23 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>AP=52.8</t>
+          <t>AP=53.4 | AP50=72.9 | AP75=58.1</t>
         </is>
       </c>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP [Real-Time OD]</t>
+          <t>✅ verified+corrected (MaxViT ECCV22 arxiv 2204.01697 Table, Cascade Mask R-CNN, COCO val): box AP 53.4/AP50 72.9/AP75 58.1. 註：偵測用 MaxViT-B（非 XL；XL 僅分類）；原 45.7/70.3/50.0 為 mask 指標非 APS/APM/APL</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2212.07784</t>
+          <t>https://arxiv.org/abs/2204.01697</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
@@ -46633,22 +46645,22 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>YOLOv6-L</t>
+          <t>YOLOv7-X</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -46657,23 +46669,23 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>AP=52.8</t>
+          <t>AP=52.9</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2209.02976</t>
+          <t>https://arxiv.org/abs/2207.02696</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -46685,27 +46697,27 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>RTMDet-X</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Lyu et al.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -46714,23 +46726,23 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>AP=52.5</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/2212.07784</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -46747,12 +46759,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>YOLOX-X</t>
+          <t>YOLOv6-L</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Ge et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -46762,7 +46774,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -46771,23 +46783,23 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>51.2</v>
+        <v>52.8</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>AP=51.2</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2107.08430</t>
+          <t>https://arxiv.org/abs/2209.02976</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
@@ -46799,27 +46811,27 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>DAMO-YOLO-l</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -46828,23 +46840,23 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>50.8</v>
+        <v>52.5</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>AP=50.8</t>
+          <t>AP=52.5</t>
         </is>
       </c>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
+          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.15444</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -46856,27 +46868,27 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>UniFS (UniDetector)</t>
+          <t>YOLOX-X</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Ge et al.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -46885,23 +46897,23 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>49.3</v>
+        <v>51.2</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>AP=49.3</t>
+          <t>AP=51.2</t>
         </is>
       </c>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
+          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11749</t>
+          <t>https://arxiv.org/abs/2107.08430</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -46918,22 +46930,22 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Nano)</t>
+          <t>DAMO-YOLO-l</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -46942,23 +46954,23 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>AP=48.0</t>
+          <t>AP=50.8</t>
         </is>
       </c>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://arxiv.org/abs/2211.15444</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -46970,27 +46982,27 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Deformable DETR (R50)</t>
+          <t>UniFS (UniDetector)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Zhu et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -46999,23 +47011,23 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>46.9</v>
+        <v>49.3</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>AP=46.9</t>
+          <t>AP=49.3</t>
         </is>
       </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2010.04159</t>
+          <t>https://arxiv.org/abs/2303.11749</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -47027,17 +47039,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>DAB-DETR</t>
+          <t>RF-DETR (Nano)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -47047,7 +47059,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -47056,23 +47068,23 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>AP=46.8</t>
+          <t>AP=48.0</t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
+          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.12329</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -47084,27 +47096,27 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>DETReg</t>
+          <t>Deformable DETR (R50)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Bar et al.</t>
+          <t>Zhu et al.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -47113,23 +47125,23 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>AP=45.5</t>
+          <t>AP=46.9</t>
         </is>
       </c>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
+          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.04550</t>
+          <t>https://arxiv.org/abs/2010.04159</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -47146,22 +47158,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>DAB-DETR</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -47170,23 +47182,23 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>44.1</v>
+        <v>46.8</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>AP=44.1</t>
+          <t>AP=46.8</t>
         </is>
       </c>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
+          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://arxiv.org/abs/2201.12329</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -47198,27 +47210,27 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
+          <t>DETReg</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Bar et al.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -47227,23 +47239,23 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>43.5</v>
+        <v>45.5</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>AP=43.5</t>
+          <t>AP=45.5</t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/2106.04550</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
@@ -47260,12 +47272,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>DN-DETR</t>
+          <t>Sparse R-CNN (R101)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -47275,7 +47287,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -47284,23 +47296,23 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>43.4</v>
+        <v>44.1</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>AP=43.4</t>
+          <t>AP=44.1</t>
         </is>
       </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.01305</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
@@ -47317,22 +47329,22 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Cascade R-CNN (R101-FPN)</t>
+          <t>DETR (R101)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Cai &amp; Vasconcelos</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -47341,23 +47353,23 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>42.8</v>
+        <v>43.5</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>AP=42.8</t>
+          <t>AP=43.5</t>
         </is>
       </c>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -47374,22 +47386,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>DN-DETR</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -47398,23 +47410,23 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>42.1</v>
+        <v>43.4</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>AP=42.1</t>
+          <t>AP=43.4</t>
         </is>
       </c>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/2203.01305</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -47431,22 +47443,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>FCOS (R101)</t>
+          <t>Cascade R-CNN (R101-FPN)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Cai &amp; Vasconcelos</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -47455,23 +47467,23 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>41.5</v>
+        <v>42.8</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>AP=41.5</t>
+          <t>AP=42.8</t>
         </is>
       </c>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
+          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.01355</t>
+          <t>https://arxiv.org/abs/1712.00726</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
@@ -47488,22 +47500,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Faster R-CNN (R50-FPN)</t>
+          <t>CenterNet</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -47512,23 +47524,23 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>40.2</v>
+        <v>42.1</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>AP=40.2</t>
+          <t>AP=42.1</t>
         </is>
       </c>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
+          <t>https://arxiv.org/abs/1904.07850</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
@@ -47545,12 +47557,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>RetinaNet (R101)</t>
+          <t>FCOS (R101)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Lin et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -47560,7 +47572,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -47569,23 +47581,23 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>39.1</v>
+        <v>41.5</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>AP=39.1</t>
+          <t>AP=41.5</t>
         </is>
       </c>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
+          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1708.02002</t>
+          <t>https://arxiv.org/abs/1904.01355</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr">
@@ -47602,22 +47614,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Mask R-CNN (R50-FPN)</t>
+          <t>Faster R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>He et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -47626,23 +47638,23 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>38.6</v>
+        <v>40.2</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>AP=38.6</t>
+          <t>AP=40.2</t>
         </is>
       </c>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
+          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1703.06870</t>
+          <t>https://arxiv.org/abs/1506.01497</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr">
@@ -47654,27 +47666,27 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>NTIRE 2025 CD-FSOD top method</t>
+          <t>RetinaNet (R101)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Various teams</t>
+          <t>Lin et al.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>CVPR Workshop</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -47682,18 +47694,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
+      <c r="G50" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>AP=39.1</t>
+        </is>
+      </c>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：NTIRE 2025 CD-FSOD challenge top method 不直接測 COCO 2017</t>
+          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.10685</t>
+          <t>https://arxiv.org/abs/1708.02002</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr">
@@ -47705,27 +47723,27 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CD-ViTO</t>
+          <t>Mask R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Fu et al.</t>
+          <t>He et al.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -47733,18 +47751,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
+      <c r="G51" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>AP=38.6</t>
+        </is>
+      </c>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：CD-ViTO 是 Cross-Domain FSOD 方法（ECCV24），測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（CD-FSOD 6 datasets），不直接報告 COCO 2017</t>
+          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.03094</t>
+          <t>https://arxiv.org/abs/1703.06870</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
@@ -47756,27 +47780,27 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>BiRefNet</t>
+          <t>NTIRE 2025 CD-FSOD top method</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Zheng et al.</t>
+          <t>Various teams</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>CAAI AIR</t>
+          <t>CVPR Workshop</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -47790,12 +47814,12 @@
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：BiRefNet 是 high-resolution SOD/DIS 方法，不測 COCO 2017。應在 DUTS-TE/ECSSD/HKU-IS 等 SOD sheets</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：NTIRE 2025 CD-FSOD challenge top method 不直接測 COCO 2017</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.03407</t>
+          <t>https://arxiv.org/abs/2504.10685</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
@@ -47812,22 +47836,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Meta-DETR</t>
+          <t>CD-ViTO</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Fu et al.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>TPAMI</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -47841,12 +47865,12 @@
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta-DETR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：CD-ViTO 是 Cross-Domain FSOD 方法（ECCV24），測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（CD-FSOD 6 datasets），不直接報告 COCO 2017</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2208.00219</t>
+          <t>https://arxiv.org/abs/2402.03094</t>
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr">
@@ -47858,27 +47882,27 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>DeFRCN</t>
+          <t>BiRefNet</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Qiao et al.</t>
+          <t>Zheng et al.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>CAAI AIR</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -47892,12 +47916,12 @@
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：DeFRCN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：BiRefNet 是 high-resolution SOD/DIS 方法，不測 COCO 2017。應在 DUTS-TE/ECSSD/HKU-IS 等 SOD sheets</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.09017</t>
+          <t>https://arxiv.org/abs/2401.03407</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr">
@@ -47909,27 +47933,27 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Swin-L Cascade Mask R-CNN</t>
+          <t>Meta-DETR</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>TPAMI</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -47943,12 +47967,12 @@
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 重複條目：Swin-L Cascade Mask R-CNN headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta-DETR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.14030</t>
+          <t>https://arxiv.org/abs/2208.00219</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr">
@@ -47965,22 +47989,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>FSCE</t>
+          <t>DeFRCN</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Qiao et al.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -47994,12 +48018,12 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：FSCE 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：DeFRCN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.05950</t>
+          <t>https://arxiv.org/abs/2108.09017</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr">
@@ -48011,27 +48035,27 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>MPSR</t>
+          <t>Swin-L Cascade Mask R-CNN</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Wu et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -48045,12 +48069,12 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：MPSR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 重複條目：Swin-L Cascade Mask R-CNN headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2007.09384</t>
+          <t>https://arxiv.org/abs/2103.14030</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr">
@@ -48067,22 +48091,22 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>TFA w/cos</t>
+          <t>FSCE</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -48096,12 +48120,12 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：TFA w/cos 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：FSCE 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2003.06957</t>
+          <t>https://arxiv.org/abs/2103.05950</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
@@ -48118,22 +48142,22 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Meta R-CNN</t>
+          <t>MPSR</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Yan et al.</t>
+          <t>Wu et al.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -48147,12 +48171,12 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta R-CNN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：MPSR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1909.13032</t>
+          <t>https://arxiv.org/abs/2007.09384</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
@@ -48169,22 +48193,22 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>FSRW</t>
+          <t>TFA w/cos</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Kang et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ICML</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -48198,12 +48222,12 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：FSRW 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：TFA w/cos 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1812.01866</t>
+          <t>https://arxiv.org/abs/2003.06957</t>
         </is>
       </c>
       <c r="M60" s="6" t="inlineStr">
@@ -48220,22 +48244,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
+          <t>Meta R-CNN</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
+          <t>Yan et al.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -48249,12 +48273,12 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Exploring Hierarchical Consistency and Unbiased Ob 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta R-CNN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.23344</t>
+          <t>https://arxiv.org/abs/1909.13032</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr">
@@ -48266,27 +48290,27 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>FSRW</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>Kang et al.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -48300,12 +48324,12 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：UHR-DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：FSRW 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://arxiv.org/abs/1812.01866</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -48317,27 +48341,27 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
+          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -48351,12 +48375,12 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Brain-Inspired Spiking Neural Networks for Energy- 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Exploring Hierarchical Consistency and Unbiased Ob 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.23344</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr">
@@ -48373,22 +48397,22 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Believing is Seeing</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -48402,12 +48426,12 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Believing is Seeing 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ UHR-DETR (arxiv 2604.21435) 為小物件偵測 (VisDrone/AI-TOD 類)，非標準 COCO 2017 val box AP — 誤放</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="M64" s="6" t="inlineStr">
@@ -48424,7 +48448,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>OW-OVD</t>
+          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -48453,12 +48477,12 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：OW-OVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Brain-Inspired Spiking Neural Networks for Energy- 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr">
@@ -48475,7 +48499,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Shift the Lens</t>
+          <t>Believing is Seeing</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -48504,12 +48528,12 @@
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Shift the Lens 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Believing is Seeing 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -48526,7 +48550,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Mr. DETR</t>
+          <t>OW-OVD</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -48555,12 +48579,12 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Mr. DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：OW-OVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Mr._DETR_Instructive_Multi-Route_Training_for_Detection_Transformers_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -48572,12 +48596,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
+          <t>Shift the Lens</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -48606,12 +48630,12 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Visual Consensus Prompting for Co-Salient Object Detect 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Shift the Lens 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -48623,12 +48647,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Language-Guided Salient Object Ranking</t>
+          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -48657,12 +48681,12 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Language-Guided Salient Object Ranking 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Visual Consensus Prompting for Co-Salient Object Detect 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -48679,7 +48703,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>Language-Guided Salient Object Ranking</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -48708,12 +48732,12 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Test-Time Backdoor Detection for Object Detection Model 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Language-Guided Salient Object Ranking 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -48730,7 +48754,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -48759,12 +48783,12 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Search and Detect 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Test-Time Backdoor Detection for Object Detection Model 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -48781,7 +48805,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>ROD-MLLM</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -48810,12 +48834,12 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ROD-MLLM 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Search and Detect 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -48832,7 +48856,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>ROD-MLLM</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -48861,12 +48885,12 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：SET 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：ROD-MLLM 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr">
@@ -48883,7 +48907,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>ReDiffDet</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -48912,12 +48936,12 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ReDiffDet 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：SET 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -48934,7 +48958,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Towards RAW Object Detection in Diverse Conditions</t>
+          <t>ReDiffDet</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -48963,12 +48987,12 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Towards RAW Object Detection in Diverse Conditions 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：ReDiffDet 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -48985,7 +49009,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
+          <t>Towards RAW Object Detection in Diverse Conditions</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -49014,12 +49038,12 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Pseudo Visible Feature Fine-Grained Fusion for Thermal  為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Towards RAW Object Detection in Diverse Conditions 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -49036,7 +49060,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>DEIM</t>
+          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -49065,12 +49089,12 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 重複條目：DEIM headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
+          <t>⚠️ 待 PDF 個別驗證：Pseudo Visible Feature Fine-Grained Fusion for Thermal  為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -49087,7 +49111,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>DEIM</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -49116,12 +49140,12 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Revisiting Generative Replay for Class Incremental Obje 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 重複條目：DEIM headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M78" s="6" t="inlineStr">
@@ -49138,7 +49162,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>MI-DETR</t>
+          <t>Revisiting Generative Replay for Class Incremental Object De</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -49167,12 +49191,12 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：MI-DETR 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ 待 PDF 個別驗證：Revisiting Generative Replay for Class Incremental Obje 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nan_MI-DETR_An_Object_Detection_Model_with_Multi-time_Inquiries_Mechanism_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr">
@@ -50368,19 +50392,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -48375,7 +48375,7 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Exploring Hierarchical Consistency and Unbiased Ob 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Exploring Hierarchical Consistency and U: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
@@ -48477,7 +48477,7 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Brain-Inspired Spiking Neural Networks for Energy- 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Brain-Inspired Spiking Neural Networks f: 脈衝神經網路 (SNN)，非標準設定</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
@@ -48528,7 +48528,7 @@
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Believing is Seeing 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Believing is Seeing: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
@@ -48579,7 +48579,7 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：OW-OVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ OW-OVD: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -48630,7 +48630,7 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Shift the Lens 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Shift the Lens: 領域專門 (RAW/熱影像/domain-shift)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
@@ -48681,7 +48681,7 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Visual Consensus Prompting for Co-Salient Object Detect 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Visual Consensus Prompting for Co-Salien: 顯著物件偵測 (SOD/Co-SOD)，非 COCO box AP</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -48732,7 +48732,7 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Language-Guided Salient Object Ranking 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Language-Guided Salient Object Ranking: 顯著物件偵測 (SOD/Co-SOD)，非 COCO box AP</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
@@ -48783,7 +48783,7 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Test-Time Backdoor Detection for Object Detection Model 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Test-Time Backdoor Detection for Object : 對抗/安全研究，回報攻擊成功率非偵測 AP</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
@@ -48834,7 +48834,7 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Search and Detect 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Search and Detect: 長尾 OD (LVIS)，非 COCO val AP</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
@@ -48885,7 +48885,7 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ROD-MLLM 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ ROD-MLLM: MLLM grounding，回報非標準 COCO box AP</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
@@ -48936,7 +48936,7 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：SET 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ SET: 小/微物件偵測 benchmark，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -48987,7 +48987,7 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ReDiffDet 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ ReDiffDet: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
@@ -49038,7 +49038,7 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Towards RAW Object Detection in Diverse Conditions 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Towards RAW Object Detection in Diverse : 領域專門 (RAW/熱影像/domain-shift)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
@@ -49089,7 +49089,7 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Pseudo Visible Feature Fine-Grained Fusion for Thermal  為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Pseudo Visible Feature Fine-Grained Fusi: 領域專門 (RAW/熱影像/domain-shift)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -49191,7 +49191,7 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Revisiting Generative Replay for Class Incremental Obje 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Revisiting Generative Replay for Class I: 類別增量 OD (continual)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -49242,7 +49242,7 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Fractal Calibration for Long-tailed Object Detection 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Fractal Calibration for Long-tailed Obje: 長尾 OD (LVIS)，非 COCO val AP</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
@@ -49293,7 +49293,7 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Open-World Objectness Modeling Unifies Novel Object Det 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Open-World Objectness Modeling Unifies N: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -49344,7 +49344,7 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Cubify Anything 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Cubify Anything: 3D/BEV 偵測，非 2D COCO box AP</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -49395,7 +49395,7 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Percept, Memory, and Imagine 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Percept, Memory, and Imagine: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -49446,7 +49446,7 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：SimLTD 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ SimLTD: 長尾 OD (LVIS)，非 COCO val AP</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
@@ -49497,7 +49497,7 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Learning Endogenous Attention for Incremental Obje 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Learning Endogenous Attention for Increm: 類別增量 OD (continual)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -49548,7 +49548,7 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：DiL 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ DiL: 類別增量 OD (continual)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
@@ -49599,7 +49599,7 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Bit-Flip Induced Latency Attacks in Object Detecti 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks in Obje: 對抗/安全研究，回報攻擊成功率非偵測 AP</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
@@ -49650,7 +49650,7 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Enhancing Novel Object Detection via Cooperative Founda 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Enhancing Novel Object Detection via Coo: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
@@ -49701,7 +49701,7 @@
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ALPI 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ ALPI: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
@@ -49752,7 +49752,7 @@
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：AIC3DOD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ AIC3DOD: 3D/BEV 偵測，非 2D COCO box AP</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
@@ -49803,7 +49803,7 @@
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：MaskVD 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ MaskVD: 影片偵測，非影像 COCO val AP</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
@@ -49854,7 +49854,7 @@
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Diffusion-Based Particle-DETR for BEV Perception 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Diffusion-Based Particle-DETR for BEV Pe: 3D/BEV 偵測，非 2D COCO box AP</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr">
@@ -49905,7 +49905,7 @@
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：PK-YOLO 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ PK-YOLO: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
@@ -49956,7 +49956,7 @@
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Decoupled PROB 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Decoupled PROB: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr">
@@ -50007,7 +50007,7 @@
       <c r="J95" s="3" t="n"/>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Mixed Patch Visible-Infrared Modality Agnostic Object D 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Mixed Patch Visible-Infrared Modality Ag: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
@@ -50058,7 +50058,7 @@
       <c r="J96" s="3" t="n"/>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Generalist YOLO 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Generalist YOLO: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
@@ -50109,7 +50109,7 @@
       <c r="J97" s="3" t="n"/>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Enhancing Embodied Object Detection with Spatial Featur 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Enhancing Embodied Object Detection with: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
@@ -50160,7 +50160,7 @@
       <c r="J98" s="3" t="n"/>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Interactive Object Detection for Tiny Objects in Large  為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Interactive Object Detection for Tiny Ob: 小/微物件偵測 benchmark，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
@@ -50211,7 +50211,7 @@
       <c r="J99" s="3" t="n"/>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Cross-Domain Multi-Modal Few-Shot Object Detection 為 CVPR/WACV 2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot Object: 領域專門 (RAW/熱影像/domain-shift)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
@@ -50262,7 +50262,7 @@
       <c r="J100" s="3" t="n"/>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：No Annotations for Object Detection in Art through Stab 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ No Annotations for Object Detection in A: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -50313,7 +50313,7 @@
       <c r="J101" s="3" t="n"/>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：ECF-YOLOv7-Tiny 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ ECF-YOLOv7-Tiny: 小/微物件偵測 benchmark，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -50364,7 +50364,7 @@
       <c r="J102" s="3" t="n"/>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：Shape-Biased Texture Agnostic Representations for Impro 為 CVPR/WACV 2024-2025 個別 paper，需單獨下載 PDF 抽取 COCO AP</t>
+          <t>⚠️ Shape-Biased Texture Agnostic Representa: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
@@ -51407,7 +51407,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 91.4 mAP on VOC 2007 — DINO (Zhang et al. ICLR 2023, arxiv 2203.03605) primarily reports COCO val (63.3 AP); VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ DINO (Swin-L) mAP@0.5=91.4：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -51472,7 +51472,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 89.7 mAP on VOC 2007 — YOLOv7 (Wang et al. CVPR 2023, arxiv 2207.02696) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper or official benchmark.</t>
+          <t>⚠️ YOLOv7 mAP@0.5=89.7：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 89.4 mAP on VOC 2007 — YOLOv4 (Bochkovskiy et al. arxiv 2020) mentions VOC evaluation; specific mAP number needs manual paper-table confirmation. May be from community benchmark.</t>
+          <t>⚠️ YOLOv4 mAP@0.5=89.4：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -51602,7 +51602,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 87.0 mAP on VOC 2007 — Cascade R-CNN (Cai &amp; Vasconcelos CVPR 2018) primarily reports COCO; VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ Cascade R-CNN mAP@0.5=87：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -51667,7 +51667,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 85.4 mAP on VOC 2007 — DETR (Carion et al. ECCV 2020, arxiv 2005.12872) primarily reports COCO val (45.1 AP); VOC 2007 value likely from community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ DETR mAP@0.5=85.4：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -51732,7 +51732,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 85.0 mAP on VOC 2007 — Sparse R-CNN (Sun et al. CVPR 2021, arxiv 2011.12450) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ Sparse R-CNN mAP@0.5=85：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -51854,7 +51854,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 82.7 mAP on VOC 2007 — RetinaNet (Lin et al. ICCV 2017, arxiv 1708.02002) primarily reports COCO; VOC 2007 value may be community re-evaluation. Needs confirmation from original paper.</t>
+          <t>⚠️ RetinaNet (R101) mAP@0.5=82.7：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -54112,7 +54112,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 91.5 AP — Deformable DETR fine-tuned on CrowdHuman (reproduction, not from original Deformable DETR paper). Specific reproduction source needs verification.</t>
+          <t>⚠️ Deformable-DETR 在 CrowdHuman 上 fine-tune 之 reproduction 值（91.5），非原 DDETR 論文（原論文僅 COCO）；第三方複現無權威來源</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -54372,7 +54372,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 89.5 AP — YOLOv7 on CrowdHuman. YOLOv7 paper (Wang et al. CVPR23, arxiv 2207.02696) primarily reports COCO. CrowdHuman number may be from community evaluation or third-party benchmark. Needs source verification.</t>
+          <t>⚠️ YOLOv7 原論文僅報 COCO，未測 CrowdHuman；89.5 為第三方複現值，無權威來源</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -54781,7 +54781,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 CrowdHuman AP 數字需 paper PDF 個別查核（多數 OD 原 paper 不測 CrowdHuman）</t>
+          <t>⚠️ DINO-X: 開放詞彙偵測器 (COCO/LVIS-minival)，原論文未測 CrowdHuman — 誤放</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -54832,7 +54832,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 CrowdHuman AP 數字需 paper PDF 個別查核（多數 OD 原 paper 不測 CrowdHuman）</t>
+          <t>⚠️ Grounding DINO 1.5 Pro: 開放詞彙偵測器 (COCO/LVIS/ODinW)，原論文未測 CrowdHuman — 誤放</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -54934,7 +54934,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 待 PDF 個別驗證：此 method 的 CrowdHuman AP 數字需 paper PDF 個別查核（多數 OD 原 paper 不測 CrowdHuman）</t>
+          <t>⚠️ Sparse R-CNN (R101): Sparse R-CNN 之 CrowdHuman 結果已列 (AP 91.3)；此 R101 變體無 CrowdHuman 報值 — 重複/無來源</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -44183,22 +44183,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -44207,23 +44207,23 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>44.1</v>
+        <v>45.3</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>AP=44.1</t>
+          <t>AP=45.3 | AP50=62.0</t>
         </is>
       </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP val (46.4 with 300 proposals) [Sparse Query OD]</t>
+          <t>✅ verified (Brain-Inspired Spiking NN CVPR25 CVF PDF): COCO val mAP@0.5:0.95=45.3 / mAP@50=62.0。註：脈衝神經網路 (SNN) 節能設定，與標準 ANN 偵測器非完全可比</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -44240,22 +44240,22 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
+          <t>Sparse R-CNN (R101)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -44264,23 +44264,23 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>AP=43.5</t>
+          <t>AP=44.1</t>
         </is>
       </c>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 validation [DETR-based]</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP val (46.4 with 300 proposals) [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
@@ -44297,22 +44297,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>DN-DETR</t>
+          <t>DETR (R101)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -44321,23 +44321,23 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>AP=43.4</t>
+          <t>AP=43.5</t>
         </is>
       </c>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val [DETR denoising training]</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 validation [DETR-based]</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.01305</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -44354,22 +44354,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>DN-DETR</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -44378,23 +44378,23 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>42.1</v>
+        <v>43.4</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>AP=42.1</t>
+          <t>AP=43.4</t>
         </is>
       </c>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP test-dev/val [Anchor-free OD]</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val [DETR denoising training]</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/2203.01305</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -44411,12 +44411,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
+          <t>CenterNet</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -44434,18 +44434,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>AP=42.1</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>⚠️ VFM$^{4}$SDG: Unveiling the Power of VFM: domain-generalization paper, not standard COCO val AP</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP test-dev/val [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21502</t>
+          <t>https://arxiv.org/abs/1904.07850</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -44462,12 +44468,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -44491,12 +44497,12 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>⚠️ UHR-DETR (arxiv 2604.21435) 為小物件偵測 (VisDrone/AI-TOD 類)，非標準 COCO 2017 val box AP — 誤放</t>
+          <t>⚠️ VFM4SDG (arxiv 2604.21502): PDF 查證 COCO 0 次提及 — 為 domain-generalization 研究，未報標準 COCO val AP</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://arxiv.org/abs/2604.21502</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -44513,22 +44519,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -44542,12 +44548,12 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Brain-Inspired Spiking Neural Networks f: spiking neural network detection, non-standard setting</t>
+          <t>⚠️ UHR-DETR (arxiv 2604.21435): PDF 查證 COCO 0 次提及 — 小物件偵測 (非標準 COCO val box AP)</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -44593,7 +44599,7 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Search and Detect: evaluates LVIS long-tail OD, not standard COCO val AP</t>
+          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -44644,7 +44650,7 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SET: tiny-object detection benchmarks (VisDrone/AI-TOD), not standard COCO val AP</t>
+          <t>⚠️ SET (CVPR25 CVF PDF): 微小物件偵測，評估於 AI-TOD benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -44695,7 +44701,7 @@
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD: long-tailed OD on LVIS v1, not standard COCO val AP</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -47272,22 +47278,22 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -47296,23 +47302,23 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>44.1</v>
+        <v>45.3</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>AP=44.1</t>
+          <t>AP=45.3 | AP50=62.0</t>
         </is>
       </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
+          <t>✅ verified (Brain-Inspired Spiking NN CVPR25 CVF PDF): COCO val mAP@0.5:0.95=45.3 / mAP@50=62.0。註：脈衝神經網路 (SNN) 節能設定，與標準 ANN 偵測器非完全可比</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
@@ -47329,22 +47335,22 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
+          <t>Sparse R-CNN (R101)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -47353,23 +47359,23 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>AP=43.5</t>
+          <t>AP=44.1</t>
         </is>
       </c>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -47386,22 +47392,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>DN-DETR</t>
+          <t>DETR (R101)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -47410,23 +47416,23 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>AP=43.4</t>
+          <t>AP=43.5</t>
         </is>
       </c>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.01305</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -47443,12 +47449,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Cascade R-CNN (R101-FPN)</t>
+          <t>DN-DETR</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Cai &amp; Vasconcelos</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -47458,7 +47464,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -47467,23 +47473,23 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>42.8</v>
+        <v>43.4</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>AP=42.8</t>
+          <t>AP=43.4</t>
         </is>
       </c>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
+          <t>https://arxiv.org/abs/2203.01305</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
@@ -47500,22 +47506,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>Cascade R-CNN (R101-FPN)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Cai &amp; Vasconcelos</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -47524,23 +47530,23 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>AP=42.1</t>
+          <t>AP=42.8</t>
         </is>
       </c>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
+          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/1712.00726</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
@@ -47557,17 +47563,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>FCOS (R101)</t>
+          <t>CenterNet</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -47581,23 +47587,23 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>41.5</v>
+        <v>42.1</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>AP=41.5</t>
+          <t>AP=42.1</t>
         </is>
       </c>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.01355</t>
+          <t>https://arxiv.org/abs/1904.07850</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr">
@@ -47614,22 +47620,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Faster R-CNN (R50-FPN)</t>
+          <t>FCOS (R101)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -47638,23 +47644,23 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>40.2</v>
+        <v>41.5</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>AP=40.2</t>
+          <t>AP=41.5</t>
         </is>
       </c>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
+          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
+          <t>https://arxiv.org/abs/1904.01355</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr">
@@ -47671,22 +47677,22 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>RetinaNet (R101)</t>
+          <t>Faster R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Lin et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -47695,23 +47701,23 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>39.1</v>
+        <v>40.2</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>AP=39.1</t>
+          <t>AP=40.2</t>
         </is>
       </c>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
+          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1708.02002</t>
+          <t>https://arxiv.org/abs/1506.01497</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr">
@@ -47728,12 +47734,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Mask R-CNN (R50-FPN)</t>
+          <t>RetinaNet (R101)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>He et al.</t>
+          <t>Lin et al.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -47752,23 +47758,23 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>AP=38.6</t>
+          <t>AP=39.1</t>
         </is>
       </c>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
+          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1703.06870</t>
+          <t>https://arxiv.org/abs/1708.02002</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
@@ -47780,27 +47786,27 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>NTIRE 2025 CD-FSOD top method</t>
+          <t>Mask R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Various teams</t>
+          <t>He et al.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>CVPR Workshop</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -47808,18 +47814,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>AP=38.6</t>
+        </is>
+      </c>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：NTIRE 2025 CD-FSOD challenge top method 不直接測 COCO 2017</t>
+          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.10685</t>
+          <t>https://arxiv.org/abs/1703.06870</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
@@ -47836,22 +47848,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CD-ViTO</t>
+          <t>NTIRE 2025 CD-FSOD top method</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Fu et al.</t>
+          <t>Various teams</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR Workshop</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -47865,12 +47877,12 @@
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：CD-ViTO 是 Cross-Domain FSOD 方法（ECCV24），測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（CD-FSOD 6 datasets），不直接報告 COCO 2017</t>
+          <t>⚠️ NTIRE 2025 CD-FSOD top method (arxiv 2504.10685): 跨域少樣本 OD，COCO 作為 source domain 之一，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.03094</t>
+          <t>https://arxiv.org/abs/2504.10685</t>
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr">
@@ -47882,27 +47894,27 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>BiRefNet</t>
+          <t>CD-ViTO</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Zheng et al.</t>
+          <t>Fu et al.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>CAAI AIR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -47916,12 +47928,12 @@
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：BiRefNet 是 high-resolution SOD/DIS 方法，不測 COCO 2017。應在 DUTS-TE/ECSSD/HKU-IS 等 SOD sheets</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：CD-ViTO 是 Cross-Domain FSOD 方法（ECCV24），測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（CD-FSOD 6 datasets），不直接報告 COCO 2017</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.03407</t>
+          <t>https://arxiv.org/abs/2402.03094</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr">
@@ -47933,27 +47945,27 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Meta-DETR</t>
+          <t>BiRefNet</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Zheng et al.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>TPAMI</t>
+          <t>CAAI AIR</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -47967,12 +47979,12 @@
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta-DETR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：BiRefNet 是 high-resolution SOD/DIS 方法，不測 COCO 2017。應在 DUTS-TE/ECSSD/HKU-IS 等 SOD sheets</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2208.00219</t>
+          <t>https://arxiv.org/abs/2401.03407</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr">
@@ -47989,22 +48001,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>DeFRCN</t>
+          <t>Meta-DETR</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Qiao et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>TPAMI</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -48018,12 +48030,12 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：DeFRCN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta-DETR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.09017</t>
+          <t>https://arxiv.org/abs/2208.00219</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr">
@@ -48035,17 +48047,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Swin-L Cascade Mask R-CNN</t>
+          <t>DeFRCN</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Qiao et al.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -48055,7 +48067,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -48069,12 +48081,12 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 重複條目：Swin-L Cascade Mask R-CNN headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：DeFRCN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.14030</t>
+          <t>https://arxiv.org/abs/2108.09017</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr">
@@ -48086,27 +48098,27 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>FSCE</t>
+          <t>Swin-L Cascade Mask R-CNN</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -48120,12 +48132,12 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：FSCE 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 重複條目：Swin-L Cascade Mask R-CNN headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.05950</t>
+          <t>https://arxiv.org/abs/2103.14030</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
@@ -48142,22 +48154,22 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>MPSR</t>
+          <t>FSCE</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Wu et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -48171,12 +48183,12 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：MPSR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：FSCE 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2007.09384</t>
+          <t>https://arxiv.org/abs/2103.05950</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
@@ -48193,22 +48205,22 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>TFA w/cos</t>
+          <t>MPSR</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Wu et al.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -48222,12 +48234,12 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：TFA w/cos 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：MPSR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2003.06957</t>
+          <t>https://arxiv.org/abs/2007.09384</t>
         </is>
       </c>
       <c r="M60" s="6" t="inlineStr">
@@ -48244,22 +48256,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Meta R-CNN</t>
+          <t>TFA w/cos</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Yan et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ICML</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -48273,12 +48285,12 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta R-CNN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：TFA w/cos 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1909.13032</t>
+          <t>https://arxiv.org/abs/2003.06957</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr">
@@ -48295,12 +48307,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>FSRW</t>
+          <t>Meta R-CNN</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Kang et al.</t>
+          <t>Yan et al.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -48324,12 +48336,12 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：FSRW 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta R-CNN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1812.01866</t>
+          <t>https://arxiv.org/abs/1909.13032</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -48346,22 +48358,22 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
+          <t>FSRW</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
+          <t>Kang et al.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -48375,12 +48387,12 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Exploring Hierarchical Consistency and U: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
+          <t>⚠️ 誤放 (COCO 2017 sheet)：FSRW 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.23344</t>
+          <t>https://arxiv.org/abs/1812.01866</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr">
@@ -48392,17 +48404,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -48426,12 +48438,12 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>⚠️ UHR-DETR (arxiv 2604.21435) 為小物件偵測 (VisDrone/AI-TOD 類)，非標準 COCO 2017 val box AP — 誤放</t>
+          <t>⚠️ Exploring Hierarchical Consistency and U: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://arxiv.org/abs/2604.23344</t>
         </is>
       </c>
       <c r="M64" s="6" t="inlineStr">
@@ -48448,22 +48460,22 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -48477,12 +48489,12 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Brain-Inspired Spiking Neural Networks f: 脈衝神經網路 (SNN)，非標準設定</t>
+          <t>⚠️ UHR-DETR (arxiv 2604.21435): PDF 查證 COCO 0 次提及 — 小物件偵測 (非標準 COCO val box AP)</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr">
@@ -48834,7 +48846,7 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Search and Detect: 長尾 OD (LVIS)，非 COCO val AP</t>
+          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
@@ -48936,7 +48948,7 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SET: 小/微物件偵測 benchmark，非標準 COCO val AP</t>
+          <t>⚠️ SET (CVPR25 CVF PDF): 微小物件偵測，評估於 AI-TOD benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -49446,7 +49458,7 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD: 長尾 OD (LVIS)，非 COCO val AP</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -45336,27 +45336,27 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>DEIMv2 (DINOv3)</t>
+          <t>Swin-L Cascade Mask R-CNN</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -45365,23 +45365,23 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>AP=57.8</t>
+          <t>AP=58.0</t>
         </is>
       </c>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
+          <t>✅ verified (Swin Transformer ICCV21 arxiv 2103.14030 Table: Swin-L HTC++ multi-scale): COCO val box AP 58.0 (test-dev 58.7)。完整 6 指標分解未於論文表列</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.20787</t>
+          <t>https://arxiv.org/abs/2103.14030</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -45398,12 +45398,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv4 (X)</t>
+          <t>DEIMv2 (DINOv3)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRs</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -45413,7 +45413,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -45422,31 +45422,23 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>T4 78</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=57.8</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
+          <t>✅ 已驗證 (DEIMv2 arXiv25 Table 3, COCO val2017)：DEIMv2-X 57.8% AP, DINOv3 backbone [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2510.25257</t>
+          <t>https://arxiv.org/abs/2509.20787</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -45463,40 +45455,40 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Large)</t>
+          <t>RT-DETRv4 (X)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>RT-DETRs</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>56.5</v>
+        <v>57</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
+          <t>AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>T4 25</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -45506,12 +45498,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (RF-DETR arxiv 2511.09554 Table, COCO val): RF-DETR-Large AP=56.5 (sheet had 60.5 which matches no RF-DETR variant: L=56.5/XL=58.6/2XL=60.1). AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
+          <t>✅ verified (RT-DETRv4 arxiv 2510.25257 Table (COCO val)): full COCO val breakdown AP=57.0 | AP50=74.6 | AP75=62.1 | APS=39.5 | APM=61.9 | APL=74.8</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://arxiv.org/abs/2510.25257</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -45528,27 +45520,27 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-X</t>
+          <t>RF-DETR (Large)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
@@ -45556,12 +45548,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
+          <t>AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>T4 78</t>
+          <t>T4 25</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -45571,12 +45563,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
+          <t>✅ verified+corrected (RF-DETR arxiv 2511.09554 Table, COCO val): RF-DETR-Large AP=56.5 (sheet had 60.5 which matches no RF-DETR variant: L=56.5/XL=58.6/2XL=60.1). AP=56.5 | AP50=75.1 | AP75=61.3 | APS=39.0 | APM=61.0 | APL=73.9</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -45588,52 +45580,60 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>DINO-X</t>
+          <t>DEIM-D-FINE-X</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>IDEA Research</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>AP=56.0</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
+          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>T4 78</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
+          <t>✅ verified (DEIM arxiv 2412.04234 Table (COCO val)): full COCO val breakdown AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2411.14347</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -45645,60 +45645,52 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-X</t>
+          <t>DINO-X</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>IDEA Research</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>T4 78</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=56.0</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
+          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2411.14347</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -45715,55 +45707,55 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>YOLOv9-E</t>
+          <t>D-FINE-X</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>55.6</v>
+        <v>55.8</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>AP=55.6</t>
+          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>57.3M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
+          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.13616</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -45780,55 +45772,55 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>YOLOv12-X</t>
+          <t>YOLOv9-E</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+          <t>AP=55.6</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>T4 ≈90</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>59.1M</t>
+          <t>57.3M</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2502.12524</t>
+          <t>https://arxiv.org/abs/2402.13616</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -45840,32 +45832,32 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ConvNeXt-XL Cascade</t>
+          <t>YOLOv12-X</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
@@ -45873,19 +45865,27 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈90</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>59.1M</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
+          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.03545</t>
+          <t>https://arxiv.org/abs/2502.12524</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -45897,17 +45897,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>EfficientDet-D7</t>
+          <t>ConvNeXt-XL Cascade</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Tan et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -45917,7 +45917,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -45926,23 +45926,23 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>AP=55.1</t>
+          <t>AP=55.2</t>
         </is>
       </c>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1911.09070</t>
+          <t>https://arxiv.org/abs/2201.03545</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -45959,22 +45959,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>YOLOv13-X</t>
+          <t>EfficientDet-D7</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>iMoonLab</t>
+          <t>Tan et al.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -45983,23 +45983,23 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>54.8</v>
+        <v>55.1</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>AP=54.8</t>
+          <t>AP=55.1</t>
         </is>
       </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
+          <t>https://arxiv.org/abs/1911.09070</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -46016,55 +46016,47 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>YOLO11x</t>
+          <t>YOLOv13-X</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Ultralytics</t>
+          <t>iMoonLab</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>AP=54.7</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈110</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>56.9M</t>
-        </is>
-      </c>
+          <t>AP=54.8</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>https://docs.ultralytics.com/models/yolo11/</t>
+          <t>https://arxiv.org/abs/2506.17733</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -46081,27 +46073,27 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-L</t>
+          <t>YOLO11x</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>Ultralytics</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
@@ -46112,16 +46104,24 @@
           <t>AP=54.7</t>
         </is>
       </c>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈110</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>56.9M</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
+          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://docs.ultralytics.com/models/yolo11/</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -46138,22 +46138,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>PP-YOLOE+ (X)</t>
+          <t>DEIM-D-FINE-L</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -46173,12 +46173,12 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16250</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -46195,22 +46195,22 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3-R101</t>
+          <t>PP-YOLOE+ (X)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>WACV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -46219,23 +46219,23 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>AP=54.6</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2409.08475</t>
+          <t>https://arxiv.org/abs/2203.16250</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -46252,22 +46252,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3</t>
+          <t>RT-DETRv3-R101</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>WACV</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -46287,12 +46287,12 @@
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2409.08475</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -46309,22 +46309,22 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>YOLOv10-X</t>
+          <t>RT-DETRv3</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -46333,23 +46333,23 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>AP=54.4</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.14458</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -46366,22 +46366,22 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv2-R101</t>
+          <t>YOLOv10-X</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Lv et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -46390,23 +46390,23 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>AP=54.3</t>
+          <t>AP=54.4</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2407.17140</t>
+          <t>https://arxiv.org/abs/2405.14458</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -46423,22 +46423,22 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>RT-DETR-R101</t>
+          <t>RT-DETRv2-R101</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Zhao et al.</t>
+          <t>Lv et al.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -46458,12 +46458,12 @@
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.08069</t>
+          <t>https://arxiv.org/abs/2407.17140</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -46475,27 +46475,27 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO 1.5 Pro</t>
+          <t>RT-DETR-R101</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Zhao et al.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -46515,12 +46515,12 @@
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：54.3 AP zero-shot COCO transfer (paper text "achieves a 54.3 AP, improving upon GD Swin-L by 1.8 AP") [Open-set OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.10300</t>
+          <t>https://arxiv.org/abs/2304.08069</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -46532,27 +46532,27 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-L</t>
+          <t>Grounding DINO 1.5 Pro</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -46561,23 +46561,23 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>AP=54.0</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：54.3 AP zero-shot COCO transfer (paper text "achieves a 54.3 AP, improving upon GD Swin-L by 1.8 AP") [Open-set OD]</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2405.10300</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -46589,27 +46589,27 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MaxViT-XL Cascade</t>
+          <t>D-FINE-L</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Tu et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -46618,23 +46618,23 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>53.4</v>
+        <v>54</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>AP=53.4 | AP50=72.9 | AP75=58.1</t>
+          <t>AP=54.0</t>
         </is>
       </c>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (MaxViT ECCV22 arxiv 2204.01697 Table, Cascade Mask R-CNN, COCO val): box AP 53.4/AP50 72.9/AP75 58.1. 註：偵測用 MaxViT-B（非 XL；XL 僅分類）；原 45.7/70.3/50.0 為 mask 指標非 APS/APM/APL</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2204.01697</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
@@ -46646,27 +46646,27 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>YOLOv7-X</t>
+          <t>MaxViT-XL Cascade</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Tu et al.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -46675,23 +46675,23 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>52.9</v>
+        <v>53.4</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>AP=52.9</t>
+          <t>AP=53.4 | AP50=72.9 | AP75=58.1</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
+          <t>✅ verified+corrected (MaxViT ECCV22 arxiv 2204.01697 Table, Cascade Mask R-CNN, COCO val): box AP 53.4/AP50 72.9/AP75 58.1. 註：偵測用 MaxViT-B（非 XL；XL 僅分類）；原 45.7/70.3/50.0 為 mask 指標非 APS/APM/APL</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2207.02696</t>
+          <t>https://arxiv.org/abs/2204.01697</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -46708,22 +46708,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>RTMDet-X</t>
+          <t>YOLOv7-X</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Lyu et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -46732,23 +46732,23 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>AP=52.8</t>
+          <t>AP=52.9</t>
         </is>
       </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2212.07784</t>
+          <t>https://arxiv.org/abs/2207.02696</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -46765,12 +46765,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>YOLOv6-L</t>
+          <t>RTMDet-X</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Lyu et al.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -46780,7 +46780,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -46800,12 +46800,12 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2209.02976</t>
+          <t>https://arxiv.org/abs/2212.07784</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
@@ -46817,27 +46817,27 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>YOLOv6-L</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -46846,23 +46846,23 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>AP=52.5</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/2209.02976</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -46874,27 +46874,27 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>YOLOX-X</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Ge et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -46903,23 +46903,23 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>51.2</v>
+        <v>52.5</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>AP=51.2</t>
+          <t>AP=52.5</t>
         </is>
       </c>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
+          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2107.08430</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -46936,12 +46936,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>DAMO-YOLO-l</t>
+          <t>YOLOX-X</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Ge et al.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -46951,7 +46951,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -46960,23 +46960,23 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>AP=50.8</t>
+          <t>AP=51.2</t>
         </is>
       </c>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
+          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.15444</t>
+          <t>https://arxiv.org/abs/2107.08430</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -46988,27 +46988,27 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>UniFS (UniDetector)</t>
+          <t>DAMO-YOLO-l</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -47017,23 +47017,23 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>49.3</v>
+        <v>50.8</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>AP=49.3</t>
+          <t>AP=50.8</t>
         </is>
       </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
+          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11749</t>
+          <t>https://arxiv.org/abs/2211.15444</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -47045,27 +47045,27 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Nano)</t>
+          <t>UniFS (UniDetector)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -47074,23 +47074,23 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>48</v>
+        <v>49.3</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>AP=48.0</t>
+          <t>AP=49.3</t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://arxiv.org/abs/2303.11749</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -47102,17 +47102,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Deformable DETR (R50)</t>
+          <t>RF-DETR (Nano)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Zhu et al.</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -47122,7 +47122,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -47131,23 +47131,23 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>46.9</v>
+        <v>48</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>AP=46.9</t>
+          <t>AP=48.0</t>
         </is>
       </c>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
+          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2010.04159</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -47164,12 +47164,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>DAB-DETR</t>
+          <t>Deformable DETR (R50)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Zhu et al.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -47179,7 +47179,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -47188,23 +47188,23 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>AP=46.8</t>
+          <t>AP=46.9</t>
         </is>
       </c>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
+          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.12329</t>
+          <t>https://arxiv.org/abs/2010.04159</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -47216,27 +47216,27 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DETReg</t>
+          <t>DAB-DETR</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Bar et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -47245,23 +47245,23 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>45.5</v>
+        <v>46.8</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>AP=45.5</t>
+          <t>AP=46.8</t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
+          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.04550</t>
+          <t>https://arxiv.org/abs/2201.12329</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
@@ -47273,27 +47273,27 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
+          <t>DETReg</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bar et al.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -47302,23 +47302,23 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>AP=45.3 | AP50=62.0</t>
+          <t>AP=45.5</t>
         </is>
       </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (Brain-Inspired Spiking NN CVPR25 CVF PDF): COCO val mAP@0.5:0.95=45.3 / mAP@50=62.0。註：脈衝神經網路 (SNN) 節能設定，與標準 ANN 偵測器非完全可比</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2106.04550</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
@@ -47335,22 +47335,22 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -47359,23 +47359,23 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>44.1</v>
+        <v>45.3</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>AP=44.1</t>
+          <t>AP=45.3 | AP50=62.0</t>
         </is>
       </c>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
+          <t>✅ verified (Brain-Inspired Spiking NN CVPR25 CVF PDF): COCO val mAP@0.5:0.95=45.3 / mAP@50=62.0。註：脈衝神經網路 (SNN) 節能設定，與標準 ANN 偵測器非完全可比</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -47392,22 +47392,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
+          <t>Sparse R-CNN (R101)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -47416,23 +47416,23 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>AP=43.5</t>
+          <t>AP=44.1</t>
         </is>
       </c>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -47449,22 +47449,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>DN-DETR</t>
+          <t>DETR (R101)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -47473,23 +47473,23 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>AP=43.4</t>
+          <t>AP=43.5</t>
         </is>
       </c>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.01305</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
@@ -47506,12 +47506,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Cascade R-CNN (R101-FPN)</t>
+          <t>DN-DETR</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Cai &amp; Vasconcelos</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -47521,7 +47521,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -47530,23 +47530,23 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>42.8</v>
+        <v>43.4</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>AP=42.8</t>
+          <t>AP=43.4</t>
         </is>
       </c>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
+          <t>https://arxiv.org/abs/2203.01305</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
@@ -47563,22 +47563,22 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>Cascade R-CNN (R101-FPN)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Cai &amp; Vasconcelos</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -47587,23 +47587,23 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>AP=42.1</t>
+          <t>AP=42.8</t>
         </is>
       </c>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
+          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/1712.00726</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr">
@@ -47620,17 +47620,17 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>FCOS (R101)</t>
+          <t>CenterNet</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -47644,23 +47644,23 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>41.5</v>
+        <v>42.1</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>AP=41.5</t>
+          <t>AP=42.1</t>
         </is>
       </c>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.01355</t>
+          <t>https://arxiv.org/abs/1904.07850</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr">
@@ -47677,22 +47677,22 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Faster R-CNN (R50-FPN)</t>
+          <t>FCOS (R101)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -47701,23 +47701,23 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>40.2</v>
+        <v>41.5</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>AP=40.2</t>
+          <t>AP=41.5</t>
         </is>
       </c>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
+          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
+          <t>https://arxiv.org/abs/1904.01355</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr">
@@ -47734,22 +47734,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>RetinaNet (R101)</t>
+          <t>Faster R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Lin et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -47758,23 +47758,23 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>39.1</v>
+        <v>40.2</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>AP=39.1</t>
+          <t>AP=40.2</t>
         </is>
       </c>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
+          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1708.02002</t>
+          <t>https://arxiv.org/abs/1506.01497</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
@@ -47791,12 +47791,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Mask R-CNN (R50-FPN)</t>
+          <t>RetinaNet (R101)</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>He et al.</t>
+          <t>Lin et al.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -47815,23 +47815,23 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>AP=38.6</t>
+          <t>AP=39.1</t>
         </is>
       </c>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
+          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1703.06870</t>
+          <t>https://arxiv.org/abs/1708.02002</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
@@ -47843,27 +47843,27 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>NTIRE 2025 CD-FSOD top method</t>
+          <t>Mask R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Various teams</t>
+          <t>He et al.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>CVPR Workshop</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -47871,18 +47871,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G53" s="3" t="n"/>
-      <c r="H53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>AP=38.6</t>
+        </is>
+      </c>
       <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>⚠️ NTIRE 2025 CD-FSOD top method (arxiv 2504.10685): 跨域少樣本 OD，COCO 作為 source domain 之一，非標準 COCO val box AP</t>
+          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.10685</t>
+          <t>https://arxiv.org/abs/1703.06870</t>
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr">
@@ -47899,22 +47905,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CD-ViTO</t>
+          <t>NTIRE 2025 CD-FSOD top method</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Fu et al.</t>
+          <t>Various teams</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR Workshop</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -47928,12 +47934,12 @@
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：CD-ViTO 是 Cross-Domain FSOD 方法（ECCV24），測試 ArTaxOr/Clipart1k/DIOR/DeepFish/NEU-DET/UODD（CD-FSOD 6 datasets），不直接報告 COCO 2017</t>
+          <t>⚠️ NTIRE 2025 CD-FSOD top method (arxiv 2504.10685): 跨域少樣本 OD，COCO 作為 source domain 之一，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.03094</t>
+          <t>https://arxiv.org/abs/2504.10685</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr">
@@ -47945,27 +47951,27 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>BiRefNet</t>
+          <t>CD-ViTO</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Zheng et al.</t>
+          <t>Fu et al.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>CAAI AIR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -47979,12 +47985,12 @@
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：BiRefNet 是 high-resolution SOD/DIS 方法，不測 COCO 2017。應在 DUTS-TE/ECSSD/HKU-IS 等 SOD sheets</t>
+          <t>⚠️ CD-ViTO (arxiv 2402.03094): 跨域少樣本 OD (CD-FSOD)，報目標域 K-shot AP，非標準 COCO 2017 val box AP — 誤放</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.03407</t>
+          <t>https://arxiv.org/abs/2402.03094</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr">
@@ -47996,27 +48002,27 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Meta-DETR</t>
+          <t>BiRefNet</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Zheng et al.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>TPAMI</t>
+          <t>CAAI AIR</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -48030,12 +48036,12 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta-DETR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ BiRefNet (arxiv 2401.03407): dichotomous/salient object segmentation (DIS-5K/SOD，S-measure/MAE/maxF)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2208.00219</t>
+          <t>https://arxiv.org/abs/2401.03407</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr">
@@ -48052,22 +48058,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>DeFRCN</t>
+          <t>Meta-DETR</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Qiao et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>TPAMI</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -48081,12 +48087,12 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：DeFRCN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ Meta-DETR (arxiv 2208.00219): few-shot OD，報 MS-COCO K-shot novel AP（見 few-shot sheets），非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.09017</t>
+          <t>https://arxiv.org/abs/2208.00219</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr">
@@ -48098,17 +48104,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Swin-L Cascade Mask R-CNN</t>
+          <t>DeFRCN</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Qiao et al.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -48118,7 +48124,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -48132,12 +48138,12 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 重複條目：Swin-L Cascade Mask R-CNN headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
+          <t>⚠️ DeFRCN (arxiv 2108.09017): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.14030</t>
+          <t>https://arxiv.org/abs/2108.09017</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
@@ -48183,7 +48189,7 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：FSCE 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ FSCE (arxiv 2103.05950): few-shot OD，報 10/30-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
@@ -48234,7 +48240,7 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：MPSR 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ MPSR (arxiv 2007.09384): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -48285,7 +48291,7 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：TFA w/cos 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ TFA w/cos (arxiv 2003.06957): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
@@ -50407,16 +50413,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -48342,7 +48342,7 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：Meta R-CNN 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ Meta R-CNN (arxiv 1909.13032): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
@@ -48393,7 +48393,7 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 誤放 (COCO 2017 sheet)：FSRW 是 few-shot OD 方法（COCO 60 base / 20 novel K-shot novel AP），非標準 COCO 80-class AP</t>
+          <t>⚠️ FSRW/Meta-YOLO (arxiv 1812.01866): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
@@ -48444,7 +48444,7 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Exploring Hierarchical Consistency and U: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
+          <t>⚠️ Exploring Hierarchical Consistency (arxiv 2604.23344): open-vocabulary OD，PDF 查證評估於 COCO+LVIS open-vocab (novel/base split)，box AP:0 — 非標準 supervised COCO val box AP</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
@@ -48546,7 +48546,7 @@
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Believing is Seeing: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
+          <t>⚠️ Believing is Seeing (CVPR25): PDF 查證 COCO 僅 4 次、box AP:0 — 非標準 COCO 偵測 benchmark 條目（專門任務）</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
@@ -48597,7 +48597,7 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>⚠️ OW-OVD: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
+          <t>⚠️ OW-OVD (CVPR25): open-world OD，PDF 查證報 U-Recall/Unknown (×17) 等 OWOD 指標，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -48648,7 +48648,7 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Shift the Lens: 領域專門 (RAW/熱影像/domain-shift)，非標準 COCO val AP</t>
+          <t>⚠️ Shift the Lens (CVPR25): PDF 查證 box AP:0、含 salient 內容 — 專門設定，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
@@ -48699,7 +48699,7 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Visual Consensus Prompting for Co-Salien: 顯著物件偵測 (SOD/Co-SOD)，非 COCO box AP</t>
+          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -48750,7 +48750,7 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Language-Guided Salient Object Ranking: 顯著物件偵測 (SOD/Co-SOD)，非 COCO box AP</t>
+          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -43104,14 +43104,14 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>AP=56.5</t>
+          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 1)：DEIM-D-FINE-X 56.5 AP COCO val (headline number) [End-to-end RT-OD]</t>
+          <t>✅ verified (DEIM CVPR25 arxiv 2412.04234 Table, DEIM-X best, COCO val): 56.5/74.0/61.5/38.8/61.4/74.2</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -45650,22 +45650,22 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>DINO-X</t>
+          <t>DEIM</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>IDEA Research</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -45674,23 +45674,23 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AP=56.0</t>
+          <t>AP=56.5 | AP50=74.0 | AP75=61.5 | APS=38.8 | APM=61.4 | APL=74.2</t>
         </is>
       </c>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
+          <t>✅ verified (DEIM CVPR25 arxiv 2412.04234 Table, DEIM-X best, COCO val): 56.5/74.0/61.5/38.8/61.4/74.2</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2411.14347</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -45702,60 +45702,52 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-X</t>
+          <t>DINO-X</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>IDEA Research</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>T4 78</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>AP=56.0</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
+          <t>✅ 已驗證 (DINO-X arXiv24 abstract)：DINO-X Pro 56.0% AP on COCO zero-shot transfer [Open-vocab Foundation Model]</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2411.14347</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -45772,55 +45764,55 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>YOLOv9-E</t>
+          <t>D-FINE-X</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>55.6</v>
+        <v>55.8</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>AP=55.6</t>
+          <t>AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>T4 78</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>57.3M</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
+          <t>✅ verified (D-FINE arxiv 2410.13842 Table (COCO val)): full COCO val breakdown AP=55.8 | AP50=73.7 | AP75=60.2 | APS=37.3 | APM=60.5 | APL=73.4</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.13616</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -45837,55 +45829,55 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>YOLOv12-X</t>
+          <t>YOLOv9-E</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+          <t>AP=55.6</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>T4 ≈90</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>59.1M</t>
+          <t>57.3M</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+          <t>✅ verified (YOLOv9 ECCV24, arxiv 2402.13616 Table 1): 55.6 box AP COCO val2017 (YOLOv9-E)</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2502.12524</t>
+          <t>https://arxiv.org/abs/2402.13616</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -45897,32 +45889,32 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ConvNeXt-XL Cascade</t>
+          <t>YOLOv12-X</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
@@ -45930,19 +45922,27 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>AP=55.2</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+          <t>AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈90</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>59.1M</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
+          <t>✅ verified (YOLOv12 arxiv 2502.12524 Table (COCO val)): full COCO val breakdown AP=55.2 | AP50=72.0 | AP75=60.2 | APS=39.6 | APM=60.7 | APL=70.9</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.03545</t>
+          <t>https://arxiv.org/abs/2502.12524</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -45954,17 +45954,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>EfficientDet-D7</t>
+          <t>ConvNeXt-XL Cascade</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Tan et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -45974,7 +45974,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -45983,23 +45983,23 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>AP=55.1</t>
+          <t>AP=55.2</t>
         </is>
       </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 8)：ConvNeXt-XL with Cascade Mask R-CNN 55.2 box AP COCO test-dev</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1911.09070</t>
+          <t>https://arxiv.org/abs/2201.03545</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -46016,22 +46016,22 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>YOLOv13-X</t>
+          <t>EfficientDet-D7</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>iMoonLab</t>
+          <t>Tan et al.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -46040,23 +46040,23 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>54.8</v>
+        <v>55.1</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>AP=54.8</t>
+          <t>AP=55.1</t>
         </is>
       </c>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (EfficientDet CVPR20 paper abstract)：EfficientDet-D7 55.1% AP on COCO test-dev, single-model single-scale [Real-Time OD]</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.17733</t>
+          <t>https://arxiv.org/abs/1911.09070</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -46073,55 +46073,47 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>YOLO11x</t>
+          <t>YOLOv13-X</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Ultralytics</t>
+          <t>iMoonLab</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Official Docs</t>
+          <t>Preprint</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>AP=54.7</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>T4 ≈110</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>56.9M</t>
-        </is>
-      </c>
+          <t>AP=54.8</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv13-X 54.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>https://docs.ultralytics.com/models/yolo11/</t>
+          <t>https://arxiv.org/abs/2506.17733</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -46138,27 +46130,27 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>DEIM-D-FINE-L</t>
+          <t>YOLO11x</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Huang et al.</t>
+          <t>Ultralytics</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Preprint</t>
+          <t>Official Docs</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
@@ -46169,16 +46161,24 @@
           <t>AP=54.7</t>
         </is>
       </c>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>T4 ≈110</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>56.9M</t>
+        </is>
+      </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
+          <t>✅ verified (Ultralytics YOLO11 official docs): 54.7 box AP COCO val2017 (YOLO11x)</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.04234</t>
+          <t>https://docs.ultralytics.com/models/yolo11/</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -46195,22 +46195,22 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>PP-YOLOE+ (X)</t>
+          <t>DEIM-D-FINE-L</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Huang et al.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -46230,12 +46230,12 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
+          <t>✅ 已驗證 (DEIM CVPR25 Table 1, COCO val2017)：DEIM-D-FINE-L 54.7% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.16250</t>
+          <t>https://arxiv.org/abs/2412.04234</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -46252,22 +46252,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3-R101</t>
+          <t>PP-YOLOE+ (X)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>WACV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -46276,23 +46276,23 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>AP=54.6</t>
+          <t>AP=54.7</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (PP-YOLOE+ arXiv22 Table 1)：PP-YOLOE+-X 54.7% AP COCO test-dev [Real-Time OD]</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2409.08475</t>
+          <t>https://arxiv.org/abs/2203.16250</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -46309,22 +46309,22 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv3</t>
+          <t>RT-DETRv3-R101</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>WACV 2025</t>
+          <t>WACV</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -46344,12 +46344,12 @@
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1, COCO val2017 6x)：RT-DETRv3-R101 54.6% AP [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2409.08475</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -46366,22 +46366,22 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>YOLOv10-X</t>
+          <t>RT-DETRv3</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -46390,23 +46390,23 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>AP=54.4</t>
+          <t>AP=54.6</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (RT-DETRv3 Table 1)：headline number from R101 6x setting [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.14458</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Wang_RT-DETRv3_Real-Time_End-to-End_Object_Detection_with_Hierarchical_Dense_Positive_Supervision_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -46423,22 +46423,22 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>RT-DETRv2-R101</t>
+          <t>YOLOv10-X</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Lv et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -46447,23 +46447,23 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>AP=54.3</t>
+          <t>AP=54.4</t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (YOLOv13 Table I, COCO val2017)：YOLOv10-X 54.4% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2407.17140</t>
+          <t>https://arxiv.org/abs/2405.14458</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -46480,22 +46480,22 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>RT-DETR-R101</t>
+          <t>RT-DETRv2-R101</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Zhao et al.</t>
+          <t>Lv et al.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -46515,12 +46515,12 @@
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETRv2-R101 54.3% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2304.08069</t>
+          <t>https://arxiv.org/abs/2407.17140</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -46532,27 +46532,27 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO 1.5 Pro</t>
+          <t>RT-DETR-R101</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Zhao et al.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -46572,12 +46572,12 @@
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：54.3 AP zero-shot COCO transfer (paper text "achieves a 54.3 AP, improving upon GD Swin-L by 1.8 AP") [Open-set OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RT-DETR-R101 54.3% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2405.10300</t>
+          <t>https://arxiv.org/abs/2304.08069</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -46589,27 +46589,27 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>D-FINE-L</t>
+          <t>Grounding DINO 1.5 Pro</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Peng et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -46618,23 +46618,23 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>AP=54.0</t>
+          <t>AP=54.3</t>
         </is>
       </c>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (Grounding DINO 1.5 Pro Table 1)：54.3 AP zero-shot COCO transfer (paper text "achieves a 54.3 AP, improving upon GD Swin-L by 1.8 AP") [Open-set OD]</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.13842</t>
+          <t>https://arxiv.org/abs/2405.10300</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
@@ -46646,27 +46646,27 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>MaxViT-XL Cascade</t>
+          <t>D-FINE-L</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Tu et al.</t>
+          <t>Peng et al.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -46675,23 +46675,23 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>53.4</v>
+        <v>54</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>AP=53.4 | AP50=72.9 | AP75=58.1</t>
+          <t>AP=54.0</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>✅ verified+corrected (MaxViT ECCV22 arxiv 2204.01697 Table, Cascade Mask R-CNN, COCO val): box AP 53.4/AP50 72.9/AP75 58.1. 註：偵測用 MaxViT-B（非 XL；XL 僅分類）；原 45.7/70.3/50.0 為 mask 指標非 APS/APM/APL</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：D-FINE-L 54.0% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2204.01697</t>
+          <t>https://arxiv.org/abs/2410.13842</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -46703,27 +46703,27 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>YOLOv7-X</t>
+          <t>MaxViT-XL Cascade</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Tu et al.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -46732,23 +46732,23 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>52.9</v>
+        <v>53.4</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>AP=52.9</t>
+          <t>AP=53.4 | AP50=72.9 | AP75=58.1</t>
         </is>
       </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
+          <t>✅ verified+corrected (MaxViT ECCV22 arxiv 2204.01697 Table, Cascade Mask R-CNN, COCO val): box AP 53.4/AP50 72.9/AP75 58.1. 註：偵測用 MaxViT-B（非 XL；XL 僅分類）；原 45.7/70.3/50.0 為 mask 指標非 APS/APM/APL</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2207.02696</t>
+          <t>https://arxiv.org/abs/2204.01697</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -46765,22 +46765,22 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>RTMDet-X</t>
+          <t>YOLOv7-X</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Lyu et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -46789,23 +46789,23 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>AP=52.8</t>
+          <t>AP=52.9</t>
         </is>
       </c>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv7-X 52.9% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2212.07784</t>
+          <t>https://arxiv.org/abs/2207.02696</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
@@ -46822,12 +46822,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>YOLOv6-L</t>
+          <t>RTMDet-X</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Lyu et al.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -46837,7 +46837,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -46857,12 +46857,12 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：RTMDet-X 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2209.02976</t>
+          <t>https://arxiv.org/abs/2212.07784</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -46874,27 +46874,27 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Grounding DINO</t>
+          <t>YOLOv6-L</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -46903,23 +46903,23 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>AP=52.5</t>
+          <t>AP=52.8</t>
         </is>
       </c>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
+          <t>✅ 已驗證 (D-FINE Table 1, COCO val2017)：YOLOv6-L 52.8% AP [Real-Time OD]</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.05499</t>
+          <t>https://arxiv.org/abs/2209.02976</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -46931,27 +46931,27 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>YOLOX-X</t>
+          <t>Grounding DINO</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Ge et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -46960,23 +46960,23 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>51.2</v>
+        <v>52.5</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>AP=51.2</t>
+          <t>AP=52.5</t>
         </is>
       </c>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
+          <t>✅ 已驗證 (Grounding DINO ECCV24 paper)：52.5 AP on COCO zero-shot transfer [Open-set OD]</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2107.08430</t>
+          <t>https://arxiv.org/abs/2303.05499</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -46993,12 +46993,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>DAMO-YOLO-l</t>
+          <t>YOLOX-X</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Xu et al.</t>
+          <t>Ge et al.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -47008,7 +47008,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -47017,23 +47017,23 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>AP=50.8</t>
+          <t>AP=51.2</t>
         </is>
       </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
+          <t>✅ 已驗證 (YOLOX arXiv21 Table 3, COCO val)：YOLOX-X 51.2% AP, 99.1M params [Real-Time OD]</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2211.15444</t>
+          <t>https://arxiv.org/abs/2107.08430</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -47045,27 +47045,27 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>UniFS (UniDetector)</t>
+          <t>DAMO-YOLO-l</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Xu et al.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -47074,23 +47074,23 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>49.3</v>
+        <v>50.8</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>AP=49.3</t>
+          <t>AP=50.8</t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
+          <t>✅ 已驗證 (DAMO-YOLO arXiv22 Table 1)：DAMO-YOLO-L 50.8% AP COCO test-dev, 42ms@T4 [Real-Time OD]</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.11749</t>
+          <t>https://arxiv.org/abs/2211.15444</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -47102,27 +47102,27 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>RF-DETR (Nano)</t>
+          <t>UniFS (UniDetector)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Roboflow</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -47131,23 +47131,23 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>48</v>
+        <v>49.3</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>AP=48.0</t>
+          <t>AP=49.3</t>
         </is>
       </c>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
+          <t>✅ 已驗證 (UniDetector CVPR23 Table 2)：UniDetector ResNet-50 1× → 49.3 AP COCO val [Universal OD]</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.09554</t>
+          <t>https://arxiv.org/abs/2303.11749</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -47159,17 +47159,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Deformable DETR (R50)</t>
+          <t>RF-DETR (Nano)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Zhu et al.</t>
+          <t>Roboflow</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -47179,7 +47179,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -47188,23 +47188,23 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>46.9</v>
+        <v>48</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>AP=46.9</t>
+          <t>AP=48.0</t>
         </is>
       </c>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
+          <t>✅ 已驗證 (RF-DETR arXiv25 abstract)：RF-DETR nano 48.0 AP COCO, beats D-FINE nano by 5.0 [End-to-end RT-OD]</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2010.04159</t>
+          <t>https://arxiv.org/abs/2511.09554</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DAB-DETR</t>
+          <t>Deformable DETR (R50)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>Zhu et al.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -47236,7 +47236,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -47245,23 +47245,23 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>AP=46.8</t>
+          <t>AP=46.9</t>
         </is>
       </c>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
+          <t>✅ 已驗證 (Deformable DETR ICLR21 Table 3)：R50 backbone, 46.9% AP, end-to-end transformer detector [DETR-based]</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2201.12329</t>
+          <t>https://arxiv.org/abs/2010.04159</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
@@ -47273,27 +47273,27 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>DETReg</t>
+          <t>DAB-DETR</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Bar et al.</t>
+          <t>Liu et al.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -47302,23 +47302,23 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45.5</v>
+        <v>46.8</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>AP=45.5</t>
+          <t>AP=46.8</t>
         </is>
       </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
+          <t>✅ 已驗證 (DAB-DETR ICLR22 Table 2)：DAB-Deformable-DETR-R50 46.8% AP COCO val (50 epochs) [DETR variant]</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2106.04550</t>
+          <t>https://arxiv.org/abs/2201.12329</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
@@ -47330,27 +47330,27 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
+          <t>DETReg</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bar et al.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -47359,23 +47359,23 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>AP=45.3 | AP50=62.0</t>
+          <t>AP=45.5</t>
         </is>
       </c>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>✅ verified (Brain-Inspired Spiking NN CVPR25 CVF PDF): COCO val mAP@0.5:0.95=45.3 / mAP@50=62.0。註：脈衝神經網路 (SNN) 節能設定，與標準 ANN 偵測器非完全可比</t>
+          <t>✅ 已驗證 (DETReg CVPR22 Table 1)：DETReg 45.5 AP COCO val under semi-supervised fine-tuning [Self-supervised pre-train OD]</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2106.04550</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -47392,22 +47392,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Sparse R-CNN (R101)</t>
+          <t>Brain-Inspired Spiking Neural Networks for Energy-Efficient</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -47416,23 +47416,23 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>44.1</v>
+        <v>45.3</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>AP=44.1</t>
+          <t>AP=45.3 | AP50=62.0</t>
         </is>
       </c>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
+          <t>✅ verified (Brain-Inspired Spiking NN CVPR25 CVF PDF): COCO val mAP@0.5:0.95=45.3 / mAP@50=62.0。註：脈衝神經網路 (SNN) 節能設定，與標準 ANN 偵測器非完全可比</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2011.12450</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Brain-Inspired_Spiking_Neural_Networks_for_Energy-Efficient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -47449,22 +47449,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>DETR (R101)</t>
+          <t>Sparse R-CNN (R101)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Carion et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -47473,23 +47473,23 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>AP=43.5</t>
+          <t>AP=44.1</t>
         </is>
       </c>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
+          <t>✅ 已驗證 (Sparse R-CNN CVPR21 Table 1)：R101-FPN 44.1% AP [Sparse Query OD]</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2005.12872</t>
+          <t>https://arxiv.org/abs/2011.12450</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
@@ -47506,22 +47506,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>DN-DETR</t>
+          <t>DETR (R101)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Carion et al.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2020-09</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -47530,23 +47530,23 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>AP=43.4</t>
+          <t>AP=43.5</t>
         </is>
       </c>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
+          <t>✅ 已驗證 (DETR ECCV20 Table 1)：DETR-R101 43.5% AP on COCO 2017 val [DETR-based OD]</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2203.01305</t>
+          <t>https://arxiv.org/abs/2005.12872</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
@@ -47563,12 +47563,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Cascade R-CNN (R101-FPN)</t>
+          <t>DN-DETR</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Cai &amp; Vasconcelos</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -47578,7 +47578,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -47587,23 +47587,23 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>42.8</v>
+        <v>43.4</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>AP=42.8</t>
+          <t>AP=43.4</t>
         </is>
       </c>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
+          <t>✅ 已驗證 (DN-DETR CVPR22 Table 1)：DN-Deformable-DETR-R50 43.4% AP COCO val (12 epochs) [DETR denoising training]</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1712.00726</t>
+          <t>https://arxiv.org/abs/2203.01305</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr">
@@ -47620,22 +47620,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CenterNet</t>
+          <t>Cascade R-CNN (R101-FPN)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Cai &amp; Vasconcelos</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -47644,23 +47644,23 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>AP=42.1</t>
+          <t>AP=42.8</t>
         </is>
       </c>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
+          <t>✅ 已驗證 (Cascade R-CNN CVPR18 Table 5)：ResNet-101 42.8% AP [Two-Stage Cascade OD]</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.07850</t>
+          <t>https://arxiv.org/abs/1712.00726</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr">
@@ -47677,17 +47677,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>FCOS (R101)</t>
+          <t>CenterNet</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tian et al.</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -47701,23 +47701,23 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>41.5</v>
+        <v>42.1</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>AP=41.5</t>
+          <t>AP=42.1</t>
         </is>
       </c>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
+          <t>✅ 已驗證 (CenterNet ICCV19 Table 2)：Hourglass-104 42.1% AP [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1904.01355</t>
+          <t>https://arxiv.org/abs/1904.07850</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr">
@@ -47734,22 +47734,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Faster R-CNN (R50-FPN)</t>
+          <t>FCOS (R101)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Tian et al.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -47758,23 +47758,23 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>40.2</v>
+        <v>41.5</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>AP=40.2</t>
+          <t>AP=41.5</t>
         </is>
       </c>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
+          <t>✅ 已驗證 (FCOS ICCV19 Table 4)：FCOS ResNet-101-FPN 41.5 AP COCO test-dev [Anchor-free OD]</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1506.01497</t>
+          <t>https://arxiv.org/abs/1904.01355</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
@@ -47791,22 +47791,22 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>RetinaNet (R101)</t>
+          <t>Faster R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Lin et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>NeurIPS</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -47815,23 +47815,23 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>39.1</v>
+        <v>40.2</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>AP=39.1</t>
+          <t>AP=40.2</t>
         </is>
       </c>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
+          <t>✅ 已驗證 (DETR Table 1 cites Detectron2 baseline)：Faster R-CNN R50-FPN 40.2% AP on COCO 2017 val [Two-Stage OD baseline]</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1708.02002</t>
+          <t>https://arxiv.org/abs/1506.01497</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
@@ -47848,12 +47848,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Mask R-CNN (R50-FPN)</t>
+          <t>RetinaNet (R101)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>He et al.</t>
+          <t>Lin et al.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -47872,23 +47872,23 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>AP=38.6</t>
+          <t>AP=39.1</t>
         </is>
       </c>
       <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
+          <t>✅ 已驗證 (RetinaNet ICCV17 Table 2)：ResNet-101-FPN 39.1% AP [Focal Loss OD]</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1703.06870</t>
+          <t>https://arxiv.org/abs/1708.02002</t>
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr">
@@ -47900,27 +47900,27 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>NTIRE 2025 CD-FSOD top method</t>
+          <t>Mask R-CNN (R50-FPN)</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Various teams</t>
+          <t>He et al.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>CVPR Workshop</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -47928,18 +47928,24 @@
           <t>Preprint</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>AP=38.6</t>
+        </is>
+      </c>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>⚠️ NTIRE 2025 CD-FSOD top method (arxiv 2504.10685): 跨域少樣本 OD，COCO 作為 source domain 之一，非標準 COCO val box AP</t>
+          <t>✅ 已驗證 (Mask R-CNN paper Table 3 + Detectron2 model zoo)：Mask R-CNN R50-FPN ~38.6 box AP COCO val (R101 paper Table 3: 38.2 test-dev box)</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2504.10685</t>
+          <t>https://arxiv.org/abs/1703.06870</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr">
@@ -47956,22 +47962,22 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CD-ViTO</t>
+          <t>NTIRE 2025 CD-FSOD top method</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Fu et al.</t>
+          <t>Various teams</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR Workshop</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -47985,12 +47991,12 @@
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>⚠️ CD-ViTO (arxiv 2402.03094): 跨域少樣本 OD (CD-FSOD)，報目標域 K-shot AP，非標準 COCO 2017 val box AP — 誤放</t>
+          <t>⚠️ NTIRE 2025 CD-FSOD top method (arxiv 2504.10685): 跨域少樣本 OD，COCO 作為 source domain 之一，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.03094</t>
+          <t>https://arxiv.org/abs/2504.10685</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr">
@@ -48002,27 +48008,27 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>BiRefNet</t>
+          <t>CD-ViTO</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Zheng et al.</t>
+          <t>Fu et al.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>CAAI AIR</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -48036,12 +48042,12 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>⚠️ BiRefNet (arxiv 2401.03407): dichotomous/salient object segmentation (DIS-5K/SOD，S-measure/MAE/maxF)，非 COCO box AP — 誤放</t>
+          <t>⚠️ CD-ViTO (arxiv 2402.03094): 跨域少樣本 OD (CD-FSOD)，報目標域 K-shot AP，非標準 COCO 2017 val box AP — 誤放</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2401.03407</t>
+          <t>https://arxiv.org/abs/2402.03094</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr">
@@ -48053,27 +48059,27 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Meta-DETR</t>
+          <t>BiRefNet</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Zheng et al.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>TPAMI</t>
+          <t>CAAI AIR</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -48087,12 +48093,12 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Meta-DETR (arxiv 2208.00219): few-shot OD，報 MS-COCO K-shot novel AP（見 few-shot sheets），非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ BiRefNet (arxiv 2401.03407): dichotomous/salient object segmentation (DIS-5K/SOD，S-measure/MAE/maxF)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2208.00219</t>
+          <t>https://arxiv.org/abs/2401.03407</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr">
@@ -48109,22 +48115,22 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>DeFRCN</t>
+          <t>Meta-DETR</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Qiao et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>TPAMI</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -48138,12 +48144,12 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DeFRCN (arxiv 2108.09017): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Meta-DETR (arxiv 2208.00219): few-shot OD，報 MS-COCO K-shot novel AP（見 few-shot sheets），非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2108.09017</t>
+          <t>https://arxiv.org/abs/2208.00219</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
@@ -48160,22 +48166,22 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>FSCE</t>
+          <t>DeFRCN</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Qiao et al.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>CVPR</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -48189,12 +48195,12 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>⚠️ FSCE (arxiv 2103.05950): few-shot OD，報 10/30-shot novel AP，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ DeFRCN (arxiv 2108.09017): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2103.05950</t>
+          <t>https://arxiv.org/abs/2108.09017</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
@@ -48211,22 +48217,22 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>MPSR</t>
+          <t>FSCE</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Wu et al.</t>
+          <t>Sun et al.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>ECCV</t>
+          <t>CVPR</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -48240,12 +48246,12 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MPSR (arxiv 2007.09384): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ FSCE (arxiv 2103.05950): few-shot OD，報 10/30-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2007.09384</t>
+          <t>https://arxiv.org/abs/2103.05950</t>
         </is>
       </c>
       <c r="M60" s="6" t="inlineStr">
@@ -48262,22 +48268,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>TFA w/cos</t>
+          <t>MPSR</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Wu et al.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>ECCV</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -48291,12 +48297,12 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>⚠️ TFA w/cos (arxiv 2003.06957): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ MPSR (arxiv 2007.09384): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2003.06957</t>
+          <t>https://arxiv.org/abs/2007.09384</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr">
@@ -48313,22 +48319,22 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Meta R-CNN</t>
+          <t>TFA w/cos</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Yan et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>ICCV</t>
+          <t>ICML</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -48342,12 +48348,12 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Meta R-CNN (arxiv 1909.13032): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ TFA w/cos (arxiv 2003.06957): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1909.13032</t>
+          <t>https://arxiv.org/abs/2003.06957</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -48364,12 +48370,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>FSRW</t>
+          <t>Meta R-CNN</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Kang et al.</t>
+          <t>Yan et al.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -48393,12 +48399,12 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>⚠️ FSRW/Meta-YOLO (arxiv 1812.01866): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Meta R-CNN (arxiv 1909.13032): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1812.01866</t>
+          <t>https://arxiv.org/abs/1909.13032</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr">
@@ -48415,22 +48421,22 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
+          <t>FSRW</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
+          <t>Kang et al.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICCV</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -48444,12 +48450,12 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Exploring Hierarchical Consistency (arxiv 2604.23344): open-vocabulary OD，PDF 查證評估於 COCO+LVIS open-vocab (novel/base split)，box AP:0 — 非標準 supervised COCO val box AP</t>
+          <t>⚠️ FSRW/Meta-YOLO (arxiv 1812.01866): few-shot OD，報 K-shot novel AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.23344</t>
+          <t>https://arxiv.org/abs/1812.01866</t>
         </is>
       </c>
       <c r="M64" s="6" t="inlineStr">
@@ -48461,17 +48467,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>Exploring Hierarchical Consistency and Unbiased Objectness for Open-Vocabulary Object Dete</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>Sanghoon Lee, Geon Lee, Hyekang Park, Bumsub Ham</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -48495,12 +48501,12 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>⚠️ UHR-DETR (arxiv 2604.21435): PDF 查證 COCO 0 次提及 — 小物件偵測 (非標準 COCO val box AP)</t>
+          <t>⚠️ Exploring Hierarchical Consistency (arxiv 2604.23344): open-vocabulary OD，PDF 查證評估於 COCO+LVIS open-vocab (novel/base split)，box AP:0 — 非標準 supervised COCO val box AP</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://arxiv.org/abs/2604.23344</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr">
@@ -48517,22 +48523,22 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Believing is Seeing</t>
+          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -48546,12 +48552,12 @@
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Believing is Seeing (CVPR25): PDF 查證 COCO 僅 4 次、box AP:0 — 非標準 COCO 偵測 benchmark 條目（專門任務）</t>
+          <t>⚠️ UHR-DETR (arxiv 2604.21435): PDF 查證 COCO 0 次提及 — 小物件偵測 (非標準 COCO val box AP)</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
+          <t>https://arxiv.org/abs/2604.21435</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -48568,7 +48574,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>OW-OVD</t>
+          <t>Believing is Seeing</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -48597,12 +48603,12 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>⚠️ OW-OVD (CVPR25): open-world OD，PDF 查證報 U-Recall/Unknown (×17) 等 OWOD 指標，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Believing is Seeing (CVPR25): PDF 查證 COCO 僅 4 次、box AP:0 — 非標準 COCO 偵測 benchmark 條目（專門任務）</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -48619,7 +48625,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Shift the Lens</t>
+          <t>OW-OVD</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -48648,12 +48654,12 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Shift the Lens (CVPR25): PDF 查證 box AP:0、含 salient 內容 — 專門設定，非標準 COCO val box AP</t>
+          <t>⚠️ OW-OVD (CVPR25): open-world OD，PDF 查證報 U-Recall/Unknown (×17) 等 OWOD 指標，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -48665,12 +48671,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
+          <t>Shift the Lens</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -48699,12 +48705,12 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
+          <t>⚠️ Shift the Lens (CVPR25): PDF 查證 box AP:0、含 salient 內容 — 專門設定，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -48716,12 +48722,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Language-Guided Salient Object Ranking</t>
+          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -48750,12 +48756,12 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
+          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -48772,7 +48778,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>Language-Guided Salient Object Ranking</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -48801,12 +48807,12 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Test-Time Backdoor Detection for Object : 對抗/安全研究，回報攻擊成功率非偵測 AP</t>
+          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -48823,7 +48829,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -48852,12 +48858,12 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
+          <t>⚠️ Test-Time Backdoor Detection (CVPR25): 安全研究 (backdoor ×71)，回報攻擊偵測指標非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -48874,7 +48880,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>ROD-MLLM</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -48903,12 +48909,12 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ROD-MLLM: MLLM grounding，回報非標準 COCO box AP</t>
+          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr">
@@ -48925,7 +48931,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>ROD-MLLM</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -48954,12 +48960,12 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SET (CVPR25 CVF PDF): 微小物件偵測，評估於 AI-TOD benchmark — 非標準 COCO val AP</t>
+          <t>⚠️ ROD-MLLM (CVPR25): referring/grounding OD (referring ×46)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -48976,7 +48982,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>ReDiffDet</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -49005,12 +49011,12 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ReDiffDet: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ SET (CVPR25 CVF PDF): 微小物件偵測，評估於 AI-TOD benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -49027,7 +49033,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Towards RAW Object Detection in Diverse Conditions</t>
+          <t>ReDiffDet</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -49056,12 +49062,12 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Towards RAW Object Detection in Diverse : 領域專門 (RAW/熱影像/domain-shift)，非標準 COCO val AP</t>
+          <t>⚠️ ReDiffDet (CVPR25, visual read): 旋轉/有向物件偵測，評估於 DIOR-R (航拍/遙測)，報 AP50/AP75 on DIOR-R，非標準 COCO 2017 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -49078,7 +49084,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
+          <t>Towards RAW Object Detection in Diverse Conditions</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -49107,12 +49113,12 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Pseudo Visible Feature Fine-Grained Fusi: 領域專門 (RAW/熱影像/domain-shift)，非標準 COCO val AP</t>
+          <t>⚠️ Towards RAW Object Detection (CVPR25): RAW 影像域 (RAW ×138)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -49129,7 +49135,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>DEIM</t>
+          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -49158,12 +49164,12 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>⚠️ 重複條目：DEIM headline number 在 COCO test-dev 或 COCO 2017 val 已驗證</t>
+          <t>⚠️ Pseudo Visible Feature Fusion (CVPR25): 熱影像/紅外 (thermal ×75)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Huang_DEIM_DETR_with_Improved_Matching_for_Fast_Convergence_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M78" s="6" t="inlineStr">
@@ -49209,7 +49215,7 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Revisiting Generative Replay for Class I: 類別增量 OD (continual)，非標準 COCO val AP</t>
+          <t>⚠️ Revisiting Generative Replay (CVPR25): 類別增量 OD (incremental ×33)，報遺忘/可塑性指標非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -49260,7 +49266,7 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Fractal Calibration for Long-tailed Obje: 長尾 OD (LVIS)，非 COCO val AP</t>
+          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
@@ -50419,10 +50425,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -49317,7 +49317,7 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Open-World Objectness Modeling Unifies N: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
+          <t>⚠️ Open-World Objectness Modeling (CVPR25): open-world OD，PDF 查證報 U-Recall(×11) 等 OWOD 指標，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -49368,7 +49368,7 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Cubify Anything: 3D/BEV 偵測，非 2D COCO box AP</t>
+          <t>⚠️ Cubify Anything (CVPR25): 3D 物件偵測 (3D ×126)，非 2D COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -49419,7 +49419,7 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
+          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -49521,7 +49521,7 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Learning Endogenous Attention for Increm: 類別增量 OD (continual)，非標準 COCO val AP</t>
+          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -49572,7 +49572,7 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DiL: 類別增量 OD (continual)，非標準 COCO val AP</t>
+          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
@@ -49623,7 +49623,7 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks in Obje: 對抗/安全研究，回報攻擊成功率非偵測 AP</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
@@ -49674,7 +49674,7 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Novel Object Detection via Coo: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
@@ -49725,7 +49725,7 @@
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ALPI: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ ALPI (WACV25): 3D 弱監督偵測 (3D ×154, point annotation ×27)，非 2D COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -49776,7 +49776,7 @@
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>⚠️ AIC3DOD: 3D/BEV 偵測，非 2D COCO box AP</t>
+          <t>⚠️ AIC3DOD (WACV25): 3D 物件偵測 (3D ×75)，非 2D COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
@@ -49827,7 +49827,7 @@
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MaskVD: 影片偵測，非影像 COCO val AP</t>
+          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
@@ -49878,7 +49878,7 @@
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Diffusion-Based Particle-DETR for BEV Pe: 3D/BEV 偵測，非 2D COCO box AP</t>
+          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr">
@@ -49929,7 +49929,7 @@
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>⚠️ PK-YOLO: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
@@ -49980,7 +49980,7 @@
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Decoupled PROB: 開放世界 OD (OWOD 指標 U-Recall/WI)，非標準 COCO val AP</t>
+          <t>⚠️ Decoupled PROB (WACV25): open-world OD (PROB 變體，open-world ×18)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr">
@@ -50031,7 +50031,7 @@
       <c r="J95" s="3" t="n"/>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Mixed Patch Visible-Infrared Modality Ag: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
@@ -50082,7 +50082,7 @@
       <c r="J96" s="3" t="n"/>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Generalist YOLO: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
@@ -50133,7 +50133,7 @@
       <c r="J97" s="3" t="n"/>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Embodied Object Detection with: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ Enhancing Embodied Object Detection (WACV25): 具身偵測 (embodied ×36, 3D ×31)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -50184,7 +50184,7 @@
       <c r="J98" s="3" t="n"/>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Interactive Object Detection for Tiny Ob: 小/微物件偵測 benchmark，非標準 COCO val AP</t>
+          <t>⚠️ Interactive OD for Tiny Objects (WACV25): 微小物件互動偵測 (tiny ×22)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
@@ -50235,7 +50235,7 @@
       <c r="J99" s="3" t="n"/>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot Object: 領域專門 (RAW/熱影像/domain-shift)，非標準 COCO val AP</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
@@ -50286,7 +50286,7 @@
       <c r="J100" s="3" t="n"/>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>⚠️ No Annotations for Object Detection in A: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -50337,7 +50337,7 @@
       <c r="J101" s="3" t="n"/>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ECF-YOLOv7-Tiny: 小/微物件偵測 benchmark，非標準 COCO val AP</t>
+          <t>⚠️ ECF-YOLOv7-Tiny (WACV25): 微小物件輕量偵測 (tiny ×67)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -50388,7 +50388,7 @@
       <c r="J102" s="3" t="n"/>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Shape-Biased Texture Agnostic Representa: specialized/個別 paper — 經分類非標準 COCO val box AP，或需單獨 PDF 確認；無標準可比指標</t>
+          <t>⚠️ Shape-Biased Texture-Agnostic (WACV25): 形狀偏好/紋理無關 domain-gen (texture ×109)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -51431,7 +51431,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DINO (Swin-L) mAP@0.5=91.4：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
+          <t>⚠️ DINO 原論文僅 COCO，未測 VOC 2007；91.4 為社群 re-eval 無權威來源</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -51496,7 +51496,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>⚠️ YOLOv7 mAP@0.5=89.7：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
+          <t>⚠️ YOLOv7 原論文僅 COCO；VOC 89.7 為社群 re-eval 無權威來源</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -51561,7 +51561,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>⚠️ YOLOv4 mAP@0.5=89.4：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
+          <t>⚠️ YOLOv4 (PDF 查證 VOC 0 提及)；89.4 為社群 re-eval 無權威來源</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -51626,7 +51626,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Cascade R-CNN mAP@0.5=87：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
+          <t>⚠️ Cascade R-CNN 原論文僅 COCO；VOC 87.0 為社群 re-eval</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -51691,7 +51691,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>⚠️ DETR mAP@0.5=85.4：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
+          <t>⚠️ DETR 原論文僅 COCO val；VOC 85.4 為社群 re-eval</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -51756,7 +51756,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Sparse R-CNN mAP@0.5=85：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
+          <t>⚠️ Sparse R-CNN 原論文僅 COCO；VOC 85.0 為社群 re-eval</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -51878,7 +51878,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>⚠️ RetinaNet (R101) mAP@0.5=82.7：原論文僅報 COCO，未測 PASCAL VOC 2007（已查證）；此值為社群 re-eval（如 mmdetection VOC config）無權威單一來源，無法對原論文核實。保留供參考但標未驗證</t>
+          <t>⚠️ RetinaNet 原論文僅 COCO；VOC 82.7 為社群 re-eval</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -52063,7 +52063,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>⚠️ YOLOv8x (Ultralytics 2023) has no peer-reviewed paper; community evaluations report VOC 2007 mAP ~95+ depending on config. Specific mAP@0.5 not from a paper-reported table — needs official Ultralytics VOC benchmark report to confirm exact value.</t>
+          <t>⚠️ YOLOv8x 無同儕審查論文；VOC mAP 無官方/論文來源</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -52126,7 +52126,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>⚠️ YOLO-NAS (Deci AI 2023) has no peer-reviewed paper; official Deci benchmarks focus on COCO. PASCAL VOC 2007 mAP not in official Deci release documentation. Needs official YOLO-NAS VOC benchmark report.</t>
+          <t>⚠️ YOLO-NAS (Deci) 無同儕審查論文；官方僅 COCO，VOC 無來源</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -52189,7 +52189,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Grounding DINO zero-shot transfer on VOC 2007: model is open-vocabulary, not trained on VOC. Zero-shot transfer AP not found in Grounding DINO paper (Liu et al. ECCV 2024, arxiv 2303.05499). Needs manual PDF or supplementary check.</t>
+          <t>⚠️ Grounding DINO 零樣本 VOC transfer，非標準訓練於 VOC；論文未報 VOC 2007 zero-shot mAP</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -52240,7 +52240,7 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>⚠️ RF-DETR (ICLR 2026) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RF-DETR focuses on COCO and Roboflow100-VL benchmarks for real-time detection. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ RF-DETR (PDF 查證) 僅報 COCO+Roboflow100-VL，未測 PASCAL VOC 2007 標準 mAP</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -52291,7 +52291,7 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>⚠️ RF-DETR Nano (ICLR 2026) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RF-DETR focuses on COCO and Roboflow100-VL benchmarks for real-time detection. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ RF-DETR Nano (PDF 查證) 僅 COCO，未測 VOC 2007</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -52342,7 +52342,7 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>⚠️ YOLOv13-X (arxiv 2506.17733) performs cross-domain evaluation: models trained on COCO are tested on PASCAL VOC 2007 as a generalization benchmark, not as a standard closed-set training+test protocol. Cross-domain transfer AP is not directly comparable to methods trained on VOC 2007 trainval. The specific cross-domain transfer AP number needs verification from the full PDF.</t>
+          <t>⚠️ YOLOv13-X：COCO 訓練後跨域測 VOC，非標準 VOC 訓練+測試協議，數值待 PDF 表確認</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -52393,7 +52393,7 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Grounding DINO (Liu et al. ECCV 2024, arxiv 2303.05499) is an open-vocabulary detector evaluated on COCO val2017, LVIS v1.0, and ODinW-13 benchmarks. It does NOT report standard PASCAL VOC 2007 closed-set 20-class mAP@0.5 (open-vocabulary protocol is not comparable to closed-set VOC evaluation). The "zero-shot VOC" row r12 captures its transfer performance separately.</t>
+          <t>⚠️ Grounding DINO 為開放詞彙偵測器 (COCO/LVIS/ODinW)，未報標準 closed-set VOC 2007 mAP</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -52444,7 +52444,7 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Relation-DETR (ECCV 2024) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Evaluated on COCO val2017 and test-dev; FocalNet-L backbone. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ Relation-DETR 僅 COCO，未測 VOC 2007</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -52495,7 +52495,7 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Grounding DINO 1.5 Pro (arxiv 2405.10300) is an open-vocabulary detector evaluated on COCO, LVIS, ODinW; does NOT report standard PASCAL VOC 2007 closed-set mAP@0.5. Open-vocabulary results are not comparable to closed-set VOC ranking.</t>
+          <t>⚠️ Grounding DINO 1.5 Pro 開放詞彙 (COCO/LVIS/ODinW)，未報標準 VOC 2007 mAP</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -52546,7 +52546,7 @@
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>⚠️ RTMDet-X (arXiv 2022) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. RTMDet-X evaluated on COCO val2017 (52.8 AP) and CrowdHuman; no PASCAL VOC 2007 evaluation in paper. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ RTMDet-X 僅 COCO，未測 VOC 2007</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -52750,7 +52750,7 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>⚠️ PoolNet+ (Liu et al. TPAMI 2022, arxiv 1904.09569) is a Salient Object Detection (SOD) method — NOT a standard object detection method. It evaluates on SOD benchmarks (DUTS-TE, DUT-OMRON, ECSSD, HKU-IS, PASCAL-S) using S-measure/MAE/F-measure. It does NOT evaluate on PASCAL VOC 2007 20-class mAP. This entry is misplaced; should only appear in SOD sheets.</t>
+          <t>⚠️ PoolNet+ 為顯著物件偵測 (SOD，S-measure/MAE)，非 VOC 物件偵測 mAP — 誤放</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -52903,7 +52903,7 @@
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>⚠️ EfficientDet-D7 (CVPR 2020) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Tan et al. CVPR 2020: evaluated on COCO test-dev only (52.2 AP). No PASCAL VOC 2007 evaluation in the EfficientDet paper. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ EfficientDet-D7 僅 COCO test-dev，未測 VOC 2007</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
@@ -53056,7 +53056,7 @@
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>⚠️ CenterNet (Objects as Points) (arXiv 2019) evaluates on MS COCO (and KITTI/LVIS/ODinW where applicable); does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5 in its paper. Zhou et al. arXiv 1904.07850: evaluated on MS COCO val2017 and KITTI (3D OD) and COCO keypoints. No standard PASCAL VOC 2007 AP evaluation in paper. This entry is misplaced or pending migration to a COCO sheet.</t>
+          <t>⚠️ CenterNet (Objects as Points) 報 COCO/KITTI/keypoints；VOC 值需 PDF 確認（原論文 VOC 結果表）</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
@@ -53158,7 +53158,7 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SEEN-DA (Li et al. CVPR 2025) is a Domain Adaptive OD paper. Evaluation uses cross-domain transfer protocols (e.g. Cityscapes→KITTI, VOC→Clipart, VOC→Watercolor) — reporting domain-adaptation mAP, NOT standard closed-set PASCAL VOC 2007 test-set mAP@0.5. This entry is misplaced in the standard VOC 2007 ranking.</t>
+          <t>⚠️ SEEN-DA (PDF: domain-adaptation ×14, weather/clipart): 領域適應 OD (VOC→Clipart/Watercolor/天候)，非標準 closed-set VOC mAP</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
@@ -53719,7 +53719,7 @@
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>⚠️ ERUP-YOLO (Ogino et al. WACV 2025) enhances YOLO robustness for adverse weather. Evaluated on COCO and adverse-weather augmented test sets (fog / rain / etc.). Results are robustness metrics under augmented conditions, NOT standard closed-set PASCAL VOC 2007 mAP@0.5 training-on-VOC protocol. Needs manual paper PDF check to confirm if standard VOC test AP is reported.</t>
+          <t>⚠️ ERUP-YOLO (PDF: weather ×59): 惡劣天候強健性 OD，非標準 VOC 2007 mAP</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -54136,7 +54136,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Deformable-DETR 在 CrowdHuman 上 fine-tune 之 reproduction 值（91.5），非原 DDETR 論文（原論文僅 COCO）；第三方複現無權威來源</t>
+          <t>⚠️ Deformable-DETR 於 CrowdHuman fine-tune 之 reproduction 值，非原論文，無權威來源</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -54589,7 +54589,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>⚠️ EOD (End-to-end Object Detection in Crowds, arXiv) — CrowdHuman metrics (MR^-2 / JI) not extractable without PDF access. Needs manual paper read. Multiple "EOD" papers exist; verify correct arXiv ID in sheet link before filling.</t>
+          <t>⚠️ EOD: sheet 內 arxiv ID 2309.00000 為無效佔位符，無法取得 PDF 驗證 — 需正確論文參照</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -54703,7 +54703,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DEIM paper Table 3 CrowdHuman 只測 D-FINE-L (57.5 AP w/ DEIM)，未直接報告 X variant；需第三方 reproduction 驗證</t>
+          <t>⚠️ DEIM-D-FINE-X 原論文僅 COCO，未測 CrowdHuman — 誤放</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -54754,7 +54754,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DEIM-D-FINE-L: 57.5 為 COCO val AP（D-FINE-L+DEIM），非 CrowdHuman AP；DEIM/D-FINE 原論文未測 CrowdHuman — 誤放</t>
+          <t>⚠️ DEIM-D-FINE-L 原論文僅 COCO，未測 CrowdHuman — 誤放</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -54805,7 +54805,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DINO-X: 開放詞彙偵測器 (COCO/LVIS-minival)，原論文未測 CrowdHuman — 誤放</t>
+          <t>⚠️ DINO-X 開放詞彙偵測器 (COCO/LVIS)，未測 CrowdHuman — 誤放</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -54907,7 +54907,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>⚠️ InternImage-H: 97.2 對 CrowdHuman 異常偏高（SOTA AP≈94）；InternImage Table 10 為 LVIS 非 CrowdHuman — 需查證</t>
+          <t>⚠️ InternImage-H 於 CrowdHuman 之 97.2 異常偏高且 InternImage 表為 LVIS；未測 CrowdHuman — 需查證/誤放</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
@@ -54958,7 +54958,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Sparse R-CNN (R101): Sparse R-CNN 之 CrowdHuman 結果已列 (AP 91.3)；此 R101 變體無 CrowdHuman 報值 — 重複/無來源</t>
+          <t>⚠️ Sparse R-CNN CrowdHuman 已列 (91.3)；R101 變體無 CrowdHuman 報值 — 重複/無來源</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -43,6 +43,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LVIS v1.0 test-dev" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODinW-13" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODinW-35" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open-World OD" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OD all papers'!$A$1:$H$84</definedName>
@@ -21953,7 +21954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="2"/>
@@ -22795,6 +22796,22 @@
       <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Object Detection in the Wild — 35 dataset suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Open-World OD</t>
+        </is>
+      </c>
+      <c r="B37">
+        <f>HYPERLINK("#'Open-World OD'!A1","Open-World OD")</f>
+        <v/>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>U-Recall (unknown) / mAP (known) — M-OWODB</t>
         </is>
       </c>
     </row>
@@ -37248,7 +37265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -38540,7 +38557,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Open-World Objectness Modeling Unifies Novel Object Detectio</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -38569,12 +38586,12 @@
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Open-World Objectness Modeling (Zhang et al. CVPR 2025) uses OWOD benchmark (M-OWODB / S-OWODB). Reports open-world metrics (U-Recall, WI, AOSE), NOT standard LVIS v1.0 val detection AP. This entry is misplaced in the standard LVIS ranking.</t>
+          <t>⚠️ SimLTD (Tran et al. CVPR 2025, arxiv 2412.20047) evaluates on LVIS v1 benchmark (supervised + semi-supervised long-tail detection). Reports new SOTA on LVIS v1 (+10.6 AP_r over previous SOTA). Specific overall LVIS v1 val AP not in abstract — needs full PDF for exact number.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Open-World_Objectness_Modeling_Unifies_Novel_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
@@ -38591,7 +38608,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -38601,12 +38618,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -38620,12 +38637,12 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (Tran et al. CVPR 2025, arxiv 2412.20047) evaluates on LVIS v1 benchmark (supervised + semi-supervised long-tail detection). Reports new SOTA on LVIS v1 (+10.6 AP_r over previous SOTA). Specific overall LVIS v1 val AP not in abstract — needs full PDF for exact number.</t>
+          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (Bharadwaj et al. WACV 2025) focuses on novel object detection using foundational model cooperation. Evaluation protocol may use LVIS or COCO novel class splits rather than standard LVIS v1.0 val full-set AP. Needs manual paper PDF check to confirm dataset split and AP value.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
@@ -38642,7 +38659,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
+          <t>Enhancing Embodied Object Detection with Spatial Feature Mem</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -38671,66 +38688,15 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (Bharadwaj et al. WACV 2025) focuses on novel object detection using foundational model cooperation. Evaluation protocol may use LVIS or COCO novel class splits rather than standard LVIS v1.0 val full-set AP. Needs manual paper PDF check to confirm dataset split and AP value.</t>
+          <t>⚠️ Enhancing Embodied OD with Spatial Feature Memory (Chapman et al. WACV 2025) is an embodied/egocentric OD paper. Evaluates on embodied/robot-facing datasets (e.g. AI2-THOR, RoboTHOR, Ego4D). Does NOT evaluate on standard LVIS v1.0 val benchmark. This entry is misplaced in the LVIS v1.0 val sheet.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chapman_Enhancing_Embodied_Object_Detection_with_Spatial_Feature_Memory_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Enhancing Embodied Object Detection with Spatial Feature Mem</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ Enhancing Embodied OD with Spatial Feature Memory (Chapman et al. WACV 2025) is an embodied/egocentric OD paper. Evaluates on embodied/robot-facing datasets (e.g. AI2-THOR, RoboTHOR, Ego4D). Does NOT evaluate on standard LVIS v1.0 val benchmark. This entry is misplaced in the LVIS v1.0 val sheet.</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chapman_Enhancing_Embodied_Object_Detection_with_Spatial_Feature_Memory_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -41395,6 +41361,222 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>作者</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>發表</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mAP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>FPS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>備註(特色/based)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>連結</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Open-World OD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OW-OVD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>U-Recall=50.0 | mAP=69.4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ verified (OW-OVD CVPR25 Table 1 (M-OWODB Task1)): M-OWODB Task1 U-Recall=50.0 / known-mAP=69.4。指標=U-Recall(未知類召回)+mAP(已知類)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Open-World OD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OWOBJ (MEPU-FS+OWOBJ)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>U-Recall=39.7 | mAP=77.4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ verified (Open-World Objectness CVPR25 Table 1 (M-OWODB Task1, MEPU-FS+OWOBJ best)): M-OWODB Task1 U-Recall=39.7 / known-mAP=77.4。指標=U-Recall(未知類召回)+mAP(已知類)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2503.20061</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Open-World OD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Decoupled PROB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>U-Recall=20.3 | mAP=59.8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>✅ verified (Decoupled PROB WACV25 Table 4 (M-OWODB Task1)): M-OWODB Task1 U-Recall=20.3 / known-mAP=59.8。指標=U-Recall(未知類召回)+mAP(已知類)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Inoue_Decoupled_PROB_Decoupled_Query_Initialization_Tasks_and_Objectness-Class_Learning_for_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -44753,7 +44935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -48625,7 +48807,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>OW-OVD</t>
+          <t>Shift the Lens</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -48654,12 +48836,12 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ OW-OVD (CVPR25): open-world OD，PDF 查證報 U-Recall/Unknown (×17) 等 OWOD 指標，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Shift the Lens (CVPR25): PDF 查證 box AP:0、含 salient 內容 — 專門設定，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -48671,12 +48853,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Shift the Lens</t>
+          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -48705,12 +48887,12 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Shift the Lens (CVPR25): PDF 查證 box AP:0、含 salient 內容 — 專門設定，非標準 COCO val box AP</t>
+          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -48722,12 +48904,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
+          <t>Language-Guided Salient Object Ranking</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -48756,12 +48938,12 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
+          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -48778,7 +48960,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Language-Guided Salient Object Ranking</t>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -48807,12 +48989,12 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
+          <t>⚠️ Test-Time Backdoor Detection (CVPR25): 安全研究 (backdoor ×71)，回報攻擊偵測指標非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -48829,7 +49011,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -48858,12 +49040,12 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Test-Time Backdoor Detection (CVPR25): 安全研究 (backdoor ×71)，回報攻擊偵測指標非標準 COCO val box AP</t>
+          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -48880,7 +49062,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>ROD-MLLM</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -48909,12 +49091,12 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
+          <t>⚠️ ROD-MLLM (CVPR25): referring/grounding OD (referring ×46)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr">
@@ -48931,7 +49113,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>ROD-MLLM</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -48960,12 +49142,12 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ROD-MLLM (CVPR25): referring/grounding OD (referring ×46)，非標準 COCO val box AP</t>
+          <t>⚠️ SET (CVPR25 CVF PDF): 微小物件偵測，評估於 AI-TOD benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -48982,7 +49164,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>ReDiffDet</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -49011,12 +49193,12 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SET (CVPR25 CVF PDF): 微小物件偵測，評估於 AI-TOD benchmark — 非標準 COCO val AP</t>
+          <t>⚠️ ReDiffDet (CVPR25, visual read): 旋轉/有向物件偵測，評估於 DIOR-R (航拍/遙測)，報 AP50/AP75 on DIOR-R，非標準 COCO 2017 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -49033,7 +49215,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>ReDiffDet</t>
+          <t>Towards RAW Object Detection in Diverse Conditions</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -49062,12 +49244,12 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ReDiffDet (CVPR25, visual read): 旋轉/有向物件偵測，評估於 DIOR-R (航拍/遙測)，報 AP50/AP75 on DIOR-R，非標準 COCO 2017 2D box AP — 誤放</t>
+          <t>⚠️ Towards RAW Object Detection (CVPR25): RAW 影像域 (RAW ×138)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -49084,7 +49266,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Towards RAW Object Detection in Diverse Conditions</t>
+          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -49113,12 +49295,12 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Towards RAW Object Detection (CVPR25): RAW 影像域 (RAW ×138)，非標準 RGB COCO val box AP</t>
+          <t>⚠️ Pseudo Visible Feature Fusion (CVPR25): 熱影像/紅外 (thermal ×75)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -49135,7 +49317,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
+          <t>Revisiting Generative Replay for Class Incremental Object De</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -49164,12 +49346,12 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Pseudo Visible Feature Fusion (CVPR25): 熱影像/紅外 (thermal ×75)，非標準 COCO val box AP</t>
+          <t>⚠️ Revisiting Generative Replay (CVPR25): 類別增量 OD (incremental ×33)，報遺忘/可塑性指標非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M78" s="6" t="inlineStr">
@@ -49186,7 +49368,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>Fractal Calibration for Long-tailed Object Detection</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -49215,12 +49397,12 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Revisiting Generative Replay (CVPR25): 類別增量 OD (incremental ×33)，報遺忘/可塑性指標非標準 COCO val box AP</t>
+          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr">
@@ -49237,7 +49419,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Fractal Calibration for Long-tailed Object Detection</t>
+          <t>Cubify Anything</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -49266,12 +49448,12 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
+          <t>⚠️ Cubify Anything (CVPR25): 3D 物件偵測 (3D ×126)，非 2D COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Lazarow_Cubify_Anything_Scaling_Indoor_3D_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M80" s="6" t="inlineStr">
@@ -49288,7 +49470,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Open-World Objectness Modeling Unifies Novel Object Detectio</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -49317,12 +49499,12 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Open-World Objectness Modeling (CVPR25): open-world OD，PDF 查證報 U-Recall(×11) 等 OWOD 指標，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Open-World_Objectness_Modeling_Unifies_Novel_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr">
@@ -49339,7 +49521,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Cubify Anything</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -49368,12 +49550,12 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Cubify Anything (CVPR25): 3D 物件偵測 (3D ×126)，非 2D COCO val box AP — 誤放</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Lazarow_Cubify_Anything_Scaling_Indoor_3D_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M82" s="6" t="inlineStr">
@@ -49390,7 +49572,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -49419,12 +49601,12 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr">
@@ -49441,7 +49623,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>DiL</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -49451,12 +49633,12 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -49470,12 +49652,12 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
+          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M84" s="6" t="inlineStr">
@@ -49492,7 +49674,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -49502,12 +49684,12 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -49521,12 +49703,12 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr">
@@ -49543,7 +49725,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>DiL</t>
+          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -49572,12 +49754,12 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M86" s="6" t="inlineStr">
@@ -49594,7 +49776,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
+          <t>ALPI</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -49623,12 +49805,12 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
+          <t>⚠️ ALPI (WACV25): 3D 弱監督偵測 (3D ×154, point annotation ×27)，非 2D COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lahlali_ALPI_Auto-Labeller_with_Proxy_Injection_for_3D_Object_Detection_using_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr">
@@ -49645,7 +49827,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
+          <t>AIC3DOD</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -49674,12 +49856,12 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
+          <t>⚠️ AIC3DOD (WACV25): 3D 物件偵測 (3D ×75)，非 2D COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Cheng_AIC3DOD_Advancing_Indoor_Class-Incremental_3D_Object_Detection_with_Point_Transformer_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M88" s="6" t="inlineStr">
@@ -49696,7 +49878,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>ALPI</t>
+          <t>MaskVD</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -49725,12 +49907,12 @@
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ALPI (WACV25): 3D 弱監督偵測 (3D ×154, point annotation ×27)，非 2D COCO val box AP — 誤放</t>
+          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lahlali_ALPI_Auto-Labeller_with_Proxy_Injection_for_3D_Object_Detection_using_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr">
@@ -49747,7 +49929,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>AIC3DOD</t>
+          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -49776,12 +49958,12 @@
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>⚠️ AIC3DOD (WACV25): 3D 物件偵測 (3D ×75)，非 2D COCO val box AP — 誤放</t>
+          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Cheng_AIC3DOD_Advancing_Indoor_Class-Incremental_3D_Object_Detection_with_Point_Transformer_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M90" s="6" t="inlineStr">
@@ -49793,12 +49975,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>MaskVD</t>
+          <t>PK-YOLO</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -49827,12 +50009,12 @@
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
+          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr">
@@ -49849,7 +50031,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
+          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -49878,12 +50060,12 @@
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
+          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M92" s="6" t="inlineStr">
@@ -49900,7 +50082,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>PK-YOLO</t>
+          <t>Generalist YOLO</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -49929,12 +50111,12 @@
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr">
@@ -49951,7 +50133,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Decoupled PROB</t>
+          <t>Enhancing Embodied Object Detection with Spatial Feature Mem</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -49980,12 +50162,12 @@
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Decoupled PROB (WACV25): open-world OD (PROB 變體，open-world ×18)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Enhancing Embodied Object Detection (WACV25): 具身偵測 (embodied ×36, 3D ×31)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Inoue_Decoupled_PROB_Decoupled_Query_Initialization_Tasks_and_Objectness-Class_Learning_for_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chapman_Enhancing_Embodied_Object_Detection_with_Spatial_Feature_Memory_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M94" s="6" t="inlineStr">
@@ -50002,7 +50184,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
+          <t>Interactive Object Detection for Tiny Objects in Large Remot</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -50031,12 +50213,12 @@
       <c r="J95" s="3" t="n"/>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
+          <t>⚠️ Interactive OD for Tiny Objects (WACV25): 微小物件互動偵測 (tiny ×22)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Burges_Interactive_Object_Detection_for_Tiny_Objects_in_Large_Remotely_Sensed_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr">
@@ -50048,12 +50230,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Generalist YOLO</t>
+          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -50082,12 +50264,12 @@
       <c r="J96" s="3" t="n"/>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M96" s="6" t="inlineStr">
@@ -50104,7 +50286,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Embodied Object Detection with Spatial Feature Mem</t>
+          <t>No Annotations for Object Detection in Art through Stable Di</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -50133,12 +50315,12 @@
       <c r="J97" s="3" t="n"/>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Embodied Object Detection (WACV25): 具身偵測 (embodied ×36, 3D ×31)，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chapman_Enhancing_Embodied_Object_Detection_with_Spatial_Feature_Memory_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr">
@@ -50150,12 +50332,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Interactive Object Detection for Tiny Objects in Large Remot</t>
+          <t>ECF-YOLOv7-Tiny</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -50184,12 +50366,12 @@
       <c r="J98" s="3" t="n"/>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Interactive OD for Tiny Objects (WACV25): 微小物件互動偵測 (tiny ×22)，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ ECF-YOLOv7-Tiny (WACV25): 微小物件輕量偵測 (tiny ×67)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Burges_Interactive_Object_Detection_for_Tiny_Objects_in_Large_Remotely_Sensed_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bacea_ECF-YOLOv7-Tiny_Improving_Feature_Fusion_and_the_Receptive_Field_for_Lightweight_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M98" s="6" t="inlineStr">
@@ -50201,12 +50383,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Few-Shot OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
+          <t>Shape-Biased Texture Agnostic Representations for Improved T</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -50235,168 +50417,15 @@
       <c r="J99" s="3" t="n"/>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Shape-Biased Texture-Agnostic (WACV25): 形狀偏好/紋理無關 domain-gen (texture ×109)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>No Annotations for Object Detection in Art through Stable Di</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="n"/>
-      <c r="H100" s="3" t="n"/>
-      <c r="I100" s="3" t="n"/>
-      <c r="J100" s="3" t="n"/>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L100" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M100" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>ECF-YOLOv7-Tiny</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="n"/>
-      <c r="H101" s="3" t="n"/>
-      <c r="I101" s="3" t="n"/>
-      <c r="J101" s="3" t="n"/>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ ECF-YOLOv7-Tiny (WACV25): 微小物件輕量偵測 (tiny ×67)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L101" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bacea_ECF-YOLOv7-Tiny_Improving_Feature_Fusion_and_the_Receptive_Field_for_Lightweight_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M101" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Shape-Biased Texture Agnostic Representations for Improved T</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="n"/>
-      <c r="H102" s="3" t="n"/>
-      <c r="I102" s="3" t="n"/>
-      <c r="J102" s="3" t="n"/>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Shape-Biased Texture-Agnostic (WACV25): 形狀偏好/紋理無關 domain-gen (texture ×109)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L102" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M102" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -51239,7 +51268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -53078,7 +53107,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>OW-OVD</t>
+          <t>SEEN-DA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -53107,12 +53136,12 @@
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>⚠️ OW-OVD (Xi et al. CVPR 2025) is an Open-World + Open-Vocabulary OD paper. Evaluation is on M-OWODB and S-OWODB benchmarks (open-world metrics: U-Recall, U-mAP for unknown classes). Does NOT report standard PASCAL VOC 2007 closed-set 20-class mAP@0.5. VOC categories appear only as the "known class" base set in the OWOD benchmark split.</t>
+          <t>⚠️ SEEN-DA (PDF: domain-adaptation ×14, weather/clipart): 領域適應 OD (VOC→Clipart/Watercolor/天候)，非標準 closed-set VOC mAP</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Xi_OW-OVD_Unified_Open_World_and_Open_Vocabulary_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_SEEN-DA_SEmantic_ENtropy_guided_Domain-aware_Attention_for_Domain_Adaptive_Object_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
@@ -53129,7 +53158,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SEEN-DA</t>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -53158,12 +53187,12 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SEEN-DA (PDF: domain-adaptation ×14, weather/clipart): 領域適應 OD (VOC→Clipart/Watercolor/天候)，非標準 closed-set VOC mAP</t>
+          <t>⚠️ Test-Time Backdoor Detection for OD Models (Zhang et al. CVPR 2025) is a security paper about backdoor attack detection. VOC 2007 is used as an attack-evaluation target (not as a standard benchmark for detection mAP). Does NOT report standard 20-class mAP@0.5; reports attack-success rate / detection accuracy.</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_SEEN-DA_SEmantic_ENtropy_guided_Domain-aware_Attention_for_Domain_Adaptive_Object_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M34" s="9" t="inlineStr">
@@ -53180,7 +53209,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -53209,12 +53238,12 @@
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Test-Time Backdoor Detection for OD Models (Zhang et al. CVPR 2025) is a security paper about backdoor attack detection. VOC 2007 is used as an attack-evaluation target (not as a standard benchmark for detection mAP). Does NOT report standard 20-class mAP@0.5; reports attack-success rate / detection accuracy.</t>
+          <t>⚠️ SET — Spectral Enhancement for Tiny Object Detection (Sun et al. CVPR 2025) is a tiny OD paper. Evaluated on tiny-object benchmarks (e.g. VisDrone, AI-TOD, DOTA). Does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5.</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
@@ -53231,7 +53260,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>Style Evolving along Chain-of-Thought for Unknown-Domain Obj</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -53260,12 +53289,12 @@
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SET — Spectral Enhancement for Tiny Object Detection (Sun et al. CVPR 2025) is a tiny OD paper. Evaluated on tiny-object benchmarks (e.g. VisDrone, AI-TOD, DOTA). Does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5.</t>
+          <t>⚠️ Style Evolving along Chain-of-Thought for Unknown-Domain OD (Zhang et al. CVPR 2025) is a domain generalization / style adaptation paper. Evaluates on unknown-domain transfer benchmarks (not standard closed-set VOC 2007 mAP@0.5). VOC may appear as a source domain but results are domain-shift metrics.</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Style_Evolving_along_Chain-of-Thought_for_Unknown-Domain_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
@@ -53282,7 +53311,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Style Evolving along Chain-of-Thought for Unknown-Domain Obj</t>
+          <t>Towards RAW Object Detection in Diverse Conditions</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -53311,12 +53340,12 @@
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Style Evolving along Chain-of-Thought for Unknown-Domain OD (Zhang et al. CVPR 2025) is a domain generalization / style adaptation paper. Evaluates on unknown-domain transfer benchmarks (not standard closed-set VOC 2007 mAP@0.5). VOC may appear as a source domain but results are domain-shift metrics.</t>
+          <t>⚠️ Towards RAW Object Detection in Diverse Conditions (Li et al. CVPR 2025) evaluates on RAW-image domain-specific datasets (not standard RGB PASCAL VOC 2007). Does NOT report standard 20-class VOC mAP@0.5; focuses on RAW-domain detection metrics.</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Style_Evolving_along_Chain-of-Thought_for_Unknown-Domain_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
@@ -53333,7 +53362,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Towards RAW Object Detection in Diverse Conditions</t>
+          <t>Revisiting Generative Replay for Class Incremental Object De</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -53362,12 +53391,12 @@
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Towards RAW Object Detection in Diverse Conditions (Li et al. CVPR 2025) evaluates on RAW-image domain-specific datasets (not standard RGB PASCAL VOC 2007). Does NOT report standard 20-class VOC mAP@0.5; focuses on RAW-domain detection metrics.</t>
+          <t>⚠️ Revisiting Generative Replay for Class Incremental OD (Zhang et al. CVPR 2025) uses VOC 2007 in a class-incremental learning protocol (multi-task splits, e.g. first 10 classes then next 10). Reports "current task AP" / "all-task AP" under incremental constraints — NOT directly comparable to standard closed-set 20-class mAP@0.5.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
@@ -53384,7 +53413,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -53413,12 +53442,12 @@
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Revisiting Generative Replay for Class Incremental OD (Zhang et al. CVPR 2025) uses VOC 2007 in a class-incremental learning protocol (multi-task splits, e.g. first 10 classes then next 10). Reports "current task AP" / "all-task AP" under incremental constraints — NOT directly comparable to standard closed-set 20-class mAP@0.5.</t>
+          <t>⚠️ Percept, Memory, and Imagine — World Feature Simulating for Open-Domain Unknown (Wu et al. CVPR 2025) is an open-domain unknown OD paper. Evaluates in open-world / open-domain setting, not standard closed-set VOC 2007 mAP@0.5.</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M39" s="9" t="inlineStr">
@@ -53435,7 +53464,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Open-World Objectness Modeling Unifies Novel Object Detectio</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -53464,12 +53493,12 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Open-World Objectness Modeling (Zhang et al. CVPR 2025) uses OWOD benchmark (M-OWODB / S-OWODB, derived from VOC+COCO categories). Reports open-world metrics (U-Recall, WI, AOSE, mAP on known classes). NOT comparable to standard closed-set PASCAL VOC 2007 20-class mAP@0.5.</t>
+          <t>⚠️ SimLTD (Tran et al. CVPR 2025) is a long-tailed OD paper evaluated on the LVIS v1 benchmark (supervised + semi-supervised settings). Does NOT evaluate on PASCAL VOC 2007. This entry is misplaced; should be in the LVIS v1.0 val sheet (r23 there).</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Open-World_Objectness_Modeling_Unifies_Novel_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr">
@@ -53486,7 +53515,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -53515,12 +53544,12 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine — World Feature Simulating for Open-Domain Unknown (Wu et al. CVPR 2025) is an open-domain unknown OD paper. Evaluates in open-world / open-domain setting, not standard closed-set VOC 2007 mAP@0.5.</t>
+          <t>⚠️ Learning Endogenous Attention for Incremental OD (Song et al. CVPR 2025) uses VOC 2007 in a class-incremental / continual learning protocol (task splits). Reports forgetting / plasticity metrics — NOT standard closed-set 20-class mAP@0.5. Not directly comparable to standard VOC ranking.</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
@@ -53537,7 +53566,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -53547,12 +53576,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -53566,12 +53595,12 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (Tran et al. CVPR 2025) is a long-tailed OD paper evaluated on the LVIS v1 benchmark (supervised + semi-supervised settings). Does NOT evaluate on PASCAL VOC 2007. This entry is misplaced; should be in the LVIS v1.0 val sheet (r23 there).</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks in OD (Sistla et al. WACV 2025) is a security / adversarial paper. VOC and COCO appear as target datasets for bit-flip attack evaluation (attack success rate / latency degradation), NOT standard detection mAP. Does NOT report standard closed-set PASCAL VOC 2007 mAP@0.5.</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M42" s="9" t="inlineStr">
@@ -53583,12 +53612,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+          <t>ERUP-YOLO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -53598,12 +53627,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -53617,12 +53646,12 @@
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Learning Endogenous Attention for Incremental OD (Song et al. CVPR 2025) uses VOC 2007 in a class-incremental / continual learning protocol (task splits). Reports forgetting / plasticity metrics — NOT standard closed-set 20-class mAP@0.5. Not directly comparable to standard VOC ranking.</t>
+          <t>⚠️ ERUP-YOLO (PDF: weather ×59): 惡劣天候強健性 OD，非標準 VOC 2007 mAP</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ogino_ERUP-YOLO_Enhancing_Object_Detection_Robustness_for_Adverse_Weather_Condition_by_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M43" s="9" t="inlineStr">
@@ -53634,12 +53663,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
+          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -53668,168 +53697,15 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks in OD (Sistla et al. WACV 2025) is a security / adversarial paper. VOC and COCO appear as target datasets for bit-flip attack evaluation (attack success rate / latency degradation), NOT standard detection mAP. Does NOT report standard closed-set PASCAL VOC 2007 mAP@0.5.</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD via Rich Text (Shangguan et al. WACV 2025) is a cross-domain few-shot OD paper. Uses VOC and COCO in few-shot cross-domain protocol (K-shot novel class AP). NOT standard closed-set PASCAL VOC 2007 20-class mAP@0.5. This entry is misplaced; should be in few-shot OD sheets.</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M44" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>ERUP-YOLO</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ ERUP-YOLO (PDF: weather ×59): 惡劣天候強健性 OD，非標準 VOC 2007 mAP</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ogino_ERUP-YOLO_Enhancing_Object_Detection_Robustness_for_Adverse_Weather_Condition_by_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Decoupled PROB</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ Decoupled PROB (Inoue et al. WACV 2025) is an open-world OD paper (variant of PROB — Probabilistic OWL OD). Evaluated on OW-DETR / M-OWODB benchmark (open-world metrics: U-Recall, WI, AOSE). VOC categories appear as "known" classes in the OWOD split — NOT standard closed-set 20-class mAP@0.5.</t>
-        </is>
-      </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Inoue_Decoupled_PROB_Decoupled_Query_Initialization_Tasks_and_Objectness-Class_Learning_for_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Few-Shot OD</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD via Rich Text (Shangguan et al. WACV 2025) is a cross-domain few-shot OD paper. Uses VOC and COCO in few-shot cross-domain protocol (K-shot novel class AP). NOT standard closed-set PASCAL VOC 2007 20-class mAP@0.5. This entry is misplaced; should be in few-shot OD sheets.</t>
-        </is>
-      </c>
-      <c r="L47" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -44,6 +44,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODinW-13" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODinW-35" sheetId="37" state="visible" r:id="rId37"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open-World OD" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-BEV OD" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OD all papers'!$A$1:$H$84</definedName>
@@ -21954,7 +21955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="2"/>
@@ -22812,6 +22813,22 @@
       <c r="C37" t="inlineStr">
         <is>
           <t>U-Recall (unknown) / mAP (known) — M-OWODB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3D-BEV OD</t>
+        </is>
+      </c>
+      <c r="B38">
+        <f>HYPERLINK("#'3D-BEV OD'!A1","3D-BEV OD")</f>
+        <v/>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3D AP (dataset-specific: CA-1M/KITTI/ScanNet)</t>
         </is>
       </c>
     </row>
@@ -41577,6 +41594,219 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>作者</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>發表</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mAP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>FPS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>備註(特色/based)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>連結</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3D-BEV OD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cubify Anything (CuTR)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CA-1M AP25=40.9 | CA-1M AP50=12.7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ verified (Cubify Anything CVPR25 Table 2, visual read): CuTR RGB-D on CA-1M (室內 3D) AP25=40.9 / AP50=12.7</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Lazarow_Cubify_Anything_Scaling_Indoor_3D_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3D-BEV OD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ALPI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>KITTI 3D AP (weakly-supervised)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>⚠️ ALPI (WACV25): KITTI 弱監督 3D 偵測 (AP3D)；論文 Ours 行數值需視覺讀表精確對位 — needs visual read</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lahlali_ALPI_Auto-Labeller_with_Proxy_Injection_for_3D_Object_Detection_using_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3D-BEV OD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AIC3DOD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ScanNet 3D mAP</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>⚠️ AIC3DOD (WACV25): ScanNet 室內 3D 偵測 (mAP@0.25/0.5)；數值 needs visual read</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Cheng_AIC3DOD_Advancing_Indoor_Class-Incremental_3D_Object_Detection_with_Point_Transformer_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3D-BEV OD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Enhancing Embodied Object Detection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ScanNet embodied 3D mAP</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>⚠️ Enhancing Embodied OD (WACV25): ScanNet 具身 3D 偵測；數值 needs visual read</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chapman_Enhancing_Embodied_Object_Detection_with_Spatial_Feature_Memory_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -44935,7 +45165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -49419,7 +49649,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Cubify Anything</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -49448,12 +49678,12 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Cubify Anything (CVPR25): 3D 物件偵測 (3D ×126)，非 2D COCO val box AP — 誤放</t>
+          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Lazarow_Cubify_Anything_Scaling_Indoor_3D_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M80" s="6" t="inlineStr">
@@ -49470,7 +49700,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -49499,12 +49729,12 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr">
@@ -49521,7 +49751,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -49550,12 +49780,12 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
+          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M82" s="6" t="inlineStr">
@@ -49572,7 +49802,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+          <t>DiL</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -49582,12 +49812,12 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -49601,12 +49831,12 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr">
@@ -49623,7 +49853,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>DiL</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -49652,12 +49882,12 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M84" s="6" t="inlineStr">
@@ -49674,7 +49904,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
+          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -49703,12 +49933,12 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
+          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr">
@@ -49725,7 +49955,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
+          <t>MaskVD</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -49754,12 +49984,12 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
+          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M86" s="6" t="inlineStr">
@@ -49776,7 +50006,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>ALPI</t>
+          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -49805,12 +50035,12 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ALPI (WACV25): 3D 弱監督偵測 (3D ×154, point annotation ×27)，非 2D COCO val box AP — 誤放</t>
+          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Lahlali_ALPI_Auto-Labeller_with_Proxy_Injection_for_3D_Object_Detection_using_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr">
@@ -49822,12 +50052,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>AIC3DOD</t>
+          <t>PK-YOLO</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -49856,12 +50086,12 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>⚠️ AIC3DOD (WACV25): 3D 物件偵測 (3D ×75)，非 2D COCO val box AP — 誤放</t>
+          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Cheng_AIC3DOD_Advancing_Indoor_Class-Incremental_3D_Object_Detection_with_Point_Transformer_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M88" s="6" t="inlineStr">
@@ -49878,7 +50108,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>MaskVD</t>
+          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -49907,12 +50137,12 @@
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
+          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr">
@@ -49924,12 +50154,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
+          <t>Generalist YOLO</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -49958,12 +50188,12 @@
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
+          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M90" s="6" t="inlineStr">
@@ -49975,12 +50205,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>PK-YOLO</t>
+          <t>Interactive Object Detection for Tiny Objects in Large Remot</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -50009,12 +50239,12 @@
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Interactive OD for Tiny Objects (WACV25): 微小物件互動偵測 (tiny ×22)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Burges_Interactive_Object_Detection_for_Tiny_Objects_in_Large_Remotely_Sensed_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr">
@@ -50026,12 +50256,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
+          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -50060,12 +50290,12 @@
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M92" s="6" t="inlineStr">
@@ -50077,12 +50307,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Generalist YOLO</t>
+          <t>No Annotations for Object Detection in Art through Stable Di</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -50111,12 +50341,12 @@
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
+          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr">
@@ -50128,12 +50358,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Embodied Object Detection with Spatial Feature Mem</t>
+          <t>ECF-YOLOv7-Tiny</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -50162,12 +50392,12 @@
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Embodied Object Detection (WACV25): 具身偵測 (embodied ×36, 3D ×31)，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ ECF-YOLOv7-Tiny (WACV25): 微小物件輕量偵測 (tiny ×67)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chapman_Enhancing_Embodied_Object_Detection_with_Spatial_Feature_Memory_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bacea_ECF-YOLOv7-Tiny_Improving_Feature_Fusion_and_the_Receptive_Field_for_Lightweight_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M94" s="6" t="inlineStr">
@@ -50184,7 +50414,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Interactive Object Detection for Tiny Objects in Large Remot</t>
+          <t>Shape-Biased Texture Agnostic Representations for Improved T</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -50213,219 +50443,15 @@
       <c r="J95" s="3" t="n"/>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Interactive OD for Tiny Objects (WACV25): 微小物件互動偵測 (tiny ×22)，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Shape-Biased Texture-Agnostic (WACV25): 形狀偏好/紋理無關 domain-gen (texture ×109)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Burges_Interactive_Object_Detection_for_Tiny_Objects_in_Large_Remotely_Sensed_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>Few-Shot OD</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="n"/>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="3" t="n"/>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L96" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M96" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>No Annotations for Object Detection in Art through Stable Di</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="n"/>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="n"/>
-      <c r="J97" s="3" t="n"/>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L97" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M97" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>ECF-YOLOv7-Tiny</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="n"/>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="n"/>
-      <c r="J98" s="3" t="n"/>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ ECF-YOLOv7-Tiny (WACV25): 微小物件輕量偵測 (tiny ×67)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L98" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bacea_ECF-YOLOv7-Tiny_Improving_Feature_Fusion_and_the_Receptive_Field_for_Lightweight_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M98" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>Shape-Biased Texture Agnostic Representations for Improved T</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="n"/>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="3" t="n"/>
-      <c r="J99" s="3" t="n"/>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Shape-Biased Texture-Agnostic (WACV25): 形狀偏好/紋理無關 domain-gen (texture ×109)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L99" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M99" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -45,6 +45,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODinW-35" sheetId="37" state="visible" r:id="rId37"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open-World OD" sheetId="38" state="visible" r:id="rId38"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-BEV OD" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny-Object OD" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OD all papers'!$A$1:$H$84</definedName>
@@ -21955,7 +21956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="2"/>
@@ -22829,6 +22830,22 @@
       <c r="C38" t="inlineStr">
         <is>
           <t>3D AP (dataset-specific: CA-1M/KITTI/ScanNet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tiny-Object OD</t>
+        </is>
+      </c>
+      <c r="B39">
+        <f>HYPERLINK("#'Tiny-Object OD'!A1","Tiny-Object OD")</f>
+        <v/>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AP (tiny: AI-TOD / DOTA / remote-sensing)</t>
         </is>
       </c>
     </row>
@@ -42642,13 +42659,229 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>作者</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>發表</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mAP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>FPS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>備註(特色/based)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>連結</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tiny-Object OD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ECF-YOLOv7-Tiny</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AP=38.2 | AP50=56.3 | AP75=40.7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>⚠️ ECF-YOLOv7-Tiny (WACV25): 輕量微小物件偵測，Ours 行 AP=38.2/AP50=56.3；確切資料集需 visual read 確認</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bacea_ECF-YOLOv7-Tiny_Improving_Feature_Fusion_and_the_Receptive_Field_for_Lightweight_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tiny-Object OD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SET (RFLA+SET)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AI-TOD AP=24.9 | AP50=55.6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ verified (SET CVPR25 Table, visual read): AI-TOD 微小物件 best RFLA+SET AP=24.9 / AP50=55.6</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tiny-Object OD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UHR-DETR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>remote-sensing UHR small-object AP</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>⚠️ UHR-DETR (arxiv 2604.21435): 超高解析遙測小物件偵測；數值 needs visual read</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.21435</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tiny-Object OD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Interactive OD for Tiny Objects</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DOTA small-object AP</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>⚠️ Interactive OD for Tiny Objects (WACV25): DOTA 遙測小物件互動偵測；數值 needs visual read</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Burges_Interactive_Object_Detection_for_Tiny_Objects_in_Large_Remotely_Sensed_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -44931,22 +45164,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -44960,12 +45193,12 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>⚠️ UHR-DETR (arxiv 2604.21435): PDF 查證 COCO 0 次提及 — 小物件偵測 (非標準 COCO val box AP)</t>
+          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -44982,7 +45215,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -45011,117 +45244,15 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ SET (CVPR25 CVF PDF): 微小物件偵測，評估於 AI-TOD benchmark — 非標準 COCO val AP</t>
-        </is>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>SimLTD</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
-        </is>
-      </c>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -45165,7 +45296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -48935,22 +49066,22 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>UHR-DETR: Efficient End-to-End Small Object Detection for Ultra-High-Resolution Remote Sen</t>
+          <t>Believing is Seeing</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Jingfang Li, Haoran Zhu, Wen Yang, Jinrui Zhang, Fang Xu, Haijian Zhang, Gui-Song Xia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -48964,12 +49095,12 @@
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>⚠️ UHR-DETR (arxiv 2604.21435): PDF 查證 COCO 0 次提及 — 小物件偵測 (非標準 COCO val box AP)</t>
+          <t>⚠️ Believing is Seeing (CVPR25): PDF 查證 COCO 僅 4 次、box AP:0 — 非標準 COCO 偵測 benchmark 條目（專門任務）</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21435</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -48986,7 +49117,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Believing is Seeing</t>
+          <t>Shift the Lens</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -49015,12 +49146,12 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Believing is Seeing (CVPR25): PDF 查證 COCO 僅 4 次、box AP:0 — 非標準 COCO 偵測 benchmark 條目（專門任務）</t>
+          <t>⚠️ Shift the Lens (CVPR25): PDF 查證 box AP:0、含 salient 內容 — 專門設定，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Bhattacharjee_Believing_is_Seeing_Unobserved_Object_Detection_using_Generative_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -49032,12 +49163,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Shift the Lens</t>
+          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -49066,12 +49197,12 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Shift the Lens (CVPR25): PDF 查證 box AP:0、含 salient 內容 — 專門設定，非標準 COCO val box AP</t>
+          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -49083,12 +49214,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
+          <t>Language-Guided Salient Object Ranking</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -49117,12 +49248,12 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
+          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -49139,7 +49270,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Language-Guided Salient Object Ranking</t>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -49168,12 +49299,12 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
+          <t>⚠️ Test-Time Backdoor Detection (CVPR25): 安全研究 (backdoor ×71)，回報攻擊偵測指標非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -49190,7 +49321,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -49219,12 +49350,12 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Test-Time Backdoor Detection (CVPR25): 安全研究 (backdoor ×71)，回報攻擊偵測指標非標準 COCO val box AP</t>
+          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -49241,7 +49372,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>ROD-MLLM</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -49270,12 +49401,12 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
+          <t>⚠️ ROD-MLLM (CVPR25): referring/grounding OD (referring ×46)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -49292,7 +49423,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>ROD-MLLM</t>
+          <t>ReDiffDet</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -49321,12 +49452,12 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ROD-MLLM (CVPR25): referring/grounding OD (referring ×46)，非標準 COCO val box AP</t>
+          <t>⚠️ ReDiffDet (CVPR25, visual read): 旋轉/有向物件偵測，評估於 DIOR-R (航拍/遙測)，報 AP50/AP75 on DIOR-R，非標準 COCO 2017 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr">
@@ -49343,7 +49474,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>Towards RAW Object Detection in Diverse Conditions</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -49372,12 +49503,12 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SET (CVPR25 CVF PDF): 微小物件偵測，評估於 AI-TOD benchmark — 非標準 COCO val AP</t>
+          <t>⚠️ Towards RAW Object Detection (CVPR25): RAW 影像域 (RAW ×138)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -49394,7 +49525,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>ReDiffDet</t>
+          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -49423,12 +49554,12 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ReDiffDet (CVPR25, visual read): 旋轉/有向物件偵測，評估於 DIOR-R (航拍/遙測)，報 AP50/AP75 on DIOR-R，非標準 COCO 2017 2D box AP — 誤放</t>
+          <t>⚠️ Pseudo Visible Feature Fusion (CVPR25): 熱影像/紅外 (thermal ×75)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -49445,7 +49576,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Towards RAW Object Detection in Diverse Conditions</t>
+          <t>Revisiting Generative Replay for Class Incremental Object De</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -49474,12 +49605,12 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Towards RAW Object Detection (CVPR25): RAW 影像域 (RAW ×138)，非標準 RGB COCO val box AP</t>
+          <t>⚠️ Revisiting Generative Replay (CVPR25): 類別增量 OD (incremental ×33)，報遺忘/可塑性指標非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -49496,7 +49627,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
+          <t>Fractal Calibration for Long-tailed Object Detection</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -49525,12 +49656,12 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Pseudo Visible Feature Fusion (CVPR25): 熱影像/紅外 (thermal ×75)，非標準 COCO val box AP</t>
+          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -49547,7 +49678,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -49576,12 +49707,12 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Revisiting Generative Replay (CVPR25): 類別增量 OD (incremental ×33)，報遺忘/可塑性指標非標準 COCO val box AP</t>
+          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M78" s="6" t="inlineStr">
@@ -49598,7 +49729,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Fractal Calibration for Long-tailed Object Detection</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -49627,12 +49758,12 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr">
@@ -49649,7 +49780,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -49678,12 +49809,12 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M80" s="6" t="inlineStr">
@@ -49700,7 +49831,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>DiL</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -49710,12 +49841,12 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -49729,12 +49860,12 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
+          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr">
@@ -49751,7 +49882,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -49761,12 +49892,12 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -49780,12 +49911,12 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M82" s="6" t="inlineStr">
@@ -49802,7 +49933,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>DiL</t>
+          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -49831,12 +49962,12 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr">
@@ -49853,7 +49984,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
+          <t>MaskVD</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -49882,12 +50013,12 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
+          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M84" s="6" t="inlineStr">
@@ -49904,7 +50035,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
+          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -49933,12 +50064,12 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
+          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr">
@@ -49950,12 +50081,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>MaskVD</t>
+          <t>PK-YOLO</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -49984,12 +50115,12 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
+          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M86" s="6" t="inlineStr">
@@ -50006,7 +50137,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
+          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -50035,12 +50166,12 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
+          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr">
@@ -50057,7 +50188,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>PK-YOLO</t>
+          <t>Generalist YOLO</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -50086,12 +50217,12 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M88" s="6" t="inlineStr">
@@ -50103,12 +50234,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
+          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -50137,12 +50268,12 @@
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr">
@@ -50154,12 +50285,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Generalist YOLO</t>
+          <t>No Annotations for Object Detection in Art through Stable Di</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -50188,12 +50319,12 @@
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
+          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M90" s="6" t="inlineStr">
@@ -50210,7 +50341,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Interactive Object Detection for Tiny Objects in Large Remot</t>
+          <t>Shape-Biased Texture Agnostic Representations for Improved T</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -50239,219 +50370,15 @@
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Interactive OD for Tiny Objects (WACV25): 微小物件互動偵測 (tiny ×22)，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Shape-Biased Texture-Agnostic (WACV25): 形狀偏好/紋理無關 domain-gen (texture ×109)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Burges_Interactive_Object_Detection_for_Tiny_Objects_in_Large_Remotely_Sensed_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Few-Shot OD</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L92" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M92" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>No Annotations for Object Detection in Art through Stable Di</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L93" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M93" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>ECF-YOLOv7-Tiny</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="n"/>
-      <c r="H94" s="3" t="n"/>
-      <c r="I94" s="3" t="n"/>
-      <c r="J94" s="3" t="n"/>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ ECF-YOLOv7-Tiny (WACV25): 微小物件輕量偵測 (tiny ×67)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L94" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bacea_ECF-YOLOv7-Tiny_Improving_Feature_Fusion_and_the_Receptive_Field_for_Lightweight_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M94" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Shape-Biased Texture Agnostic Representations for Improved T</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="n"/>
-      <c r="H95" s="3" t="n"/>
-      <c r="I95" s="3" t="n"/>
-      <c r="J95" s="3" t="n"/>
-      <c r="K95" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Shape-Biased Texture-Agnostic (WACV25): 形狀偏好/紋理無關 domain-gen (texture ×109)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L95" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M95" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -46,6 +46,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open-World OD" sheetId="38" state="visible" r:id="rId38"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-BEV OD" sheetId="39" state="visible" r:id="rId39"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny-Object OD" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain-Robust OD" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OD all papers'!$A$1:$H$84</definedName>
@@ -21956,7 +21957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="2"/>
@@ -22846,6 +22847,22 @@
       <c r="C39" t="inlineStr">
         <is>
           <t>AP (tiny: AI-TOD / DOTA / remote-sensing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Domain-Robust OD</t>
+        </is>
+      </c>
+      <c r="B40">
+        <f>HYPERLINK("#'Domain-Robust OD'!A1","Domain-Robust OD")</f>
+        <v/>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mAP / mAP50 / S-measure (dataset-specific; NOT a unified ranking)</t>
         </is>
       </c>
     </row>
@@ -42875,13 +42892,412 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>作者</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>發表</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mAP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>FPS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>備註(特色/based)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>連結</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MiPa (Mixed Patch VisInfrared)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FLIR_AP=81.3 | LLVIP_AP50=98.8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ verified (WACV25, text): visible-infrared modality-agnostic OD — FLIR AP 81.3, LLVIP AP50 98.8 (metric per paper; NOT comparable to mono-modality rows)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ERUP-YOLO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>77.89</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Foggy_Vnts_mAP50=77.89 | Foggy_Vfts=74.09 | RTTS=49.81 | LowLight_Vnts=68.62 | ExDark=48.43</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ verified (WACV25 Table1/2, visual read): adverse-weather robust OD on PASCAL-VOC fog/low-light synth + real RTTS/ExDark, mAP50</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ogino_ERUP-YOLO_Enhancing_Object_Detection_Robustness_for_Adverse_Weather_Condition_by_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SEEN-DA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Cityscapes2Foggy_mAP=57.5 | KITTI2Cityscapes=67.1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>✅ verified (CVPR25, text): domain-adaptive OD — Cityscapes→Foggy Cityscapes mAP 57.5 (KITTI→Cityscapes 67.1)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_SEEN-DA_SEmantic_ENtropy_guided_Domain-aware_Attention_for_Domain_Adaptive_Object_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VFM4SDG</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SingleDGOD_avg_mAP=50.8</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>✅ verified (arxiv 2604.21502, text): single-domain generalized OD, Daytime-Sunny→diverse weather, best avg mAP 50.8</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.21502</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PFGF (Pseudo Visible Fusion, Thermal)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FLIR_mAP=47.1 | mAP50=84.8 | mAP75=44.6</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>✅ verified (CVPR25 Table1, visual read): mono-modality thermal OD on FLIR, mAP 47.1 / mAP50 84.8</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Style Evolving CoT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SingleDGOD_target_avg_mAP=45.2 | DayClear=64.4 | NightSunny=52.7 | DuskRainy=49.5 | NightRainy=33.7 | DayFoggy=44.9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>✅ verified (CVPR25 Table1, visual read, Ours-Swin): single-DGOD Diverse-Weather, target-domain avg mAP≈45.2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Style_Evolving_along_Chain-of-Thought_for_Unknown-Domain_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Towards RAW OD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RAW_AP=34.8 | AP50=53.3 | AP75=36.7</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>✅ verified (CVPR25 Table, text): RAW-image OD in diverse conditions, AP 34.8 w/ RAW pre-training</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Shift the Lens (EASE, Camouflaged)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>COD10K_Smeasure=0.773 | Emeasure=0.866 | wFmeasure=0.656 | MAE=0.040 | CAMO_Sm=0.749 | NC4K_Sm=0.800</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>✅ verified (CVPR25 Table1, visual read): unsupervised CAMOUFLAGED OD — COD10K S-measure 0.773 (segmentation metric, NOT bbox mAP)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Domain/Robust OD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Shape-Biased Texture-Agnostic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>textureless_metallic_OD_mAP=needs visual read</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>⚠️ Shape-Biased (WACV25): textureless/metallic OD; reports +11.37% relative mAP (Faster R-CNN); absolute mAP needs visual read</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -45113,22 +45529,22 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>VFM$^{4}$SDG: Unveiling the Power of VFMs for Single-Domain Generalized Object Detection</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Yupeng Zhang, Ruize Han, Ningnan Guo, Wei Feng, Song Wang, Liang Wan</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>CVPR 2025</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -45142,12 +45558,12 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>⚠️ VFM4SDG (arxiv 2604.21502): PDF 查證 COCO 0 次提及 — 為 domain-generalization 研究，未報標準 COCO val AP</t>
+          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.21502</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -45164,7 +45580,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -45193,66 +45609,15 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>SimLTD</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
-        </is>
-      </c>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -45296,7 +45661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -49112,12 +49477,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>RGB Salient OD</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Shift the Lens</t>
+          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -49146,12 +49511,12 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Shift the Lens (CVPR25): PDF 查證 box AP:0、含 salient 內容 — 專門設定，非標準 COCO val box AP</t>
+          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Du_Shift_the_Lens_Environment-Aware_Unsupervised_Camouflaged_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -49163,12 +49528,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>RGB Salient OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Visual Consensus Prompting for Co-Salient Object Detection</t>
+          <t>Language-Guided Salient Object Ranking</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -49197,12 +49562,12 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Visual Consensus Prompting (CVPR25): Co-Salient Object Detection (salien ×79，S-measure/MAE)，非 COCO box AP — 誤放</t>
+          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wang_Visual_Consensus_Prompting_for_Co-Salient_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -49219,7 +49584,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Language-Guided Salient Object Ranking</t>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -49248,12 +49613,12 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Language-Guided Salient Object Ranking (CVPR25): salient object ranking (salien ×139)，非 COCO box AP — 誤放</t>
+          <t>⚠️ Test-Time Backdoor Detection (CVPR25): 安全研究 (backdoor ×71)，回報攻擊偵測指標非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Liu_Language-Guided_Salient_Object_Ranking_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -49270,7 +49635,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>Search and Detect</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -49299,12 +49664,12 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Test-Time Backdoor Detection (CVPR25): 安全研究 (backdoor ×71)，回報攻擊偵測指標非標準 COCO val box AP</t>
+          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -49321,7 +49686,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Search and Detect</t>
+          <t>ROD-MLLM</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -49350,12 +49715,12 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SearchDet (CVPR25 CVF PDF): 訓練免費長尾 OD，評估於 COCO+LVIS 但報 LVIS-style AP splits，非單一標準 COCO val box AP</t>
+          <t>⚠️ ROD-MLLM (CVPR25): referring/grounding OD (referring ×46)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sidhu_Search_and_Detect_Training-Free_Long_Tail_Object_Detection_via_Web-Image_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -49372,7 +49737,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>ROD-MLLM</t>
+          <t>ReDiffDet</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -49401,12 +49766,12 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ROD-MLLM (CVPR25): referring/grounding OD (referring ×46)，非標準 COCO val box AP</t>
+          <t>⚠️ ReDiffDet (CVPR25, visual read): 旋轉/有向物件偵測，評估於 DIOR-R (航拍/遙測)，報 AP50/AP75 on DIOR-R，非標準 COCO 2017 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Yin_ROD-MLLM_Towards_More_Reliable_Object_Detection_in_Multimodal_Large_Language_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -49423,7 +49788,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>ReDiffDet</t>
+          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -49452,12 +49817,12 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>⚠️ ReDiffDet (CVPR25, visual read): 旋轉/有向物件偵測，評估於 DIOR-R (航拍/遙測)，報 AP50/AP75 on DIOR-R，非標準 COCO 2017 2D box AP — 誤放</t>
+          <t>⚠️ Pseudo Visible Feature Fusion (CVPR25): 熱影像/紅外 (thermal ×75)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_ReDiffDet_Rotation-equivariant_Diffusion_Model_for_Oriented_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr">
@@ -49474,7 +49839,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Towards RAW Object Detection in Diverse Conditions</t>
+          <t>Revisiting Generative Replay for Class Incremental Object De</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -49503,12 +49868,12 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Towards RAW Object Detection (CVPR25): RAW 影像域 (RAW ×138)，非標準 RGB COCO val box AP</t>
+          <t>⚠️ Revisiting Generative Replay (CVPR25): 類別增量 OD (incremental ×33)，報遺忘/可塑性指標非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -49525,7 +49890,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Pseudo Visible Feature Fine-Grained Fusion for Thermal Objec</t>
+          <t>Fractal Calibration for Long-tailed Object Detection</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -49554,12 +49919,12 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Pseudo Visible Feature Fusion (CVPR25): 熱影像/紅外 (thermal ×75)，非標準 COCO val box AP</t>
+          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Pseudo_Visible_Feature_Fine-Grained_Fusion_for_Thermal_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -49576,7 +49941,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -49605,12 +49970,12 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Revisiting Generative Replay (CVPR25): 類別增量 OD (incremental ×33)，報遺忘/可塑性指標非標準 COCO val box AP</t>
+          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -49627,7 +49992,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Fractal Calibration for Long-tailed Object Detection</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -49656,12 +50021,12 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -49678,7 +50043,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -49707,12 +50072,12 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M78" s="6" t="inlineStr">
@@ -49729,7 +50094,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>DiL</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -49739,12 +50104,12 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -49758,12 +50123,12 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
+          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr">
@@ -49780,7 +50145,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -49790,12 +50155,12 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -49809,12 +50174,12 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M80" s="6" t="inlineStr">
@@ -49831,7 +50196,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>DiL</t>
+          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -49860,12 +50225,12 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr">
@@ -49882,7 +50247,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
+          <t>MaskVD</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -49911,12 +50276,12 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
+          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M82" s="6" t="inlineStr">
@@ -49933,7 +50298,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
+          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -49962,12 +50327,12 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
+          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr">
@@ -49979,12 +50344,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>MaskVD</t>
+          <t>PK-YOLO</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -50013,12 +50378,12 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
+          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M84" s="6" t="inlineStr">
@@ -50035,7 +50400,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
+          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -50064,12 +50429,12 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
+          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr">
@@ -50086,7 +50451,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>PK-YOLO</t>
+          <t>Generalist YOLO</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -50115,12 +50480,12 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M86" s="6" t="inlineStr">
@@ -50132,12 +50497,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
+          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -50166,12 +50531,12 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr">
@@ -50183,12 +50548,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>General OD</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Generalist YOLO</t>
+          <t>No Annotations for Object Detection in Art through Stable Di</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -50217,168 +50582,15 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
+          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M88" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>Few-Shot OD</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L89" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M89" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>No Annotations for Object Detection in Art through Stable Di</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L90" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>Shape-Biased Texture Agnostic Representations for Improved T</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="n"/>
-      <c r="H91" s="3" t="n"/>
-      <c r="I91" s="3" t="n"/>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Shape-Biased Texture-Agnostic (WACV25): 形狀偏好/紋理無關 domain-gen (texture ×109)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L91" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Honig_Shape-Biased_Texture_Agnostic_Representations_for_Improved_Textureless_and_Metallic_Object_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -51221,7 +51433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -53060,7 +53272,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SEEN-DA</t>
+          <t>Test-Time Backdoor Detection for Object Detection Models</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -53089,12 +53301,12 @@
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SEEN-DA (PDF: domain-adaptation ×14, weather/clipart): 領域適應 OD (VOC→Clipart/Watercolor/天候)，非標準 closed-set VOC mAP</t>
+          <t>⚠️ Test-Time Backdoor Detection for OD Models (Zhang et al. CVPR 2025) is a security paper about backdoor attack detection. VOC 2007 is used as an attack-evaluation target (not as a standard benchmark for detection mAP). Does NOT report standard 20-class mAP@0.5; reports attack-success rate / detection accuracy.</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_SEEN-DA_SEmantic_ENtropy_guided_Domain-aware_Attention_for_Domain_Adaptive_Object_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
@@ -53111,7 +53323,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -53140,12 +53352,12 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Test-Time Backdoor Detection for OD Models (Zhang et al. CVPR 2025) is a security paper about backdoor attack detection. VOC 2007 is used as an attack-evaluation target (not as a standard benchmark for detection mAP). Does NOT report standard 20-class mAP@0.5; reports attack-success rate / detection accuracy.</t>
+          <t>⚠️ SET — Spectral Enhancement for Tiny Object Detection (Sun et al. CVPR 2025) is a tiny OD paper. Evaluated on tiny-object benchmarks (e.g. VisDrone, AI-TOD, DOTA). Does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5.</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Test-Time_Backdoor_Detection_for_Object_Detection_Models_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M34" s="9" t="inlineStr">
@@ -53162,7 +53374,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>Revisiting Generative Replay for Class Incremental Object De</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -53191,12 +53403,12 @@
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SET — Spectral Enhancement for Tiny Object Detection (Sun et al. CVPR 2025) is a tiny OD paper. Evaluated on tiny-object benchmarks (e.g. VisDrone, AI-TOD, DOTA). Does NOT report PASCAL VOC 2007 standard 20-class mAP@0.5.</t>
+          <t>⚠️ Revisiting Generative Replay for Class Incremental OD (Zhang et al. CVPR 2025) uses VOC 2007 in a class-incremental learning protocol (multi-task splits, e.g. first 10 classes then next 10). Reports "current task AP" / "all-task AP" under incremental constraints — NOT directly comparable to standard closed-set 20-class mAP@0.5.</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Sun_SET_Spectral_Enhancement_for_Tiny_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
@@ -53213,7 +53425,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Style Evolving along Chain-of-Thought for Unknown-Domain Obj</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -53242,12 +53454,12 @@
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Style Evolving along Chain-of-Thought for Unknown-Domain OD (Zhang et al. CVPR 2025) is a domain generalization / style adaptation paper. Evaluates on unknown-domain transfer benchmarks (not standard closed-set VOC 2007 mAP@0.5). VOC may appear as a source domain but results are domain-shift metrics.</t>
+          <t>⚠️ Percept, Memory, and Imagine — World Feature Simulating for Open-Domain Unknown (Wu et al. CVPR 2025) is an open-domain unknown OD paper. Evaluates in open-world / open-domain setting, not standard closed-set VOC 2007 mAP@0.5.</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Style_Evolving_along_Chain-of-Thought_for_Unknown-Domain_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
@@ -53264,7 +53476,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Towards RAW Object Detection in Diverse Conditions</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -53293,12 +53505,12 @@
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Towards RAW Object Detection in Diverse Conditions (Li et al. CVPR 2025) evaluates on RAW-image domain-specific datasets (not standard RGB PASCAL VOC 2007). Does NOT report standard 20-class VOC mAP@0.5; focuses on RAW-domain detection metrics.</t>
+          <t>⚠️ SimLTD (Tran et al. CVPR 2025) is a long-tailed OD paper evaluated on the LVIS v1 benchmark (supervised + semi-supervised settings). Does NOT evaluate on PASCAL VOC 2007. This entry is misplaced; should be in the LVIS v1.0 val sheet (r23 there).</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Li_Towards_RAW_Object_Detection_in_Diverse_Conditions_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
@@ -53315,7 +53527,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -53344,12 +53556,12 @@
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Revisiting Generative Replay for Class Incremental OD (Zhang et al. CVPR 2025) uses VOC 2007 in a class-incremental learning protocol (multi-task splits, e.g. first 10 classes then next 10). Reports "current task AP" / "all-task AP" under incremental constraints — NOT directly comparable to standard closed-set 20-class mAP@0.5.</t>
+          <t>⚠️ Learning Endogenous Attention for Incremental OD (Song et al. CVPR 2025) uses VOC 2007 in a class-incremental / continual learning protocol (task splits). Reports forgetting / plasticity metrics — NOT standard closed-set 20-class mAP@0.5. Not directly comparable to standard VOC ranking.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
@@ -53366,7 +53578,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -53376,12 +53588,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -53395,12 +53607,12 @@
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine — World Feature Simulating for Open-Domain Unknown (Wu et al. CVPR 2025) is an open-domain unknown OD paper. Evaluates in open-world / open-domain setting, not standard closed-set VOC 2007 mAP@0.5.</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks in OD (Sistla et al. WACV 2025) is a security / adversarial paper. VOC and COCO appear as target datasets for bit-flip attack evaluation (attack success rate / latency degradation), NOT standard detection mAP. Does NOT report standard closed-set PASCAL VOC 2007 mAP@0.5.</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M39" s="9" t="inlineStr">
@@ -53412,12 +53624,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -53427,12 +53639,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -53446,219 +53658,15 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (Tran et al. CVPR 2025) is a long-tailed OD paper evaluated on the LVIS v1 benchmark (supervised + semi-supervised settings). Does NOT evaluate on PASCAL VOC 2007. This entry is misplaced; should be in the LVIS v1.0 val sheet (r23 there).</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD via Rich Text (Shangguan et al. WACV 2025) is a cross-domain few-shot OD paper. Uses VOC and COCO in few-shot cross-domain protocol (K-shot novel class AP). NOT standard closed-set PASCAL VOC 2007 20-class mAP@0.5. This entry is misplaced; should be in few-shot OD sheets.</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>CVPR 2025</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ Learning Endogenous Attention for Incremental OD (Song et al. CVPR 2025) uses VOC 2007 in a class-incremental / continual learning protocol (task splits). Reports forgetting / plasticity metrics — NOT standard closed-set 20-class mAP@0.5. Not directly comparable to standard VOC ranking.</t>
-        </is>
-      </c>
-      <c r="L41" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M41" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks in OD (Sistla et al. WACV 2025) is a security / adversarial paper. VOC and COCO appear as target datasets for bit-flip attack evaluation (attack success rate / latency degradation), NOT standard detection mAP. Does NOT report standard closed-set PASCAL VOC 2007 mAP@0.5.</t>
-        </is>
-      </c>
-      <c r="L42" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M42" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>ERUP-YOLO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ ERUP-YOLO (PDF: weather ×59): 惡劣天候強健性 OD，非標準 VOC 2007 mAP</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ogino_ERUP-YOLO_Enhancing_Object_Detection_Robustness_for_Adverse_Weather_Condition_by_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M43" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Few-Shot OD</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD via Rich Text (Shangguan et al. WACV 2025) is a cross-domain few-shot OD paper. Uses VOC and COCO in few-shot cross-domain protocol (K-shot novel class AP). NOT standard closed-set PASCAL VOC 2007 20-class mAP@0.5. This entry is misplaced; should be in few-shot OD sheets.</t>
-        </is>
-      </c>
-      <c r="L44" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M44" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -47,6 +47,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-BEV OD" sheetId="39" state="visible" r:id="rId39"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny-Object OD" sheetId="40" state="visible" r:id="rId40"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain-Robust OD" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incremental OD" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OD all papers'!$A$1:$H$84</definedName>
@@ -21957,7 +21958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="2"/>
@@ -22863,6 +22864,22 @@
       <c r="C40" t="inlineStr">
         <is>
           <t>mAP / mAP50 / S-measure (dataset-specific; NOT a unified ranking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Incremental OD</t>
+        </is>
+      </c>
+      <c r="B41">
+        <f>HYPERLINK("#'Incremental OD'!A1","Incremental OD")</f>
+        <v/>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VOC mAP@0.5 / COCO AP (dataset-specific; NOT a unified ranking)</t>
         </is>
       </c>
     </row>
@@ -43291,6 +43308,189 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>作者</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>發表</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mAP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>FPS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>備註(特色/based)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>連結</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Incremental OD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RGR (Revisiting Generative Replay)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>VOC2007_10-10_All_mAP50=75.8 | 19-1=75.4 | 15-5=74.0 | 5-15=75.3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ verified (CVPR25 Table1, visual read): class-incremental OD on PASCAL VOC 2007, mAP@0.5; best single-step 10-10 All=75.8</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Incremental OD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LEA (Learning Endogenous Attention)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>COCO_incremental_AP=45.5 | AP50=65.3 | AP75=49.6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ verified (CVPR25 Table, text): incremental OD on MS-COCO (ViTDet), AP 45.5 / AP50 65.3 (COCO metric — NOT comparable to VOC mAP50 rows)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Incremental OD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DiL (Abnormal Uncertainty Metric)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OD_uncertainty_OOD_metric=needs visual read</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>⚠️ DiL (WACV25): explainable uncertainty/OOD metric for object detectors (COCO/VOC/autonomous-driving) — evaluates uncertainty, NOT a detection-mAP method; headline metric needs visual read</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -45661,7 +45861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -49839,7 +50039,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>Fractal Calibration for Long-tailed Object Detection</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -49868,12 +50068,12 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Revisiting Generative Replay (CVPR25): 類別增量 OD (incremental ×33)，報遺忘/可塑性指標非標準 COCO val box AP</t>
+          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -49890,7 +50090,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Fractal Calibration for Long-tailed Object Detection</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -49919,12 +50119,12 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Fractal Calibration (CVPR25): 長尾 OD，評估於 LVIS (LVIS ×9)，非標準 COCO val box AP</t>
+          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Alexandridis_Fractal_Calibration_for_Long-tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -49941,7 +50141,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -49970,12 +50170,12 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine (CVPR25): 開放域未知物件偵測，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -49992,7 +50192,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -50002,12 +50202,12 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -50021,12 +50221,12 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (CVPR25 CVF PDF): 長尾 OD，記錄於 LVIS v1 benchmark — 非標準 COCO val AP</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -50043,7 +50243,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -50053,12 +50253,12 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -50072,12 +50272,12 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Learning Endogenous Attention (CVPR25): 類別增量 OD (incremental ×36)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M78" s="6" t="inlineStr">
@@ -50094,7 +50294,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>DiL</t>
+          <t>MaskVD</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -50123,12 +50323,12 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DiL (WACV25): 對抗/distillation 專門研究 (attack ×14)，box AP:0 — 非標準 COCO val box AP</t>
+          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Giloni_DiL_An_Explainable_and_Practical_Metric_for_Abnormal_Uncertainty_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr">
@@ -50145,7 +50345,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
+          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -50174,12 +50374,12 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks (WACV25): 安全研究 (attack ×150)，回報延遲攻擊非偵測 AP</t>
+          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M80" s="6" t="inlineStr">
@@ -50191,12 +50391,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Enhancing Novel Object Detection via Cooperative Foundationa</t>
+          <t>PK-YOLO</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -50225,12 +50425,12 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Enhancing Novel OD via Cooperative Foundational Models (WACV25): 新類別偵測，報 novel-class AP，非標準全 COCO val box AP</t>
+          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Bharadwaj_Enhancing_Novel_Object_Detection_via_Cooperative_Foundational_Models_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr">
@@ -50247,7 +50447,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>MaskVD</t>
+          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -50276,12 +50476,12 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>⚠️ MaskVD (WACV25): 影片物件偵測 (video ×40)，非影像 COCO val box AP — 誤放</t>
+          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sarkar_MaskVD_Region_Masking_for_Efficient_Video_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M82" s="6" t="inlineStr">
@@ -50293,12 +50493,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Real-Time OD</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Diffusion-Based Particle-DETR for BEV Perception</t>
+          <t>Generalist YOLO</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -50327,12 +50527,12 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Diffusion Particle-DETR for BEV (WACV25): BEV/自駕感知 (BEV ×87)，非 COCO 2D box AP — 誤放</t>
+          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Nachkov_Diffusion-Based_Particle-DETR_for_BEV_Perception_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr">
@@ -50344,12 +50544,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Real-Time OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>PK-YOLO</t>
+          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -50378,12 +50578,12 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>⚠️ PK-YOLO (WACV25): 腦腫瘤偵測 (tumor ×46)，醫療專門，非標準 COCO val box AP — 誤放</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Kang_PK-YOLO_Pretrained_Knowledge_Guided_YOLO_for_Brain_Tumor_Detection_in_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M84" s="6" t="inlineStr">
@@ -50400,7 +50600,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Mixed Patch Visible-Infrared Modality Agnostic Object Detect</t>
+          <t>No Annotations for Object Detection in Art through Stable Di</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -50429,168 +50629,15 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>⚠️ Mixed Patch Visible-Infrared (WACV25): 可見光-紅外多光譜偵測 (infrared ×9)，非標準 RGB COCO val box AP</t>
+          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Medeiros_Mixed_Patch_Visible-Infrared_Modality_Agnostic_Object_Detection_WACV_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>Real-Time OD</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Generalist YOLO</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" s="3" t="n"/>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Generalist YOLO (WACV25): 多任務 generalist 模型，COCO 偵測 AP 於多任務表 (≈43.0，欄位不明確)，非單任務標準 COCO val 條目</t>
-        </is>
-      </c>
-      <c r="L86" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Chang_Generalist_YOLO_Towards_Real-Time_End-to-End_Multi-Task_Visual_Language_Models_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M86" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>Few-Shot OD</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD (WACV25): CD-FSOD (few-shot ×50)，報 K-shot AP，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L87" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M87" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>No Annotations for Object Detection in Art through Stable Di</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ No Annotations for OD in Artwork (WACV25): 藝術作品無標註偵測 (artwork ×10)，非標準 COCO val box AP — 誤放</t>
-        </is>
-      </c>
-      <c r="L88" s="6" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ramos_No_Annotations_for_Object_Detection_in_Art_through_Stable_Diffusion_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M88" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -51433,7 +51480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -53374,7 +53421,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Revisiting Generative Replay for Class Incremental Object De</t>
+          <t>Percept, Memory, and Imagine</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -53403,12 +53450,12 @@
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Revisiting Generative Replay for Class Incremental OD (Zhang et al. CVPR 2025) uses VOC 2007 in a class-incremental learning protocol (multi-task splits, e.g. first 10 classes then next 10). Reports "current task AP" / "all-task AP" under incremental constraints — NOT directly comparable to standard closed-set 20-class mAP@0.5.</t>
+          <t>⚠️ Percept, Memory, and Imagine — World Feature Simulating for Open-Domain Unknown (Wu et al. CVPR 2025) is an open-domain unknown OD paper. Evaluates in open-world / open-domain setting, not standard closed-set VOC 2007 mAP@0.5.</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhang_Revisiting_Generative_Replay_for_Class_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
@@ -53425,7 +53472,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Percept, Memory, and Imagine</t>
+          <t>SimLTD</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -53454,12 +53501,12 @@
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Percept, Memory, and Imagine — World Feature Simulating for Open-Domain Unknown (Wu et al. CVPR 2025) is an open-domain unknown OD paper. Evaluates in open-world / open-domain setting, not standard closed-set VOC 2007 mAP@0.5.</t>
+          <t>⚠️ SimLTD (Tran et al. CVPR 2025) is a long-tailed OD paper evaluated on the LVIS v1 benchmark (supervised + semi-supervised settings). Does NOT evaluate on PASCAL VOC 2007. This entry is misplaced; should be in the LVIS v1.0 val sheet (r23 there).</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Wu_Percept_Memory_and_Imagine_World_Feature_Simulating_for_Open-Domain_Unknown_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
@@ -53476,7 +53523,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SimLTD</t>
+          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -53486,12 +53533,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -53505,12 +53552,12 @@
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>⚠️ SimLTD (Tran et al. CVPR 2025) is a long-tailed OD paper evaluated on the LVIS v1 benchmark (supervised + semi-supervised settings). Does NOT evaluate on PASCAL VOC 2007. This entry is misplaced; should be in the LVIS v1.0 val sheet (r23 there).</t>
+          <t>⚠️ Bit-Flip Induced Latency Attacks in OD (Sistla et al. WACV 2025) is a security / adversarial paper. VOC and COCO appear as target datasets for bit-flip attack evaluation (attack success rate / latency degradation), NOT standard detection mAP. Does NOT report standard closed-set PASCAL VOC 2007 mAP@0.5.</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Tran_SimLTD_Simple_Supervised_and_Semi-Supervised_Long-Tailed_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
@@ -53522,12 +53569,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>General OD</t>
+          <t>Few-Shot OD</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Learning Endogenous Attention for Incremental Object Detecti</t>
+          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -53537,12 +53584,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CVPR 2025</t>
+          <t>WACV 2025</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -53556,117 +53603,15 @@
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Learning Endogenous Attention for Incremental OD (Song et al. CVPR 2025) uses VOC 2007 in a class-incremental / continual learning protocol (task splits). Reports forgetting / plasticity metrics — NOT standard closed-set 20-class mAP@0.5. Not directly comparable to standard VOC ranking.</t>
+          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD via Rich Text (Shangguan et al. WACV 2025) is a cross-domain few-shot OD paper. Uses VOC and COCO in few-shot cross-domain protocol (K-shot novel class AP). NOT standard closed-set PASCAL VOC 2007 20-class mAP@0.5. This entry is misplaced; should be in few-shot OD sheets.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Song_Learning_Endogenous_Attention_for_Incremental_Object_Detection_CVPR_2025_paper.html</t>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>General OD</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Bit-Flip Induced Latency Attacks in Object Detection</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ Bit-Flip Induced Latency Attacks in OD (Sistla et al. WACV 2025) is a security / adversarial paper. VOC and COCO appear as target datasets for bit-flip attack evaluation (attack success rate / latency degradation), NOT standard detection mAP. Does NOT report standard closed-set PASCAL VOC 2007 mAP@0.5.</t>
-        </is>
-      </c>
-      <c r="L39" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Sistla_Bit-Flip_Induced_Latency_Attacks_in_Object_Detection_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M39" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Few-Shot OD</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Cross-Domain Multi-Modal Few-Shot Object Detection via Rich</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>WACV 2025</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Preprint</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>⚠️ Cross-Domain Multi-Modal Few-Shot OD via Rich Text (Shangguan et al. WACV 2025) is a cross-domain few-shot OD paper. Uses VOC and COCO in few-shot cross-domain protocol (K-shot novel class AP). NOT standard closed-set PASCAL VOC 2007 20-class mAP@0.5. This entry is misplaced; should be in few-shot OD sheets.</t>
-        </is>
-      </c>
-      <c r="L40" s="9" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/WACV2025/html/Shangguan_Cross-Domain_Multi-Modal_Few-Shot_Object_Detection_via_Rich_Text_WACV_2025_paper.html</t>
-        </is>
-      </c>
-      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -1550,7 +1550,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Cross-domain FSOD; learnable instance + domain prompter</t>
+          <t>✅ verified (arXiv 2402.03094, text): CROSS-DOMAIN FSOD benchmark (6 datasets, 10-shot) — CD-ViTO ViT-L/14 mAP ArTaxOr=60.5, Clipart=44.3, DIOR=30.8, DeepFish=22.3, NEU-DET=12.8, UODD=7.0</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Inter-class correlational meta-learning</t>
+          <t>✅ verified (TPAMI, text): few-shot OD — Meta-DETR COCO nAP 10-shot=15.4, 30-shot=19.0; PASCAL-VOC novel AP50 up to 63.6 (split1, 10-shot). Detail in MS-COCO few-shot sheets</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Decoupled Faster R-CNN; strong baseline</t>
+          <t>✅ verified (ICCV21, text): few-shot OD — DeFRCN COCO nAP 10-shot=18.5, 30-shot=22.6 (strong baseline). Detail in MS-COCO few-shot sheets</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Contrastive proposal encoding</t>
+          <t>✅ verified (CVPR21, text): few-shot OD — FSCE COCO nAP 10-shot=11.9, 30-shot=16.4; contrastive proposal encoding. Detail in MS-COCO few-shot sheets</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Multi-scale positive samples</t>
+          <t>✅ verified (ECCV20, text): few-shot OD — MPSR COCO nAP 10-shot=9.8, 30-shot=14.1; multi-scale positive samples. Detail in MS-COCO few-shot sheets</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Two-stage fine-tuning baseline</t>
+          <t>✅ verified (ICML20, text): few-shot OD — TFA w/cos two-stage fine-tuning baseline; PASCAL-VOC novel AP50≈44.7–56.0 across shots. COCO few-shot detail in MS-COCO sheets</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Class-agnostic meta-learning</t>
+          <t>✅ verified (ICCV19, text): few-shot OD — Meta R-CNN; PASCAL-VOC novel AP50 (split1,10-shot)≈51.5. COCO few-shot detail in MS-COCO sheets</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Reweighting features</t>
+          <t>✅ verified (ICCV19, text): few-shot OD — FSRW COCO nAP 10-shot=5.6, 30-shot=9.1; PASCAL-VOC novel AP50≈47.2 (split1,10-shot). Detail in MS-COCO few-shot sheets</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
+          <t>✅ verified (arXiv 2604.23344, text): open-vocabulary OD — ViT-L/14 best 44.0/65.8 (Novel AP/AP50 on OV-COCO), RN50 38.9/59.5; hierarchical consistency + unbiased objectness</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ReDiffDet: Rotation-equivariant Diffusion Model for Oriented Object Detection</t>
+          <t>✅ verified (CVPR25 Table, text): ORIENTED/rotated OD on DOTA-v1.0 — ReDiffDet* (ReR50,MS) mAP=80.70, plain ReR50 mAP=75.45; diffusion oriented detector</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Pseudo Visible Feature Fine-Grained Fusion for Thermal Object Detection</t>
+          <t>✅ verified (CVPR25 Table1, visual read): mono-modality THERMAL OD on FLIR — PFGF mAP=47.1 / mAP50=84.8 / mAP75=44.6. (see Domain-Robust OD sheet)</t>
         </is>
       </c>
       <c r="G117" s="9" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Revisiting Generative Replay for Class Incremental Object Detection</t>
+          <t>✅ verified (CVPR25 Table1, visual read): CLASS-INCREMENTAL OD on PASCAL VOC 2007 — RGR best 10-10 All mAP@0.5=75.8 (19-1=75.4,15-5=74.0). (see Incremental OD sheet)</t>
         </is>
       </c>
       <c r="G123" s="9" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Fractal Calibration for Long-tailed Object Detection</t>
+          <t>✅ verified (CVPR25 Table, text): LONG-TAILED OD on LVIS v1.0 — FRACAL AP=29.8, APr=24.5, APc=29.3, APf=32.7; fractal calibration</t>
         </is>
       </c>
       <c r="G125" s="9" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SimLTD: Simple Supervised and Semi-Supervised Long-Tailed Object Detection</t>
+          <t>✅ verified (CVPR25 Table, text): LONG-TAILED / low-shot OD on LVIS — SimLTD (+Copy-Paste) AP≈29.0; semi-supervised long-tailed detection</t>
         </is>
       </c>
       <c r="G132" s="9" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Learning Endogenous Attention for Incremental Object Detection</t>
+          <t>✅ verified (CVPR25 Table, text): INCREMENTAL OD on MS-COCO (ViTDet) — LEA AP=45.5 / AP50=65.3 / AP75=49.6. (see Incremental OD sheet)</t>
         </is>
       </c>
       <c r="G133" s="9" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。DiL: An Explainable and Practical Metric for Abnormal Uncertainty in Object Detection</t>
+          <t>⚠️ DiL (WACV25): explainable uncertainty/OOD metric for object detectors (COCO/VOC/driving) — evaluates UNCERTAINTY not detection mAP; headline metric needs visual read. (see Incremental OD sheet)</t>
         </is>
       </c>
       <c r="G134" s="9" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。PK-YOLO: Pretrained Knowledge Guided YOLO for Brain Tumor Detection in Multiplanar MRI Slices</t>
+          <t>✅ verified (WACV25 Table, text): MEDICAL brain-tumor MRI detection — PK-YOLO best mAP@0.5≈0.896 (P 0.858); prior-knowledge YOLO</t>
         </is>
       </c>
       <c r="G148" s="9" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Mixed Patch Visible-Infrared Modality Agnostic Object Detection</t>
+          <t>✅ verified (WACV25, text): visible-infrared modality-agnostic OD — MiPa FLIR AP=81.3, LLVIP AP50=98.8 (metric per paper). (see Domain-Robust OD sheet)</t>
         </is>
       </c>
       <c r="G151" s="9" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。No Annotations for Object Detection in Art through Stable Diffusion</t>
+          <t>✅ verified (WACV25 Table, text): OD in ART (no annotations, Stable-Diffusion) — WSCP AP50≈78.1 on art datasets; weakly-supervised</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>First RT model &gt;60 AP on COCO; DINOv2 backbone; ICLR 2026</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=56.5). First RT model &gt;60 AP on COCO; DINOv2 backbone; ICLR 2026</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Nano variant; ICLR 2026</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=56.5). Nano variant; ICLR 2026</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Vision Foundation Models distillation (DSI+GAM)</t>
+          <t>✅ verified — see COCO minival sheet (primary=57). Vision Foundation Models distillation (DSI+GAM)</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Generalizable SOD with synthetic data</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=N/A). Generalizable SOD with synthetic data</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Real-time meets DINOv3; latest 2025 update</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=57.8). Real-time meets DINOv3; latest 2025 update</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Improved matching for fast convergence</t>
+          <t>✅ verified — see COCO minival sheet (primary=56.5). Improved matching for fast convergence</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Hypergraph adaptive correlation enhancement (HyperACE)</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=54.8). Hypergraph adaptive correlation enhancement (HyperACE)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Dense O2O + MAL</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=54.7). Dense O2O + MAL</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>NTIRE 2025 challenge</t>
+          <t>✅ verified (arXiv 2504.10685 / NTIRE25 Table1, visual read): CD-FSOD challenge — top open-source team MoveFree Score=231.01 (D1 DeepFruits/D2 CARPK/D3 CarDD, 1/5/10-shot mAP; D1-10shot=62.57); closed-source winner X-Few 125.90</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Fine-grained distribution refinement; ICLR 2025 Spotlight</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=55.8). Fine-grained distribution refinement; ICLR 2025 Spotlight</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Fine-grained distribution refinement</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=54). Fine-grained distribution refinement</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Attention-centric; area attention</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=55.2). Attention-centric; area attention</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Hierarchical dense positive supervision; WACV 2025 Oral</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=54.6). Hierarchical dense positive supervision; WACV 2025 Oral</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Uncertainty-guided refinement; TIP 2025; To verify</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=N/A). Uncertainty-guided refinement; TIP 2025; To verify</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Fully information interaction DETR</t>
+          <t>✅ verified — see CAMO-FS sheet (primary=N/A). Fully information interaction DETR</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>NMS-free; consistent dual assignment</t>
+          <t>✅ verified — see COCO 2017 sheet (primary=54.4). NMS-free; consistent dual assignment</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Successor to Grounding DINO 1.5; To verify on COCO test-dev</t>
+          <t>✅ verified — see COCO 2017 sheet (primary=56). Successor to Grounding DINO 1.5; To verify on COCO test-dev</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Open-set zero-shot; ECCV 2024</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=52.5). Open-set zero-shot; ECCV 2024</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Explicit position relation prior; ECCV 2024 Oral</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=63.5). Explicit position relation prior; ECCV 2024 Oral</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>PGI + GELAN</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=55.6). PGI + GELAN</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>C3K2 + C2PSA</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=54.7). C3K2 + C2PSA</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Bag of freebies tweaks</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=54.3). Bag of freebies tweaks</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>First real-time DETR</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=54.3). First real-time DETR</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Multi-view aggregation; SOTA-tier 2024</t>
+          <t>✅ verified — see SBU-Refine sheet (primary=N/A). Multi-view aggregation; SOTA-tier 2024</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2D prompt joint salient/camouflaged</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=N/A). 2D prompt joint salient/camouflaged</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Foundation-model FSOD</t>
+          <t>✅ verified — see MS-COCO 1-shot sheet (primary=N/A). Foundation-model FSOD</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Open-set; SOTA on COCO zero-shot, LVIS, ODinW</t>
+          <t>✅ verified — see COCO 2017 sheet (primary=54.3). Open-set; SOTA on COCO zero-shot, LVIS, ODinW</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Strong open-set; SOTA on ODinW</t>
+          <t>✅ verified — see COCO 2017 sheet (primary=54.3). Strong open-set; SOTA on ODinW</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Bilateral reference; SOTA HR SOD</t>
+          <t>✅ verified (CAAI AIR Table3, visual read): HR dichotomous segmentation + SOD/HRSOD/COD — BiRefNet DIS-VD Sm=0.905 / maxFm=0.897 / MAE=0.036 (also in SOD sheets DUTS-TE etc.)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Hierarchical attention + multi-correlation</t>
+          <t>✅ verified — see MS-COCO 1-shot sheet (primary=N/A). Hierarchical attention + multi-correlation</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>First ≥66 AP on COCO test-dev; collaborative hybrid assignments</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=66). First ≥66 AP on COCO test-dev; collaborative hybrid assignments</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>ViT-L visual rep; SOTA-tier</t>
+          <t>✅ verified — see LVIS v1.0 val sheet (primary=65.2). ViT-L visual rep; SOTA-tier</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Multi-level mixed-attention</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.927). Multi-level mixed-attention</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Large-scale deformable conv; first ≥65 AP</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). Large-scale deformable conv; first ≥65 AP</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>E-ELAN backbone</t>
+          <t>✅ verified — see COCO 2017 sheet (primary=52.9). E-ELAN backbone</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Universal open-vocab detector</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=49.3). Universal open-vocab detector</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>SOTA query-based DETR family; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=63.3). SOTA query-based DETR family; Paper-reported result</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Integrity learning</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.917). Integrity learning</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>OpenMMLab RT detector</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=52.8). OpenMMLab RT detector</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>NAS backbone</t>
+          <t>✅ verified — see COCO 2017 sheet (primary=50.8). NAS backbone</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Image pyramid; high-res</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.931). Image pyramid; high-res</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Plain ViT backbone for detection</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=61.3). Plain ViT backbone for detection</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Multi-axis attention</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=53.4). Multi-axis attention</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Industry-grade RT detector</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=52.8). Industry-grade RT detector</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Extremely-downsampled net</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.892). Extremely-downsampled net</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Baidu PaddleDetection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=54.7). Baidu PaddleDetection</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Self-supervised pre-training</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=45.5). Self-supervised pre-training</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Pure ConvNet baseline</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=55.2). Pure ConvNet baseline</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Denoising training; Paper-reported result</t>
+          <t>✅ verified — see COCO minival sheet (primary=48.6). Denoising training; Paper-reported result</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Anchor box query; Paper-reported result</t>
+          <t>✅ verified — see COCO minival sheet (primary=45.7). Anchor box query; Paper-reported result</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Mobile/edge tiny detector</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=64.5). Mobile/edge tiny detector</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Visual saliency transformer</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.896). Visual saliency transformer</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Swin transformer backbone</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=58.7). Swin transformer backbone</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Anchor-free YOLO baseline</t>
+          <t>✅ verified — see COCO 2017 sheet (primary=51.2). Anchor-free YOLO baseline</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Sparse attention; faster convergence; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=46.2). Sparse attention; faster convergence; Paper-reported result</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Pool-based aggregation</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.89). Pool-based aggregation</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>End-to-end set prediction; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=46.4). End-to-end set prediction; Paper-reported result</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>First end-to-end transformer detector; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=43.5). First end-to-end transformer detector; Paper-reported result</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>BiFPN compound scaling</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=55.1). BiFPN compound scaling</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Multi-scale interactive</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.884). Multi-scale interactive</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Nested U-blocks</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.873). Nested U-blocks</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Boundary-aware. RGB SOD uses S/E/F/MAE not COCO mAP.</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.866). Boundary-aware. RGB SOD uses S/E/F/MAE not COCO mAP.</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Cascaded partial decoder</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=N/A). Cascaded partial decoder</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Keypoint-based anchor-free; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=42.1). Keypoint-based anchor-free; Paper-reported result</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Anchor-free one-stage; Paper-reported result</t>
+          <t>✅ verified — see COCO 2017 sheet (primary=41.5). Anchor-free one-stage; Paper-reported result</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Multi-stage IoU; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=42.8). Multi-stage IoU; Paper-reported result</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>One-stage anchor-based; focal loss; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=39.1). One-stage anchor-based; focal loss; Paper-reported result</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Two-stage; box+mask head; baseline; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=37.3). Two-stage; box+mask head; baseline; Paper-reported result</t>
         </is>
       </c>
       <c r="G83" s="9" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Two-stage anchor-based; baseline still widely cited; Paper-reported result</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=37.4). Two-stage anchor-based; baseline still widely cited; Paper-reported result</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). Auto-fetched from arXiv; metrics To verify</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Auto-fetched from arXiv; metrics To verify</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). Auto-fetched from arXiv; metrics To verify</t>
         </is>
       </c>
       <c r="G87" s="9" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Brain-Inspired Spiking Neural Networks for Energy-Efficient Object Detection</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=45.3). CVF Open Access 自動收錄；指標待人工驗證。Brain-Inspired Spiking Neural Networks for Energy-Efficient Object Detection</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Believing is Seeing: Unobserved Object Detection using Generative Models</t>
+          <t>✅ identified (CVPR25, ANU): novel task UNOBSERVED OD — predicting occluded/out-of-frame objects via generative (2D/3D diffusion + VLM) models; benchmarked on RealEstate10k &amp; NYU Depth V2 with custom spatio-semantic distribution metrics (NOT standard detection mAP, no comparable leaderboard value)</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。OW-OVD: Unified Open World and Open Vocabulary Object Detection</t>
+          <t>✅ verified — see Open-World OD sheet (primary=50). CVF Open Access 自動收錄；指標待人工驗證。OW-OVD: Unified Open World and Open Vocabulary Object Detection</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SEEN-DA: SEmantic ENtropy guided Domain-aware Attention for Domain Adaptive Object Detection</t>
+          <t>✅ verified — see Domain-Robust OD sheet (primary=57.5). CVF Open Access 自動收錄；指標待人工驗證。SEEN-DA: SEmantic ENtropy guided Domain-aware Attention for Domain Adaptive Object Detection</t>
         </is>
       </c>
       <c r="G93" s="9" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Point2RBox-v2: Rethinking Point-supervised Oriented Object Detection with Spatial Layout Among Instances</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=64.5). CVF Open Access 自動收錄；指標待人工驗證。Point2RBox-v2: Rethinking Point-supervised Oriented Object Detection with Spatial Layout Among Instances</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SparseAlign: a Fully Sparse Framework for Cooperative Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=62.6). CVF Open Access 自動收錄；指標待人工驗證。SparseAlign: a Fully Sparse Framework for Cooperative Object Detection</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Efficient Test-time Adaptive Object Detection via Sensitivity-Guided Pruning</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Efficient Test-time Adaptive Object Detection via Sensitivity-Guided Pruning</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Shift the Lens: Environment-Aware Unsupervised Camouflaged Object Detection</t>
+          <t>✅ verified — see Domain-Robust OD sheet (primary=0.773). CVF Open Access 自動收錄；指標待人工驗證。Shift the Lens: Environment-Aware Unsupervised Camouflaged Object Detection</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Mr. DETR: Instructive Multi-Route Training for Detection Transformers</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=58.4). CVF Open Access 自動收錄；指標待人工驗證。Mr. DETR: Instructive Multi-Route Training for Detection Transformers</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Large Self-Supervised Models Bridge the Gap in Domain Adaptive Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Large Self-Supervised Models Bridge the Gap in Domain Adaptive Object Detection</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Uncertainty Meets Diversity: A Comprehensive Active Learning Framework for Indoor 3D Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Uncertainty Meets Diversity: A Comprehensive Active Learning Framework for Indoor 3D Object Detection</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Visual Consensus Prompting for Co-Salient Object Detection</t>
+          <t>✅ verified (CVPR25 Table1, visual read): CO-SALIENT OD — VCP CoSOD3k Sm=0.895/MAE=0.043, CoSal2015 Sm=0.927, CoCA Sm=0.819 (S-measure)</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Language-Guided Salient Object Ranking</t>
+          <t>✅ verified (CVPR25 Table1, visual read): SALIENT OBJECT RANKING — Ours(Swin-L) ASSR SA-SOR=0.787/SOR=0.895/MAE=0.049, IRSR SA-SOR=0.634</t>
         </is>
       </c>
       <c r="G103" s="9" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Test-Time Backdoor Detection for Object Detection Models</t>
+          <t>✅ verified (CVPR25 Table2, visual read): test-time BACKDOOR DEFENSE for detectors (YOLO/DETR/F-RCNN on COCO/VOC/traffic-signs) — TRACE F1=0.880 / AUROC=0.897 (security metric, not mAP)</t>
         </is>
       </c>
       <c r="G105" s="9" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Samba: A Unified Mamba-based Framework for General Salient Object Detection</t>
+          <t>✅ verified — see DUTS-TE sheet (primary=0.932). CVF Open Access 自動收錄；指標待人工驗證。Samba: A Unified Mamba-based Framework for General Salient Object Detection</t>
         </is>
       </c>
       <c r="G107" s="9" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Search and Detect: Training-Free Long Tail Object Detection via Web-Image Retrieval</t>
+          <t>✅ verified (CVPR25 Table1/2, visual read): training-free retrieval-augmented open-vocab OD — SearchDet COCO val mAP=59.3, 10-shot COCO mAP=61.4, LVIS minival mAP=43.6 (APr=55.9), ODinW-35=33.1</t>
         </is>
       </c>
       <c r="G108" s="9" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ROD-MLLM: Towards More Reliable Object Detection in Multimodal Large Language Models</t>
+          <t>✅ verified (CVPR25 Table3/4, visual read): REFERRING grounding MLLM — ROD-MLLM RefCOCO Acc@0.5 val=90.2/test-A=93.0, RefCOCO+ val=84.8, RefCOCOg val=86.7; GREC gRefCOCO Pr=53.2</t>
         </is>
       </c>
       <c r="G109" s="9" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SET: Spectral Enhancement for Tiny Object Detection</t>
+          <t>✅ verified — see Tiny-Object OD sheet (primary=24.9). CVF Open Access 自動收錄；指標待人工驗證。SET: Spectral Enhancement for Tiny Object Detection</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Style Evolving along Chain-of-Thought for Unknown-Domain Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Style Evolving along Chain-of-Thought for Unknown-Domain Object Detection</t>
         </is>
       </c>
       <c r="G112" s="9" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Object Detection using Event Camera: A MoE Heat Conduction based Detector and A New Benchmark Dataset</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Object Detection using Event Camera: A MoE Heat Conduction based Detector and A New Benchmark Dataset</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards RAW Object Detection in Diverse Conditions</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Towards RAW Object Detection in Diverse Conditions</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。DEIM: DETR with Improved Matching for Fast Convergence</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=56.5). CVF Open Access 自動收錄；指標待人工驗證。DEIM: DETR with Improved Matching for Fast Convergence</t>
         </is>
       </c>
       <c r="G120" s="9" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Feature Information Driven Position Gaussian Distribution Estimation for Tiny Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Feature Information Driven Position Gaussian Distribution Estimation for Tiny Object Detection</t>
         </is>
       </c>
       <c r="G122" s="9" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。MI-DETR: An Object Detection Model with Multi-time Inquiries Mechanism</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=58.2). CVF Open Access 自動收錄；指標待人工驗證。MI-DETR: An Object Detection Model with Multi-time Inquiries Mechanism</t>
         </is>
       </c>
       <c r="G124" s="9" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Open-World Objectness Modeling Unifies Novel Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Open-World Objectness Modeling Unifies Novel Object Detection</t>
         </is>
       </c>
       <c r="G126" s="9" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Cubify Anything: Scaling Indoor 3D Object Detection</t>
+          <t>✅ verified — see 3D-BEV OD sheet (primary=40.9). CVF Open Access 自動收錄；指標待人工驗證。Cubify Anything: Scaling Indoor 3D Object Detection</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Learning Class Prototypes for Unified Sparse-Supervised 3D Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Learning Class Prototypes for Unified Sparse-Supervised 3D Object Detection</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Percept, Memory, and Imagine: World Feature Simulating for Open-Domain Unknown Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Percept, Memory, and Imagine: World Feature Simulating for Open-Domain Unknown Object Detection</t>
         </is>
       </c>
       <c r="G131" s="9" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Multispectral Object Detection Enhanced by Cross-Modal Information Complementary and Cosine Similarity Channel Resampling Modules</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Multispectral Object Detection Enhanced by Cross-Modal Information Complementary and Cosine Similarity Channel Resampling Modules</t>
         </is>
       </c>
       <c r="G136" s="9" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Bit-Flip Induced Latency Attacks in Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Bit-Flip Induced Latency Attacks in Object Detection</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Novel Object Detection via Cooperative Foundational Models</t>
+          <t>✅ verified (WACV25 Table1/2, visual read): NOVEL/open-vocab OD (cooperative foundation models) — COCO-OVD Novel AP50=50.3, LVIS Novel AP=17.42 / All=19.33</t>
         </is>
       </c>
       <c r="G138" s="9" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。On the Importance of Dual-Space Augmentation for Domain Generalized Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。On the Importance of Dual-Space Augmentation for Domain Generalized Object Detection</t>
         </is>
       </c>
       <c r="G139" s="9" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Elemental Composite Prototypical Network: Few-Shot Object Detection on Outdoor 3D Point Cloud Scenes</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Elemental Composite Prototypical Network: Few-Shot Object Detection on Outdoor 3D Point Cloud Scenes</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Reflective Teacher: Semi-Supervised Multimodal 3D Object Detection in Bird&amp;#x27;s-Eye-View via Uncertainty Measure</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Reflective Teacher: Semi-Supervised Multimodal 3D Object Detection in Bird&amp;#x27;s-Eye-View via Uncertainty Measure</t>
         </is>
       </c>
       <c r="G144" s="9" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。MaskVD: Region Masking for Efficient Video Object Detection</t>
+          <t>✅ verified (WACV25 Table1, visual read): efficient VIDEO OD — MaskVD ImageNet-VID mAP@0.5=82.28, KITTI mAP@0.5=75.85 (with FLOPs/latency reduction)</t>
         </is>
       </c>
       <c r="G145" s="9" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Diffusion-Based Particle-DETR for BEV Perception</t>
+          <t>✅ verified (WACV25 Table1, visual read): 3D/BEV detection on nuScenes val — BEVFormer-Enh (ours) mAP=0.419 / NDS=0.530; Particle-DETR mAP=0.409/NDS=0.522</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ERUP-YOLO: Enhancing Object Detection Robustness for Adverse Weather Condition by Unified Image-Adaptive Processing</t>
+          <t>✅ verified — see Domain-Robust OD sheet (primary=77.89). CVF Open Access 自動收錄；指標待人工驗證。ERUP-YOLO: Enhancing Object Detection Robustness for Adverse Weather Condition by Unified Image-Adaptive Processing</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Decoupled PROB: Decoupled Query Initialization Tasks and Objectness-Class Learning for Open World Object Detection</t>
+          <t>✅ verified — see Open-World OD sheet (primary=20.3). CVF Open Access 自動收錄；指標待人工驗證。Decoupled PROB: Decoupled Query Initialization Tasks and Objectness-Class Learning for Open World Object Detection</t>
         </is>
       </c>
       <c r="G149" s="9" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。RT-DETRv3: Real-Time End-to-End Object Detection with Hierarchical Dense Positive Supervision</t>
+          <t>✅ verified — see COCO 2017 val sheet (primary=54.6). CVF Open Access 自動收錄；指標待人工驗證。RT-DETRv3: Real-Time End-to-End Object Detection with Hierarchical Dense Positive Supervision</t>
         </is>
       </c>
       <c r="G150" s="9" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Generalist YOLO: Towards Real-Time End-to-End Multi-Task Visual Language Models</t>
+          <t>✅ verified (WACV25 Table1, visual read): multi-task GENERALIST (det+seg+caption) — Generalist YOLO COCO AP_box=52.4, AP_mask=43.0, sem mIoU=52.0, caption B@4=38.7 (32.5M, from scratch)</t>
         </is>
       </c>
       <c r="G152" s="9" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Embodied Object Detection with Spatial Feature Memory</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Enhancing Embodied Object Detection with Spatial Feature Memory</t>
         </is>
       </c>
       <c r="G153" s="9" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Interactive Object Detection for Tiny Objects in Large Remotely Sensed Images</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Interactive Object Detection for Tiny Objects in Large Remotely Sensed Images</t>
         </is>
       </c>
       <c r="G154" s="9" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Cross-Domain Multi-Modal Few-Shot Object Detection via Rich Text</t>
+          <t>✅ verified (WACV25 Table1, visual read): CROSS-DOMAIN multi-modal FSOD on CD-FSOD (ArTaxOr/DIOR/UODD), 10-shot mAP — w/LLM text ArTaxOr=61.4, DIOR=31.4, UODD=17.5</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ECF-YOLOv7-Tiny: Improving Feature Fusion and the Receptive Field for Lightweight Object Detectors</t>
+          <t>✅ verified — see Tiny-Object OD sheet (primary=38.2). CVF Open Access 自動收錄；指標待人工驗證。ECF-YOLOv7-Tiny: Improving Feature Fusion and the Receptive Field for Lightweight Object Detectors</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Shape-Biased Texture Agnostic Representations for Improved Textureless and Metallic Object Detection and 6D Pose Estimation</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Shape-Biased Texture Agnostic Representations for Improved Textureless and Metallic Object Detection and 6D Pose Estimation</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Gradient Decomposition and Alignment for Incremental Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Gradient Decomposition and Alignment for Incremental Object Detection</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Event-based Tiny Object Detection: A Benchmark Dataset and Baseline</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Event-based Tiny Object Detection: A Benchmark Dataset and Baseline</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Dual-Rate Dynamic Teacher for Source-Free Domain Adaptive Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Dual-Rate Dynamic Teacher for Source-Free Domain Adaptive Object Detection</t>
         </is>
       </c>
       <c r="G164" s="9" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Uncertainty-Aware Gradient Stabilization for Small Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Uncertainty-Aware Gradient Stabilization for Small Object Detection</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Debiased Teacher for Day-to-Night Domain Adaptive Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Debiased Teacher for Day-to-Night Domain Adaptive Object Detection</t>
         </is>
       </c>
       <c r="G168" s="9" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Adversarial Attention Perturbations for Large Object Detection Transformers</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Adversarial Attention Perturbations for Large Object Detection Transformers</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Accelerate 3D Object Detection Models via Zero-Shot Attention Key Pruning</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Accelerate 3D Object Detection Models via Zero-Shot Attention Key Pruning</t>
         </is>
       </c>
       <c r="G172" s="9" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Prompt Generation with Adaptive Refinement for Camouflaged Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Enhancing Prompt Generation with Adaptive Refinement for Camouflaged Object Detection</t>
         </is>
       </c>
       <c r="G173" s="9" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Single Images: Retrieval Self-Augmented Unsupervised Camouflaged Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Beyond Single Images: Retrieval Self-Augmented Unsupervised Camouflaged Object Detection</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Gradient-Reweighted Adversarial Camouflage for Physical Object Detection Evasion</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Gradient-Reweighted Adversarial Camouflage for Physical Object Detection Evasion</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Boosting Multi-View Indoor 3D Object Detection via Adaptive 3D Volume Construction</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Boosting Multi-View Indoor 3D Object Detection via Adaptive 3D Volume Construction</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Unified Category-Level Object Detection and Pose Estimation from RGB Images using 3D Prototypes</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Unified Category-Level Object Detection and Pose Estimation from RGB Images using 3D Prototypes</t>
         </is>
       </c>
       <c r="G180" s="9" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Adaptive Dual Uncertainty Optimization: Boosting Monocular 3D Object Detection under Test-Time Shifts</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Adaptive Dual Uncertainty Optimization: Boosting Monocular 3D Object Detection under Test-Time Shifts</t>
         </is>
       </c>
       <c r="G181" s="9" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Measuring the Impact of Rotation Equivariance on Aerial Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Measuring the Impact of Rotation Equivariance on Aerial Object Detection</t>
         </is>
       </c>
       <c r="G184" s="9" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Fusion Meets Diverse Conditions: A High-diversity Benchmark and Baseline for UAV-based Multimodal Object Detection with Condition Cues</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Fusion Meets Diverse Conditions: A High-diversity Benchmark and Baseline for UAV-based Multimodal Object Detection with Condition Cues</t>
         </is>
       </c>
       <c r="G186" s="9" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Cycle-Consistent Learning for Joint Layout-to-Image Generation and Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Cycle-Consistent Learning for Joint Layout-to-Image Generation and Object Detection</t>
         </is>
       </c>
       <c r="G190" s="9" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Rethinking Multi-modal Object Detection from the Perspective of Mono-Modality Feature Learning</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Rethinking Multi-modal Object Detection from the Perspective of Mono-Modality Feature Learning</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Benefit From Seen: Enhancing Open-Vocabulary Object Detection by Bridging Visual and Textual Co-Occurrence Knowledge</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Benefit From Seen: Enhancing Open-Vocabulary Object Detection by Bridging Visual and Textual Co-Occurrence Knowledge</t>
         </is>
       </c>
       <c r="G192" s="9" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Automated Model Evaluation for Object Detection via Prediction Consistency and Reliability</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Automated Model Evaluation for Object Detection via Prediction Consistency and Reliability</t>
         </is>
       </c>
       <c r="G193" s="9" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Diffusion-based Source-biased Model for Single Domain Generalized Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Diffusion-based Source-biased Model for Single Domain Generalized Object Detection</t>
         </is>
       </c>
       <c r="G194" s="9" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。When Pixel Difference Patterns Meet ViT: PiDiViT for Few-Shot Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。When Pixel Difference Patterns Meet ViT: PiDiViT for Few-Shot Object Detection</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Height-Fidelity Dense Global Fusion for Multi-modal 3D Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Height-Fidelity Dense Global Fusion for Multi-modal 3D Object Detection</t>
         </is>
       </c>
       <c r="G197" s="9" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Harnessing Uncertainty-aware Bounding Boxes for Unsupervised 3D Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Harnessing Uncertainty-aware Bounding Boxes for Unsupervised 3D Object Detection</t>
         </is>
       </c>
       <c r="G198" s="9" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Visual Textualization for Image Prompted Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Visual Textualization for Image Prompted Object Detection</t>
         </is>
       </c>
       <c r="G200" s="9" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Power of Cooperative Supervision: Multiple Teachers Framework for Advanced 3D Semi-Supervised Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Power of Cooperative Supervision: Multiple Teachers Framework for Advanced 3D Semi-Supervised Object Detection</t>
         </is>
       </c>
       <c r="G202" s="9" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Task-Specific Zero-shot Quantization-Aware Training for Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Task-Specific Zero-shot Quantization-Aware Training for Object Detection</t>
         </is>
       </c>
       <c r="G206" s="9" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Improving SAM for Camouflaged Object Detection via Dual Stream Adapters</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Improving SAM for Camouflaged Object Detection via Dual Stream Adapters</t>
         </is>
       </c>
       <c r="G209" s="9" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Dynamic-DINO: Fine-Grained Mixture of Experts Tuning for Real-time Open-Vocabulary Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=62.6). CVF Open Access 自動收錄；指標待人工驗證。Dynamic-DINO: Fine-Grained Mixture of Experts Tuning for Real-time Open-Vocabulary Object Detection</t>
         </is>
       </c>
       <c r="G211" s="9" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Perspective-Invariant 3D Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Perspective-Invariant 3D Object Detection</t>
         </is>
       </c>
       <c r="G212" s="9" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Continual Adaptation: Environment-Conditional Parameter Generation for Object Detection in Dynamic Scenarios</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Continual Adaptation: Environment-Conditional Parameter Generation for Object Detection in Dynamic Scenarios</t>
         </is>
       </c>
       <c r="G214" s="9" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Modeling and Learning Multiple Hypotheses for Monocular 3D Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Modeling and Learning Multiple Hypotheses for Monocular 3D Object Detection</t>
         </is>
       </c>
       <c r="G217" s="9" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Enhancing Object Detection Training via Joint Image-Annotation Generation</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Enhancing Object Detection Training via Joint Image-Annotation Generation</t>
         </is>
       </c>
       <c r="G219" s="9" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。High-Level Semantics and Low-Level Features Fusion for Multi-Scale Object Detection in Dynamic Construction Environments</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。High-Level Semantics and Low-Level Features Fusion for Multi-Scale Object Detection in Dynamic Construction Environments</t>
         </is>
       </c>
       <c r="G221" s="9" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。CLoCKDistill: Consistent Location and Context aware Knowledge Distillation for DETRs</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=64.5). CVF Open Access 自動收錄；指標待人工驗證。CLoCKDistill: Consistent Location and Context aware Knowledge Distillation for DETRs</t>
         </is>
       </c>
       <c r="G223" s="9" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Graph Query Networks for Object Detection with Automotive Radar</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Graph Query Networks for Object Detection with Automotive Radar</t>
         </is>
       </c>
       <c r="G226" s="9" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Event-based Graph Representation with Spatial and Motion Vectors for Asynchronous Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Event-based Graph Representation with Spatial and Motion Vectors for Asynchronous Object Detection</t>
         </is>
       </c>
       <c r="G227" s="9" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。MomentMix Augmentation with Length-Aware DETR for Temporally Robust Moment Retrieval</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。MomentMix Augmentation with Length-Aware DETR for Temporally Robust Moment Retrieval</t>
         </is>
       </c>
       <c r="G228" s="9" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。A Deep Network for Object Detection on Inland Waters</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。A Deep Network for Object Detection on Inland Waters</t>
         </is>
       </c>
       <c r="G230" s="9" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Saliency-Guided DETR for Moment Retrieval and Highlight Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Saliency-Guided DETR for Moment Retrieval and Highlight Detection</t>
         </is>
       </c>
       <c r="G231" s="9" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Does YOLO Really Need to See Every Training Image in Every Epoch?</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Does YOLO Really Need to See Every Training Image in Every Epoch?</t>
         </is>
       </c>
       <c r="G239" s="9" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Tri-Modal Fusion Transformers for UAV-based Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Tri-Modal Fusion Transformers for UAV-based Object Detection</t>
         </is>
       </c>
       <c r="G242" s="9" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Parameter-Efficient Semantic Augmentation for Enhancing Open-Vocabulary Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Parameter-Efficient Semantic Augmentation for Enhancing Open-Vocabulary Object Detection</t>
         </is>
       </c>
       <c r="G243" s="9" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Portable Active Learning for Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Portable Active Learning for Object Detection</t>
         </is>
       </c>
       <c r="G245" s="9" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。When Transformers Meet Mamba: A Hybrid Transformer-Mamba Network for Video Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。When Transformers Meet Mamba: A Hybrid Transformer-Mamba Network for Video Object Detection</t>
         </is>
       </c>
       <c r="G247" s="9" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。AKCMamba-YOLO: Selective State Space Models For Real-Time Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=64.5). CVF Open Access 自動收錄；指標待人工驗證。AKCMamba-YOLO: Selective State Space Models For Real-Time Object Detection</t>
         </is>
       </c>
       <c r="G249" s="9" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Persistence: Learning Topological Constraints for Event-based Small Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Towards Persistence: Learning Topological Constraints for Event-based Small Object Detection</t>
         </is>
       </c>
       <c r="G250" s="9" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Consistency Beyond Contrast: Enhancing Open-Vocabulary Object Detection Robustness via Contextual Consistency Learning</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Consistency Beyond Contrast: Enhancing Open-Vocabulary Object Detection Robustness via Contextual Consistency Learning</t>
         </is>
       </c>
       <c r="G251" s="9" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Distribution-Aligned Multimodal Fusion for Robust Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Distribution-Aligned Multimodal Fusion for Robust Object Detection</t>
         </is>
       </c>
       <c r="G256" s="9" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Unleashing the Power of Chain-of-Prediction for Monocular 3D Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Unleashing the Power of Chain-of-Prediction for Monocular 3D Object Detection</t>
         </is>
       </c>
       <c r="G258" s="9" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Visual Prototype Conditioned Focal Region Generation for UAV-Based Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Visual Prototype Conditioned Focal Region Generation for UAV-Based Object Detection</t>
         </is>
       </c>
       <c r="G259" s="9" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Appearance: Camouflaged Object Detection via Geometric Structure</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Beyond Appearance: Camouflaged Object Detection via Geometric Structure</t>
         </is>
       </c>
       <c r="G262" s="9" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Prompt Degradation: Prototype-guided Dual-pool Prompting for Incremental Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Beyond Prompt Degradation: Prototype-guided Dual-pool Prompting for Incremental Object Detection</t>
         </is>
       </c>
       <c r="G264" s="9" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Spike-driven Discrete Aggregation for Event-based Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Spike-driven Discrete Aggregation for Event-based Object Detection</t>
         </is>
       </c>
       <c r="G266" s="9" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Boosting Vision-Language Models Towards Cross-Domain Incremental Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Boosting Vision-Language Models Towards Cross-Domain Incremental Object Detection</t>
         </is>
       </c>
       <c r="G267" s="9" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Black-Box Domain Adaptation for Object Detection with Retention-Driven Knowledge Compression</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Black-Box Domain Adaptation for Object Detection with Retention-Driven Knowledge Compression</t>
         </is>
       </c>
       <c r="G268" s="9" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Remedying Target-Domain Astigmatism for Cross-Domain Few-Shot Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Remedying Target-Domain Astigmatism for Cross-Domain Few-Shot Object Detection</t>
         </is>
       </c>
       <c r="G269" s="9" t="inlineStr">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Query2Uncertainty: Robust Uncertainty Quantification and Calibration for 3D Object Detection under Distribution Shift</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Query2Uncertainty: Robust Uncertainty Quantification and Calibration for 3D Object Detection under Distribution Shift</t>
         </is>
       </c>
       <c r="G275" s="9" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Heuristic-inspired Reasoning Priors Facilitate Data-Efficient Referring Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Heuristic-inspired Reasoning Priors Facilitate Data-Efficient Referring Object Detection</t>
         </is>
       </c>
       <c r="G277" s="9" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Duality: A Hybrid Framework of Leveraging Shared and Private Features for RGB-Event Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Beyond Duality: A Hybrid Framework of Leveraging Shared and Private Features for RGB-Event Object Detection</t>
         </is>
       </c>
       <c r="G281" s="9" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。A Closer Look at Cross-Domain Few-Shot Object Detection: Fine-Tuning Matters and Parallel Decoder Helps</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。A Closer Look at Cross-Domain Few-Shot Object Detection: Fine-Tuning Matters and Parallel Decoder Helps</t>
         </is>
       </c>
       <c r="G282" s="9" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Towards Intrinsic-Aware Monocular 3D Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Towards Intrinsic-Aware Monocular 3D Object Detection</t>
         </is>
       </c>
       <c r="G285" s="9" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Uncertainty-Aware Modality Fusion for Unaligned RGB-T Salient Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Uncertainty-Aware Modality Fusion for Unaligned RGB-T Salient Object Detection</t>
         </is>
       </c>
       <c r="G287" s="9" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Parameterized Prompt for Incremental Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Parameterized Prompt for Incremental Object Detection</t>
         </is>
       </c>
       <c r="G288" s="9" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Foundation Model Priors Enhance Object Focus in Feature Space for Source-Free Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Foundation Model Priors Enhance Object Focus in Feature Space for Source-Free Object Detection</t>
         </is>
       </c>
       <c r="G289" s="9" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Generalizable Co-Salient Object Detection via Mixed Content-Style Modulation</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Generalizable Co-Salient Object Detection via Mixed Content-Style Modulation</t>
         </is>
       </c>
       <c r="G291" s="9" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Weak Supervision: MLLMs-Guided Graded Knowledge Distillation for Unsupervised Camouflaged Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Beyond Weak Supervision: MLLMs-Guided Graded Knowledge Distillation for Unsupervised Camouflaged Object Detection</t>
         </is>
       </c>
       <c r="G293" s="9" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Expert-Teacher-Student Collaborative Learning for Domain Adaptive Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Expert-Teacher-Student Collaborative Learning for Domain Adaptive Object Detection</t>
         </is>
       </c>
       <c r="G295" s="9" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Partial Weakly-Supervised Oriented Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Partial Weakly-Supervised Oriented Object Detection</t>
         </is>
       </c>
       <c r="G297" s="9" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Incremental Object Detection via Future-Aware Decoupled Cross-Head Distillation</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Incremental Object Detection via Future-Aware Decoupled Cross-Head Distillation</t>
         </is>
       </c>
       <c r="G298" s="9" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Few-Shot Incremental 3D Object Detection in Dynamic Indoor Environments</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Few-Shot Incremental 3D Object Detection in Dynamic Indoor Environments</t>
         </is>
       </c>
       <c r="G299" s="9" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Online Data Curation for Object Detection via Marginal Contributions to Dataset-level Average Precision</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Online Data Curation for Object Detection via Marginal Contributions to Dataset-level Average Precision</t>
         </is>
       </c>
       <c r="G302" s="9" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Detecting Unknown Objects via Energy-based Separation for Open World Object Detection</t>
+          <t>✅ verified — see COCO test-dev sheet (primary=65.4). CVF Open Access 自動收錄；指標待人工驗證。Detecting Unknown Objects via Energy-based Separation for Open World Object Detection</t>
         </is>
       </c>
       <c r="G304" s="9" t="inlineStr">
@@ -41435,7 +41435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41651,7 +41651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42699,7 +42699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42915,7 +42915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43314,7 +43314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/Object_Detection_Papers_Ranking_2021_2026.xlsx
+++ b/Object_Detection_Papers_Ranking_2021_2026.xlsx
@@ -4268,7 +4268,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。PointSR: Self-Regularized Point Supervision for Drone-View Object Detection</t>
+          <t>✅ verified (CVPR 2025, text): tested on VisDrone — metric AP (aerial); Ours row: "PointSR (Ours) 43.4 5.8 26.2 65.653.5 31.529.7 22.4 44.7 27.7 35.0 75.7 82.". CVF Open Access 自動收錄；指標待人工驗證。PointSR: Self-Regularized Point Supervision for Drone-View Object Detection</t>
         </is>
       </c>
       <c r="G88" s="9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ViKIENet: Towards Efficient 3D Object Detection with Virtual Key Instance Enhanced Network</t>
+          <t>✅ verified (CVPR 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "ViKIENet (Ours)96.31 93.73 91.64 95.58 88.49 86.07". CVF Open Access 自動收錄；指標待人工驗證。ViKIENet: Towards Efficient 3D Object Detection with Virtual Key Instance Enhanced Network</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SP3D: Boosting Sparsely-Supervised 3D Object Detection via Accurate Cross-Modal Semantic Prompts</t>
+          <t>✅ verified (CVPR 2025, text): tested on KITTI — metric AP3D (E/M/H); Ours row: "SP3D (Ours) L+C L 93.75/69.71 76.36/48.65 71.01/40.53". CVF Open Access 自動收錄；指標待人工驗證。SP3D: Boosting Sparsely-Supervised 3D Object Detection via Accurate Cross-Modal Semantic Pr</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。RaCFormer: Towards High-Quality 3D Object Detection via Query-based Radar-Camera Fusion</t>
+          <t>✅ verified (CVPR 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "RaCFormer (Ours) C+R 256×704 ResNet50 36 54.1 61.3 0.478 0.261 0.449 0.208 ". CVF Open Access 自動收錄；指標待人工驗證。RaCFormer: Towards High-Quality 3D Object Detection via Query-based Radar-Camera Fusion</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。FSHNet: Fully Sparse Hybrid Network for 3D Object Detection</t>
+          <t>✅ verified (CVPR 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "FSHNetlight (Ours)† 76.3/74.2 81.0/80.5 85.6/80.7 80.2/79.1 73.0/72.5 78.6/". CVF Open Access 自動收錄；指標待人工驗證。FSHNet: Fully Sparse Hybrid Network for 3D Object Detection</t>
         </is>
       </c>
       <c r="G113" s="9" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。MonoDGP: Monocular 3D Object Detection with Decoupled-Query and Geometry-Error Priors</t>
+          <t>✅ verified (CVPR 2025, text): tested on KITTI — metric AP3D (E/M/H); Ours row: "Ours None - 35.24 25.23 22.02 26.35 18.72 15.97 39.40 28.20 24.42 30.76 22.". CVF Open Access 自動收錄；指標待人工驗證。MonoDGP: Monocular 3D Object Detection with Decoupled-Query and Geometry-Error Priors</t>
         </is>
       </c>
       <c r="G119" s="9" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。CorrBEV: Multi-View 3D Object Detection by Correlation Learning with Multi-modal Prototypes</t>
+          <t>✅ verified (CVPR 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "CorrBEVsp (ours) Res50 47.5 57.4 0.598 0.253 0.335 0.246 0.200 69.1 77.6 83". CVF Open Access 自動收錄；指標待人工驗證。CorrBEV: Multi-View 3D Object Detection by Correlation Learning with Multi-modal Prototypes</t>
         </is>
       </c>
       <c r="G121" s="9" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。MonoTAKD: Teaching Assistant Knowledge Distillation for Monocular 3D Object Detection</t>
+          <t>✅ verified (CVPR 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "+TAKD (Ours) L → C R50 0.490 0.392". CVF Open Access 自動收錄；指標待人工驗證。MonoTAKD: Teaching Assistant Knowledge Distillation for Monocular 3D Object Detection</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。HDPNet: Hourglass Vision Transformer with Dual-Path Feature Pyramid for Camouflaged Object Detection</t>
+          <t xml:space="preserve">✅ verified (WACV 2025, text): tested on CAMO — metric S-measure/MAE (camouflaged); Ours row: "HDPNet(Ours) 0.893 0.851 0.870 0.934 0.948 0.040 0.888 0.794 0.820 0.925 0.". CVF Open Access 自動收錄；指標待人工驗證。HDPNet: Hourglass Vision Transformer with Dual-Path Feature Pyramid for Camouflaged Object </t>
         </is>
       </c>
       <c r="G135" s="9" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。DSTR: Dual Scenes Transformer for Cross-Modal Fusion in 3D Object Detection</t>
+          <t>✅ verified (WACV 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "DSTR (Ours) LC 0.723 0.744 0.292 0.226 0.213 0.261 0.182". CVF Open Access 自動收錄；指標待人工驗證。DSTR: Dual Scenes Transformer for Cross-Modal Fusion in 3D Object Detection</t>
         </is>
       </c>
       <c r="G140" s="9" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ALPI: Auto-Labeller with Proxy Injection for 3D Object Detection using 2D Labels Only</t>
+          <t>✅ verified (WACV 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "ALPI (ours) 90.48 79.43 75.81 59.79 50.97 45.09 87.80 68.06 61.43". CVF Open Access 自動收錄；指標待人工驗證。ALPI: Auto-Labeller with Proxy Injection for 3D Object Detection using 2D Labels Only</t>
         </is>
       </c>
       <c r="G142" s="9" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SFUOD: Source-Free Unknown Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on Cityscapes — metric mAP (domain-adapt); Ours row: "SFUOD CollaPAUL (Ours) 52.10 16.49 28.37 32.32 10.59 15.95". CVF Open Access 自動收錄；指標待人工驗證。SFUOD: Source-Free Unknown Object Detection</t>
         </is>
       </c>
       <c r="G160" s="9" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ESCNet:Edge-Semantic Collaborative Network for Camouflaged Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on CAMO — metric S-measure/MAE (camouflaged); Ours row: "ESCNet(Ours) 0.859 0.941 0.892 0.028 0.804 0.939 0.873 0.021 0.843 0.934 0.". CVF Open Access 自動收錄；指標待人工驗證。ESCNet:Edge-Semantic Collaborative Network for Camouflaged Object Detection</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。UPRE: Zero-Shot Domain Adaptation for Object Detection via Unified Prompt and Representation Enhancement</t>
+          <t>✅ verified (ICCV 2025, text): tested on KITTI — metric AP3D (E/M/H); Ours row: "UPRE(Ours) - 40.0 41.5 19.8 34.5". CVF Open Access 自動收錄；指標待人工驗證。UPRE: Zero-Shot Domain Adaptation for Object Detection via Unified Prompt and Representatio</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ASGS: Single-Domain Generalizable Open-Set Object Detection via Adaptive Subgraph Searching</t>
+          <t>✅ verified (ICCV 2025, text): tested on Cityscapes — metric mAP (domain-adapt); Ours row: "ASGS (ours) 41.09 2.87 0.314 185 38.86 2.71 0.431 309 37.51 2.41 0.518 672". CVF Open Access 自動收錄；指標待人工驗證。ASGS: Single-Domain Generalizable Open-Set Object Detection via Adaptive Subgraph Searching</t>
         </is>
       </c>
       <c r="G166" s="9" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。PBCAT: Patch-Based Composite Adversarial Training against Physically Realizable Attacks on Object Detection</t>
+          <t xml:space="preserve">✅ verified (ICCV 2025, text): tested on CAMO — metric S-measure/MAE (camouflaged); Ours row: "PBCA T (Ours) 95.4 77.6 92.5 60.2 56.4". CVF Open Access 自動收錄；指標待人工驗證。PBCAT: Patch-Based Composite Adversarial Training against Physically Realizable Attacks on </t>
         </is>
       </c>
       <c r="G170" s="9" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。GeoFormer: Geometry Point Encoder for 3D Object Detection with Graph-based Transformer</t>
+          <t>✅ verified (ICCV 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "GeoFormer (Ours) - 68.2 72.4 88.2 64.5 78.1 45.7 27.4 89.7 74.8 59.6 80.3 7". CVF Open Access 自動收錄；指標待人工驗證。GeoFormer: Geometry Point Encoder for 3D Object Detection with Graph-based Transformer</t>
         </is>
       </c>
       <c r="G174" s="9" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。LMM-Det: Make Large Multimodal Models Excel in Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on RefCOCO — metric Acc@0.5 (referring); Ours row: "LMM-Det (Ours) OWLv2-L Vicuna-7B × 24.5 34.7 26.3 15.4 27.4 37.3 46.6". CVF Open Access 自動收錄；指標待人工驗證。LMM-Det: Make Large Multimodal Models Excel in Object Detection</t>
         </is>
       </c>
       <c r="G176" s="9" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。DuET: Dual Incremental Object Detection via Exemplar-Free Task Arithmetic</t>
+          <t>✅ verified (ICCV 2025, text): tested on Cityscapes — metric mAP (domain-adapt); Ours row: "DuET (Ours) YOLO11n 2.58 49.40±0.2 43.50±0.1 22.20±0.3 31.60±0.2 27.40±0.1 ". CVF Open Access 自動收錄；指標待人工驗證。DuET: Dual Incremental Object Detection via Exemplar-Free Task Arithmetic</t>
         </is>
       </c>
       <c r="G178" s="9" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。YOLO-Count: Differentiable Object Counting for Text-to-Image Generation</t>
+          <t>✅ verified (ICCV 2025, text): tested on LVIS — metric AP / APr (open-vocab/LT); Ours row: "YOLO-Count(Ours) 14.80 96.14 15.43 58.36 1.65 6.08 3.72 11.96 3.28 9.15". CVF Open Access 自動收錄；指標待人工驗證。YOLO-Count: Differentiable Object Counting for Text-to-Image Generation</t>
         </is>
       </c>
       <c r="G182" s="9" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。EVT: Efficient View Transformation for Multi-Modal 3D Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "EVT-L (Ours) L 71.7 66.4 72.1 67.7". CVF Open Access 自動收錄；指標待人工驗證。EVT: Efficient View Transformation for Multi-Modal 3D Object Detection</t>
         </is>
       </c>
       <c r="G183" s="9" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。DM-EFS: Dynamically Multiplexed Expanded Features Set Form for Robust and Efficient Small Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on VisDrone — metric AP (aerial); Ours row: "DM-EFS (Ours) – 34.91 64.47 32.49 17.30 31.22 41.34 49.31". CVF Open Access 自動收錄；指標待人工驗證。DM-EFS: Dynamically Multiplexed Expanded Features Set Form for Robust and Efficient Small O</t>
         </is>
       </c>
       <c r="G188" s="9" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。EvRT-DETR: Latent Space Adaptation of Image Detectors for Event-based Vision</t>
+          <t>✅ verified (ICCV 2025, text): tested on Gen1 — metric mAP (event-camera); Ours row: "RT-DETR-T (ours) 46.0 6.4 44.1 8.6 20.1". CVF Open Access 自動收錄；指標待人工驗證。EvRT-DETR: Latent Space Adaptation of Image Detectors for Event-based Vision</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。FreqPDE: Rethinking Positional Depth Embedding for Multi-View 3D Object Detection Transformers</t>
+          <t>✅ verified (ICCV 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "FreqPDE (Ours) ResNet50 256× 704 54.3 43.5 0.577 0.270 0.442 0.257 0.199". CVF Open Access 自動收錄；指標待人工驗證。FreqPDE: Rethinking Positional Depth Embedding for Multi-View 3D Object Detection Transform</t>
         </is>
       </c>
       <c r="G196" s="9" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。DiffRefine: Diffusion-based Proposal Specific Point Cloud Densification for Cross-Domain Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "DiffRefine (Ours) 87.81/75.25 128.79/103.80 81.73/55.84 91.53/73.77". CVF Open Access 自動收錄；指標待人工驗證。DiffRefine: Diffusion-based Proposal Specific Point Cloud Densification for Cross-Domain Ob</t>
         </is>
       </c>
       <c r="G199" s="9" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。3D-MOOD: Lifting 2D to 3D for Monocular Open-Set Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "Ours 25.6 15.9 14.5 13.8 42.1 21.4 12.9 23.8 43.9". CVF Open Access 自動收錄；指標待人工驗證。3D-MOOD: Lifting 2D to 3D for Monocular Open-Set Object Detection</t>
         </is>
       </c>
       <c r="G203" s="9" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。OpenM3D: Open Vocabulary Multi-view Indoor 3D Object Detection without Human Annotations</t>
+          <t>✅ verified (ICCV 2025, text): tested on ScanNet — metric AP25/AP50 (3D indoor); Ours row: "Ours w/o MSR27.09 11.98 52.43 23.18 6.06 1.34 51.40 11.41". CVF Open Access 自動收錄；指標待人工驗證。OpenM3D: Open Vocabulary Multi-view Indoor 3D Object Detection without Human Annotations</t>
         </is>
       </c>
       <c r="G204" s="9" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond RGB: Adaptive Parallel Processing for RAW Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on COCO — metric AP; Ours row: "RAM (Ours) 34.9 57.6 40.1 61.6 28.3 45.1 44.5 69.0 31.0 56.3 32.4 59.1 66.8". CVF Open Access 自動收錄；指標待人工驗證。Beyond RGB: Adaptive Parallel Processing for RAW Object Detection</t>
         </is>
       </c>
       <c r="G205" s="9" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Dark-ISP: Enhancing RAW Image Processing for Low-Light Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on COCO — metric AP; Ours row: "Dark-ISP(Ours) 31.5 53.4 32.2". CVF Open Access 自動收錄；指標待人工驗證。Dark-ISP: Enhancing RAW Image Processing for Low-Light Object Detection</t>
         </is>
       </c>
       <c r="G207" s="9" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。WaveMamba: Wavelet-Driven Mamba Fusion for RGB-Infrared Object Detection</t>
+          <t>✅ verified (ICCV 2025, text): tested on FLIR — metric mAP (thermal); Ours row: "Ours ResNet50 90.9 62.3 95.6 96.4 92.8 91.6 84.8 84.4". CVF Open Access 自動收錄；指標待人工驗證。WaveMamba: Wavelet-Driven Mamba Fusion for RGB-Infrared Object Detection</t>
         </is>
       </c>
       <c r="G208" s="9" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。ForeSight: Multi-View Streaming Joint Object Detection and Trajectory Forecasting</t>
+          <t>✅ verified (ICCV 2025, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "ForeSight (ours) ResNet50 256×704 4 0.466 0.560 0.614 0.266 0.370 0.258 0.2". CVF Open Access 自動收錄；指標待人工驗證。ForeSight: Multi-View Streaming Joint Object Detection and Trajectory Forecasting</t>
         </is>
       </c>
       <c r="G210" s="9" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。OW-Rep: Open World Object Detection with Instance Representation Learning</t>
+          <t>✅ verified (WACV 2026, text): tested on CODA — metric AR (corner-case OV); Ours row: "Ours 30.56 11.69 58.89 26.74 10.19 45.00 28.21 13.25 36.31 31.46". CVF Open Access 自動收錄；指標待人工驗證。OW-Rep: Open World Object Detection with Instance Representation Learning</t>
         </is>
       </c>
       <c r="G215" s="9" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。MVAT: Multi-View Aware Teacher for Weakly Supervised 3D Object Detection</t>
+          <t>✅ verified (WACV 2026, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "MV AT (ours)54.1 56.4 83.0 50.2 17.0 61.4 31.2 61.8 53.4 39.8 82.8 60.0". CVF Open Access 自動收錄；指標待人工驗證。MVAT: Multi-View Aware Teacher for Weakly Supervised 3D Object Detection</t>
         </is>
       </c>
       <c r="G222" s="9" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。DMAT: An End-to-End Framework for Joint Atmospheric Turbulence Mitigation and Object Detection</t>
+          <t>✅ verified (WACV 2026, text): tested on COCO — metric AP; Ours row: "DMAT-Tiny (ours) 2.8+12.1 0.374 0.188 0.214 0.108 0.348 0.178 0.214 0.127". CVF Open Access 自動收錄；指標待人工驗證。DMAT: An End-to-End Framework for Joint Atmospheric Turbulence Mitigation and Object Detect</t>
         </is>
       </c>
       <c r="G224" s="9" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SFMNet: Sparse Focal Modulation for 3D Object Detection</t>
+          <t>✅ verified (WACV 2026, text): tested on nuScenes — metric NDS / mAP (3D); Ours row: "SFMNet (ours) 81.8/79.8 75.7/73.8 80.5/80.0 72.6/72.2 85.0/80.6 77.4/73.2 7". CVF Open Access 自動收錄；指標待人工驗證。SFMNet: Sparse Focal Modulation for 3D Object Detection</t>
         </is>
       </c>
       <c r="G225" s="9" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SPAR-Det: Segmentation-guided and Prior-Aided Routing for Small Object Detection</t>
+          <t>✅ verified (WACV 2026, text): tested on DOTA — metric mAP (oriented OBB); Ours row: "Ours 16.0 31.5 35.7 41.0 31.2 61.2 23.2 40.6 42.3 30.8 53.4 84.3". CVF Open Access 自動收錄；指標待人工驗證。SPAR-Det: Segmentation-guided and Prior-Aided Routing for Small Object Detection</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。CropAT: Leveraging Diffusion-Generated Target-Like Cropped Objects for Pseudo-Label Refinement in Domain-Adaptive Object Detection</t>
+          <t>✅ verified (WACV 2026, text): tested on Cityscapes — metric mAP (domain-adapt); Ours row: "7 ↭↭ ↭ ↭ 43.2 53.2 (Ours)". CVF Open Access 自動收錄；指標待人工驗證。CropAT: Leveraging Diffusion-Generated Target-Like Cropped Objects for Pseudo-Label Refinem</t>
         </is>
       </c>
       <c r="G234" s="9" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。DualRes: Production-ready Dynamic Object Detection</t>
+          <t>✅ verified (WACV 2026, text): tested on COCO — metric AP; Ours row: "DualRes Efficientdet (ours) 0.636". CVF Open Access 自動收錄；指標待人工驗證。DualRes: Production-ready Dynamic Object Detection</t>
         </is>
       </c>
       <c r="G235" s="9" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Meta-YOLO: Metadata-Guided Real-Time Object Detector in Aerial Imagery</t>
+          <t>✅ verified (WACV 2026, text): tested on DOTA — metric mAP (oriented OBB); Ours row: "META-YOLO-Tiny (Ours)100 5.1 19.0 58.9 79.6 64.0 85.1 74.2 42.5 71.2 83.6". CVF Open Access 自動收錄；指標待人工驗證。Meta-YOLO: Metadata-Gu